--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EE1D795-8B2A-4A29-94D3-19A5FFC660CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0ACEB975-3F30-418E-9DEB-C5F786D3E252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9C6706AB-2526-4E25-B30D-5FA144D52571}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8EE2C18E-8BBA-4AAB-A0D7-C974876B5754}"/>
   </bookViews>
   <sheets>
-    <sheet name="08-06" sheetId="1" r:id="rId1"/>
+    <sheet name="09-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="41">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,6 +83,9 @@
     <t>KIAD</t>
   </si>
   <si>
+    <t>KONT</t>
+  </si>
+  <si>
     <t>MHLM</t>
   </si>
   <si>
@@ -116,12 +119,15 @@
     <t>KSFO</t>
   </si>
   <si>
+    <t>KEWR</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
     <t>KMIA</t>
   </si>
   <si>
-    <t>AAL</t>
-  </si>
-  <si>
     <t>KIAH</t>
   </si>
   <si>
@@ -140,25 +146,19 @@
     <t>AMX</t>
   </si>
   <si>
-    <t>FFT</t>
-  </si>
-  <si>
     <t>SKRG</t>
   </si>
   <si>
-    <t>KMCO</t>
+    <t>MMUN</t>
   </si>
   <si>
     <t>IBE</t>
   </si>
   <si>
-    <t>CYUL</t>
-  </si>
-  <si>
-    <t>KBOS</t>
-  </si>
-  <si>
-    <t>KEWR</t>
+    <t>KORD</t>
+  </si>
+  <si>
+    <t>KLAS</t>
   </si>
   <si>
     <t>LEMD</t>
@@ -536,8 +536,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6495C6AE-173B-4E7E-B9A0-46E372FA8ACB}">
-  <dimension ref="A1:G138"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{561175C3-E192-4EB2-8193-48083BA8856D}">
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -580,7 +580,7 @@
         <v>2203</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2" s="1">
         <v>5.2083333333333336E-2</v>
@@ -618,14 +618,14 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
         <v>879</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1">
         <v>0.20347222222222219</v>
@@ -687,37 +687,37 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D9">
-        <v>575</v>
+        <v>531</v>
       </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1">
-        <v>0.24444444444444444</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="D10">
-        <v>4309</v>
+        <v>575</v>
       </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C11" s="1">
-        <v>0.24652777777777779</v>
+        <v>0.24444444444444444</v>
       </c>
       <c r="D11">
-        <v>456</v>
+        <v>4309</v>
       </c>
       <c r="G11" s="1"/>
     </row>
@@ -732,35 +732,35 @@
         <v>0.24652777777777779</v>
       </c>
       <c r="D12">
-        <v>661</v>
+        <v>456</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="E13">
-        <v>3154</v>
-      </c>
-      <c r="F13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0.25</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.24652777777777779</v>
+      </c>
+      <c r="D13">
+        <v>661</v>
+      </c>
+      <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C14" s="1"/>
       <c r="E14">
-        <v>1467</v>
+        <v>3154</v>
       </c>
       <c r="F14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G14" s="1">
         <v>0.25</v>
@@ -768,33 +768,33 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15">
-        <v>3154</v>
+        <v>1467</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G15" s="1">
-        <v>0.25069444444444444</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="1">
-        <v>0.25694444444444442</v>
-      </c>
-      <c r="D16">
-        <v>433</v>
-      </c>
-      <c r="G16" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="E16">
+        <v>3154</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0.25069444444444444</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -807,7 +807,7 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="D17">
-        <v>579</v>
+        <v>433</v>
       </c>
       <c r="G17" s="1"/>
     </row>
@@ -816,13 +816,13 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C18" s="1">
-        <v>0.26041666666666669</v>
+        <v>0.25694444444444442</v>
       </c>
       <c r="D18">
-        <v>529</v>
+        <v>579</v>
       </c>
       <c r="G18" s="1"/>
     </row>
@@ -831,13 +831,13 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1">
-        <v>0.2638888888888889</v>
+        <v>0.26041666666666669</v>
       </c>
       <c r="D19">
-        <v>314</v>
+        <v>529</v>
       </c>
       <c r="G19" s="1"/>
     </row>
@@ -849,10 +849,10 @@
         <v>20</v>
       </c>
       <c r="C20" s="1">
-        <v>0.2673611111111111</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="D20">
-        <v>428</v>
+        <v>314</v>
       </c>
       <c r="G20" s="1"/>
     </row>
@@ -867,7 +867,7 @@
         <v>0.2673611111111111</v>
       </c>
       <c r="D21">
-        <v>626</v>
+        <v>428</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -879,10 +879,10 @@
         <v>22</v>
       </c>
       <c r="C22" s="1">
-        <v>0.27083333333333331</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D22">
-        <v>316</v>
+        <v>626</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -897,7 +897,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D23">
-        <v>366</v>
+        <v>316</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -912,7 +912,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D24">
-        <v>561</v>
+        <v>366</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -921,13 +921,13 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C25" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D25">
-        <v>591</v>
+        <v>561</v>
       </c>
       <c r="G25" s="1"/>
     </row>
@@ -936,13 +936,13 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D26">
-        <v>671</v>
+        <v>591</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -951,13 +951,13 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C27" s="1">
-        <v>0.29166666666666669</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="D27">
-        <v>521</v>
+        <v>671</v>
       </c>
       <c r="G27" s="1"/>
     </row>
@@ -965,30 +965,30 @@
       <c r="A28" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="1"/>
-      <c r="E28">
-        <v>319</v>
-      </c>
-      <c r="F28" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0.3125</v>
-      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="D28">
+        <v>521</v>
+      </c>
+      <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C29" s="1"/>
       <c r="E29">
-        <v>323</v>
+        <v>3154</v>
       </c>
       <c r="F29" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G29" s="1">
-        <v>0.3125</v>
+        <v>0.29236111111111113</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -997,10 +997,10 @@
       </c>
       <c r="C30" s="1"/>
       <c r="E30">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="F30" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G30" s="1">
         <v>0.3125</v>
@@ -1012,10 +1012,10 @@
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>396</v>
+        <v>323</v>
       </c>
       <c r="F31" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G31" s="1">
         <v>0.3125</v>
@@ -1023,14 +1023,14 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>884</v>
+        <v>396</v>
       </c>
       <c r="F32" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G32" s="1">
         <v>0.3125</v>
@@ -1045,7 +1045,7 @@
         <v>310</v>
       </c>
       <c r="F33" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G33" s="1">
         <v>0.31597222222222221</v>
@@ -1060,7 +1060,7 @@
         <v>440</v>
       </c>
       <c r="F34" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G34" s="1">
         <v>0.31597222222222221</v>
@@ -1072,29 +1072,29 @@
       </c>
       <c r="C35" s="1"/>
       <c r="E35">
-        <v>444</v>
+        <v>536</v>
       </c>
       <c r="F35" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G35" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.31597222222222221</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="E36">
-        <v>562</v>
-      </c>
-      <c r="F36" t="s">
-        <v>24</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0.32291666666666669</v>
-      </c>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="D36">
+        <v>321</v>
+      </c>
+      <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
@@ -1102,13 +1102,13 @@
       </c>
       <c r="C37" s="1"/>
       <c r="E37">
-        <v>368</v>
+        <v>562</v>
       </c>
       <c r="F37" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G37" s="1">
-        <v>0.33333333333333331</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1117,10 +1117,10 @@
       </c>
       <c r="C38" s="1"/>
       <c r="E38">
-        <v>522</v>
+        <v>368</v>
       </c>
       <c r="F38" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="G38" s="1">
         <v>0.33333333333333331</v>
@@ -1130,16 +1130,16 @@
       <c r="A39" t="s">
         <v>9</v>
       </c>
-      <c r="B39" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D39">
-        <v>309</v>
-      </c>
-      <c r="G39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="E39">
+        <v>522</v>
+      </c>
+      <c r="F39" t="s">
+        <v>8</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.33333333333333331</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
@@ -1152,7 +1152,7 @@
         <v>0.33680555555555558</v>
       </c>
       <c r="D40">
-        <v>601</v>
+        <v>581</v>
       </c>
       <c r="G40" s="1"/>
     </row>
@@ -1165,7 +1165,7 @@
         <v>383</v>
       </c>
       <c r="F41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G41" s="1">
         <v>0.33680555555555558</v>
@@ -1207,10 +1207,10 @@
       </c>
       <c r="C44" s="1"/>
       <c r="E44">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="F44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G44" s="1">
         <v>0.34375</v>
@@ -1218,17 +1218,17 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C45" s="1"/>
       <c r="E45">
-        <v>422</v>
+        <v>884</v>
       </c>
       <c r="F45" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G45" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.35347222222222219</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1240,7 +1240,7 @@
         <v>430</v>
       </c>
       <c r="F46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G46" s="1">
         <v>0.36458333333333331</v>
@@ -1250,16 +1250,16 @@
       <c r="A47" t="s">
         <v>9</v>
       </c>
-      <c r="C47" s="1"/>
-      <c r="E47">
-        <v>524</v>
-      </c>
-      <c r="F47" t="s">
-        <v>8</v>
-      </c>
-      <c r="G47" s="1">
-        <v>0.38194444444444442</v>
-      </c>
+      <c r="B47" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="D47">
+        <v>451</v>
+      </c>
+      <c r="G47" s="1"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -1267,13 +1267,13 @@
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>369</v>
+        <v>526</v>
       </c>
       <c r="F48" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G48" s="1">
-        <v>0.3888888888888889</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1282,57 +1282,57 @@
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>582</v>
+        <v>369</v>
       </c>
       <c r="F49" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="G49" s="1">
-        <v>0.39930555555555558</v>
+        <v>0.3888888888888889</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>9</v>
       </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" s="1">
-        <v>0.41319444444444442</v>
-      </c>
-      <c r="D50">
-        <v>569</v>
-      </c>
-      <c r="G50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="E50">
+        <v>582</v>
+      </c>
+      <c r="F50" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0.39930555555555558</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C51" s="1"/>
-      <c r="E51">
-        <v>609</v>
-      </c>
-      <c r="F51" t="s">
-        <v>21</v>
-      </c>
-      <c r="G51" s="1">
-        <v>0.4236111111111111</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.40902777777777777</v>
+      </c>
+      <c r="D51">
+        <v>4337</v>
+      </c>
+      <c r="G51" s="1"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C52" s="1">
-        <v>0.44791666666666669</v>
+        <v>0.41319444444444442</v>
       </c>
       <c r="D52">
-        <v>455</v>
+        <v>569</v>
       </c>
       <c r="G52" s="1"/>
     </row>
@@ -1340,59 +1340,59 @@
       <c r="A53" t="s">
         <v>9</v>
       </c>
-      <c r="B53" t="s">
-        <v>21</v>
-      </c>
-      <c r="C53" s="1">
-        <v>0.4548611111111111</v>
-      </c>
-      <c r="D53">
-        <v>318</v>
-      </c>
-      <c r="G53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="E53">
+        <v>392</v>
+      </c>
+      <c r="F53" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0.41319444444444442</v>
+      </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>9</v>
       </c>
-      <c r="B54" t="s">
-        <v>23</v>
-      </c>
-      <c r="C54" s="1">
-        <v>0.46180555555555558</v>
-      </c>
-      <c r="D54">
-        <v>384</v>
-      </c>
-      <c r="G54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="E54">
+        <v>408</v>
+      </c>
+      <c r="F54" t="s">
+        <v>38</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0.41319444444444442</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>26</v>
-      </c>
-      <c r="B55" t="s">
-        <v>25</v>
-      </c>
-      <c r="C55" s="1">
-        <v>0.47291666666666665</v>
-      </c>
-      <c r="D55">
-        <v>495</v>
-      </c>
-      <c r="G55" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C55" s="1"/>
+      <c r="E55">
+        <v>609</v>
+      </c>
+      <c r="F55" t="s">
+        <v>22</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0.4236111111111111</v>
+      </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C56" s="1">
-        <v>0.47847222222222219</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="D56">
-        <v>1194</v>
+        <v>537</v>
       </c>
       <c r="G56" s="1"/>
     </row>
@@ -1400,224 +1400,224 @@
       <c r="A57" t="s">
         <v>9</v>
       </c>
-      <c r="C57" s="1"/>
-      <c r="E57">
-        <v>584</v>
-      </c>
-      <c r="F57" t="s">
-        <v>13</v>
-      </c>
-      <c r="G57" s="1">
-        <v>0.49305555555555558</v>
-      </c>
+      <c r="B57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="1">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D57">
+        <v>455</v>
+      </c>
+      <c r="G57" s="1"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>9</v>
       </c>
-      <c r="C58" s="1"/>
-      <c r="E58">
-        <v>385</v>
-      </c>
-      <c r="F58" t="s">
-        <v>23</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+      <c r="B58" t="s">
+        <v>19</v>
+      </c>
+      <c r="C58" s="1">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="D58">
+        <v>573</v>
+      </c>
+      <c r="G58" s="1"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>9</v>
       </c>
-      <c r="C59" s="1"/>
-      <c r="E59">
-        <v>424</v>
-      </c>
-      <c r="F59" t="s">
-        <v>27</v>
-      </c>
-      <c r="G59" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+      <c r="B59" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" s="1">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="D59">
+        <v>318</v>
+      </c>
+      <c r="G59" s="1"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C60" s="1">
-        <v>0.51041666666666663</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D60">
-        <v>1441</v>
+        <v>384</v>
       </c>
       <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>26</v>
-      </c>
-      <c r="C61" s="1"/>
-      <c r="E61">
-        <v>1508</v>
-      </c>
-      <c r="F61" t="s">
-        <v>25</v>
-      </c>
-      <c r="G61" s="1">
-        <v>0.51597222222222228</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B61" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" s="1">
+        <v>0.47291666666666665</v>
+      </c>
+      <c r="D61">
+        <v>495</v>
+      </c>
+      <c r="G61" s="1"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C62" s="1">
-        <v>0.5180555555555556</v>
+        <v>0.47847222222222219</v>
       </c>
       <c r="D62">
-        <v>1910</v>
+        <v>1194</v>
       </c>
       <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>26</v>
-      </c>
-      <c r="B63" t="s">
-        <v>30</v>
-      </c>
-      <c r="C63" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D63">
-        <v>937</v>
-      </c>
-      <c r="G63" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C63" s="1"/>
+      <c r="E63">
+        <v>584</v>
+      </c>
+      <c r="F63" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0.49305555555555558</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>31</v>
-      </c>
-      <c r="B64" t="s">
-        <v>22</v>
-      </c>
-      <c r="C64" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D64">
-        <v>816</v>
-      </c>
-      <c r="G64" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="E64">
+        <v>434</v>
+      </c>
+      <c r="F64" t="s">
+        <v>36</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0.49652777777777779</v>
+      </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C65" s="1"/>
       <c r="E65">
-        <v>1458</v>
+        <v>385</v>
       </c>
       <c r="F65" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G65" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C66" s="1"/>
       <c r="E66">
-        <v>380</v>
+        <v>424</v>
       </c>
       <c r="F66" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G66" s="1">
-        <v>0.57222222222222219</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C67" s="1"/>
       <c r="E67">
-        <v>1468</v>
+        <v>442</v>
       </c>
       <c r="F67" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G67" s="1">
-        <v>0.57638888888888895</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>28</v>
-      </c>
-      <c r="C68" s="1"/>
-      <c r="E68">
-        <v>1978</v>
-      </c>
-      <c r="F68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" t="s">
         <v>29</v>
       </c>
-      <c r="G68" s="1">
-        <v>0.57708333333333328</v>
-      </c>
+      <c r="C68" s="1">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D68">
+        <v>1441</v>
+      </c>
+      <c r="G68" s="1"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C69" s="1"/>
       <c r="E69">
-        <v>871</v>
+        <v>1508</v>
       </c>
       <c r="F69" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G69" s="1">
-        <v>0.58194444444444449</v>
+        <v>0.51597222222222228</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B70" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C70" s="1">
-        <v>0.59375</v>
+        <v>0.5180555555555556</v>
       </c>
       <c r="D70">
-        <v>628</v>
+        <v>1910</v>
       </c>
       <c r="G70" s="1"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B71" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C71" s="1">
-        <v>0.60416666666666663</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="D71">
-        <v>1290</v>
+        <v>937</v>
       </c>
       <c r="G71" s="1"/>
     </row>
@@ -1626,45 +1626,45 @@
         <v>33</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C72" s="1">
-        <v>0.61458333333333337</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="D72">
-        <v>342</v>
+        <v>816</v>
       </c>
       <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C73" s="1"/>
       <c r="E73">
-        <v>629</v>
+        <v>1458</v>
       </c>
       <c r="F73" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G73" s="1">
-        <v>0.64722222222222225</v>
+        <v>0.55555555555555558</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>9</v>
-      </c>
-      <c r="B74" t="s">
-        <v>23</v>
-      </c>
-      <c r="C74" s="1">
-        <v>0.65277777777777779</v>
-      </c>
-      <c r="D74">
-        <v>382</v>
-      </c>
-      <c r="G74" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="E74">
+        <v>380</v>
+      </c>
+      <c r="F74" t="s">
+        <v>32</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0.57222222222222219</v>
+      </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
@@ -1672,132 +1672,132 @@
       </c>
       <c r="C75" s="1"/>
       <c r="E75">
-        <v>1130</v>
+        <v>1468</v>
       </c>
       <c r="F75" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G75" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.57638888888888895</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C76" s="1"/>
       <c r="E76">
-        <v>343</v>
+        <v>1978</v>
       </c>
       <c r="F76" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G76" s="1">
-        <v>0.65972222222222221</v>
+        <v>0.57708333333333328</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>9</v>
-      </c>
-      <c r="B77" t="s">
-        <v>27</v>
-      </c>
-      <c r="C77" s="1">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D77">
-        <v>367</v>
-      </c>
-      <c r="G77" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="E77">
+        <v>871</v>
+      </c>
+      <c r="F77" t="s">
+        <v>23</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0.58194444444444449</v>
+      </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B78" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C78" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.59236111111111112</v>
       </c>
       <c r="D78">
-        <v>370</v>
+        <v>628</v>
       </c>
       <c r="G78" s="1"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B79" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C79" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D79">
-        <v>397</v>
+        <v>1290</v>
       </c>
       <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>9</v>
-      </c>
-      <c r="B80" t="s">
+        <v>34</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="E80">
+        <v>629</v>
+      </c>
+      <c r="F80" t="s">
         <v>18</v>
       </c>
-      <c r="C80" s="1">
-        <v>0.67361111111111116</v>
-      </c>
-      <c r="D80">
-        <v>553</v>
-      </c>
-      <c r="G80" s="1"/>
+      <c r="G80" s="1">
+        <v>0.64722222222222225</v>
+      </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>9</v>
       </c>
       <c r="B81" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C81" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="D81">
-        <v>441</v>
+        <v>382</v>
       </c>
       <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>9</v>
-      </c>
-      <c r="B82" t="s">
-        <v>35</v>
-      </c>
-      <c r="C82" s="1">
-        <v>0.68402777777777779</v>
-      </c>
-      <c r="D82">
-        <v>423</v>
-      </c>
-      <c r="G82" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="E82">
+        <v>1130</v>
+      </c>
+      <c r="F82" t="s">
+        <v>29</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>9</v>
       </c>
       <c r="B83" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C83" s="1">
-        <v>0.6875</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D83">
-        <v>311</v>
+        <v>367</v>
       </c>
       <c r="G83" s="1"/>
     </row>
@@ -1806,13 +1806,13 @@
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C84" s="1">
-        <v>0.6875</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D84">
-        <v>555</v>
+        <v>370</v>
       </c>
       <c r="G84" s="1"/>
     </row>
@@ -1821,13 +1821,13 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C85" s="1">
-        <v>0.6875</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D85">
-        <v>610</v>
+        <v>397</v>
       </c>
       <c r="G85" s="1"/>
     </row>
@@ -1836,13 +1836,13 @@
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C86" s="1">
-        <v>0.70138888888888884</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D86">
-        <v>322</v>
+        <v>553</v>
       </c>
       <c r="G86" s="1"/>
     </row>
@@ -1850,76 +1850,76 @@
       <c r="A87" t="s">
         <v>9</v>
       </c>
-      <c r="C87" s="1"/>
-      <c r="E87">
-        <v>326</v>
-      </c>
-      <c r="F87" t="s">
-        <v>10</v>
-      </c>
-      <c r="G87" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+      <c r="B87" t="s">
+        <v>32</v>
+      </c>
+      <c r="C87" s="1">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="D87">
+        <v>441</v>
+      </c>
+      <c r="G87" s="1"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>9</v>
       </c>
-      <c r="C88" s="1"/>
-      <c r="E88">
-        <v>560</v>
-      </c>
-      <c r="F88" t="s">
-        <v>24</v>
-      </c>
-      <c r="G88" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+      <c r="B88" t="s">
+        <v>36</v>
+      </c>
+      <c r="C88" s="1">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="D88">
+        <v>435</v>
+      </c>
+      <c r="G88" s="1"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>9</v>
       </c>
-      <c r="C89" s="1"/>
-      <c r="E89">
-        <v>313</v>
-      </c>
-      <c r="F89" t="s">
-        <v>21</v>
-      </c>
-      <c r="G89" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+      <c r="B89" t="s">
+        <v>28</v>
+      </c>
+      <c r="C89" s="1">
+        <v>0.6875</v>
+      </c>
+      <c r="D89">
+        <v>311</v>
+      </c>
+      <c r="G89" s="1"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>9</v>
       </c>
-      <c r="C90" s="1"/>
-      <c r="E90">
-        <v>450</v>
-      </c>
-      <c r="F90" t="s">
-        <v>19</v>
-      </c>
-      <c r="G90" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+      <c r="B90" t="s">
+        <v>22</v>
+      </c>
+      <c r="C90" s="1">
+        <v>0.6875</v>
+      </c>
+      <c r="D90">
+        <v>610</v>
+      </c>
+      <c r="G90" s="1"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>9</v>
       </c>
-      <c r="C91" s="1"/>
-      <c r="E91">
-        <v>520</v>
-      </c>
-      <c r="F91" t="s">
-        <v>8</v>
-      </c>
-      <c r="G91" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+      <c r="B91" t="s">
+        <v>23</v>
+      </c>
+      <c r="C91" s="1">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="D91">
+        <v>322</v>
+      </c>
+      <c r="G91" s="1"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
@@ -1927,13 +1927,13 @@
       </c>
       <c r="C92" s="1"/>
       <c r="E92">
-        <v>588</v>
+        <v>320</v>
       </c>
       <c r="F92" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G92" s="1">
-        <v>0.73611111111111116</v>
+        <v>0.72222222222222221</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -1942,13 +1942,13 @@
       </c>
       <c r="C93" s="1"/>
       <c r="E93">
-        <v>448</v>
+        <v>326</v>
       </c>
       <c r="F93" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G93" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -1957,28 +1957,28 @@
       </c>
       <c r="C94" s="1"/>
       <c r="E94">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="F94" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G94" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C95" s="1"/>
       <c r="E95">
-        <v>4308</v>
+        <v>313</v>
       </c>
       <c r="F95" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="G95" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -1987,29 +1987,29 @@
       </c>
       <c r="C96" s="1"/>
       <c r="E96">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="F96" t="s">
         <v>8</v>
       </c>
       <c r="G96" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>36</v>
-      </c>
-      <c r="B97" t="s">
-        <v>18</v>
-      </c>
-      <c r="C97" s="1">
-        <v>0.76736111111111116</v>
-      </c>
-      <c r="D97">
-        <v>222</v>
-      </c>
-      <c r="G97" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C97" s="1"/>
+      <c r="E97">
+        <v>530</v>
+      </c>
+      <c r="F97" t="s">
+        <v>14</v>
+      </c>
+      <c r="G97" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
@@ -2017,29 +2017,29 @@
       </c>
       <c r="C98" s="1"/>
       <c r="E98">
-        <v>660</v>
+        <v>588</v>
       </c>
       <c r="F98" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G98" s="1">
-        <v>0.77083333333333337</v>
+        <v>0.73611111111111116</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>7</v>
-      </c>
-      <c r="B99" t="s">
-        <v>27</v>
-      </c>
-      <c r="C99" s="1">
-        <v>0.79027777777777775</v>
-      </c>
-      <c r="D99">
-        <v>742</v>
-      </c>
-      <c r="G99" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C99" s="1"/>
+      <c r="E99">
+        <v>534</v>
+      </c>
+      <c r="F99" t="s">
+        <v>15</v>
+      </c>
+      <c r="G99" s="1">
+        <v>0.74305555555555558</v>
+      </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
@@ -2047,84 +2047,84 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>4312</v>
+        <v>4308</v>
       </c>
       <c r="F100" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G100" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>9</v>
       </c>
-      <c r="B101" t="s">
-        <v>17</v>
-      </c>
-      <c r="C101" s="1">
-        <v>0.79513888888888884</v>
-      </c>
-      <c r="D101">
-        <v>431</v>
-      </c>
-      <c r="G101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="E101">
+        <v>528</v>
+      </c>
+      <c r="F101" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="1">
+        <v>0.76041666666666663</v>
+      </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>9</v>
-      </c>
-      <c r="C102" s="1"/>
-      <c r="E102">
-        <v>670</v>
-      </c>
-      <c r="F102" t="s">
-        <v>16</v>
-      </c>
-      <c r="G102" s="1">
-        <v>0.80555555555555558</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B102" t="s">
+        <v>19</v>
+      </c>
+      <c r="C102" s="1">
+        <v>0.76736111111111116</v>
+      </c>
+      <c r="D102">
+        <v>222</v>
+      </c>
+      <c r="G102" s="1"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>9</v>
       </c>
-      <c r="B103" t="s">
-        <v>27</v>
-      </c>
-      <c r="C103" s="1">
-        <v>0.81944444444444442</v>
-      </c>
-      <c r="D103">
-        <v>425</v>
-      </c>
-      <c r="G103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="E103">
+        <v>660</v>
+      </c>
+      <c r="F103" t="s">
+        <v>17</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0.77083333333333337</v>
+      </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>9</v>
       </c>
-      <c r="B104" t="s">
-        <v>37</v>
-      </c>
-      <c r="C104" s="1">
-        <v>0.82291666666666663</v>
-      </c>
-      <c r="D104">
-        <v>329</v>
-      </c>
-      <c r="G104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="E104">
+        <v>558</v>
+      </c>
+      <c r="F104" t="s">
+        <v>25</v>
+      </c>
+      <c r="G104" s="1">
+        <v>0.77777777777777779</v>
+      </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B105" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C105" s="1">
-        <v>0.82430555555555551</v>
+        <v>0.77847222222222223</v>
       </c>
       <c r="D105">
         <v>2657</v>
@@ -2133,91 +2133,91 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C106" s="1">
-        <v>0.82499999999999996</v>
+        <v>0.79027777777777775</v>
       </c>
       <c r="D106">
-        <v>2657</v>
+        <v>742</v>
       </c>
       <c r="G106" s="1"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>9</v>
-      </c>
-      <c r="B107" t="s">
-        <v>8</v>
-      </c>
-      <c r="C107" s="1">
-        <v>0.82638888888888884</v>
-      </c>
-      <c r="D107">
-        <v>523</v>
-      </c>
-      <c r="G107" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C107" s="1"/>
+      <c r="E107">
+        <v>4312</v>
+      </c>
+      <c r="F107" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107" s="1">
+        <v>0.79027777777777775</v>
+      </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>36</v>
-      </c>
-      <c r="C108" s="1"/>
-      <c r="E108">
-        <v>222</v>
-      </c>
-      <c r="F108" t="s">
-        <v>40</v>
-      </c>
-      <c r="G108" s="1">
-        <v>0.82986111111111116</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B108" t="s">
+        <v>18</v>
+      </c>
+      <c r="C108" s="1">
+        <v>0.79513888888888884</v>
+      </c>
+      <c r="D108">
+        <v>431</v>
+      </c>
+      <c r="G108" s="1"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>9</v>
       </c>
-      <c r="B109" t="s">
-        <v>13</v>
-      </c>
-      <c r="C109" s="1">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D109">
-        <v>583</v>
-      </c>
-      <c r="G109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="E109">
+        <v>670</v>
+      </c>
+      <c r="F109" t="s">
+        <v>17</v>
+      </c>
+      <c r="G109" s="1">
+        <v>0.80555555555555558</v>
+      </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>9</v>
-      </c>
-      <c r="B110" t="s">
-        <v>10</v>
-      </c>
-      <c r="C110" s="1">
-        <v>0.84375</v>
-      </c>
-      <c r="D110">
-        <v>325</v>
-      </c>
-      <c r="G110" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C110" s="1"/>
+      <c r="E110">
+        <v>4300</v>
+      </c>
+      <c r="F110" t="s">
+        <v>18</v>
+      </c>
+      <c r="G110" s="1">
+        <v>0.81388888888888888</v>
+      </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C111" s="1">
-        <v>0.84375</v>
+        <v>0.81944444444444442</v>
       </c>
       <c r="D111">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="G111" s="1"/>
     </row>
@@ -2225,59 +2225,59 @@
       <c r="A112" t="s">
         <v>9</v>
       </c>
-      <c r="C112" s="1"/>
-      <c r="E112">
-        <v>590</v>
-      </c>
-      <c r="F112" t="s">
-        <v>13</v>
-      </c>
-      <c r="G112" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+      <c r="B112" t="s">
+        <v>8</v>
+      </c>
+      <c r="C112" s="1">
+        <v>0.82638888888888884</v>
+      </c>
+      <c r="D112">
+        <v>523</v>
+      </c>
+      <c r="G112" s="1"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>9</v>
-      </c>
-      <c r="B113" t="s">
-        <v>11</v>
-      </c>
-      <c r="C113" s="1">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="D113">
-        <v>449</v>
-      </c>
-      <c r="G113" s="1"/>
+        <v>37</v>
+      </c>
+      <c r="C113" s="1"/>
+      <c r="E113">
+        <v>222</v>
+      </c>
+      <c r="F113" t="s">
+        <v>40</v>
+      </c>
+      <c r="G113" s="1">
+        <v>0.82986111111111116</v>
+      </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C114" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D114">
-        <v>881</v>
+        <v>583</v>
       </c>
       <c r="G114" s="1"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C115" s="1">
-        <v>0.86736111111111114</v>
+        <v>0.84375</v>
       </c>
       <c r="D115">
-        <v>1461</v>
+        <v>325</v>
       </c>
       <c r="G115" s="1"/>
     </row>
@@ -2286,13 +2286,13 @@
         <v>9</v>
       </c>
       <c r="B116" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C116" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.85069444444444442</v>
       </c>
       <c r="D116">
-        <v>563</v>
+        <v>393</v>
       </c>
       <c r="G116" s="1"/>
     </row>
@@ -2300,44 +2300,44 @@
       <c r="A117" t="s">
         <v>9</v>
       </c>
-      <c r="B117" t="s">
-        <v>14</v>
-      </c>
-      <c r="C117" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="D117">
-        <v>535</v>
-      </c>
-      <c r="G117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="E117">
+        <v>590</v>
+      </c>
+      <c r="F117" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B118" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C118" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D118">
-        <v>312</v>
+        <v>881</v>
       </c>
       <c r="G118" s="1"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B119" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C119" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D119">
-        <v>525</v>
+        <v>1461</v>
       </c>
       <c r="G119" s="1"/>
     </row>
@@ -2346,28 +2346,28 @@
         <v>9</v>
       </c>
       <c r="B120" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C120" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D120">
-        <v>589</v>
+        <v>443</v>
       </c>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B121" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C121" s="1">
-        <v>0.89930555555555547</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D121">
-        <v>1425</v>
+        <v>563</v>
       </c>
       <c r="G121" s="1"/>
     </row>
@@ -2376,13 +2376,13 @@
         <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C122" s="1">
-        <v>0.91319444444444442</v>
+        <v>0.87152777777777779</v>
       </c>
       <c r="D122">
-        <v>585</v>
+        <v>409</v>
       </c>
       <c r="G122" s="1"/>
     </row>
@@ -2390,91 +2390,91 @@
       <c r="A123" t="s">
         <v>9</v>
       </c>
-      <c r="C123" s="1"/>
-      <c r="E123">
-        <v>315</v>
-      </c>
-      <c r="F123" t="s">
-        <v>19</v>
-      </c>
-      <c r="G123" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B123" t="s">
+        <v>39</v>
+      </c>
+      <c r="C123" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="D123">
+        <v>527</v>
+      </c>
+      <c r="G123" s="1"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>9</v>
       </c>
-      <c r="C124" s="1"/>
-      <c r="E124">
-        <v>365</v>
-      </c>
-      <c r="F124" t="s">
-        <v>23</v>
-      </c>
-      <c r="G124" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B124" t="s">
+        <v>15</v>
+      </c>
+      <c r="C124" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="D124">
+        <v>535</v>
+      </c>
+      <c r="G124" s="1"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>9</v>
       </c>
-      <c r="C125" s="1"/>
-      <c r="E125">
-        <v>580</v>
-      </c>
-      <c r="F125" t="s">
-        <v>13</v>
-      </c>
-      <c r="G125" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B125" t="s">
+        <v>22</v>
+      </c>
+      <c r="C125" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D125">
+        <v>312</v>
+      </c>
+      <c r="G125" s="1"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>9</v>
       </c>
-      <c r="C126" s="1"/>
-      <c r="E126">
-        <v>429</v>
-      </c>
-      <c r="F126" t="s">
-        <v>20</v>
-      </c>
-      <c r="G126" s="1">
-        <v>0.92708333333333337</v>
-      </c>
+      <c r="B126" t="s">
+        <v>19</v>
+      </c>
+      <c r="C126" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D126">
+        <v>589</v>
+      </c>
+      <c r="G126" s="1"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>9</v>
-      </c>
-      <c r="C127" s="1"/>
-      <c r="E127">
-        <v>578</v>
-      </c>
-      <c r="F127" t="s">
-        <v>18</v>
-      </c>
-      <c r="G127" s="1">
-        <v>0.93055555555555558</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B127" t="s">
+        <v>26</v>
+      </c>
+      <c r="C127" s="1">
+        <v>0.89930555555555547</v>
+      </c>
+      <c r="D127">
+        <v>1425</v>
+      </c>
+      <c r="G127" s="1"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>9</v>
       </c>
-      <c r="C128" s="1"/>
-      <c r="E128">
-        <v>627</v>
-      </c>
-      <c r="F128" t="s">
-        <v>21</v>
-      </c>
-      <c r="G128" s="1">
-        <v>0.93402777777777779</v>
-      </c>
+      <c r="B128" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" s="1">
+        <v>0.91319444444444442</v>
+      </c>
+      <c r="D128">
+        <v>585</v>
+      </c>
+      <c r="G128" s="1"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
@@ -2482,13 +2482,13 @@
       </c>
       <c r="C129" s="1"/>
       <c r="E129">
-        <v>574</v>
+        <v>315</v>
       </c>
       <c r="F129" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G129" s="1">
-        <v>0.9375</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -2497,13 +2497,13 @@
       </c>
       <c r="C130" s="1"/>
       <c r="E130">
-        <v>568</v>
+        <v>365</v>
       </c>
       <c r="F130" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G130" s="1">
-        <v>0.94097222222222221</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -2512,43 +2512,43 @@
       </c>
       <c r="C131" s="1"/>
       <c r="E131">
-        <v>452</v>
+        <v>580</v>
       </c>
       <c r="F131" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G131" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C132" s="1"/>
       <c r="E132">
-        <v>339</v>
+        <v>308</v>
       </c>
       <c r="F132" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="G132" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.92361111111111116</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C133" s="1"/>
       <c r="E133">
-        <v>4336</v>
+        <v>429</v>
       </c>
       <c r="F133" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="G133" s="1">
-        <v>0.9506944444444444</v>
+        <v>0.92708333333333337</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -2557,13 +2557,13 @@
       </c>
       <c r="C134" s="1"/>
       <c r="E134">
-        <v>317</v>
+        <v>578</v>
       </c>
       <c r="F134" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G134" s="1">
-        <v>0.95486111111111116</v>
+        <v>0.93055555555555558</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -2572,13 +2572,13 @@
       </c>
       <c r="C135" s="1"/>
       <c r="E135">
-        <v>432</v>
+        <v>627</v>
       </c>
       <c r="F135" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G135" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.93402777777777779</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -2587,13 +2587,13 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>457</v>
+        <v>574</v>
       </c>
       <c r="F136" t="s">
         <v>15</v>
       </c>
       <c r="G136" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -2602,29 +2602,104 @@
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="F137" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G137" s="1">
-        <v>0.97222222222222221</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>31</v>
-      </c>
-      <c r="B138" t="s">
-        <v>22</v>
-      </c>
-      <c r="C138" s="1">
+        <v>9</v>
+      </c>
+      <c r="C138" s="1"/>
+      <c r="E138">
+        <v>452</v>
+      </c>
+      <c r="F138" t="s">
+        <v>11</v>
+      </c>
+      <c r="G138" s="1">
+        <v>0.94791666666666663</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>7</v>
+      </c>
+      <c r="C139" s="1"/>
+      <c r="E139">
+        <v>339</v>
+      </c>
+      <c r="F139" t="s">
+        <v>26</v>
+      </c>
+      <c r="G139" s="1">
+        <v>0.94791666666666663</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>9</v>
+      </c>
+      <c r="C140" s="1"/>
+      <c r="E140">
+        <v>317</v>
+      </c>
+      <c r="F140" t="s">
+        <v>23</v>
+      </c>
+      <c r="G140" s="1">
+        <v>0.95486111111111116</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>9</v>
+      </c>
+      <c r="C141" s="1"/>
+      <c r="E141">
+        <v>457</v>
+      </c>
+      <c r="F141" t="s">
+        <v>16</v>
+      </c>
+      <c r="G141" s="1">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="1"/>
+      <c r="E142">
+        <v>556</v>
+      </c>
+      <c r="F142" t="s">
+        <v>19</v>
+      </c>
+      <c r="G142" s="1">
+        <v>0.97222222222222221</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>33</v>
+      </c>
+      <c r="B143" t="s">
+        <v>23</v>
+      </c>
+      <c r="C143" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D138">
+      <c r="D143">
         <v>878</v>
       </c>
-      <c r="G138" s="1"/>
+      <c r="G143" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0ACEB975-3F30-418E-9DEB-C5F786D3E252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C3B3E85-B5F0-44B4-A4C5-BFCFAD1A484D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8EE2C18E-8BBA-4AAB-A0D7-C974876B5754}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9A99B0D8-2876-44EC-9A89-B05B613E14B2}"/>
   </bookViews>
   <sheets>
-    <sheet name="09-06" sheetId="1" r:id="rId1"/>
+    <sheet name="10-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="41">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,9 +83,6 @@
     <t>KIAD</t>
   </si>
   <si>
-    <t>KONT</t>
-  </si>
-  <si>
     <t>MHLM</t>
   </si>
   <si>
@@ -119,46 +116,49 @@
     <t>KSFO</t>
   </si>
   <si>
+    <t>KMIA</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
+    <t>KIAH</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>KATL</t>
+  </si>
+  <si>
+    <t>KDFW</t>
+  </si>
+  <si>
+    <t>CMP</t>
+  </si>
+  <si>
+    <t>AMX</t>
+  </si>
+  <si>
+    <t>SKRG</t>
+  </si>
+  <si>
+    <t>KMCO</t>
+  </si>
+  <si>
+    <t>IBE</t>
+  </si>
+  <si>
+    <t>CYUL</t>
+  </si>
+  <si>
+    <t>KBOS</t>
+  </si>
+  <si>
+    <t>KOAK</t>
+  </si>
+  <si>
     <t>KEWR</t>
-  </si>
-  <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>KMIA</t>
-  </si>
-  <si>
-    <t>KIAH</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>KATL</t>
-  </si>
-  <si>
-    <t>KDFW</t>
-  </si>
-  <si>
-    <t>CMP</t>
-  </si>
-  <si>
-    <t>AMX</t>
-  </si>
-  <si>
-    <t>SKRG</t>
-  </si>
-  <si>
-    <t>MMUN</t>
-  </si>
-  <si>
-    <t>IBE</t>
-  </si>
-  <si>
-    <t>KORD</t>
-  </si>
-  <si>
-    <t>KLAS</t>
   </si>
   <si>
     <t>LEMD</t>
@@ -536,8 +536,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{561175C3-E192-4EB2-8193-48083BA8856D}">
-  <dimension ref="A1:G143"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC9DEF6C-F095-4AED-8798-ADF68C8354DE}">
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -580,7 +580,7 @@
         <v>2203</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" s="1">
         <v>5.2083333333333336E-2</v>
@@ -618,14 +618,14 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
         <v>879</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="1">
         <v>0.20347222222222219</v>
@@ -687,37 +687,37 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D9">
-        <v>531</v>
+        <v>575</v>
       </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1">
-        <v>0.22222222222222221</v>
+        <v>0.24444444444444444</v>
       </c>
       <c r="D10">
-        <v>575</v>
+        <v>4309</v>
       </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C11" s="1">
-        <v>0.24444444444444444</v>
+        <v>0.24652777777777779</v>
       </c>
       <c r="D11">
-        <v>4309</v>
+        <v>456</v>
       </c>
       <c r="G11" s="1"/>
     </row>
@@ -732,35 +732,35 @@
         <v>0.24652777777777779</v>
       </c>
       <c r="D12">
-        <v>456</v>
+        <v>661</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0.24652777777777779</v>
-      </c>
-      <c r="D13">
-        <v>661</v>
-      </c>
-      <c r="G13" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="E13">
+        <v>3154</v>
+      </c>
+      <c r="F13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C14" s="1"/>
       <c r="E14">
-        <v>3154</v>
+        <v>1467</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1">
         <v>0.25</v>
@@ -768,33 +768,33 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15">
-        <v>1467</v>
+        <v>3154</v>
       </c>
       <c r="F15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G15" s="1">
-        <v>0.25</v>
+        <v>0.25069444444444444</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="E16">
-        <v>3154</v>
-      </c>
-      <c r="F16" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0.25069444444444444</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.25694444444444442</v>
+      </c>
+      <c r="D16">
+        <v>433</v>
+      </c>
+      <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -807,7 +807,7 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="D17">
-        <v>433</v>
+        <v>579</v>
       </c>
       <c r="G17" s="1"/>
     </row>
@@ -816,13 +816,13 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C18" s="1">
-        <v>0.25694444444444442</v>
+        <v>0.26041666666666669</v>
       </c>
       <c r="D18">
-        <v>579</v>
+        <v>529</v>
       </c>
       <c r="G18" s="1"/>
     </row>
@@ -831,13 +831,13 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1">
-        <v>0.26041666666666669</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="D19">
-        <v>529</v>
+        <v>314</v>
       </c>
       <c r="G19" s="1"/>
     </row>
@@ -849,10 +849,10 @@
         <v>20</v>
       </c>
       <c r="C20" s="1">
-        <v>0.2638888888888889</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D20">
-        <v>314</v>
+        <v>428</v>
       </c>
       <c r="G20" s="1"/>
     </row>
@@ -867,7 +867,7 @@
         <v>0.2673611111111111</v>
       </c>
       <c r="D21">
-        <v>428</v>
+        <v>626</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -879,10 +879,10 @@
         <v>22</v>
       </c>
       <c r="C22" s="1">
-        <v>0.2673611111111111</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="D22">
-        <v>626</v>
+        <v>316</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -897,7 +897,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D23">
-        <v>316</v>
+        <v>366</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -912,7 +912,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D24">
-        <v>366</v>
+        <v>561</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -921,13 +921,13 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C25" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D25">
-        <v>561</v>
+        <v>591</v>
       </c>
       <c r="G25" s="1"/>
     </row>
@@ -936,13 +936,13 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C26" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D26">
-        <v>591</v>
+        <v>671</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -951,44 +951,44 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C27" s="1">
-        <v>0.27083333333333331</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="D27">
-        <v>671</v>
+        <v>521</v>
       </c>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="D28">
-        <v>521</v>
-      </c>
-      <c r="G28" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="E28">
+        <v>3154</v>
+      </c>
+      <c r="F28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0.29236111111111113</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C29" s="1"/>
       <c r="E29">
-        <v>3154</v>
+        <v>319</v>
       </c>
       <c r="F29" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G29" s="1">
-        <v>0.29236111111111113</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -997,7 +997,7 @@
       </c>
       <c r="C30" s="1"/>
       <c r="E30">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F30" t="s">
         <v>22</v>
@@ -1012,10 +1012,10 @@
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G31" s="1">
         <v>0.3125</v>
@@ -1030,7 +1030,7 @@
         <v>396</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G32" s="1">
         <v>0.3125</v>
@@ -1045,7 +1045,7 @@
         <v>310</v>
       </c>
       <c r="F33" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G33" s="1">
         <v>0.31597222222222221</v>
@@ -1060,7 +1060,7 @@
         <v>440</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G34" s="1">
         <v>0.31597222222222221</v>
@@ -1075,7 +1075,7 @@
         <v>536</v>
       </c>
       <c r="F35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G35" s="1">
         <v>0.31597222222222221</v>
@@ -1085,16 +1085,16 @@
       <c r="A36" t="s">
         <v>9</v>
       </c>
-      <c r="B36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" s="1">
-        <v>0.31944444444444442</v>
-      </c>
-      <c r="D36">
-        <v>321</v>
-      </c>
-      <c r="G36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="E36">
+        <v>444</v>
+      </c>
+      <c r="F36" t="s">
+        <v>37</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0.32291666666666669</v>
+      </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
@@ -1105,7 +1105,7 @@
         <v>562</v>
       </c>
       <c r="F37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G37" s="1">
         <v>0.32291666666666669</v>
@@ -1113,17 +1113,17 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C38" s="1"/>
       <c r="E38">
-        <v>368</v>
+        <v>4322</v>
       </c>
       <c r="F38" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G38" s="1">
-        <v>0.33333333333333331</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -1132,10 +1132,10 @@
       </c>
       <c r="C39" s="1"/>
       <c r="E39">
-        <v>522</v>
+        <v>368</v>
       </c>
       <c r="F39" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="G39" s="1">
         <v>0.33333333333333331</v>
@@ -1145,46 +1145,46 @@
       <c r="A40" t="s">
         <v>9</v>
       </c>
-      <c r="B40" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D40">
-        <v>581</v>
-      </c>
-      <c r="G40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="E40">
+        <v>522</v>
+      </c>
+      <c r="F40" t="s">
+        <v>8</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0.33333333333333331</v>
+      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="1"/>
-      <c r="E41">
-        <v>383</v>
-      </c>
-      <c r="F41" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" s="1">
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="1">
         <v>0.33680555555555558</v>
       </c>
+      <c r="D41">
+        <v>309</v>
+      </c>
+      <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="1"/>
-      <c r="E42">
-        <v>454</v>
-      </c>
-      <c r="F42" t="s">
-        <v>11</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0.34027777777777779</v>
-      </c>
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="D42">
+        <v>581</v>
+      </c>
+      <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -1192,13 +1192,13 @@
       </c>
       <c r="C43" s="1"/>
       <c r="E43">
-        <v>324</v>
+        <v>383</v>
       </c>
       <c r="F43" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G43" s="1">
-        <v>0.34375</v>
+        <v>0.33680555555555558</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1207,28 +1207,28 @@
       </c>
       <c r="C44" s="1"/>
       <c r="E44">
-        <v>572</v>
+        <v>454</v>
       </c>
       <c r="F44" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G44" s="1">
-        <v>0.34375</v>
+        <v>0.34027777777777779</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C45" s="1"/>
       <c r="E45">
-        <v>884</v>
+        <v>324</v>
       </c>
       <c r="F45" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G45" s="1">
-        <v>0.35347222222222219</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1237,29 +1237,29 @@
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>430</v>
+        <v>554</v>
       </c>
       <c r="F46" t="s">
         <v>18</v>
       </c>
       <c r="G46" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>9</v>
-      </c>
-      <c r="B47" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47" s="1">
-        <v>0.37152777777777779</v>
-      </c>
-      <c r="D47">
-        <v>451</v>
-      </c>
-      <c r="G47" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="E47">
+        <v>884</v>
+      </c>
+      <c r="F47" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0.35347222222222219</v>
+      </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -1267,13 +1267,13 @@
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>526</v>
+        <v>422</v>
       </c>
       <c r="F48" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G48" s="1">
-        <v>0.375</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1282,59 +1282,59 @@
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>369</v>
+        <v>430</v>
       </c>
       <c r="F49" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="G49" s="1">
-        <v>0.3888888888888889</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>9</v>
       </c>
-      <c r="C50" s="1"/>
-      <c r="E50">
-        <v>582</v>
-      </c>
-      <c r="F50" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="1">
-        <v>0.39930555555555558</v>
-      </c>
+      <c r="B50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.37847222222222221</v>
+      </c>
+      <c r="D50">
+        <v>559</v>
+      </c>
+      <c r="G50" s="1"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>12</v>
-      </c>
-      <c r="B51" t="s">
-        <v>26</v>
-      </c>
-      <c r="C51" s="1">
-        <v>0.40902777777777777</v>
-      </c>
-      <c r="D51">
-        <v>4337</v>
-      </c>
-      <c r="G51" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="E51">
+        <v>524</v>
+      </c>
+      <c r="F51" t="s">
+        <v>8</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.38194444444444442</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>9</v>
       </c>
-      <c r="B52" t="s">
-        <v>17</v>
-      </c>
-      <c r="C52" s="1">
-        <v>0.41319444444444442</v>
-      </c>
-      <c r="D52">
-        <v>569</v>
-      </c>
-      <c r="G52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="E52">
+        <v>369</v>
+      </c>
+      <c r="F52" t="s">
+        <v>33</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.3888888888888889</v>
+      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -1342,29 +1342,29 @@
       </c>
       <c r="C53" s="1"/>
       <c r="E53">
-        <v>392</v>
+        <v>582</v>
       </c>
       <c r="F53" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G53" s="1">
-        <v>0.41319444444444442</v>
+        <v>0.39930555555555558</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="1"/>
-      <c r="E54">
-        <v>408</v>
-      </c>
-      <c r="F54" t="s">
-        <v>38</v>
-      </c>
-      <c r="G54" s="1">
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="1">
         <v>0.41319444444444442</v>
       </c>
+      <c r="D54">
+        <v>569</v>
+      </c>
+      <c r="G54" s="1"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
@@ -1375,7 +1375,7 @@
         <v>609</v>
       </c>
       <c r="F55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G55" s="1">
         <v>0.4236111111111111</v>
@@ -1386,7 +1386,7 @@
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C56" s="1">
         <v>0.42708333333333331</v>
@@ -1416,13 +1416,13 @@
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C58" s="1">
-        <v>0.4513888888888889</v>
+        <v>0.4548611111111111</v>
       </c>
       <c r="D58">
-        <v>573</v>
+        <v>318</v>
       </c>
       <c r="G58" s="1"/>
     </row>
@@ -1431,75 +1431,75 @@
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C59" s="1">
-        <v>0.4548611111111111</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D59">
-        <v>318</v>
+        <v>384</v>
       </c>
       <c r="G59" s="1"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C60" s="1">
-        <v>0.46180555555555558</v>
+        <v>0.47291666666666665</v>
       </c>
       <c r="D60">
-        <v>384</v>
+        <v>495</v>
       </c>
       <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C61" s="1">
-        <v>0.47291666666666665</v>
+        <v>0.47847222222222219</v>
       </c>
       <c r="D61">
-        <v>495</v>
+        <v>1194</v>
       </c>
       <c r="G61" s="1"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>7</v>
-      </c>
-      <c r="B62" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="E62">
+        <v>584</v>
+      </c>
+      <c r="F62" t="s">
         <v>13</v>
       </c>
-      <c r="C62" s="1">
-        <v>0.47847222222222219</v>
-      </c>
-      <c r="D62">
-        <v>1194</v>
-      </c>
-      <c r="G62" s="1"/>
+      <c r="G62" s="1">
+        <v>0.49305555555555558</v>
+      </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>9</v>
-      </c>
-      <c r="C63" s="1"/>
-      <c r="E63">
-        <v>584</v>
-      </c>
-      <c r="F63" t="s">
-        <v>13</v>
-      </c>
-      <c r="G63" s="1">
-        <v>0.49305555555555558</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" s="1">
+        <v>0.49444444444444446</v>
+      </c>
+      <c r="D63">
+        <v>4301</v>
+      </c>
+      <c r="G63" s="1"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
@@ -1507,13 +1507,13 @@
       </c>
       <c r="C64" s="1"/>
       <c r="E64">
-        <v>434</v>
+        <v>385</v>
       </c>
       <c r="F64" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G64" s="1">
-        <v>0.49652777777777779</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -1522,10 +1522,10 @@
       </c>
       <c r="C65" s="1"/>
       <c r="E65">
-        <v>385</v>
+        <v>424</v>
       </c>
       <c r="F65" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G65" s="1">
         <v>0.50347222222222221</v>
@@ -1533,108 +1533,108 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>9</v>
-      </c>
-      <c r="C66" s="1"/>
-      <c r="E66">
-        <v>424</v>
-      </c>
-      <c r="F66" t="s">
-        <v>29</v>
-      </c>
-      <c r="G66" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B66" t="s">
+        <v>27</v>
+      </c>
+      <c r="C66" s="1">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D66">
+        <v>1441</v>
+      </c>
+      <c r="G66" s="1"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C67" s="1"/>
       <c r="E67">
-        <v>442</v>
+        <v>1508</v>
       </c>
       <c r="F67" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G67" s="1">
-        <v>0.50347222222222221</v>
+        <v>0.51597222222222228</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B68" t="s">
         <v>29</v>
       </c>
       <c r="C68" s="1">
-        <v>0.51041666666666663</v>
+        <v>0.5180555555555556</v>
       </c>
       <c r="D68">
-        <v>1441</v>
+        <v>1910</v>
       </c>
       <c r="G68" s="1"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>27</v>
-      </c>
-      <c r="C69" s="1"/>
-      <c r="E69">
-        <v>1508</v>
-      </c>
-      <c r="F69" t="s">
-        <v>28</v>
-      </c>
-      <c r="G69" s="1">
-        <v>0.51597222222222228</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B69" t="s">
+        <v>30</v>
+      </c>
+      <c r="C69" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D69">
+        <v>937</v>
+      </c>
+      <c r="G69" s="1"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B70" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C70" s="1">
-        <v>0.5180555555555556</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="D70">
-        <v>1910</v>
+        <v>816</v>
       </c>
       <c r="G70" s="1"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>27</v>
-      </c>
-      <c r="B71" t="s">
-        <v>32</v>
-      </c>
-      <c r="C71" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D71">
-        <v>937</v>
-      </c>
-      <c r="G71" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C71" s="1"/>
+      <c r="E71">
+        <v>1458</v>
+      </c>
+      <c r="F71" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0.55555555555555558</v>
+      </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>33</v>
-      </c>
-      <c r="B72" t="s">
-        <v>23</v>
-      </c>
-      <c r="C72" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D72">
-        <v>816</v>
-      </c>
-      <c r="G72" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="C72" s="1"/>
+      <c r="E72">
+        <v>380</v>
+      </c>
+      <c r="F72" t="s">
+        <v>30</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0.57222222222222219</v>
+      </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
@@ -1642,162 +1642,162 @@
       </c>
       <c r="C73" s="1"/>
       <c r="E73">
-        <v>1458</v>
+        <v>1468</v>
       </c>
       <c r="F73" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G73" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.57638888888888895</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C74" s="1"/>
       <c r="E74">
-        <v>380</v>
+        <v>1978</v>
       </c>
       <c r="F74" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G74" s="1">
-        <v>0.57222222222222219</v>
+        <v>0.57708333333333328</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C75" s="1"/>
       <c r="E75">
-        <v>1468</v>
+        <v>871</v>
       </c>
       <c r="F75" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G75" s="1">
-        <v>0.57638888888888895</v>
+        <v>0.58194444444444449</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>30</v>
-      </c>
-      <c r="C76" s="1"/>
-      <c r="E76">
-        <v>1978</v>
-      </c>
-      <c r="F76" t="s">
-        <v>31</v>
-      </c>
-      <c r="G76" s="1">
-        <v>0.57708333333333328</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B76" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" s="1">
+        <v>0.59236111111111112</v>
+      </c>
+      <c r="D76">
+        <v>628</v>
+      </c>
+      <c r="G76" s="1"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>33</v>
-      </c>
-      <c r="C77" s="1"/>
-      <c r="E77">
-        <v>871</v>
-      </c>
-      <c r="F77" t="s">
-        <v>23</v>
-      </c>
-      <c r="G77" s="1">
-        <v>0.58194444444444449</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B77" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77" s="1">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D77">
+        <v>1290</v>
+      </c>
+      <c r="G77" s="1"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B78" t="s">
         <v>18</v>
       </c>
       <c r="C78" s="1">
-        <v>0.59236111111111112</v>
+        <v>0.625</v>
       </c>
       <c r="D78">
-        <v>628</v>
+        <v>557</v>
       </c>
       <c r="G78" s="1"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>7</v>
-      </c>
-      <c r="B79" t="s">
-        <v>29</v>
-      </c>
-      <c r="C79" s="1">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D79">
-        <v>1290</v>
-      </c>
-      <c r="G79" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="E79">
+        <v>629</v>
+      </c>
+      <c r="F79" t="s">
+        <v>17</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0.64722222222222225</v>
+      </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>34</v>
-      </c>
-      <c r="C80" s="1"/>
-      <c r="E80">
-        <v>629</v>
-      </c>
-      <c r="F80" t="s">
-        <v>18</v>
-      </c>
-      <c r="G80" s="1">
-        <v>0.64722222222222225</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B80" t="s">
+        <v>23</v>
+      </c>
+      <c r="C80" s="1">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D80">
+        <v>382</v>
+      </c>
+      <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>9</v>
-      </c>
-      <c r="B81" t="s">
-        <v>24</v>
-      </c>
-      <c r="C81" s="1">
+        <v>7</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="E81">
+        <v>1130</v>
+      </c>
+      <c r="F81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G81" s="1">
         <v>0.65277777777777779</v>
       </c>
-      <c r="D81">
-        <v>382</v>
-      </c>
-      <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="1"/>
-      <c r="E82">
-        <v>1130</v>
-      </c>
-      <c r="F82" t="s">
-        <v>29</v>
-      </c>
-      <c r="G82" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B82" t="s">
+        <v>27</v>
+      </c>
+      <c r="C82" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D82">
+        <v>367</v>
+      </c>
+      <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>9</v>
       </c>
       <c r="B83" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C83" s="1">
         <v>0.66666666666666663</v>
       </c>
       <c r="D83">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G83" s="1"/>
     </row>
@@ -1806,13 +1806,13 @@
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C84" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D84">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="G84" s="1"/>
     </row>
@@ -1821,13 +1821,13 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C85" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.68055555555555558</v>
       </c>
       <c r="D85">
-        <v>397</v>
+        <v>441</v>
       </c>
       <c r="G85" s="1"/>
     </row>
@@ -1836,13 +1836,13 @@
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C86" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D86">
-        <v>553</v>
+        <v>423</v>
       </c>
       <c r="G86" s="1"/>
     </row>
@@ -1851,13 +1851,13 @@
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C87" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.6875</v>
       </c>
       <c r="D87">
-        <v>441</v>
+        <v>311</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1866,13 +1866,13 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C88" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.6875</v>
       </c>
       <c r="D88">
-        <v>435</v>
+        <v>555</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -1881,13 +1881,13 @@
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C89" s="1">
         <v>0.6875</v>
       </c>
       <c r="D89">
-        <v>311</v>
+        <v>610</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -1899,10 +1899,10 @@
         <v>22</v>
       </c>
       <c r="C90" s="1">
-        <v>0.6875</v>
+        <v>0.70138888888888884</v>
       </c>
       <c r="D90">
-        <v>610</v>
+        <v>322</v>
       </c>
       <c r="G90" s="1"/>
     </row>
@@ -1910,16 +1910,16 @@
       <c r="A91" t="s">
         <v>9</v>
       </c>
-      <c r="B91" t="s">
-        <v>23</v>
-      </c>
-      <c r="C91" s="1">
-        <v>0.70138888888888884</v>
-      </c>
-      <c r="D91">
-        <v>322</v>
-      </c>
-      <c r="G91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="E91">
+        <v>326</v>
+      </c>
+      <c r="F91" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
@@ -1927,13 +1927,13 @@
       </c>
       <c r="C92" s="1"/>
       <c r="E92">
-        <v>320</v>
+        <v>560</v>
       </c>
       <c r="F92" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G92" s="1">
-        <v>0.72222222222222221</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -1942,13 +1942,13 @@
       </c>
       <c r="C93" s="1"/>
       <c r="E93">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="F93" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G93" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -1957,13 +1957,13 @@
       </c>
       <c r="C94" s="1"/>
       <c r="E94">
-        <v>560</v>
+        <v>450</v>
       </c>
       <c r="F94" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G94" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -1972,10 +1972,10 @@
       </c>
       <c r="C95" s="1"/>
       <c r="E95">
-        <v>313</v>
+        <v>520</v>
       </c>
       <c r="F95" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="G95" s="1">
         <v>0.73263888888888884</v>
@@ -1987,13 +1987,13 @@
       </c>
       <c r="C96" s="1"/>
       <c r="E96">
-        <v>520</v>
+        <v>588</v>
       </c>
       <c r="F96" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G96" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.73611111111111116</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -2002,13 +2002,13 @@
       </c>
       <c r="C97" s="1"/>
       <c r="E97">
-        <v>530</v>
+        <v>448</v>
       </c>
       <c r="F97" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G97" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -2017,43 +2017,43 @@
       </c>
       <c r="C98" s="1"/>
       <c r="E98">
-        <v>588</v>
+        <v>534</v>
       </c>
       <c r="F98" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G98" s="1">
-        <v>0.73611111111111116</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>534</v>
+        <v>4308</v>
       </c>
       <c r="F99" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G99" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>4308</v>
+        <v>528</v>
       </c>
       <c r="F100" t="s">
         <v>8</v>
       </c>
       <c r="G100" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.76041666666666663</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -2062,24 +2062,24 @@
       </c>
       <c r="C101" s="1"/>
       <c r="E101">
-        <v>528</v>
+        <v>660</v>
       </c>
       <c r="F101" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G101" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B102" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C102" s="1">
-        <v>0.76736111111111116</v>
+        <v>0.77430555555555558</v>
       </c>
       <c r="D102">
         <v>222</v>
@@ -2088,77 +2088,77 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>9</v>
-      </c>
-      <c r="C103" s="1"/>
-      <c r="E103">
-        <v>660</v>
-      </c>
-      <c r="F103" t="s">
-        <v>17</v>
-      </c>
-      <c r="G103" s="1">
-        <v>0.77083333333333337</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B103" t="s">
+        <v>25</v>
+      </c>
+      <c r="C103" s="1">
+        <v>0.77847222222222223</v>
+      </c>
+      <c r="D103">
+        <v>2657</v>
+      </c>
+      <c r="G103" s="1"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>9</v>
-      </c>
-      <c r="C104" s="1"/>
-      <c r="E104">
-        <v>558</v>
-      </c>
-      <c r="F104" t="s">
-        <v>25</v>
-      </c>
-      <c r="G104" s="1">
-        <v>0.77777777777777779</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B104" t="s">
+        <v>27</v>
+      </c>
+      <c r="C104" s="1">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="D104">
+        <v>742</v>
+      </c>
+      <c r="G104" s="1"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>27</v>
-      </c>
-      <c r="B105" t="s">
-        <v>28</v>
-      </c>
-      <c r="C105" s="1">
-        <v>0.77847222222222223</v>
-      </c>
-      <c r="D105">
-        <v>2657</v>
-      </c>
-      <c r="G105" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C105" s="1"/>
+      <c r="E105">
+        <v>4312</v>
+      </c>
+      <c r="F105" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" s="1">
+        <v>0.79027777777777775</v>
+      </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B106" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C106" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.79513888888888884</v>
       </c>
       <c r="D106">
-        <v>742</v>
+        <v>431</v>
       </c>
       <c r="G106" s="1"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C107" s="1"/>
       <c r="E107">
-        <v>4312</v>
+        <v>670</v>
       </c>
       <c r="F107" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G107" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.80555555555555558</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -2166,13 +2166,13 @@
         <v>9</v>
       </c>
       <c r="B108" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C108" s="1">
-        <v>0.79513888888888884</v>
+        <v>0.81944444444444442</v>
       </c>
       <c r="D108">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="G108" s="1"/>
     </row>
@@ -2180,89 +2180,89 @@
       <c r="A109" t="s">
         <v>9</v>
       </c>
-      <c r="C109" s="1"/>
-      <c r="E109">
-        <v>670</v>
-      </c>
-      <c r="F109" t="s">
-        <v>17</v>
-      </c>
-      <c r="G109" s="1">
-        <v>0.80555555555555558</v>
-      </c>
+      <c r="B109" t="s">
+        <v>36</v>
+      </c>
+      <c r="C109" s="1">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D109">
+        <v>329</v>
+      </c>
+      <c r="G109" s="1"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>12</v>
-      </c>
-      <c r="C110" s="1"/>
-      <c r="E110">
-        <v>4300</v>
-      </c>
-      <c r="F110" t="s">
-        <v>18</v>
-      </c>
-      <c r="G110" s="1">
-        <v>0.81388888888888888</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B110" t="s">
+        <v>8</v>
+      </c>
+      <c r="C110" s="1">
+        <v>0.82638888888888884</v>
+      </c>
+      <c r="D110">
+        <v>523</v>
+      </c>
+      <c r="G110" s="1"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C111" s="1">
-        <v>0.81944444444444442</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D111">
-        <v>425</v>
+        <v>583</v>
       </c>
       <c r="G111" s="1"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>9</v>
-      </c>
-      <c r="B112" t="s">
-        <v>8</v>
-      </c>
-      <c r="C112" s="1">
-        <v>0.82638888888888884</v>
-      </c>
-      <c r="D112">
-        <v>523</v>
-      </c>
-      <c r="G112" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="C112" s="1"/>
+      <c r="E112">
+        <v>222</v>
+      </c>
+      <c r="F112" t="s">
+        <v>40</v>
+      </c>
+      <c r="G112" s="1">
+        <v>0.83680555555555558</v>
+      </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>37</v>
-      </c>
-      <c r="C113" s="1"/>
-      <c r="E113">
-        <v>222</v>
-      </c>
-      <c r="F113" t="s">
-        <v>40</v>
-      </c>
-      <c r="G113" s="1">
-        <v>0.82986111111111116</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B113" t="s">
+        <v>10</v>
+      </c>
+      <c r="C113" s="1">
+        <v>0.84375</v>
+      </c>
+      <c r="D113">
+        <v>325</v>
+      </c>
+      <c r="G113" s="1"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C114" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.84375</v>
       </c>
       <c r="D114">
-        <v>583</v>
+        <v>445</v>
       </c>
       <c r="G114" s="1"/>
     </row>
@@ -2270,59 +2270,59 @@
       <c r="A115" t="s">
         <v>9</v>
       </c>
-      <c r="B115" t="s">
-        <v>10</v>
-      </c>
-      <c r="C115" s="1">
-        <v>0.84375</v>
-      </c>
-      <c r="D115">
-        <v>325</v>
-      </c>
-      <c r="G115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="E115">
+        <v>590</v>
+      </c>
+      <c r="F115" t="s">
+        <v>13</v>
+      </c>
+      <c r="G115" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>9</v>
       </c>
       <c r="B116" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C116" s="1">
-        <v>0.85069444444444442</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D116">
-        <v>393</v>
+        <v>449</v>
       </c>
       <c r="G116" s="1"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>9</v>
-      </c>
-      <c r="C117" s="1"/>
-      <c r="E117">
-        <v>590</v>
-      </c>
-      <c r="F117" t="s">
-        <v>13</v>
-      </c>
-      <c r="G117" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B117" t="s">
+        <v>22</v>
+      </c>
+      <c r="C117" s="1">
+        <v>0.8569444444444444</v>
+      </c>
+      <c r="D117">
+        <v>881</v>
+      </c>
+      <c r="G117" s="1"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C118" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.86111111111111116</v>
       </c>
       <c r="D118">
-        <v>881</v>
+        <v>4323</v>
       </c>
       <c r="G118" s="1"/>
     </row>
@@ -2331,7 +2331,7 @@
         <v>7</v>
       </c>
       <c r="B119" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C119" s="1">
         <v>0.86736111111111114</v>
@@ -2346,13 +2346,13 @@
         <v>9</v>
       </c>
       <c r="B120" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C120" s="1">
         <v>0.86805555555555558</v>
       </c>
       <c r="D120">
-        <v>443</v>
+        <v>563</v>
       </c>
       <c r="G120" s="1"/>
     </row>
@@ -2361,13 +2361,13 @@
         <v>9</v>
       </c>
       <c r="B121" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C121" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.875</v>
       </c>
       <c r="D121">
-        <v>563</v>
+        <v>535</v>
       </c>
       <c r="G121" s="1"/>
     </row>
@@ -2376,13 +2376,13 @@
         <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C122" s="1">
-        <v>0.87152777777777779</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D122">
-        <v>409</v>
+        <v>312</v>
       </c>
       <c r="G122" s="1"/>
     </row>
@@ -2391,13 +2391,13 @@
         <v>9</v>
       </c>
       <c r="B123" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="C123" s="1">
-        <v>0.875</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D123">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G123" s="1"/>
     </row>
@@ -2406,28 +2406,28 @@
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C124" s="1">
-        <v>0.875</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D124">
-        <v>535</v>
+        <v>589</v>
       </c>
       <c r="G124" s="1"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B125" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C125" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.89930555555555547</v>
       </c>
       <c r="D125">
-        <v>312</v>
+        <v>1425</v>
       </c>
       <c r="G125" s="1"/>
     </row>
@@ -2436,45 +2436,45 @@
         <v>9</v>
       </c>
       <c r="B126" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C126" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.91319444444444442</v>
       </c>
       <c r="D126">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G126" s="1"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>7</v>
-      </c>
-      <c r="B127" t="s">
-        <v>26</v>
-      </c>
-      <c r="C127" s="1">
-        <v>0.89930555555555547</v>
-      </c>
-      <c r="D127">
-        <v>1425</v>
-      </c>
-      <c r="G127" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C127" s="1"/>
+      <c r="E127">
+        <v>315</v>
+      </c>
+      <c r="F127" t="s">
+        <v>19</v>
+      </c>
+      <c r="G127" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>9</v>
       </c>
-      <c r="B128" t="s">
-        <v>13</v>
-      </c>
-      <c r="C128" s="1">
-        <v>0.91319444444444442</v>
-      </c>
-      <c r="D128">
-        <v>585</v>
-      </c>
-      <c r="G128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="E128">
+        <v>365</v>
+      </c>
+      <c r="F128" t="s">
+        <v>23</v>
+      </c>
+      <c r="G128" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
@@ -2482,10 +2482,10 @@
       </c>
       <c r="C129" s="1"/>
       <c r="E129">
-        <v>315</v>
+        <v>600</v>
       </c>
       <c r="F129" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G129" s="1">
         <v>0.92013888888888884</v>
@@ -2497,13 +2497,13 @@
       </c>
       <c r="C130" s="1"/>
       <c r="E130">
-        <v>365</v>
+        <v>429</v>
       </c>
       <c r="F130" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G130" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.92708333333333337</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -2512,13 +2512,13 @@
       </c>
       <c r="C131" s="1"/>
       <c r="E131">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F131" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G131" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.93055555555555558</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -2527,13 +2527,13 @@
       </c>
       <c r="C132" s="1"/>
       <c r="E132">
-        <v>308</v>
+        <v>627</v>
       </c>
       <c r="F132" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G132" s="1">
-        <v>0.92361111111111116</v>
+        <v>0.93402777777777779</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -2542,13 +2542,13 @@
       </c>
       <c r="C133" s="1"/>
       <c r="E133">
-        <v>429</v>
+        <v>568</v>
       </c>
       <c r="F133" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G133" s="1">
-        <v>0.92708333333333337</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -2557,43 +2557,43 @@
       </c>
       <c r="C134" s="1"/>
       <c r="E134">
-        <v>578</v>
+        <v>452</v>
       </c>
       <c r="F134" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G134" s="1">
-        <v>0.93055555555555558</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C135" s="1"/>
       <c r="E135">
-        <v>627</v>
+        <v>339</v>
       </c>
       <c r="F135" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="G135" s="1">
-        <v>0.93402777777777779</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>574</v>
+        <v>4336</v>
       </c>
       <c r="F136" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="G136" s="1">
-        <v>0.9375</v>
+        <v>0.9506944444444444</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -2602,13 +2602,13 @@
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>568</v>
+        <v>317</v>
       </c>
       <c r="F137" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G137" s="1">
-        <v>0.94097222222222221</v>
+        <v>0.95486111111111116</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -2617,28 +2617,28 @@
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="F138" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G138" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>339</v>
+        <v>457</v>
       </c>
       <c r="F139" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G139" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -2647,59 +2647,29 @@
       </c>
       <c r="C140" s="1"/>
       <c r="E140">
-        <v>317</v>
+        <v>552</v>
       </c>
       <c r="F140" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G140" s="1">
-        <v>0.95486111111111116</v>
+        <v>0.97222222222222221</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>9</v>
-      </c>
-      <c r="C141" s="1"/>
-      <c r="E141">
-        <v>457</v>
-      </c>
-      <c r="F141" t="s">
-        <v>16</v>
-      </c>
-      <c r="G141" s="1">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>9</v>
-      </c>
-      <c r="C142" s="1"/>
-      <c r="E142">
-        <v>556</v>
-      </c>
-      <c r="F142" t="s">
-        <v>19</v>
-      </c>
-      <c r="G142" s="1">
-        <v>0.97222222222222221</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>33</v>
-      </c>
-      <c r="B143" t="s">
-        <v>23</v>
-      </c>
-      <c r="C143" s="1">
+        <v>31</v>
+      </c>
+      <c r="B141" t="s">
+        <v>22</v>
+      </c>
+      <c r="C141" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D143">
+      <c r="D141">
         <v>878</v>
       </c>
-      <c r="G143" s="1"/>
+      <c r="G141" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C3B3E85-B5F0-44B4-A4C5-BFCFAD1A484D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CE2C9B0-8A3F-4641-B71A-DCF43A1EAE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9A99B0D8-2876-44EC-9A89-B05B613E14B2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{98711CBC-1F14-49A0-B491-A108215DF5BF}"/>
   </bookViews>
   <sheets>
-    <sheet name="10-06" sheetId="1" r:id="rId1"/>
+    <sheet name="11-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="43">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,45 +83,51 @@
     <t>KIAD</t>
   </si>
   <si>
+    <t>KONT</t>
+  </si>
+  <si>
+    <t>SEQM</t>
+  </si>
+  <si>
+    <t>KJFK</t>
+  </si>
+  <si>
+    <t>MMMX</t>
+  </si>
+  <si>
+    <t>MGGT</t>
+  </si>
+  <si>
+    <t>MNMG</t>
+  </si>
+  <si>
+    <t>SPJC</t>
+  </si>
+  <si>
+    <t>MROC</t>
+  </si>
+  <si>
+    <t>MPTO</t>
+  </si>
+  <si>
+    <t>SKBO</t>
+  </si>
+  <si>
+    <t>KSFO</t>
+  </si>
+  <si>
+    <t>KEWR</t>
+  </si>
+  <si>
     <t>MHLM</t>
   </si>
   <si>
-    <t>SEQM</t>
-  </si>
-  <si>
-    <t>KJFK</t>
-  </si>
-  <si>
-    <t>MMMX</t>
-  </si>
-  <si>
-    <t>MGGT</t>
-  </si>
-  <si>
-    <t>MNMG</t>
-  </si>
-  <si>
-    <t>SPJC</t>
-  </si>
-  <si>
-    <t>MROC</t>
-  </si>
-  <si>
-    <t>MPTO</t>
-  </si>
-  <si>
-    <t>SKBO</t>
-  </si>
-  <si>
-    <t>KSFO</t>
+    <t>AAL</t>
   </si>
   <si>
     <t>KMIA</t>
   </si>
   <si>
-    <t>AAL</t>
-  </si>
-  <si>
     <t>KIAH</t>
   </si>
   <si>
@@ -131,6 +137,12 @@
     <t>KATL</t>
   </si>
   <si>
+    <t>TAG</t>
+  </si>
+  <si>
+    <t>MHRO</t>
+  </si>
+  <si>
     <t>KDFW</t>
   </si>
   <si>
@@ -143,22 +155,16 @@
     <t>SKRG</t>
   </si>
   <si>
-    <t>KMCO</t>
+    <t>MMUN</t>
   </si>
   <si>
     <t>IBE</t>
   </si>
   <si>
-    <t>CYUL</t>
-  </si>
-  <si>
-    <t>KBOS</t>
-  </si>
-  <si>
-    <t>KOAK</t>
-  </si>
-  <si>
-    <t>KEWR</t>
+    <t>KORD</t>
+  </si>
+  <si>
+    <t>KLAS</t>
   </si>
   <si>
     <t>LEMD</t>
@@ -536,8 +542,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC9DEF6C-F095-4AED-8798-ADF68C8354DE}">
-  <dimension ref="A1:G141"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{424AD4F2-BAB2-4904-A23D-19880E5291BA}">
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -580,7 +586,7 @@
         <v>2203</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2" s="1">
         <v>5.2083333333333336E-2</v>
@@ -618,7 +624,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
@@ -687,7 +693,7 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D9">
-        <v>575</v>
+        <v>531</v>
       </c>
       <c r="G9" s="1"/>
     </row>
@@ -738,14 +744,14 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" s="1"/>
       <c r="E13">
         <v>3154</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G13" s="1">
         <v>0.25</v>
@@ -760,7 +766,7 @@
         <v>1467</v>
       </c>
       <c r="F14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G14" s="1">
         <v>0.25</v>
@@ -768,14 +774,14 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15">
         <v>3154</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G15" s="1">
         <v>0.25069444444444444</v>
@@ -963,17 +969,17 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C28" s="1"/>
       <c r="E28">
-        <v>3154</v>
+        <v>319</v>
       </c>
       <c r="F28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G28" s="1">
-        <v>0.29236111111111113</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -982,10 +988,10 @@
       </c>
       <c r="C29" s="1"/>
       <c r="E29">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G29" s="1">
         <v>0.3125</v>
@@ -997,10 +1003,10 @@
       </c>
       <c r="C30" s="1"/>
       <c r="E30">
-        <v>323</v>
+        <v>396</v>
       </c>
       <c r="F30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G30" s="1">
         <v>0.3125</v>
@@ -1008,14 +1014,14 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>328</v>
+        <v>884</v>
       </c>
       <c r="F31" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G31" s="1">
         <v>0.3125</v>
@@ -1027,13 +1033,13 @@
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>396</v>
+        <v>310</v>
       </c>
       <c r="F32" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G32" s="1">
-        <v>0.3125</v>
+        <v>0.31597222222222221</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1042,10 +1048,10 @@
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>310</v>
+        <v>440</v>
       </c>
       <c r="F33" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G33" s="1">
         <v>0.31597222222222221</v>
@@ -1057,10 +1063,10 @@
       </c>
       <c r="C34" s="1"/>
       <c r="E34">
-        <v>440</v>
+        <v>536</v>
       </c>
       <c r="F34" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G34" s="1">
         <v>0.31597222222222221</v>
@@ -1070,16 +1076,16 @@
       <c r="A35" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="1"/>
-      <c r="E35">
-        <v>536</v>
-      </c>
-      <c r="F35" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0.31597222222222221</v>
-      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="D35">
+        <v>321</v>
+      </c>
+      <c r="G35" s="1"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
@@ -1087,10 +1093,10 @@
       </c>
       <c r="C36" s="1"/>
       <c r="E36">
-        <v>444</v>
+        <v>562</v>
       </c>
       <c r="F36" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G36" s="1">
         <v>0.32291666666666669</v>
@@ -1102,44 +1108,44 @@
       </c>
       <c r="C37" s="1"/>
       <c r="E37">
-        <v>562</v>
+        <v>368</v>
       </c>
       <c r="F37" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G37" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C38" s="1"/>
       <c r="E38">
-        <v>4322</v>
+        <v>522</v>
       </c>
       <c r="F38" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="G38" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="1"/>
-      <c r="E39">
-        <v>368</v>
-      </c>
-      <c r="F39" t="s">
-        <v>27</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0.33333333333333331</v>
-      </c>
+      <c r="B39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="D39">
+        <v>601</v>
+      </c>
+      <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
@@ -1147,44 +1153,44 @@
       </c>
       <c r="C40" s="1"/>
       <c r="E40">
-        <v>522</v>
+        <v>383</v>
       </c>
       <c r="F40" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G40" s="1">
-        <v>0.33333333333333331</v>
+        <v>0.33680555555555558</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>9</v>
       </c>
-      <c r="B41" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D41">
-        <v>309</v>
-      </c>
-      <c r="G41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="E41">
+        <v>454</v>
+      </c>
+      <c r="F41" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0.34027777777777779</v>
+      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>9</v>
       </c>
-      <c r="B42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D42">
-        <v>581</v>
-      </c>
-      <c r="G42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="E42">
+        <v>324</v>
+      </c>
+      <c r="F42" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.34375</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -1192,13 +1198,13 @@
       </c>
       <c r="C43" s="1"/>
       <c r="E43">
-        <v>383</v>
+        <v>572</v>
       </c>
       <c r="F43" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G43" s="1">
-        <v>0.33680555555555558</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1207,29 +1213,29 @@
       </c>
       <c r="C44" s="1"/>
       <c r="E44">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G44" s="1">
-        <v>0.34027777777777779</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>9</v>
       </c>
-      <c r="C45" s="1"/>
-      <c r="E45">
-        <v>324</v>
-      </c>
-      <c r="F45" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="1">
-        <v>0.34375</v>
-      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="D45">
+        <v>451</v>
+      </c>
+      <c r="G45" s="1"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
@@ -1237,28 +1243,28 @@
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>554</v>
+        <v>526</v>
       </c>
       <c r="F46" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="G46" s="1">
-        <v>0.34375</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C47" s="1"/>
       <c r="E47">
-        <v>884</v>
+        <v>4320</v>
       </c>
       <c r="F47" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G47" s="1">
-        <v>0.35347222222222219</v>
+        <v>0.38333333333333336</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -1267,13 +1273,13 @@
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>422</v>
+        <v>369</v>
       </c>
       <c r="F48" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G48" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.3888888888888889</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1282,27 +1288,27 @@
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>430</v>
+        <v>582</v>
       </c>
       <c r="F49" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G49" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.39930555555555558</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C50" s="1">
-        <v>0.37847222222222221</v>
+        <v>0.40902777777777777</v>
       </c>
       <c r="D50">
-        <v>559</v>
+        <v>4337</v>
       </c>
       <c r="G50" s="1"/>
     </row>
@@ -1310,16 +1316,16 @@
       <c r="A51" t="s">
         <v>9</v>
       </c>
-      <c r="C51" s="1"/>
-      <c r="E51">
-        <v>524</v>
-      </c>
-      <c r="F51" t="s">
-        <v>8</v>
-      </c>
-      <c r="G51" s="1">
-        <v>0.38194444444444442</v>
-      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="D51">
+        <v>569</v>
+      </c>
+      <c r="G51" s="1"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
@@ -1327,13 +1333,13 @@
       </c>
       <c r="C52" s="1"/>
       <c r="E52">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="F52" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G52" s="1">
-        <v>0.3888888888888889</v>
+        <v>0.41319444444444442</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -1342,57 +1348,57 @@
       </c>
       <c r="C53" s="1"/>
       <c r="E53">
-        <v>582</v>
+        <v>408</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="G53" s="1">
-        <v>0.39930555555555558</v>
+        <v>0.41319444444444442</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>9</v>
       </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" s="1">
-        <v>0.41319444444444442</v>
-      </c>
-      <c r="D54">
-        <v>569</v>
-      </c>
-      <c r="G54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="E54">
+        <v>609</v>
+      </c>
+      <c r="F54" t="s">
+        <v>21</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0.4236111111111111</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>9</v>
       </c>
-      <c r="C55" s="1"/>
-      <c r="E55">
-        <v>609</v>
-      </c>
-      <c r="F55" t="s">
-        <v>21</v>
-      </c>
-      <c r="G55" s="1">
-        <v>0.4236111111111111</v>
-      </c>
+      <c r="B55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" s="1">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D55">
+        <v>537</v>
+      </c>
+      <c r="G55" s="1"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C56" s="1">
-        <v>0.42708333333333331</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="D56">
-        <v>537</v>
+        <v>455</v>
       </c>
       <c r="G56" s="1"/>
     </row>
@@ -1401,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C57" s="1">
-        <v>0.44791666666666669</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="D57">
-        <v>455</v>
+        <v>573</v>
       </c>
       <c r="G57" s="1"/>
     </row>
@@ -1443,10 +1449,10 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B60" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C60" s="1">
         <v>0.47291666666666665</v>
@@ -1488,18 +1494,18 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>12</v>
-      </c>
-      <c r="B63" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63" s="1">
-        <v>0.49444444444444446</v>
-      </c>
-      <c r="D63">
-        <v>4301</v>
-      </c>
-      <c r="G63" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C63" s="1"/>
+      <c r="E63">
+        <v>434</v>
+      </c>
+      <c r="F63" t="s">
+        <v>38</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0.49652777777777779</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
@@ -1525,7 +1531,7 @@
         <v>424</v>
       </c>
       <c r="F65" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G65" s="1">
         <v>0.50347222222222221</v>
@@ -1533,242 +1539,242 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>7</v>
-      </c>
-      <c r="B66" t="s">
-        <v>27</v>
-      </c>
-      <c r="C66" s="1">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="D66">
-        <v>1441</v>
-      </c>
-      <c r="G66" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="E66">
+        <v>442</v>
+      </c>
+      <c r="F66" t="s">
+        <v>34</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>26</v>
-      </c>
-      <c r="C67" s="1"/>
-      <c r="E67">
-        <v>1508</v>
-      </c>
-      <c r="F67" t="s">
-        <v>25</v>
-      </c>
-      <c r="G67" s="1">
-        <v>0.51597222222222228</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B67" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" s="1">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D67">
+        <v>1441</v>
+      </c>
+      <c r="G67" s="1"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="E68">
+        <v>1508</v>
+      </c>
+      <c r="F68" t="s">
         <v>28</v>
       </c>
-      <c r="B68" t="s">
-        <v>29</v>
-      </c>
-      <c r="C68" s="1">
-        <v>0.5180555555555556</v>
-      </c>
-      <c r="D68">
-        <v>1910</v>
-      </c>
-      <c r="G68" s="1"/>
+      <c r="G68" s="1">
+        <v>0.51597222222222228</v>
+      </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B69" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C69" s="1">
-        <v>0.52916666666666667</v>
+        <v>0.5180555555555556</v>
       </c>
       <c r="D69">
-        <v>937</v>
+        <v>1910</v>
       </c>
       <c r="G69" s="1"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B70" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C70" s="1">
-        <v>0.52916666666666667</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D70">
-        <v>816</v>
+        <v>420</v>
       </c>
       <c r="G70" s="1"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="1"/>
-      <c r="E71">
-        <v>1458</v>
-      </c>
-      <c r="F71" t="s">
-        <v>13</v>
-      </c>
-      <c r="G71" s="1">
-        <v>0.55555555555555558</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B71" t="s">
+        <v>34</v>
+      </c>
+      <c r="C71" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D71">
+        <v>937</v>
+      </c>
+      <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>26</v>
-      </c>
-      <c r="C72" s="1"/>
-      <c r="E72">
-        <v>380</v>
-      </c>
-      <c r="F72" t="s">
-        <v>30</v>
-      </c>
-      <c r="G72" s="1">
-        <v>0.57222222222222219</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B72" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D72">
+        <v>816</v>
+      </c>
+      <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C73" s="1"/>
       <c r="E73">
-        <v>1468</v>
+        <v>421</v>
       </c>
       <c r="F73" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G73" s="1">
-        <v>0.57638888888888895</v>
+        <v>0.55208333333333337</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C74" s="1"/>
       <c r="E74">
-        <v>1978</v>
+        <v>1458</v>
       </c>
       <c r="F74" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G74" s="1">
-        <v>0.57708333333333328</v>
+        <v>0.55555555555555558</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C75" s="1"/>
       <c r="E75">
-        <v>871</v>
+        <v>380</v>
       </c>
       <c r="F75" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G75" s="1">
-        <v>0.58194444444444449</v>
+        <v>0.57222222222222219</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>32</v>
-      </c>
-      <c r="B76" t="s">
-        <v>17</v>
-      </c>
-      <c r="C76" s="1">
-        <v>0.59236111111111112</v>
-      </c>
-      <c r="D76">
-        <v>628</v>
-      </c>
-      <c r="G76" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="E76">
+        <v>1468</v>
+      </c>
+      <c r="F76" t="s">
+        <v>29</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0.57638888888888895</v>
+      </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>7</v>
-      </c>
-      <c r="B77" t="s">
-        <v>27</v>
-      </c>
-      <c r="C77" s="1">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D77">
-        <v>1290</v>
-      </c>
-      <c r="G77" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="E77">
+        <v>1978</v>
+      </c>
+      <c r="F77" t="s">
+        <v>31</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0.57708333333333328</v>
+      </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>9</v>
-      </c>
-      <c r="B78" t="s">
-        <v>18</v>
-      </c>
-      <c r="C78" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="D78">
-        <v>557</v>
-      </c>
-      <c r="G78" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="E78">
+        <v>871</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0.58194444444444449</v>
+      </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>32</v>
-      </c>
-      <c r="C79" s="1"/>
-      <c r="E79">
-        <v>629</v>
-      </c>
-      <c r="F79" t="s">
+        <v>36</v>
+      </c>
+      <c r="B79" t="s">
         <v>17</v>
       </c>
-      <c r="G79" s="1">
-        <v>0.64722222222222225</v>
-      </c>
+      <c r="C79" s="1">
+        <v>0.59375</v>
+      </c>
+      <c r="D79">
+        <v>628</v>
+      </c>
+      <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B80" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C80" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D80">
-        <v>382</v>
+        <v>1290</v>
       </c>
       <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="C81" s="1"/>
       <c r="E81">
-        <v>1130</v>
+        <v>629</v>
       </c>
       <c r="F81" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G81" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.64722222222222225</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -1776,43 +1782,43 @@
         <v>9</v>
       </c>
       <c r="B82" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C82" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="D82">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>9</v>
-      </c>
-      <c r="B83" t="s">
-        <v>33</v>
-      </c>
-      <c r="C83" s="1">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D83">
-        <v>370</v>
-      </c>
-      <c r="G83" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C83" s="1"/>
+      <c r="E83">
+        <v>1130</v>
+      </c>
+      <c r="F83" t="s">
+        <v>29</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C84" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D84">
-        <v>397</v>
+        <v>367</v>
       </c>
       <c r="G84" s="1"/>
     </row>
@@ -1821,13 +1827,13 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C85" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D85">
-        <v>441</v>
+        <v>370</v>
       </c>
       <c r="G85" s="1"/>
     </row>
@@ -1836,13 +1842,13 @@
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="C86" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D86">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="G86" s="1"/>
     </row>
@@ -1851,13 +1857,13 @@
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C87" s="1">
-        <v>0.6875</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D87">
-        <v>311</v>
+        <v>553</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1866,13 +1872,13 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C88" s="1">
-        <v>0.6875</v>
+        <v>0.68055555555555558</v>
       </c>
       <c r="D88">
-        <v>555</v>
+        <v>441</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -1881,13 +1887,13 @@
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="C89" s="1">
-        <v>0.6875</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D89">
-        <v>610</v>
+        <v>435</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -1896,13 +1902,13 @@
         <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C90" s="1">
-        <v>0.70138888888888884</v>
+        <v>0.6875</v>
       </c>
       <c r="D90">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="G90" s="1"/>
     </row>
@@ -1910,46 +1916,46 @@
       <c r="A91" t="s">
         <v>9</v>
       </c>
-      <c r="C91" s="1"/>
-      <c r="E91">
-        <v>326</v>
-      </c>
-      <c r="F91" t="s">
-        <v>10</v>
-      </c>
-      <c r="G91" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+      <c r="B91" t="s">
+        <v>21</v>
+      </c>
+      <c r="C91" s="1">
+        <v>0.6875</v>
+      </c>
+      <c r="D91">
+        <v>610</v>
+      </c>
+      <c r="G91" s="1"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>9</v>
-      </c>
-      <c r="C92" s="1"/>
-      <c r="E92">
-        <v>560</v>
-      </c>
-      <c r="F92" t="s">
-        <v>24</v>
-      </c>
-      <c r="G92" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B92" t="s">
+        <v>29</v>
+      </c>
+      <c r="C92" s="1">
+        <v>0.6958333333333333</v>
+      </c>
+      <c r="D92">
+        <v>4321</v>
+      </c>
+      <c r="G92" s="1"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>9</v>
       </c>
-      <c r="C93" s="1"/>
-      <c r="E93">
-        <v>313</v>
-      </c>
-      <c r="F93" t="s">
-        <v>21</v>
-      </c>
-      <c r="G93" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+      <c r="B93" t="s">
+        <v>22</v>
+      </c>
+      <c r="C93" s="1">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="D93">
+        <v>322</v>
+      </c>
+      <c r="G93" s="1"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
@@ -1957,13 +1963,13 @@
       </c>
       <c r="C94" s="1"/>
       <c r="E94">
-        <v>450</v>
+        <v>320</v>
       </c>
       <c r="F94" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G94" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.72222222222222221</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -1972,13 +1978,13 @@
       </c>
       <c r="C95" s="1"/>
       <c r="E95">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="F95" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G95" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -1987,13 +1993,13 @@
       </c>
       <c r="C96" s="1"/>
       <c r="E96">
-        <v>588</v>
+        <v>560</v>
       </c>
       <c r="F96" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G96" s="1">
-        <v>0.73611111111111116</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -2002,13 +2008,13 @@
       </c>
       <c r="C97" s="1"/>
       <c r="E97">
-        <v>448</v>
+        <v>313</v>
       </c>
       <c r="F97" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G97" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -2017,28 +2023,28 @@
       </c>
       <c r="C98" s="1"/>
       <c r="E98">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="F98" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G98" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>4308</v>
+        <v>530</v>
       </c>
       <c r="F99" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G99" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2047,13 +2053,13 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>528</v>
+        <v>448</v>
       </c>
       <c r="F100" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G100" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -2062,132 +2068,132 @@
       </c>
       <c r="C101" s="1"/>
       <c r="E101">
-        <v>660</v>
+        <v>534</v>
       </c>
       <c r="F101" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G101" s="1">
-        <v>0.77083333333333337</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>35</v>
-      </c>
-      <c r="B102" t="s">
-        <v>18</v>
-      </c>
-      <c r="C102" s="1">
-        <v>0.77430555555555558</v>
-      </c>
-      <c r="D102">
-        <v>222</v>
-      </c>
-      <c r="G102" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C102" s="1"/>
+      <c r="E102">
+        <v>4308</v>
+      </c>
+      <c r="F102" t="s">
+        <v>8</v>
+      </c>
+      <c r="G102" s="1">
+        <v>0.75763888888888886</v>
+      </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>26</v>
-      </c>
-      <c r="B103" t="s">
-        <v>25</v>
-      </c>
-      <c r="C103" s="1">
-        <v>0.77847222222222223</v>
-      </c>
-      <c r="D103">
-        <v>2657</v>
-      </c>
-      <c r="G103" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C103" s="1"/>
+      <c r="E103">
+        <v>528</v>
+      </c>
+      <c r="F103" t="s">
+        <v>8</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0.76041666666666663</v>
+      </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>7</v>
-      </c>
-      <c r="B104" t="s">
-        <v>27</v>
-      </c>
-      <c r="C104" s="1">
-        <v>0.79027777777777775</v>
-      </c>
-      <c r="D104">
-        <v>742</v>
-      </c>
-      <c r="G104" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C104" s="1"/>
+      <c r="E104">
+        <v>660</v>
+      </c>
+      <c r="F104" t="s">
+        <v>16</v>
+      </c>
+      <c r="G104" s="1">
+        <v>0.77083333333333337</v>
+      </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>12</v>
-      </c>
-      <c r="C105" s="1"/>
-      <c r="E105">
-        <v>4312</v>
-      </c>
-      <c r="F105" t="s">
-        <v>13</v>
-      </c>
-      <c r="G105" s="1">
-        <v>0.79027777777777775</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B105" t="s">
+        <v>18</v>
+      </c>
+      <c r="C105" s="1">
+        <v>0.77430555555555558</v>
+      </c>
+      <c r="D105">
+        <v>222</v>
+      </c>
+      <c r="G105" s="1"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>9</v>
       </c>
-      <c r="B106" t="s">
-        <v>17</v>
-      </c>
-      <c r="C106" s="1">
-        <v>0.79513888888888884</v>
-      </c>
-      <c r="D106">
-        <v>431</v>
-      </c>
-      <c r="G106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="E106">
+        <v>558</v>
+      </c>
+      <c r="F106" t="s">
+        <v>24</v>
+      </c>
+      <c r="G106" s="1">
+        <v>0.77777777777777779</v>
+      </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>9</v>
-      </c>
-      <c r="C107" s="1"/>
-      <c r="E107">
-        <v>670</v>
-      </c>
-      <c r="F107" t="s">
-        <v>16</v>
-      </c>
-      <c r="G107" s="1">
-        <v>0.80555555555555558</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B107" t="s">
+        <v>29</v>
+      </c>
+      <c r="C107" s="1">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="D107">
+        <v>742</v>
+      </c>
+      <c r="G107" s="1"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>9</v>
-      </c>
-      <c r="B108" t="s">
-        <v>27</v>
-      </c>
-      <c r="C108" s="1">
-        <v>0.81944444444444442</v>
-      </c>
-      <c r="D108">
-        <v>425</v>
-      </c>
-      <c r="G108" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C108" s="1"/>
+      <c r="E108">
+        <v>4312</v>
+      </c>
+      <c r="F108" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" s="1">
+        <v>0.79027777777777775</v>
+      </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>9</v>
       </c>
       <c r="B109" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C109" s="1">
-        <v>0.82291666666666663</v>
+        <v>0.79513888888888884</v>
       </c>
       <c r="D109">
-        <v>329</v>
+        <v>431</v>
       </c>
       <c r="G109" s="1"/>
     </row>
@@ -2195,59 +2201,59 @@
       <c r="A110" t="s">
         <v>9</v>
       </c>
-      <c r="B110" t="s">
-        <v>8</v>
-      </c>
-      <c r="C110" s="1">
-        <v>0.82638888888888884</v>
-      </c>
-      <c r="D110">
-        <v>523</v>
-      </c>
-      <c r="G110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="E110">
+        <v>670</v>
+      </c>
+      <c r="F110" t="s">
+        <v>16</v>
+      </c>
+      <c r="G110" s="1">
+        <v>0.80555555555555558</v>
+      </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C111" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.81944444444444442</v>
       </c>
       <c r="D111">
-        <v>583</v>
+        <v>425</v>
       </c>
       <c r="G111" s="1"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>35</v>
-      </c>
-      <c r="C112" s="1"/>
-      <c r="E112">
-        <v>222</v>
-      </c>
-      <c r="F112" t="s">
-        <v>40</v>
-      </c>
-      <c r="G112" s="1">
-        <v>0.83680555555555558</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B112" t="s">
+        <v>28</v>
+      </c>
+      <c r="C112" s="1">
+        <v>0.82430555555555551</v>
+      </c>
+      <c r="D112">
+        <v>2657</v>
+      </c>
+      <c r="G112" s="1"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C113" s="1">
-        <v>0.84375</v>
+        <v>0.82638888888888884</v>
       </c>
       <c r="D113">
-        <v>325</v>
+        <v>523</v>
       </c>
       <c r="G113" s="1"/>
     </row>
@@ -2256,29 +2262,29 @@
         <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C114" s="1">
-        <v>0.84375</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D114">
-        <v>445</v>
+        <v>583</v>
       </c>
       <c r="G114" s="1"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C115" s="1"/>
       <c r="E115">
-        <v>590</v>
+        <v>222</v>
       </c>
       <c r="F115" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="G115" s="1">
-        <v>0.85069444444444442</v>
+        <v>0.83680555555555558</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -2286,88 +2292,88 @@
         <v>9</v>
       </c>
       <c r="B116" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C116" s="1">
-        <v>0.85416666666666663</v>
+        <v>0.84375</v>
       </c>
       <c r="D116">
-        <v>449</v>
+        <v>325</v>
       </c>
       <c r="G116" s="1"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B117" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C117" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.85069444444444442</v>
       </c>
       <c r="D117">
-        <v>881</v>
+        <v>393</v>
       </c>
       <c r="G117" s="1"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>12</v>
-      </c>
-      <c r="B118" t="s">
-        <v>38</v>
-      </c>
-      <c r="C118" s="1">
-        <v>0.86111111111111116</v>
-      </c>
-      <c r="D118">
-        <v>4323</v>
-      </c>
-      <c r="G118" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C118" s="1"/>
+      <c r="E118">
+        <v>590</v>
+      </c>
+      <c r="F118" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B119" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C119" s="1">
-        <v>0.86736111111111114</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D119">
-        <v>1461</v>
+        <v>449</v>
       </c>
       <c r="G119" s="1"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B120" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C120" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D120">
-        <v>563</v>
+        <v>881</v>
       </c>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C121" s="1">
-        <v>0.875</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D121">
-        <v>535</v>
+        <v>1461</v>
       </c>
       <c r="G121" s="1"/>
     </row>
@@ -2376,13 +2382,13 @@
         <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C122" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D122">
-        <v>312</v>
+        <v>443</v>
       </c>
       <c r="G122" s="1"/>
     </row>
@@ -2391,13 +2397,13 @@
         <v>9</v>
       </c>
       <c r="B123" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C123" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D123">
-        <v>525</v>
+        <v>563</v>
       </c>
       <c r="G123" s="1"/>
     </row>
@@ -2406,28 +2412,28 @@
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C124" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.87152777777777779</v>
       </c>
       <c r="D124">
-        <v>589</v>
+        <v>409</v>
       </c>
       <c r="G124" s="1"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B125" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C125" s="1">
-        <v>0.89930555555555547</v>
+        <v>0.875</v>
       </c>
       <c r="D125">
-        <v>1425</v>
+        <v>527</v>
       </c>
       <c r="G125" s="1"/>
     </row>
@@ -2436,13 +2442,13 @@
         <v>9</v>
       </c>
       <c r="B126" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C126" s="1">
-        <v>0.91319444444444442</v>
+        <v>0.875</v>
       </c>
       <c r="D126">
-        <v>585</v>
+        <v>535</v>
       </c>
       <c r="G126" s="1"/>
     </row>
@@ -2450,31 +2456,31 @@
       <c r="A127" t="s">
         <v>9</v>
       </c>
-      <c r="C127" s="1"/>
-      <c r="E127">
-        <v>315</v>
-      </c>
-      <c r="F127" t="s">
-        <v>19</v>
-      </c>
-      <c r="G127" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B127" t="s">
+        <v>21</v>
+      </c>
+      <c r="C127" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D127">
+        <v>312</v>
+      </c>
+      <c r="G127" s="1"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>9</v>
       </c>
-      <c r="C128" s="1"/>
-      <c r="E128">
-        <v>365</v>
-      </c>
-      <c r="F128" t="s">
-        <v>23</v>
-      </c>
-      <c r="G128" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B128" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" s="1">
+        <v>0.91319444444444442</v>
+      </c>
+      <c r="D128">
+        <v>585</v>
+      </c>
+      <c r="G128" s="1"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
@@ -2482,10 +2488,10 @@
       </c>
       <c r="C129" s="1"/>
       <c r="E129">
-        <v>600</v>
+        <v>315</v>
       </c>
       <c r="F129" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G129" s="1">
         <v>0.92013888888888884</v>
@@ -2497,13 +2503,13 @@
       </c>
       <c r="C130" s="1"/>
       <c r="E130">
-        <v>429</v>
+        <v>365</v>
       </c>
       <c r="F130" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G130" s="1">
-        <v>0.92708333333333337</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -2512,13 +2518,13 @@
       </c>
       <c r="C131" s="1"/>
       <c r="E131">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F131" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G131" s="1">
-        <v>0.93055555555555558</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -2527,13 +2533,13 @@
       </c>
       <c r="C132" s="1"/>
       <c r="E132">
-        <v>627</v>
+        <v>308</v>
       </c>
       <c r="F132" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G132" s="1">
-        <v>0.93402777777777779</v>
+        <v>0.92361111111111116</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -2542,13 +2548,13 @@
       </c>
       <c r="C133" s="1"/>
       <c r="E133">
-        <v>568</v>
+        <v>429</v>
       </c>
       <c r="F133" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G133" s="1">
-        <v>0.94097222222222221</v>
+        <v>0.92708333333333337</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -2557,43 +2563,43 @@
       </c>
       <c r="C134" s="1"/>
       <c r="E134">
-        <v>452</v>
+        <v>578</v>
       </c>
       <c r="F134" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G134" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.93055555555555558</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C135" s="1"/>
       <c r="E135">
-        <v>339</v>
+        <v>627</v>
       </c>
       <c r="F135" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="G135" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.93402777777777779</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>4336</v>
+        <v>574</v>
       </c>
       <c r="F136" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G136" s="1">
-        <v>0.9506944444444444</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -2602,13 +2608,13 @@
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>317</v>
+        <v>568</v>
       </c>
       <c r="F137" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G137" s="1">
-        <v>0.95486111111111116</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -2617,13 +2623,13 @@
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="F138" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G138" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -2632,13 +2638,13 @@
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>457</v>
+        <v>317</v>
       </c>
       <c r="F139" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G139" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.95486111111111116</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -2647,29 +2653,44 @@
       </c>
       <c r="C140" s="1"/>
       <c r="E140">
-        <v>552</v>
+        <v>457</v>
       </c>
       <c r="F140" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G140" s="1">
-        <v>0.97222222222222221</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>31</v>
-      </c>
-      <c r="B141" t="s">
+        <v>9</v>
+      </c>
+      <c r="C141" s="1"/>
+      <c r="E141">
+        <v>556</v>
+      </c>
+      <c r="F141" t="s">
+        <v>18</v>
+      </c>
+      <c r="G141" s="1">
+        <v>0.97222222222222221</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>35</v>
+      </c>
+      <c r="B142" t="s">
         <v>22</v>
       </c>
-      <c r="C141" s="1">
+      <c r="C142" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D141">
+      <c r="D142">
         <v>878</v>
       </c>
-      <c r="G141" s="1"/>
+      <c r="G142" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CE2C9B0-8A3F-4641-B71A-DCF43A1EAE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1737197B-4A0D-4172-91CF-A310AFDB480A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{98711CBC-1F14-49A0-B491-A108215DF5BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B71B96C6-46E8-4F86-ABBB-38A5E567C0C1}"/>
   </bookViews>
   <sheets>
-    <sheet name="11-06" sheetId="1" r:id="rId1"/>
+    <sheet name="12-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="42">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,7 +83,7 @@
     <t>KIAD</t>
   </si>
   <si>
-    <t>KONT</t>
+    <t>MHLM</t>
   </si>
   <si>
     <t>SEQM</t>
@@ -116,55 +116,52 @@
     <t>KSFO</t>
   </si>
   <si>
+    <t>KMIA</t>
+  </si>
+  <si>
+    <t>FFT</t>
+  </si>
+  <si>
+    <t>KDFW</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
+    <t>KIAH</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>KATL</t>
+  </si>
+  <si>
+    <t>CMP</t>
+  </si>
+  <si>
+    <t>AMX</t>
+  </si>
+  <si>
+    <t>SKRG</t>
+  </si>
+  <si>
+    <t>KMCO</t>
+  </si>
+  <si>
+    <t>IBE</t>
+  </si>
+  <si>
+    <t>CYUL</t>
+  </si>
+  <si>
+    <t>KBOS</t>
+  </si>
+  <si>
+    <t>KOAK</t>
+  </si>
+  <si>
     <t>KEWR</t>
-  </si>
-  <si>
-    <t>MHLM</t>
-  </si>
-  <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>KMIA</t>
-  </si>
-  <si>
-    <t>KIAH</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>KATL</t>
-  </si>
-  <si>
-    <t>TAG</t>
-  </si>
-  <si>
-    <t>MHRO</t>
-  </si>
-  <si>
-    <t>KDFW</t>
-  </si>
-  <si>
-    <t>CMP</t>
-  </si>
-  <si>
-    <t>AMX</t>
-  </si>
-  <si>
-    <t>SKRG</t>
-  </si>
-  <si>
-    <t>MMUN</t>
-  </si>
-  <si>
-    <t>IBE</t>
-  </si>
-  <si>
-    <t>KORD</t>
-  </si>
-  <si>
-    <t>KLAS</t>
   </si>
   <si>
     <t>LEMD</t>
@@ -542,8 +539,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{424AD4F2-BAB2-4904-A23D-19880E5291BA}">
-  <dimension ref="A1:G142"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F161E40-1CB6-4204-85BC-36B1FA08A1F7}">
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -624,7 +621,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
@@ -693,7 +690,7 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D9">
-        <v>531</v>
+        <v>575</v>
       </c>
       <c r="G9" s="1"/>
     </row>
@@ -744,14 +741,14 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" s="1"/>
       <c r="E13">
         <v>3154</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G13" s="1">
         <v>0.25</v>
@@ -774,14 +771,14 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15">
         <v>3154</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G15" s="1">
         <v>0.25069444444444444</v>
@@ -969,17 +966,17 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C28" s="1"/>
       <c r="E28">
-        <v>319</v>
+        <v>4326</v>
       </c>
       <c r="F28" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G28" s="1">
-        <v>0.3125</v>
+        <v>0.29791666666666666</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -988,10 +985,10 @@
       </c>
       <c r="C29" s="1"/>
       <c r="E29">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G29" s="1">
         <v>0.3125</v>
@@ -1003,10 +1000,10 @@
       </c>
       <c r="C30" s="1"/>
       <c r="E30">
-        <v>396</v>
+        <v>323</v>
       </c>
       <c r="F30" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G30" s="1">
         <v>0.3125</v>
@@ -1014,14 +1011,14 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>884</v>
+        <v>328</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="G31" s="1">
         <v>0.3125</v>
@@ -1033,13 +1030,13 @@
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>310</v>
+        <v>396</v>
       </c>
       <c r="F32" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G32" s="1">
-        <v>0.31597222222222221</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1048,10 +1045,10 @@
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>440</v>
+        <v>310</v>
       </c>
       <c r="F33" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G33" s="1">
         <v>0.31597222222222221</v>
@@ -1063,10 +1060,10 @@
       </c>
       <c r="C34" s="1"/>
       <c r="E34">
-        <v>536</v>
+        <v>440</v>
       </c>
       <c r="F34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G34" s="1">
         <v>0.31597222222222221</v>
@@ -1076,16 +1073,16 @@
       <c r="A35" t="s">
         <v>9</v>
       </c>
-      <c r="B35" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="1">
-        <v>0.31944444444444442</v>
-      </c>
-      <c r="D35">
-        <v>321</v>
-      </c>
-      <c r="G35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="E35">
+        <v>536</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.31597222222222221</v>
+      </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
@@ -1093,10 +1090,10 @@
       </c>
       <c r="C36" s="1"/>
       <c r="E36">
-        <v>562</v>
+        <v>444</v>
       </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="G36" s="1">
         <v>0.32291666666666669</v>
@@ -1108,44 +1105,44 @@
       </c>
       <c r="C37" s="1"/>
       <c r="E37">
-        <v>368</v>
+        <v>562</v>
       </c>
       <c r="F37" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G37" s="1">
-        <v>0.33333333333333331</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C38" s="1"/>
       <c r="E38">
-        <v>522</v>
+        <v>4322</v>
       </c>
       <c r="F38" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="G38" s="1">
-        <v>0.33333333333333331</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>9</v>
       </c>
-      <c r="B39" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D39">
-        <v>601</v>
-      </c>
-      <c r="G39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="E39">
+        <v>368</v>
+      </c>
+      <c r="F39" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.33333333333333331</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
@@ -1153,44 +1150,44 @@
       </c>
       <c r="C40" s="1"/>
       <c r="E40">
-        <v>383</v>
+        <v>522</v>
       </c>
       <c r="F40" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G40" s="1">
-        <v>0.33680555555555558</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="1"/>
-      <c r="E41">
-        <v>454</v>
-      </c>
-      <c r="F41" t="s">
-        <v>11</v>
-      </c>
-      <c r="G41" s="1">
-        <v>0.34027777777777779</v>
-      </c>
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="1">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="D41">
+        <v>309</v>
+      </c>
+      <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="1"/>
-      <c r="E42">
-        <v>324</v>
-      </c>
-      <c r="F42" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0.34375</v>
-      </c>
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="D42">
+        <v>581</v>
+      </c>
+      <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -1198,13 +1195,13 @@
       </c>
       <c r="C43" s="1"/>
       <c r="E43">
-        <v>572</v>
+        <v>383</v>
       </c>
       <c r="F43" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G43" s="1">
-        <v>0.34375</v>
+        <v>0.33680555555555558</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1213,29 +1210,29 @@
       </c>
       <c r="C44" s="1"/>
       <c r="E44">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="F44" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G44" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.34027777777777779</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>9</v>
       </c>
-      <c r="B45" t="s">
-        <v>19</v>
-      </c>
-      <c r="C45" s="1">
-        <v>0.37152777777777779</v>
-      </c>
-      <c r="D45">
-        <v>451</v>
-      </c>
-      <c r="G45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="E45">
+        <v>324</v>
+      </c>
+      <c r="F45" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0.34375</v>
+      </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
@@ -1243,28 +1240,28 @@
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>526</v>
+        <v>554</v>
       </c>
       <c r="F46" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="G46" s="1">
-        <v>0.375</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C47" s="1"/>
       <c r="E47">
-        <v>4320</v>
+        <v>884</v>
       </c>
       <c r="F47" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G47" s="1">
-        <v>0.38333333333333336</v>
+        <v>0.35347222222222219</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -1273,13 +1270,13 @@
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>369</v>
+        <v>422</v>
       </c>
       <c r="F48" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G48" s="1">
-        <v>0.3888888888888889</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1288,27 +1285,27 @@
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>582</v>
+        <v>430</v>
       </c>
       <c r="F49" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G49" s="1">
-        <v>0.39930555555555558</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C50" s="1">
-        <v>0.40902777777777777</v>
+        <v>0.37847222222222221</v>
       </c>
       <c r="D50">
-        <v>4337</v>
+        <v>559</v>
       </c>
       <c r="G50" s="1"/>
     </row>
@@ -1316,16 +1313,16 @@
       <c r="A51" t="s">
         <v>9</v>
       </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" s="1">
-        <v>0.41319444444444442</v>
-      </c>
-      <c r="D51">
-        <v>569</v>
-      </c>
-      <c r="G51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="E51">
+        <v>524</v>
+      </c>
+      <c r="F51" t="s">
+        <v>8</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.38194444444444442</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
@@ -1333,13 +1330,13 @@
       </c>
       <c r="C52" s="1"/>
       <c r="E52">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="F52" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G52" s="1">
-        <v>0.41319444444444442</v>
+        <v>0.3888888888888889</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -1348,42 +1345,42 @@
       </c>
       <c r="C53" s="1"/>
       <c r="E53">
-        <v>408</v>
+        <v>582</v>
       </c>
       <c r="F53" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="G53" s="1">
-        <v>0.41319444444444442</v>
+        <v>0.39930555555555558</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="1"/>
-      <c r="E54">
-        <v>609</v>
-      </c>
-      <c r="F54" t="s">
-        <v>21</v>
-      </c>
-      <c r="G54" s="1">
-        <v>0.4236111111111111</v>
-      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="1">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="D54">
+        <v>569</v>
+      </c>
+      <c r="G54" s="1"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C55" s="1">
-        <v>0.42708333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D55">
-        <v>537</v>
+        <v>342</v>
       </c>
       <c r="G55" s="1"/>
     </row>
@@ -1391,29 +1388,29 @@
       <c r="A56" t="s">
         <v>9</v>
       </c>
-      <c r="B56" t="s">
-        <v>11</v>
-      </c>
-      <c r="C56" s="1">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="D56">
-        <v>455</v>
-      </c>
-      <c r="G56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="E56">
+        <v>609</v>
+      </c>
+      <c r="F56" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0.4236111111111111</v>
+      </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C57" s="1">
-        <v>0.4513888888888889</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="D57">
-        <v>573</v>
+        <v>537</v>
       </c>
       <c r="G57" s="1"/>
     </row>
@@ -1422,13 +1419,13 @@
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C58" s="1">
-        <v>0.4548611111111111</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="D58">
-        <v>318</v>
+        <v>455</v>
       </c>
       <c r="G58" s="1"/>
     </row>
@@ -1437,75 +1434,75 @@
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C59" s="1">
-        <v>0.46180555555555558</v>
+        <v>0.4548611111111111</v>
       </c>
       <c r="D59">
-        <v>384</v>
+        <v>318</v>
       </c>
       <c r="G59" s="1"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C60" s="1">
-        <v>0.47291666666666665</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D60">
-        <v>495</v>
+        <v>384</v>
       </c>
       <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>7</v>
-      </c>
-      <c r="B61" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="1">
-        <v>0.47847222222222219</v>
-      </c>
-      <c r="D61">
-        <v>1194</v>
-      </c>
-      <c r="G61" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="C61" s="1"/>
+      <c r="E61">
+        <v>343</v>
+      </c>
+      <c r="F61" t="s">
+        <v>27</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0.46180555555555558</v>
+      </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>9</v>
-      </c>
-      <c r="C62" s="1"/>
-      <c r="E62">
-        <v>584</v>
-      </c>
-      <c r="F62" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" s="1">
-        <v>0.49305555555555558</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B62" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="1">
+        <v>0.47291666666666665</v>
+      </c>
+      <c r="D62">
+        <v>495</v>
+      </c>
+      <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>9</v>
-      </c>
-      <c r="C63" s="1"/>
-      <c r="E63">
-        <v>434</v>
-      </c>
-      <c r="F63" t="s">
-        <v>38</v>
-      </c>
-      <c r="G63" s="1">
-        <v>0.49652777777777779</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B63" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="1">
+        <v>0.47847222222222219</v>
+      </c>
+      <c r="D63">
+        <v>1194</v>
+      </c>
+      <c r="G63" s="1"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
@@ -1513,13 +1510,13 @@
       </c>
       <c r="C64" s="1"/>
       <c r="E64">
-        <v>385</v>
+        <v>584</v>
       </c>
       <c r="F64" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G64" s="1">
-        <v>0.50347222222222221</v>
+        <v>0.49305555555555558</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -1528,10 +1525,10 @@
       </c>
       <c r="C65" s="1"/>
       <c r="E65">
-        <v>424</v>
+        <v>385</v>
       </c>
       <c r="F65" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G65" s="1">
         <v>0.50347222222222221</v>
@@ -1543,10 +1540,10 @@
       </c>
       <c r="C66" s="1"/>
       <c r="E66">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="F66" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G66" s="1">
         <v>0.50347222222222221</v>
@@ -1569,14 +1566,14 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C68" s="1"/>
       <c r="E68">
         <v>1508</v>
       </c>
       <c r="F68" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G68" s="1">
         <v>0.51597222222222228</v>
@@ -1599,62 +1596,62 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B70" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C70" s="1">
-        <v>0.52083333333333337</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="D70">
-        <v>420</v>
+        <v>937</v>
       </c>
       <c r="G70" s="1"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C71" s="1">
         <v>0.52916666666666667</v>
       </c>
       <c r="D71">
-        <v>937</v>
+        <v>816</v>
       </c>
       <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>35</v>
-      </c>
-      <c r="B72" t="s">
-        <v>22</v>
-      </c>
-      <c r="C72" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D72">
-        <v>816</v>
-      </c>
-      <c r="G72" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C72" s="1"/>
+      <c r="E72">
+        <v>1458</v>
+      </c>
+      <c r="F72" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0.55555555555555558</v>
+      </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C73" s="1"/>
       <c r="E73">
-        <v>421</v>
+        <v>380</v>
       </c>
       <c r="F73" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G73" s="1">
-        <v>0.55208333333333337</v>
+        <v>0.57222222222222219</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -1663,162 +1660,162 @@
       </c>
       <c r="C74" s="1"/>
       <c r="E74">
-        <v>1458</v>
+        <v>1468</v>
       </c>
       <c r="F74" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G74" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.57638888888888895</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C75" s="1"/>
       <c r="E75">
-        <v>380</v>
+        <v>1978</v>
       </c>
       <c r="F75" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G75" s="1">
-        <v>0.57222222222222219</v>
+        <v>0.57708333333333328</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C76" s="1"/>
       <c r="E76">
-        <v>1468</v>
+        <v>871</v>
       </c>
       <c r="F76" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G76" s="1">
-        <v>0.57638888888888895</v>
+        <v>0.58194444444444449</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>30</v>
-      </c>
-      <c r="C77" s="1"/>
-      <c r="E77">
-        <v>1978</v>
-      </c>
-      <c r="F77" t="s">
-        <v>31</v>
-      </c>
-      <c r="G77" s="1">
-        <v>0.57708333333333328</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B77" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" s="1">
+        <v>0.59375</v>
+      </c>
+      <c r="D77">
+        <v>628</v>
+      </c>
+      <c r="G77" s="1"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>35</v>
-      </c>
-      <c r="C78" s="1"/>
-      <c r="E78">
-        <v>871</v>
-      </c>
-      <c r="F78" t="s">
-        <v>22</v>
-      </c>
-      <c r="G78" s="1">
-        <v>0.58194444444444449</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B78" t="s">
+        <v>29</v>
+      </c>
+      <c r="C78" s="1">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D78">
+        <v>1290</v>
+      </c>
+      <c r="G78" s="1"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C79" s="1">
-        <v>0.59375</v>
+        <v>0.625</v>
       </c>
       <c r="D79">
-        <v>628</v>
+        <v>557</v>
       </c>
       <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>7</v>
-      </c>
-      <c r="B80" t="s">
-        <v>29</v>
-      </c>
-      <c r="C80" s="1">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D80">
-        <v>1290</v>
-      </c>
-      <c r="G80" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="E80">
+        <v>629</v>
+      </c>
+      <c r="F80" t="s">
+        <v>17</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0.64722222222222225</v>
+      </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>36</v>
-      </c>
-      <c r="C81" s="1"/>
-      <c r="E81">
-        <v>629</v>
-      </c>
-      <c r="F81" t="s">
-        <v>17</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0.64722222222222225</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B81" t="s">
+        <v>23</v>
+      </c>
+      <c r="C81" s="1">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D81">
+        <v>382</v>
+      </c>
+      <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>9</v>
-      </c>
-      <c r="B82" t="s">
-        <v>23</v>
-      </c>
-      <c r="C82" s="1">
+        <v>7</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="E82">
+        <v>1130</v>
+      </c>
+      <c r="F82" t="s">
+        <v>29</v>
+      </c>
+      <c r="G82" s="1">
         <v>0.65277777777777779</v>
       </c>
-      <c r="D82">
-        <v>382</v>
-      </c>
-      <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="1"/>
-      <c r="E83">
-        <v>1130</v>
-      </c>
-      <c r="F83" t="s">
+        <v>9</v>
+      </c>
+      <c r="B83" t="s">
         <v>29</v>
       </c>
-      <c r="G83" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+      <c r="C83" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D83">
+        <v>367</v>
+      </c>
+      <c r="G83" s="1"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C84" s="1">
         <v>0.66666666666666663</v>
       </c>
       <c r="D84">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G84" s="1"/>
     </row>
@@ -1827,13 +1824,13 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C85" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D85">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="G85" s="1"/>
     </row>
@@ -1842,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C86" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.68055555555555558</v>
       </c>
       <c r="D86">
-        <v>397</v>
+        <v>441</v>
       </c>
       <c r="G86" s="1"/>
     </row>
@@ -1857,13 +1854,13 @@
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C87" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D87">
-        <v>553</v>
+        <v>423</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1872,13 +1869,13 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C88" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.6875</v>
       </c>
       <c r="D88">
-        <v>441</v>
+        <v>311</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -1887,13 +1884,13 @@
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C89" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.6875</v>
       </c>
       <c r="D89">
-        <v>435</v>
+        <v>555</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -1902,13 +1899,13 @@
         <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C90" s="1">
         <v>0.6875</v>
       </c>
       <c r="D90">
-        <v>311</v>
+        <v>610</v>
       </c>
       <c r="G90" s="1"/>
     </row>
@@ -1917,13 +1914,13 @@
         <v>9</v>
       </c>
       <c r="B91" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C91" s="1">
-        <v>0.6875</v>
+        <v>0.70138888888888884</v>
       </c>
       <c r="D91">
-        <v>610</v>
+        <v>322</v>
       </c>
       <c r="G91" s="1"/>
     </row>
@@ -1935,10 +1932,10 @@
         <v>29</v>
       </c>
       <c r="C92" s="1">
-        <v>0.6958333333333333</v>
+        <v>0.72777777777777775</v>
       </c>
       <c r="D92">
-        <v>4321</v>
+        <v>4327</v>
       </c>
       <c r="G92" s="1"/>
     </row>
@@ -1946,16 +1943,16 @@
       <c r="A93" t="s">
         <v>9</v>
       </c>
-      <c r="B93" t="s">
-        <v>22</v>
-      </c>
-      <c r="C93" s="1">
-        <v>0.70138888888888884</v>
-      </c>
-      <c r="D93">
-        <v>322</v>
-      </c>
-      <c r="G93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="E93">
+        <v>326</v>
+      </c>
+      <c r="F93" t="s">
+        <v>10</v>
+      </c>
+      <c r="G93" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
@@ -1963,13 +1960,13 @@
       </c>
       <c r="C94" s="1"/>
       <c r="E94">
-        <v>320</v>
+        <v>560</v>
       </c>
       <c r="F94" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G94" s="1">
-        <v>0.72222222222222221</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -1978,13 +1975,13 @@
       </c>
       <c r="C95" s="1"/>
       <c r="E95">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="F95" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G95" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -1993,13 +1990,13 @@
       </c>
       <c r="C96" s="1"/>
       <c r="E96">
-        <v>560</v>
+        <v>450</v>
       </c>
       <c r="F96" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G96" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -2008,10 +2005,10 @@
       </c>
       <c r="C97" s="1"/>
       <c r="E97">
-        <v>313</v>
+        <v>520</v>
       </c>
       <c r="F97" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G97" s="1">
         <v>0.73263888888888884</v>
@@ -2023,13 +2020,13 @@
       </c>
       <c r="C98" s="1"/>
       <c r="E98">
-        <v>520</v>
+        <v>588</v>
       </c>
       <c r="F98" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G98" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.73611111111111116</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -2038,13 +2035,13 @@
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>530</v>
+        <v>448</v>
       </c>
       <c r="F99" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G99" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2053,10 +2050,10 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>448</v>
+        <v>534</v>
       </c>
       <c r="F100" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G100" s="1">
         <v>0.74305555555555558</v>
@@ -2064,48 +2061,48 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C101" s="1"/>
       <c r="E101">
-        <v>534</v>
+        <v>4308</v>
       </c>
       <c r="F101" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G101" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C102" s="1"/>
       <c r="E102">
-        <v>4308</v>
+        <v>528</v>
       </c>
       <c r="F102" t="s">
         <v>8</v>
       </c>
       <c r="G102" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.76041666666666663</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>9</v>
-      </c>
-      <c r="C103" s="1"/>
-      <c r="E103">
-        <v>528</v>
-      </c>
-      <c r="F103" t="s">
-        <v>8</v>
-      </c>
-      <c r="G103" s="1">
-        <v>0.76041666666666663</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B103" t="s">
+        <v>18</v>
+      </c>
+      <c r="C103" s="1">
+        <v>0.76736111111111116</v>
+      </c>
+      <c r="D103">
+        <v>222</v>
+      </c>
+      <c r="G103" s="1"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
@@ -2124,62 +2121,62 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C105" s="1">
-        <v>0.77430555555555558</v>
+        <v>0.79027777777777775</v>
       </c>
       <c r="D105">
-        <v>222</v>
+        <v>742</v>
       </c>
       <c r="G105" s="1"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C106" s="1"/>
       <c r="E106">
-        <v>558</v>
+        <v>4312</v>
       </c>
       <c r="F106" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G106" s="1">
-        <v>0.77777777777777779</v>
+        <v>0.79027777777777775</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B107" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C107" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.79513888888888884</v>
       </c>
       <c r="D107">
-        <v>742</v>
+        <v>431</v>
       </c>
       <c r="G107" s="1"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C108" s="1"/>
       <c r="E108">
-        <v>4312</v>
+        <v>670</v>
       </c>
       <c r="F108" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G108" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.80555555555555558</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -2187,13 +2184,13 @@
         <v>9</v>
       </c>
       <c r="B109" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C109" s="1">
-        <v>0.79513888888888884</v>
+        <v>0.81944444444444442</v>
       </c>
       <c r="D109">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="G109" s="1"/>
     </row>
@@ -2201,61 +2198,61 @@
       <c r="A110" t="s">
         <v>9</v>
       </c>
-      <c r="C110" s="1"/>
-      <c r="E110">
-        <v>670</v>
-      </c>
-      <c r="F110" t="s">
-        <v>16</v>
-      </c>
-      <c r="G110" s="1">
-        <v>0.80555555555555558</v>
-      </c>
+      <c r="B110" t="s">
+        <v>37</v>
+      </c>
+      <c r="C110" s="1">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D110">
+        <v>329</v>
+      </c>
+      <c r="G110" s="1"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B111" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C111" s="1">
-        <v>0.81944444444444442</v>
+        <v>0.82430555555555551</v>
       </c>
       <c r="D111">
-        <v>425</v>
+        <v>2657</v>
       </c>
       <c r="G111" s="1"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B112" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C112" s="1">
-        <v>0.82430555555555551</v>
+        <v>0.82638888888888884</v>
       </c>
       <c r="D112">
-        <v>2657</v>
+        <v>523</v>
       </c>
       <c r="G112" s="1"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>9</v>
-      </c>
-      <c r="B113" t="s">
-        <v>8</v>
-      </c>
-      <c r="C113" s="1">
-        <v>0.82638888888888884</v>
-      </c>
-      <c r="D113">
-        <v>523</v>
-      </c>
-      <c r="G113" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="C113" s="1"/>
+      <c r="E113">
+        <v>222</v>
+      </c>
+      <c r="F113" t="s">
+        <v>41</v>
+      </c>
+      <c r="G113" s="1">
+        <v>0.82986111111111116</v>
+      </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
@@ -2274,31 +2271,31 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>39</v>
-      </c>
-      <c r="C115" s="1"/>
-      <c r="E115">
-        <v>222</v>
-      </c>
-      <c r="F115" t="s">
-        <v>42</v>
-      </c>
-      <c r="G115" s="1">
-        <v>0.83680555555555558</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B115" t="s">
+        <v>10</v>
+      </c>
+      <c r="C115" s="1">
+        <v>0.84375</v>
+      </c>
+      <c r="D115">
+        <v>325</v>
+      </c>
+      <c r="G115" s="1"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>9</v>
       </c>
       <c r="B116" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="C116" s="1">
         <v>0.84375</v>
       </c>
       <c r="D116">
-        <v>325</v>
+        <v>445</v>
       </c>
       <c r="G116" s="1"/>
     </row>
@@ -2306,59 +2303,59 @@
       <c r="A117" t="s">
         <v>9</v>
       </c>
-      <c r="B117" t="s">
-        <v>19</v>
-      </c>
-      <c r="C117" s="1">
+      <c r="C117" s="1"/>
+      <c r="E117">
+        <v>590</v>
+      </c>
+      <c r="F117" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117" s="1">
         <v>0.85069444444444442</v>
       </c>
-      <c r="D117">
-        <v>393</v>
-      </c>
-      <c r="G117" s="1"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>9</v>
       </c>
-      <c r="C118" s="1"/>
-      <c r="E118">
-        <v>590</v>
-      </c>
-      <c r="F118" t="s">
-        <v>13</v>
-      </c>
-      <c r="G118" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+      <c r="B118" t="s">
+        <v>11</v>
+      </c>
+      <c r="C118" s="1">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D118">
+        <v>449</v>
+      </c>
+      <c r="G118" s="1"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B119" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C119" s="1">
-        <v>0.85416666666666663</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D119">
-        <v>449</v>
+        <v>881</v>
       </c>
       <c r="G119" s="1"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C120" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.86111111111111116</v>
       </c>
       <c r="D120">
-        <v>881</v>
+        <v>4323</v>
       </c>
       <c r="G120" s="1"/>
     </row>
@@ -2382,13 +2379,13 @@
         <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C122" s="1">
         <v>0.86805555555555558</v>
       </c>
       <c r="D122">
-        <v>443</v>
+        <v>563</v>
       </c>
       <c r="G122" s="1"/>
     </row>
@@ -2397,13 +2394,13 @@
         <v>9</v>
       </c>
       <c r="B123" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C123" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.875</v>
       </c>
       <c r="D123">
-        <v>563</v>
+        <v>535</v>
       </c>
       <c r="G123" s="1"/>
     </row>
@@ -2412,13 +2409,13 @@
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C124" s="1">
-        <v>0.87152777777777779</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D124">
-        <v>409</v>
+        <v>312</v>
       </c>
       <c r="G124" s="1"/>
     </row>
@@ -2427,13 +2424,13 @@
         <v>9</v>
       </c>
       <c r="B125" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="C125" s="1">
-        <v>0.875</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D125">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G125" s="1"/>
     </row>
@@ -2442,28 +2439,28 @@
         <v>9</v>
       </c>
       <c r="B126" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C126" s="1">
-        <v>0.875</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D126">
-        <v>535</v>
+        <v>589</v>
       </c>
       <c r="G126" s="1"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C127" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.89930555555555547</v>
       </c>
       <c r="D127">
-        <v>312</v>
+        <v>1425</v>
       </c>
       <c r="G127" s="1"/>
     </row>
@@ -2518,7 +2515,7 @@
       </c>
       <c r="C131" s="1"/>
       <c r="E131">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="F131" t="s">
         <v>13</v>
@@ -2533,13 +2530,13 @@
       </c>
       <c r="C132" s="1"/>
       <c r="E132">
-        <v>308</v>
+        <v>429</v>
       </c>
       <c r="F132" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G132" s="1">
-        <v>0.92361111111111116</v>
+        <v>0.92708333333333337</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -2548,13 +2545,13 @@
       </c>
       <c r="C133" s="1"/>
       <c r="E133">
-        <v>429</v>
+        <v>578</v>
       </c>
       <c r="F133" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G133" s="1">
-        <v>0.92708333333333337</v>
+        <v>0.93055555555555558</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -2563,13 +2560,13 @@
       </c>
       <c r="C134" s="1"/>
       <c r="E134">
-        <v>578</v>
+        <v>627</v>
       </c>
       <c r="F134" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G134" s="1">
-        <v>0.93055555555555558</v>
+        <v>0.93402777777777779</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -2578,13 +2575,13 @@
       </c>
       <c r="C135" s="1"/>
       <c r="E135">
-        <v>627</v>
+        <v>574</v>
       </c>
       <c r="F135" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G135" s="1">
-        <v>0.93402777777777779</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -2593,13 +2590,13 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="F136" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G136" s="1">
-        <v>0.9375</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -2608,25 +2605,25 @@
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>568</v>
+        <v>452</v>
       </c>
       <c r="F137" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G137" s="1">
-        <v>0.94097222222222221</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>452</v>
+        <v>339</v>
       </c>
       <c r="F138" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="G138" s="1">
         <v>0.94791666666666663</v>
@@ -2634,17 +2631,17 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>317</v>
+        <v>4336</v>
       </c>
       <c r="F139" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G139" s="1">
-        <v>0.95486111111111116</v>
+        <v>0.9506944444444444</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -2653,13 +2650,13 @@
       </c>
       <c r="C140" s="1"/>
       <c r="E140">
-        <v>457</v>
+        <v>317</v>
       </c>
       <c r="F140" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G140" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.95486111111111116</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -2668,29 +2665,59 @@
       </c>
       <c r="C141" s="1"/>
       <c r="E141">
-        <v>556</v>
+        <v>432</v>
       </c>
       <c r="F141" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G141" s="1">
-        <v>0.97222222222222221</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>35</v>
-      </c>
-      <c r="B142" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="1"/>
+      <c r="E142">
+        <v>457</v>
+      </c>
+      <c r="F142" t="s">
+        <v>15</v>
+      </c>
+      <c r="G142" s="1">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143" s="1"/>
+      <c r="E143">
+        <v>552</v>
+      </c>
+      <c r="F143" t="s">
+        <v>18</v>
+      </c>
+      <c r="G143" s="1">
+        <v>0.97222222222222221</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>32</v>
+      </c>
+      <c r="B144" t="s">
         <v>22</v>
       </c>
-      <c r="C142" s="1">
+      <c r="C144" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D142">
+      <c r="D144">
         <v>878</v>
       </c>
-      <c r="G142" s="1"/>
+      <c r="G144" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1737197B-4A0D-4172-91CF-A310AFDB480A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FAEECE2-F178-4721-9CF8-1B287F36A5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B71B96C6-46E8-4F86-ABBB-38A5E567C0C1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3126E712-A340-4158-8690-A24CF878AA78}"/>
   </bookViews>
   <sheets>
-    <sheet name="12-06" sheetId="1" r:id="rId1"/>
+    <sheet name="13-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="41">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,6 +83,9 @@
     <t>KIAD</t>
   </si>
   <si>
+    <t>KONT</t>
+  </si>
+  <si>
     <t>MHLM</t>
   </si>
   <si>
@@ -116,27 +119,27 @@
     <t>KSFO</t>
   </si>
   <si>
+    <t>KEWR</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
     <t>KMIA</t>
   </si>
   <si>
-    <t>FFT</t>
+    <t>KIAH</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>KATL</t>
   </si>
   <si>
     <t>KDFW</t>
   </si>
   <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>KIAH</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>KATL</t>
-  </si>
-  <si>
     <t>CMP</t>
   </si>
   <si>
@@ -146,22 +149,16 @@
     <t>SKRG</t>
   </si>
   <si>
-    <t>KMCO</t>
+    <t>MMUN</t>
   </si>
   <si>
     <t>IBE</t>
   </si>
   <si>
-    <t>CYUL</t>
-  </si>
-  <si>
-    <t>KBOS</t>
-  </si>
-  <si>
-    <t>KOAK</t>
-  </si>
-  <si>
-    <t>KEWR</t>
+    <t>KORD</t>
+  </si>
+  <si>
+    <t>KLAS</t>
   </si>
   <si>
     <t>LEMD</t>
@@ -539,8 +536,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F161E40-1CB6-4204-85BC-36B1FA08A1F7}">
-  <dimension ref="A1:G144"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFE2BF70-6640-4725-89D9-3E51C7BADE5E}">
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -621,14 +618,14 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
         <v>879</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1">
         <v>0.20347222222222219</v>
@@ -690,37 +687,37 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D9">
-        <v>575</v>
+        <v>531</v>
       </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1">
-        <v>0.24444444444444444</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="D10">
-        <v>4309</v>
+        <v>575</v>
       </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C11" s="1">
-        <v>0.24652777777777779</v>
+        <v>0.24444444444444444</v>
       </c>
       <c r="D11">
-        <v>456</v>
+        <v>4309</v>
       </c>
       <c r="G11" s="1"/>
     </row>
@@ -735,35 +732,35 @@
         <v>0.24652777777777779</v>
       </c>
       <c r="D12">
-        <v>661</v>
+        <v>456</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="E13">
-        <v>3154</v>
-      </c>
-      <c r="F13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0.25</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.24652777777777779</v>
+      </c>
+      <c r="D13">
+        <v>661</v>
+      </c>
+      <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C14" s="1"/>
       <c r="E14">
-        <v>1467</v>
+        <v>3154</v>
       </c>
       <c r="F14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G14" s="1">
         <v>0.25</v>
@@ -771,33 +768,33 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15">
-        <v>3154</v>
+        <v>1467</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G15" s="1">
-        <v>0.25069444444444444</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="1">
-        <v>0.25694444444444442</v>
-      </c>
-      <c r="D16">
-        <v>433</v>
-      </c>
-      <c r="G16" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="E16">
+        <v>3154</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0.25069444444444444</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -810,7 +807,7 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="D17">
-        <v>579</v>
+        <v>433</v>
       </c>
       <c r="G17" s="1"/>
     </row>
@@ -819,13 +816,13 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C18" s="1">
-        <v>0.26041666666666669</v>
+        <v>0.25694444444444442</v>
       </c>
       <c r="D18">
-        <v>529</v>
+        <v>579</v>
       </c>
       <c r="G18" s="1"/>
     </row>
@@ -834,13 +831,13 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1">
-        <v>0.2638888888888889</v>
+        <v>0.26041666666666669</v>
       </c>
       <c r="D19">
-        <v>314</v>
+        <v>529</v>
       </c>
       <c r="G19" s="1"/>
     </row>
@@ -852,10 +849,10 @@
         <v>20</v>
       </c>
       <c r="C20" s="1">
-        <v>0.2673611111111111</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="D20">
-        <v>428</v>
+        <v>314</v>
       </c>
       <c r="G20" s="1"/>
     </row>
@@ -870,7 +867,7 @@
         <v>0.2673611111111111</v>
       </c>
       <c r="D21">
-        <v>626</v>
+        <v>428</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -882,10 +879,10 @@
         <v>22</v>
       </c>
       <c r="C22" s="1">
-        <v>0.27083333333333331</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D22">
-        <v>316</v>
+        <v>626</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -900,7 +897,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D23">
-        <v>366</v>
+        <v>316</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -915,7 +912,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D24">
-        <v>561</v>
+        <v>366</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -924,13 +921,13 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C25" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D25">
-        <v>591</v>
+        <v>561</v>
       </c>
       <c r="G25" s="1"/>
     </row>
@@ -939,13 +936,13 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D26">
-        <v>671</v>
+        <v>591</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -954,44 +951,44 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C27" s="1">
-        <v>0.29166666666666669</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="D27">
-        <v>521</v>
+        <v>671</v>
       </c>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="1"/>
-      <c r="E28">
-        <v>4326</v>
-      </c>
-      <c r="F28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0.29791666666666666</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="D28">
+        <v>521</v>
+      </c>
+      <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C29" s="1"/>
       <c r="E29">
-        <v>319</v>
+        <v>4326</v>
       </c>
       <c r="F29" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G29" s="1">
-        <v>0.3125</v>
+        <v>0.29791666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1000,7 +997,7 @@
       </c>
       <c r="C30" s="1"/>
       <c r="E30">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F30" t="s">
         <v>22</v>
@@ -1015,10 +1012,10 @@
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G31" s="1">
         <v>0.3125</v>
@@ -1033,7 +1030,7 @@
         <v>396</v>
       </c>
       <c r="F32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G32" s="1">
         <v>0.3125</v>
@@ -1041,17 +1038,17 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>310</v>
+        <v>884</v>
       </c>
       <c r="F33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G33" s="1">
-        <v>0.31597222222222221</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1060,10 +1057,10 @@
       </c>
       <c r="C34" s="1"/>
       <c r="E34">
-        <v>440</v>
+        <v>310</v>
       </c>
       <c r="F34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G34" s="1">
         <v>0.31597222222222221</v>
@@ -1075,10 +1072,10 @@
       </c>
       <c r="C35" s="1"/>
       <c r="E35">
-        <v>536</v>
+        <v>440</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="G35" s="1">
         <v>0.31597222222222221</v>
@@ -1090,40 +1087,40 @@
       </c>
       <c r="C36" s="1"/>
       <c r="E36">
-        <v>444</v>
+        <v>536</v>
       </c>
       <c r="F36" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G36" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.31597222222222221</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>9</v>
       </c>
-      <c r="C37" s="1"/>
-      <c r="E37">
-        <v>562</v>
-      </c>
-      <c r="F37" t="s">
-        <v>24</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0.32291666666666669</v>
-      </c>
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="D37">
+        <v>321</v>
+      </c>
+      <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C38" s="1"/>
       <c r="E38">
-        <v>4322</v>
+        <v>562</v>
       </c>
       <c r="F38" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G38" s="1">
         <v>0.32291666666666669</v>
@@ -1164,13 +1161,13 @@
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C41" s="1">
         <v>0.33680555555555558</v>
       </c>
       <c r="D41">
-        <v>309</v>
+        <v>601</v>
       </c>
       <c r="G41" s="1"/>
     </row>
@@ -1178,16 +1175,16 @@
       <c r="A42" t="s">
         <v>9</v>
       </c>
-      <c r="B42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="1">
+      <c r="C42" s="1"/>
+      <c r="E42">
+        <v>383</v>
+      </c>
+      <c r="F42" t="s">
+        <v>24</v>
+      </c>
+      <c r="G42" s="1">
         <v>0.33680555555555558</v>
       </c>
-      <c r="D42">
-        <v>581</v>
-      </c>
-      <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -1195,13 +1192,13 @@
       </c>
       <c r="C43" s="1"/>
       <c r="E43">
-        <v>383</v>
+        <v>454</v>
       </c>
       <c r="F43" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G43" s="1">
-        <v>0.33680555555555558</v>
+        <v>0.34027777777777779</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1210,13 +1207,13 @@
       </c>
       <c r="C44" s="1"/>
       <c r="E44">
-        <v>454</v>
+        <v>324</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G44" s="1">
-        <v>0.34027777777777779</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1225,10 +1222,10 @@
       </c>
       <c r="C45" s="1"/>
       <c r="E45">
-        <v>324</v>
+        <v>572</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G45" s="1">
         <v>0.34375</v>
@@ -1240,29 +1237,29 @@
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>554</v>
+        <v>430</v>
       </c>
       <c r="F46" t="s">
         <v>18</v>
       </c>
       <c r="G46" s="1">
-        <v>0.34375</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47" s="1"/>
-      <c r="E47">
-        <v>884</v>
-      </c>
-      <c r="F47" t="s">
-        <v>22</v>
-      </c>
-      <c r="G47" s="1">
-        <v>0.35347222222222219</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B47" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="D47">
+        <v>451</v>
+      </c>
+      <c r="G47" s="1"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -1270,44 +1267,44 @@
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>422</v>
+        <v>526</v>
       </c>
       <c r="F48" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G48" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>430</v>
+        <v>4320</v>
       </c>
       <c r="F49" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G49" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.38333333333333336</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>9</v>
       </c>
-      <c r="B50" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="1">
-        <v>0.37847222222222221</v>
-      </c>
-      <c r="D50">
-        <v>559</v>
-      </c>
-      <c r="G50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="E50">
+        <v>369</v>
+      </c>
+      <c r="F50" t="s">
+        <v>35</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0.3888888888888889</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
@@ -1315,74 +1312,74 @@
       </c>
       <c r="C51" s="1"/>
       <c r="E51">
-        <v>524</v>
+        <v>582</v>
       </c>
       <c r="F51" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G51" s="1">
-        <v>0.38194444444444442</v>
+        <v>0.39930555555555558</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" s="1"/>
-      <c r="E52">
-        <v>369</v>
-      </c>
-      <c r="F52" t="s">
-        <v>34</v>
-      </c>
-      <c r="G52" s="1">
-        <v>0.3888888888888889</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.40902777777777777</v>
+      </c>
+      <c r="D52">
+        <v>4337</v>
+      </c>
+      <c r="G52" s="1"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>9</v>
       </c>
-      <c r="C53" s="1"/>
-      <c r="E53">
-        <v>582</v>
-      </c>
-      <c r="F53" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="1">
-        <v>0.39930555555555558</v>
-      </c>
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="D53">
+        <v>569</v>
+      </c>
+      <c r="G53" s="1"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>9</v>
       </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" s="1">
+      <c r="C54" s="1"/>
+      <c r="E54">
+        <v>392</v>
+      </c>
+      <c r="F54" t="s">
+        <v>20</v>
+      </c>
+      <c r="G54" s="1">
         <v>0.41319444444444442</v>
       </c>
-      <c r="D54">
-        <v>569</v>
-      </c>
-      <c r="G54" s="1"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>26</v>
-      </c>
-      <c r="B55" t="s">
-        <v>27</v>
-      </c>
-      <c r="C55" s="1">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D55">
-        <v>342</v>
-      </c>
-      <c r="G55" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C55" s="1"/>
+      <c r="E55">
+        <v>408</v>
+      </c>
+      <c r="F55" t="s">
+        <v>38</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0.41319444444444442</v>
+      </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
@@ -1393,7 +1390,7 @@
         <v>609</v>
       </c>
       <c r="F56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G56" s="1">
         <v>0.4236111111111111</v>
@@ -1404,7 +1401,7 @@
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C57" s="1">
         <v>0.42708333333333331</v>
@@ -1434,13 +1431,13 @@
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C59" s="1">
-        <v>0.4548611111111111</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="D59">
-        <v>318</v>
+        <v>573</v>
       </c>
       <c r="G59" s="1"/>
     </row>
@@ -1449,37 +1446,37 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C60" s="1">
-        <v>0.46180555555555558</v>
+        <v>0.4548611111111111</v>
       </c>
       <c r="D60">
-        <v>384</v>
+        <v>318</v>
       </c>
       <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>26</v>
-      </c>
-      <c r="C61" s="1"/>
-      <c r="E61">
-        <v>343</v>
-      </c>
-      <c r="F61" t="s">
-        <v>27</v>
-      </c>
-      <c r="G61" s="1">
+        <v>9</v>
+      </c>
+      <c r="B61" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="1">
         <v>0.46180555555555558</v>
       </c>
+      <c r="D61">
+        <v>384</v>
+      </c>
+      <c r="G61" s="1"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>27</v>
+      </c>
+      <c r="B62" t="s">
         <v>28</v>
-      </c>
-      <c r="B62" t="s">
-        <v>25</v>
       </c>
       <c r="C62" s="1">
         <v>0.47291666666666665</v>
@@ -1525,13 +1522,13 @@
       </c>
       <c r="C65" s="1"/>
       <c r="E65">
-        <v>385</v>
+        <v>434</v>
       </c>
       <c r="F65" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G65" s="1">
-        <v>0.50347222222222221</v>
+        <v>0.49652777777777779</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -1540,10 +1537,10 @@
       </c>
       <c r="C66" s="1"/>
       <c r="E66">
-        <v>424</v>
+        <v>385</v>
       </c>
       <c r="F66" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G66" s="1">
         <v>0.50347222222222221</v>
@@ -1551,108 +1548,108 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>7</v>
-      </c>
-      <c r="B67" t="s">
+        <v>9</v>
+      </c>
+      <c r="C67" s="1"/>
+      <c r="E67">
+        <v>424</v>
+      </c>
+      <c r="F67" t="s">
         <v>29</v>
       </c>
-      <c r="C67" s="1">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="D67">
-        <v>1441</v>
-      </c>
-      <c r="G67" s="1"/>
+      <c r="G67" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C68" s="1"/>
       <c r="E68">
-        <v>1508</v>
+        <v>442</v>
       </c>
       <c r="F68" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G68" s="1">
-        <v>0.51597222222222228</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C69" s="1">
-        <v>0.5180555555555556</v>
+        <v>0.51041666666666663</v>
       </c>
       <c r="D69">
-        <v>1910</v>
+        <v>1441</v>
       </c>
       <c r="G69" s="1"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="E70">
+        <v>1508</v>
+      </c>
+      <c r="F70" t="s">
         <v>28</v>
       </c>
-      <c r="B70" t="s">
-        <v>27</v>
-      </c>
-      <c r="C70" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D70">
-        <v>937</v>
-      </c>
-      <c r="G70" s="1"/>
+      <c r="G70" s="1">
+        <v>0.51597222222222228</v>
+      </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B71" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C71" s="1">
-        <v>0.52916666666666667</v>
+        <v>0.5180555555555556</v>
       </c>
       <c r="D71">
-        <v>816</v>
+        <v>1910</v>
       </c>
       <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>7</v>
-      </c>
-      <c r="C72" s="1"/>
-      <c r="E72">
-        <v>1458</v>
-      </c>
-      <c r="F72" t="s">
-        <v>13</v>
-      </c>
-      <c r="G72" s="1">
-        <v>0.55555555555555558</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B72" t="s">
+        <v>32</v>
+      </c>
+      <c r="C72" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D72">
+        <v>937</v>
+      </c>
+      <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>28</v>
-      </c>
-      <c r="C73" s="1"/>
-      <c r="E73">
-        <v>380</v>
-      </c>
-      <c r="F73" t="s">
-        <v>27</v>
-      </c>
-      <c r="G73" s="1">
-        <v>0.57222222222222219</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B73" t="s">
+        <v>23</v>
+      </c>
+      <c r="C73" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D73">
+        <v>816</v>
+      </c>
+      <c r="G73" s="1"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
@@ -1660,162 +1657,162 @@
       </c>
       <c r="C74" s="1"/>
       <c r="E74">
-        <v>1468</v>
+        <v>1458</v>
       </c>
       <c r="F74" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G74" s="1">
-        <v>0.57638888888888895</v>
+        <v>0.55555555555555558</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C75" s="1"/>
       <c r="E75">
-        <v>1978</v>
+        <v>380</v>
       </c>
       <c r="F75" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G75" s="1">
-        <v>0.57708333333333328</v>
+        <v>0.57222222222222219</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C76" s="1"/>
       <c r="E76">
-        <v>871</v>
+        <v>1468</v>
       </c>
       <c r="F76" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G76" s="1">
-        <v>0.58194444444444449</v>
+        <v>0.57638888888888895</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>33</v>
-      </c>
-      <c r="B77" t="s">
-        <v>17</v>
-      </c>
-      <c r="C77" s="1">
-        <v>0.59375</v>
-      </c>
-      <c r="D77">
-        <v>628</v>
-      </c>
-      <c r="G77" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="E77">
+        <v>1978</v>
+      </c>
+      <c r="F77" t="s">
+        <v>31</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0.57708333333333328</v>
+      </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>7</v>
-      </c>
-      <c r="B78" t="s">
-        <v>29</v>
-      </c>
-      <c r="C78" s="1">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D78">
-        <v>1290</v>
-      </c>
-      <c r="G78" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="E78">
+        <v>871</v>
+      </c>
+      <c r="F78" t="s">
+        <v>23</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0.58194444444444449</v>
+      </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B79" t="s">
         <v>18</v>
       </c>
       <c r="C79" s="1">
-        <v>0.625</v>
+        <v>0.59236111111111112</v>
       </c>
       <c r="D79">
-        <v>557</v>
+        <v>628</v>
       </c>
       <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>33</v>
-      </c>
-      <c r="C80" s="1"/>
-      <c r="E80">
-        <v>629</v>
-      </c>
-      <c r="F80" t="s">
-        <v>17</v>
-      </c>
-      <c r="G80" s="1">
-        <v>0.64722222222222225</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B80" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" s="1">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D80">
+        <v>1290</v>
+      </c>
+      <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>9</v>
-      </c>
-      <c r="B81" t="s">
-        <v>23</v>
-      </c>
-      <c r="C81" s="1">
-        <v>0.65277777777777779</v>
-      </c>
-      <c r="D81">
-        <v>382</v>
-      </c>
-      <c r="G81" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="E81">
+        <v>629</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0.64722222222222225</v>
+      </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="1"/>
-      <c r="E82">
-        <v>1130</v>
-      </c>
-      <c r="F82" t="s">
-        <v>29</v>
-      </c>
-      <c r="G82" s="1">
+        <v>9</v>
+      </c>
+      <c r="B82" t="s">
+        <v>24</v>
+      </c>
+      <c r="C82" s="1">
         <v>0.65277777777777779</v>
       </c>
+      <c r="D82">
+        <v>382</v>
+      </c>
+      <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>9</v>
-      </c>
-      <c r="B83" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="1"/>
+      <c r="E83">
+        <v>1130</v>
+      </c>
+      <c r="F83" t="s">
         <v>29</v>
       </c>
-      <c r="C83" s="1">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D83">
-        <v>367</v>
-      </c>
-      <c r="G83" s="1"/>
+      <c r="G83" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C84" s="1">
         <v>0.66666666666666663</v>
       </c>
       <c r="D84">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G84" s="1"/>
     </row>
@@ -1824,13 +1821,13 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C85" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D85">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="G85" s="1"/>
     </row>
@@ -1839,13 +1836,13 @@
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C86" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D86">
-        <v>441</v>
+        <v>397</v>
       </c>
       <c r="G86" s="1"/>
     </row>
@@ -1854,13 +1851,13 @@
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C87" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D87">
-        <v>423</v>
+        <v>553</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1869,13 +1866,13 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C88" s="1">
-        <v>0.6875</v>
+        <v>0.68055555555555558</v>
       </c>
       <c r="D88">
-        <v>311</v>
+        <v>441</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -1884,13 +1881,13 @@
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C89" s="1">
-        <v>0.6875</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D89">
-        <v>555</v>
+        <v>435</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -1899,13 +1896,13 @@
         <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C90" s="1">
         <v>0.6875</v>
       </c>
       <c r="D90">
-        <v>610</v>
+        <v>311</v>
       </c>
       <c r="G90" s="1"/>
     </row>
@@ -1917,10 +1914,10 @@
         <v>22</v>
       </c>
       <c r="C91" s="1">
-        <v>0.70138888888888884</v>
+        <v>0.6875</v>
       </c>
       <c r="D91">
-        <v>322</v>
+        <v>610</v>
       </c>
       <c r="G91" s="1"/>
     </row>
@@ -1932,10 +1929,10 @@
         <v>29</v>
       </c>
       <c r="C92" s="1">
-        <v>0.72777777777777775</v>
+        <v>0.6958333333333333</v>
       </c>
       <c r="D92">
-        <v>4327</v>
+        <v>4321</v>
       </c>
       <c r="G92" s="1"/>
     </row>
@@ -1943,16 +1940,16 @@
       <c r="A93" t="s">
         <v>9</v>
       </c>
-      <c r="C93" s="1"/>
-      <c r="E93">
-        <v>326</v>
-      </c>
-      <c r="F93" t="s">
-        <v>10</v>
-      </c>
-      <c r="G93" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+      <c r="B93" t="s">
+        <v>23</v>
+      </c>
+      <c r="C93" s="1">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="D93">
+        <v>322</v>
+      </c>
+      <c r="G93" s="1"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
@@ -1960,29 +1957,29 @@
       </c>
       <c r="C94" s="1"/>
       <c r="E94">
-        <v>560</v>
+        <v>320</v>
       </c>
       <c r="F94" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G94" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.72222222222222221</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>9</v>
-      </c>
-      <c r="C95" s="1"/>
-      <c r="E95">
-        <v>313</v>
-      </c>
-      <c r="F95" t="s">
-        <v>21</v>
-      </c>
-      <c r="G95" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B95" t="s">
+        <v>29</v>
+      </c>
+      <c r="C95" s="1">
+        <v>0.72777777777777775</v>
+      </c>
+      <c r="D95">
+        <v>4327</v>
+      </c>
+      <c r="G95" s="1"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
@@ -1990,13 +1987,13 @@
       </c>
       <c r="C96" s="1"/>
       <c r="E96">
-        <v>450</v>
+        <v>326</v>
       </c>
       <c r="F96" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G96" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -2005,13 +2002,13 @@
       </c>
       <c r="C97" s="1"/>
       <c r="E97">
-        <v>520</v>
+        <v>560</v>
       </c>
       <c r="F97" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="G97" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -2020,13 +2017,13 @@
       </c>
       <c r="C98" s="1"/>
       <c r="E98">
-        <v>588</v>
+        <v>313</v>
       </c>
       <c r="F98" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G98" s="1">
-        <v>0.73611111111111116</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -2035,13 +2032,13 @@
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>448</v>
+        <v>520</v>
       </c>
       <c r="F99" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G99" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2050,28 +2047,28 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="F100" t="s">
         <v>14</v>
       </c>
       <c r="G100" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C101" s="1"/>
       <c r="E101">
-        <v>4308</v>
+        <v>448</v>
       </c>
       <c r="F101" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G101" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -2080,29 +2077,29 @@
       </c>
       <c r="C102" s="1"/>
       <c r="E102">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="F102" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G102" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>36</v>
-      </c>
-      <c r="B103" t="s">
-        <v>18</v>
-      </c>
-      <c r="C103" s="1">
-        <v>0.76736111111111116</v>
-      </c>
-      <c r="D103">
-        <v>222</v>
-      </c>
-      <c r="G103" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C103" s="1"/>
+      <c r="E103">
+        <v>4308</v>
+      </c>
+      <c r="F103" t="s">
+        <v>8</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0.75763888888888886</v>
+      </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
@@ -2110,192 +2107,192 @@
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>660</v>
+        <v>528</v>
       </c>
       <c r="F104" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G104" s="1">
-        <v>0.77083333333333337</v>
+        <v>0.76041666666666663</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B105" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C105" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.76736111111111116</v>
       </c>
       <c r="D105">
-        <v>742</v>
+        <v>222</v>
       </c>
       <c r="G105" s="1"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C106" s="1"/>
       <c r="E106">
-        <v>4312</v>
+        <v>660</v>
       </c>
       <c r="F106" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G106" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>9</v>
       </c>
-      <c r="B107" t="s">
-        <v>17</v>
-      </c>
-      <c r="C107" s="1">
-        <v>0.79513888888888884</v>
-      </c>
-      <c r="D107">
-        <v>431</v>
-      </c>
-      <c r="G107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="E107">
+        <v>558</v>
+      </c>
+      <c r="F107" t="s">
+        <v>25</v>
+      </c>
+      <c r="G107" s="1">
+        <v>0.77777777777777779</v>
+      </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>9</v>
-      </c>
-      <c r="C108" s="1"/>
-      <c r="E108">
-        <v>670</v>
-      </c>
-      <c r="F108" t="s">
-        <v>16</v>
-      </c>
-      <c r="G108" s="1">
-        <v>0.80555555555555558</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B108" t="s">
+        <v>29</v>
+      </c>
+      <c r="C108" s="1">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="D108">
+        <v>742</v>
+      </c>
+      <c r="G108" s="1"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>9</v>
-      </c>
-      <c r="B109" t="s">
-        <v>29</v>
-      </c>
-      <c r="C109" s="1">
-        <v>0.81944444444444442</v>
-      </c>
-      <c r="D109">
-        <v>425</v>
-      </c>
-      <c r="G109" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C109" s="1"/>
+      <c r="E109">
+        <v>4312</v>
+      </c>
+      <c r="F109" t="s">
+        <v>13</v>
+      </c>
+      <c r="G109" s="1">
+        <v>0.79027777777777775</v>
+      </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>9</v>
       </c>
       <c r="B110" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C110" s="1">
-        <v>0.82291666666666663</v>
+        <v>0.79513888888888884</v>
       </c>
       <c r="D110">
-        <v>329</v>
+        <v>431</v>
       </c>
       <c r="G110" s="1"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>28</v>
-      </c>
-      <c r="B111" t="s">
-        <v>25</v>
-      </c>
-      <c r="C111" s="1">
-        <v>0.82430555555555551</v>
-      </c>
-      <c r="D111">
-        <v>2657</v>
-      </c>
-      <c r="G111" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C111" s="1"/>
+      <c r="E111">
+        <v>670</v>
+      </c>
+      <c r="F111" t="s">
+        <v>17</v>
+      </c>
+      <c r="G111" s="1">
+        <v>0.80555555555555558</v>
+      </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>9</v>
       </c>
       <c r="B112" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C112" s="1">
-        <v>0.82638888888888884</v>
+        <v>0.81944444444444442</v>
       </c>
       <c r="D112">
-        <v>523</v>
+        <v>425</v>
       </c>
       <c r="G112" s="1"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>36</v>
-      </c>
-      <c r="C113" s="1"/>
-      <c r="E113">
-        <v>222</v>
-      </c>
-      <c r="F113" t="s">
-        <v>41</v>
-      </c>
-      <c r="G113" s="1">
-        <v>0.82986111111111116</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B113" t="s">
+        <v>28</v>
+      </c>
+      <c r="C113" s="1">
+        <v>0.82430555555555551</v>
+      </c>
+      <c r="D113">
+        <v>2657</v>
+      </c>
+      <c r="G113" s="1"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C114" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.82638888888888884</v>
       </c>
       <c r="D114">
-        <v>583</v>
+        <v>523</v>
       </c>
       <c r="G114" s="1"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>9</v>
-      </c>
-      <c r="B115" t="s">
-        <v>10</v>
-      </c>
-      <c r="C115" s="1">
-        <v>0.84375</v>
-      </c>
-      <c r="D115">
-        <v>325</v>
-      </c>
-      <c r="G115" s="1"/>
+        <v>37</v>
+      </c>
+      <c r="C115" s="1"/>
+      <c r="E115">
+        <v>222</v>
+      </c>
+      <c r="F115" t="s">
+        <v>40</v>
+      </c>
+      <c r="G115" s="1">
+        <v>0.82986111111111116</v>
+      </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>9</v>
       </c>
       <c r="B116" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C116" s="1">
-        <v>0.84375</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D116">
-        <v>445</v>
+        <v>583</v>
       </c>
       <c r="G116" s="1"/>
     </row>
@@ -2303,89 +2300,89 @@
       <c r="A117" t="s">
         <v>9</v>
       </c>
-      <c r="C117" s="1"/>
-      <c r="E117">
-        <v>590</v>
-      </c>
-      <c r="F117" t="s">
-        <v>13</v>
-      </c>
-      <c r="G117" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+      <c r="B117" t="s">
+        <v>10</v>
+      </c>
+      <c r="C117" s="1">
+        <v>0.84375</v>
+      </c>
+      <c r="D117">
+        <v>325</v>
+      </c>
+      <c r="G117" s="1"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>9</v>
       </c>
       <c r="B118" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C118" s="1">
-        <v>0.85416666666666663</v>
+        <v>0.85069444444444442</v>
       </c>
       <c r="D118">
-        <v>449</v>
+        <v>393</v>
       </c>
       <c r="G118" s="1"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>32</v>
-      </c>
-      <c r="B119" t="s">
-        <v>22</v>
-      </c>
-      <c r="C119" s="1">
-        <v>0.8569444444444444</v>
-      </c>
-      <c r="D119">
-        <v>881</v>
-      </c>
-      <c r="G119" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C119" s="1"/>
+      <c r="E119">
+        <v>590</v>
+      </c>
+      <c r="F119" t="s">
+        <v>13</v>
+      </c>
+      <c r="G119" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B120" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="C120" s="1">
-        <v>0.86111111111111116</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D120">
-        <v>4323</v>
+        <v>449</v>
       </c>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B121" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C121" s="1">
-        <v>0.86736111111111114</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D121">
-        <v>1461</v>
+        <v>881</v>
       </c>
       <c r="G121" s="1"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C122" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D122">
-        <v>563</v>
+        <v>1461</v>
       </c>
       <c r="G122" s="1"/>
     </row>
@@ -2394,13 +2391,13 @@
         <v>9</v>
       </c>
       <c r="B123" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C123" s="1">
-        <v>0.875</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D123">
-        <v>535</v>
+        <v>443</v>
       </c>
       <c r="G123" s="1"/>
     </row>
@@ -2409,13 +2406,13 @@
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C124" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D124">
-        <v>312</v>
+        <v>563</v>
       </c>
       <c r="G124" s="1"/>
     </row>
@@ -2424,13 +2421,13 @@
         <v>9</v>
       </c>
       <c r="B125" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C125" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.87152777777777779</v>
       </c>
       <c r="D125">
-        <v>525</v>
+        <v>409</v>
       </c>
       <c r="G125" s="1"/>
     </row>
@@ -2439,28 +2436,28 @@
         <v>9</v>
       </c>
       <c r="B126" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C126" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.875</v>
       </c>
       <c r="D126">
-        <v>589</v>
+        <v>527</v>
       </c>
       <c r="G126" s="1"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B127" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C127" s="1">
-        <v>0.89930555555555547</v>
+        <v>0.875</v>
       </c>
       <c r="D127">
-        <v>1425</v>
+        <v>535</v>
       </c>
       <c r="G127" s="1"/>
     </row>
@@ -2469,13 +2466,13 @@
         <v>9</v>
       </c>
       <c r="B128" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C128" s="1">
-        <v>0.91319444444444442</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D128">
-        <v>585</v>
+        <v>312</v>
       </c>
       <c r="G128" s="1"/>
     </row>
@@ -2483,16 +2480,16 @@
       <c r="A129" t="s">
         <v>9</v>
       </c>
-      <c r="C129" s="1"/>
-      <c r="E129">
-        <v>315</v>
-      </c>
-      <c r="F129" t="s">
-        <v>19</v>
-      </c>
-      <c r="G129" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B129" t="s">
+        <v>13</v>
+      </c>
+      <c r="C129" s="1">
+        <v>0.91319444444444442</v>
+      </c>
+      <c r="D129">
+        <v>585</v>
+      </c>
+      <c r="G129" s="1"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
@@ -2500,10 +2497,10 @@
       </c>
       <c r="C130" s="1"/>
       <c r="E130">
-        <v>365</v>
+        <v>315</v>
       </c>
       <c r="F130" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G130" s="1">
         <v>0.92013888888888884</v>
@@ -2515,10 +2512,10 @@
       </c>
       <c r="C131" s="1"/>
       <c r="E131">
-        <v>600</v>
+        <v>365</v>
       </c>
       <c r="F131" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G131" s="1">
         <v>0.92013888888888884</v>
@@ -2530,13 +2527,13 @@
       </c>
       <c r="C132" s="1"/>
       <c r="E132">
-        <v>429</v>
+        <v>580</v>
       </c>
       <c r="F132" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G132" s="1">
-        <v>0.92708333333333337</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -2545,13 +2542,13 @@
       </c>
       <c r="C133" s="1"/>
       <c r="E133">
-        <v>578</v>
+        <v>308</v>
       </c>
       <c r="F133" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G133" s="1">
-        <v>0.93055555555555558</v>
+        <v>0.92361111111111116</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -2560,13 +2557,13 @@
       </c>
       <c r="C134" s="1"/>
       <c r="E134">
-        <v>627</v>
+        <v>429</v>
       </c>
       <c r="F134" t="s">
         <v>21</v>
       </c>
       <c r="G134" s="1">
-        <v>0.93402777777777779</v>
+        <v>0.92708333333333337</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -2575,13 +2572,13 @@
       </c>
       <c r="C135" s="1"/>
       <c r="E135">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="F135" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G135" s="1">
-        <v>0.9375</v>
+        <v>0.93055555555555558</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -2590,13 +2587,13 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>568</v>
+        <v>627</v>
       </c>
       <c r="F136" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G136" s="1">
-        <v>0.94097222222222221</v>
+        <v>0.93402777777777779</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -2605,43 +2602,43 @@
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>452</v>
+        <v>574</v>
       </c>
       <c r="F137" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G137" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>339</v>
+        <v>568</v>
       </c>
       <c r="F138" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="G138" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>4336</v>
+        <v>452</v>
       </c>
       <c r="F139" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G139" s="1">
-        <v>0.9506944444444444</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -2653,7 +2650,7 @@
         <v>317</v>
       </c>
       <c r="F140" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G140" s="1">
         <v>0.95486111111111116</v>
@@ -2665,10 +2662,10 @@
       </c>
       <c r="C141" s="1"/>
       <c r="E141">
-        <v>432</v>
+        <v>457</v>
       </c>
       <c r="F141" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G141" s="1">
         <v>0.95833333333333337</v>
@@ -2680,44 +2677,29 @@
       </c>
       <c r="C142" s="1"/>
       <c r="E142">
-        <v>457</v>
+        <v>556</v>
       </c>
       <c r="F142" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G142" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.97222222222222221</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>9</v>
-      </c>
-      <c r="C143" s="1"/>
-      <c r="E143">
-        <v>552</v>
-      </c>
-      <c r="F143" t="s">
-        <v>18</v>
-      </c>
-      <c r="G143" s="1">
-        <v>0.97222222222222221</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>32</v>
-      </c>
-      <c r="B144" t="s">
-        <v>22</v>
-      </c>
-      <c r="C144" s="1">
+        <v>33</v>
+      </c>
+      <c r="B143" t="s">
+        <v>23</v>
+      </c>
+      <c r="C143" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D144">
+      <c r="D143">
         <v>878</v>
       </c>
-      <c r="G144" s="1"/>
+      <c r="G143" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FAEECE2-F178-4721-9CF8-1B287F36A5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9537AE65-B86F-4977-AB07-AF662CB87675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3126E712-A340-4158-8690-A24CF878AA78}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4066A129-BC5A-43F8-B098-DF160A207239}"/>
   </bookViews>
   <sheets>
-    <sheet name="13-06" sheetId="1" r:id="rId1"/>
+    <sheet name="14-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="43">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,9 +83,6 @@
     <t>KIAD</t>
   </si>
   <si>
-    <t>KONT</t>
-  </si>
-  <si>
     <t>MHLM</t>
   </si>
   <si>
@@ -119,46 +116,55 @@
     <t>KSFO</t>
   </si>
   <si>
+    <t>KMIA</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
+    <t>KIAH</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>KATL</t>
+  </si>
+  <si>
+    <t>TAG</t>
+  </si>
+  <si>
+    <t>MHRO</t>
+  </si>
+  <si>
+    <t>KDFW</t>
+  </si>
+  <si>
+    <t>CMP</t>
+  </si>
+  <si>
+    <t>AMX</t>
+  </si>
+  <si>
+    <t>SKRG</t>
+  </si>
+  <si>
+    <t>KMCO</t>
+  </si>
+  <si>
+    <t>IBE</t>
+  </si>
+  <si>
+    <t>CYUL</t>
+  </si>
+  <si>
+    <t>KBOS</t>
+  </si>
+  <si>
+    <t>KOAK</t>
+  </si>
+  <si>
     <t>KEWR</t>
-  </si>
-  <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>KMIA</t>
-  </si>
-  <si>
-    <t>KIAH</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>KATL</t>
-  </si>
-  <si>
-    <t>KDFW</t>
-  </si>
-  <si>
-    <t>CMP</t>
-  </si>
-  <si>
-    <t>AMX</t>
-  </si>
-  <si>
-    <t>SKRG</t>
-  </si>
-  <si>
-    <t>MMUN</t>
-  </si>
-  <si>
-    <t>IBE</t>
-  </si>
-  <si>
-    <t>KORD</t>
-  </si>
-  <si>
-    <t>KLAS</t>
   </si>
   <si>
     <t>LEMD</t>
@@ -536,8 +542,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFE2BF70-6640-4725-89D9-3E51C7BADE5E}">
-  <dimension ref="A1:G143"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10682C0A-2E84-47FF-B848-AA473D428D2F}">
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -580,7 +586,7 @@
         <v>2203</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" s="1">
         <v>5.2083333333333336E-2</v>
@@ -625,7 +631,7 @@
         <v>879</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="1">
         <v>0.20347222222222219</v>
@@ -687,37 +693,37 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D9">
-        <v>531</v>
+        <v>575</v>
       </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1">
-        <v>0.22222222222222221</v>
+        <v>0.24444444444444444</v>
       </c>
       <c r="D10">
-        <v>575</v>
+        <v>4309</v>
       </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C11" s="1">
-        <v>0.24444444444444444</v>
+        <v>0.24652777777777779</v>
       </c>
       <c r="D11">
-        <v>4309</v>
+        <v>456</v>
       </c>
       <c r="G11" s="1"/>
     </row>
@@ -732,35 +738,35 @@
         <v>0.24652777777777779</v>
       </c>
       <c r="D12">
-        <v>456</v>
+        <v>661</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0.24652777777777779</v>
-      </c>
-      <c r="D13">
-        <v>661</v>
-      </c>
-      <c r="G13" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="E13">
+        <v>3154</v>
+      </c>
+      <c r="F13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C14" s="1"/>
       <c r="E14">
-        <v>3154</v>
+        <v>1467</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1">
         <v>0.25</v>
@@ -768,33 +774,33 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15">
-        <v>1467</v>
+        <v>3154</v>
       </c>
       <c r="F15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G15" s="1">
-        <v>0.25</v>
+        <v>0.25069444444444444</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="E16">
-        <v>3154</v>
-      </c>
-      <c r="F16" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0.25069444444444444</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.25694444444444442</v>
+      </c>
+      <c r="D16">
+        <v>433</v>
+      </c>
+      <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -807,7 +813,7 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="D17">
-        <v>433</v>
+        <v>579</v>
       </c>
       <c r="G17" s="1"/>
     </row>
@@ -816,13 +822,13 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C18" s="1">
-        <v>0.25694444444444442</v>
+        <v>0.26041666666666669</v>
       </c>
       <c r="D18">
-        <v>579</v>
+        <v>529</v>
       </c>
       <c r="G18" s="1"/>
     </row>
@@ -831,13 +837,13 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1">
-        <v>0.26041666666666669</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="D19">
-        <v>529</v>
+        <v>314</v>
       </c>
       <c r="G19" s="1"/>
     </row>
@@ -849,10 +855,10 @@
         <v>20</v>
       </c>
       <c r="C20" s="1">
-        <v>0.2638888888888889</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D20">
-        <v>314</v>
+        <v>428</v>
       </c>
       <c r="G20" s="1"/>
     </row>
@@ -867,7 +873,7 @@
         <v>0.2673611111111111</v>
       </c>
       <c r="D21">
-        <v>428</v>
+        <v>626</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -879,10 +885,10 @@
         <v>22</v>
       </c>
       <c r="C22" s="1">
-        <v>0.2673611111111111</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="D22">
-        <v>626</v>
+        <v>316</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -897,7 +903,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D23">
-        <v>316</v>
+        <v>366</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -912,7 +918,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D24">
-        <v>366</v>
+        <v>561</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -921,13 +927,13 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C25" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D25">
-        <v>561</v>
+        <v>591</v>
       </c>
       <c r="G25" s="1"/>
     </row>
@@ -936,13 +942,13 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C26" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D26">
-        <v>591</v>
+        <v>671</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -951,44 +957,44 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C27" s="1">
-        <v>0.27083333333333331</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="D27">
-        <v>671</v>
+        <v>521</v>
       </c>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="D28">
-        <v>521</v>
-      </c>
-      <c r="G28" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="E28">
+        <v>4326</v>
+      </c>
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0.29791666666666666</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C29" s="1"/>
       <c r="E29">
-        <v>4326</v>
+        <v>319</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G29" s="1">
-        <v>0.29791666666666666</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -997,7 +1003,7 @@
       </c>
       <c r="C30" s="1"/>
       <c r="E30">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F30" t="s">
         <v>22</v>
@@ -1012,10 +1018,10 @@
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G31" s="1">
         <v>0.3125</v>
@@ -1030,7 +1036,7 @@
         <v>396</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G32" s="1">
         <v>0.3125</v>
@@ -1038,17 +1044,17 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>884</v>
+        <v>310</v>
       </c>
       <c r="F33" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G33" s="1">
-        <v>0.3125</v>
+        <v>0.31597222222222221</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1057,10 +1063,10 @@
       </c>
       <c r="C34" s="1"/>
       <c r="E34">
-        <v>310</v>
+        <v>440</v>
       </c>
       <c r="F34" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G34" s="1">
         <v>0.31597222222222221</v>
@@ -1072,10 +1078,10 @@
       </c>
       <c r="C35" s="1"/>
       <c r="E35">
-        <v>440</v>
+        <v>536</v>
       </c>
       <c r="F35" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="G35" s="1">
         <v>0.31597222222222221</v>
@@ -1087,40 +1093,40 @@
       </c>
       <c r="C36" s="1"/>
       <c r="E36">
-        <v>536</v>
+        <v>444</v>
       </c>
       <c r="F36" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="G36" s="1">
-        <v>0.31597222222222221</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>9</v>
       </c>
-      <c r="B37" t="s">
-        <v>19</v>
-      </c>
-      <c r="C37" s="1">
-        <v>0.31944444444444442</v>
-      </c>
-      <c r="D37">
-        <v>321</v>
-      </c>
-      <c r="G37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="E37">
+        <v>562</v>
+      </c>
+      <c r="F37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.32291666666666669</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C38" s="1"/>
       <c r="E38">
-        <v>562</v>
+        <v>4322</v>
       </c>
       <c r="F38" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G38" s="1">
         <v>0.32291666666666669</v>
@@ -1135,7 +1141,7 @@
         <v>368</v>
       </c>
       <c r="F39" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G39" s="1">
         <v>0.33333333333333331</v>
@@ -1161,13 +1167,13 @@
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C41" s="1">
         <v>0.33680555555555558</v>
       </c>
       <c r="D41">
-        <v>601</v>
+        <v>309</v>
       </c>
       <c r="G41" s="1"/>
     </row>
@@ -1175,16 +1181,16 @@
       <c r="A42" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="1"/>
-      <c r="E42">
-        <v>383</v>
-      </c>
-      <c r="F42" t="s">
-        <v>24</v>
-      </c>
-      <c r="G42" s="1">
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="1">
         <v>0.33680555555555558</v>
       </c>
+      <c r="D42">
+        <v>581</v>
+      </c>
+      <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -1192,13 +1198,13 @@
       </c>
       <c r="C43" s="1"/>
       <c r="E43">
-        <v>454</v>
+        <v>383</v>
       </c>
       <c r="F43" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G43" s="1">
-        <v>0.34027777777777779</v>
+        <v>0.33680555555555558</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1222,10 +1228,10 @@
       </c>
       <c r="C45" s="1"/>
       <c r="E45">
-        <v>572</v>
+        <v>554</v>
       </c>
       <c r="F45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G45" s="1">
         <v>0.34375</v>
@@ -1233,33 +1239,33 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>430</v>
+        <v>884</v>
       </c>
       <c r="F46" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G46" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.35347222222222219</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>9</v>
       </c>
-      <c r="B47" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47" s="1">
-        <v>0.37152777777777779</v>
-      </c>
-      <c r="D47">
-        <v>451</v>
-      </c>
-      <c r="G47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="E47">
+        <v>422</v>
+      </c>
+      <c r="F47" t="s">
+        <v>36</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0.36458333333333331</v>
+      </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -1267,29 +1273,29 @@
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>526</v>
+        <v>430</v>
       </c>
       <c r="F48" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G48" s="1">
-        <v>0.375</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="1"/>
-      <c r="E49">
-        <v>4320</v>
-      </c>
-      <c r="F49" t="s">
-        <v>29</v>
-      </c>
-      <c r="G49" s="1">
-        <v>0.38333333333333336</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B49" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="1">
+        <v>0.37847222222222221</v>
+      </c>
+      <c r="D49">
+        <v>559</v>
+      </c>
+      <c r="G49" s="1"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -1297,13 +1303,13 @@
       </c>
       <c r="C50" s="1"/>
       <c r="E50">
-        <v>369</v>
+        <v>524</v>
       </c>
       <c r="F50" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G50" s="1">
-        <v>0.3888888888888889</v>
+        <v>0.38194444444444442</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -1312,36 +1318,36 @@
       </c>
       <c r="C51" s="1"/>
       <c r="E51">
-        <v>582</v>
+        <v>369</v>
       </c>
       <c r="F51" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="G51" s="1">
-        <v>0.39930555555555558</v>
+        <v>0.3888888888888889</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>12</v>
-      </c>
-      <c r="B52" t="s">
-        <v>26</v>
-      </c>
-      <c r="C52" s="1">
-        <v>0.40902777777777777</v>
-      </c>
-      <c r="D52">
-        <v>4337</v>
-      </c>
-      <c r="G52" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="E52">
+        <v>582</v>
+      </c>
+      <c r="F52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.39930555555555558</v>
+      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C53" s="1">
         <v>0.41319444444444442</v>
@@ -1360,7 +1366,7 @@
         <v>392</v>
       </c>
       <c r="F54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G54" s="1">
         <v>0.41319444444444442</v>
@@ -1372,42 +1378,42 @@
       </c>
       <c r="C55" s="1"/>
       <c r="E55">
-        <v>408</v>
+        <v>609</v>
       </c>
       <c r="F55" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G55" s="1">
-        <v>0.41319444444444442</v>
+        <v>0.4236111111111111</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
-      <c r="C56" s="1"/>
-      <c r="E56">
-        <v>609</v>
-      </c>
-      <c r="F56" t="s">
-        <v>22</v>
-      </c>
-      <c r="G56" s="1">
-        <v>0.4236111111111111</v>
-      </c>
+      <c r="B56" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56" s="1">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D56">
+        <v>537</v>
+      </c>
+      <c r="G56" s="1"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C57" s="1">
-        <v>0.42708333333333331</v>
+        <v>0.4548611111111111</v>
       </c>
       <c r="D57">
-        <v>537</v>
+        <v>318</v>
       </c>
       <c r="G57" s="1"/>
     </row>
@@ -1416,43 +1422,43 @@
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C58" s="1">
-        <v>0.44791666666666669</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D58">
-        <v>455</v>
+        <v>70</v>
       </c>
       <c r="G58" s="1"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B59" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C59" s="1">
-        <v>0.4513888888888889</v>
+        <v>0.47291666666666665</v>
       </c>
       <c r="D59">
-        <v>573</v>
+        <v>495</v>
       </c>
       <c r="G59" s="1"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C60" s="1">
-        <v>0.4548611111111111</v>
+        <v>0.47847222222222219</v>
       </c>
       <c r="D60">
-        <v>318</v>
+        <v>1194</v>
       </c>
       <c r="G60" s="1"/>
     </row>
@@ -1460,315 +1466,315 @@
       <c r="A61" t="s">
         <v>9</v>
       </c>
-      <c r="B61" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="1">
-        <v>0.46180555555555558</v>
-      </c>
-      <c r="D61">
-        <v>384</v>
-      </c>
-      <c r="G61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="E61">
+        <v>584</v>
+      </c>
+      <c r="F61" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0.49305555555555558</v>
+      </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>27</v>
-      </c>
-      <c r="B62" t="s">
-        <v>28</v>
-      </c>
-      <c r="C62" s="1">
-        <v>0.47291666666666665</v>
-      </c>
-      <c r="D62">
-        <v>495</v>
-      </c>
-      <c r="G62" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="E62">
+        <v>71</v>
+      </c>
+      <c r="F62" t="s">
+        <v>23</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>7</v>
-      </c>
-      <c r="B63" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="1">
-        <v>0.47847222222222219</v>
-      </c>
-      <c r="D63">
-        <v>1194</v>
-      </c>
-      <c r="G63" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C63" s="1"/>
+      <c r="E63">
+        <v>424</v>
+      </c>
+      <c r="F63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" s="1"/>
-      <c r="E64">
-        <v>584</v>
-      </c>
-      <c r="F64" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" s="1">
-        <v>0.49305555555555558</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B64" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" s="1">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D64">
+        <v>1441</v>
+      </c>
+      <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C65" s="1"/>
       <c r="E65">
-        <v>434</v>
+        <v>1508</v>
       </c>
       <c r="F65" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G65" s="1">
-        <v>0.49652777777777779</v>
+        <v>0.51597222222222228</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>9</v>
-      </c>
-      <c r="C66" s="1"/>
-      <c r="E66">
-        <v>385</v>
-      </c>
-      <c r="F66" t="s">
-        <v>24</v>
-      </c>
-      <c r="G66" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B66" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66" s="1">
+        <v>0.5180555555555556</v>
+      </c>
+      <c r="D66">
+        <v>1910</v>
+      </c>
+      <c r="G66" s="1"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>9</v>
-      </c>
-      <c r="C67" s="1"/>
-      <c r="E67">
-        <v>424</v>
-      </c>
-      <c r="F67" t="s">
-        <v>29</v>
-      </c>
-      <c r="G67" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B67" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="1">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D67">
+        <v>420</v>
+      </c>
+      <c r="G67" s="1"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" s="1"/>
-      <c r="E68">
-        <v>442</v>
-      </c>
-      <c r="F68" t="s">
+        <v>26</v>
+      </c>
+      <c r="B68" t="s">
         <v>32</v>
       </c>
-      <c r="G68" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+      <c r="C68" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D68">
+        <v>937</v>
+      </c>
+      <c r="G68" s="1"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B69" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C69" s="1">
-        <v>0.51041666666666663</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="D69">
-        <v>1441</v>
+        <v>816</v>
       </c>
       <c r="G69" s="1"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C70" s="1"/>
       <c r="E70">
-        <v>1508</v>
+        <v>421</v>
       </c>
       <c r="F70" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G70" s="1">
-        <v>0.51597222222222228</v>
+        <v>0.55208333333333337</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>30</v>
-      </c>
-      <c r="B71" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="1">
-        <v>0.5180555555555556</v>
-      </c>
-      <c r="D71">
-        <v>1910</v>
-      </c>
-      <c r="G71" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C71" s="1"/>
+      <c r="E71">
+        <v>1458</v>
+      </c>
+      <c r="F71" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0.55555555555555558</v>
+      </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>27</v>
-      </c>
-      <c r="B72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" s="1"/>
+      <c r="E72">
+        <v>380</v>
+      </c>
+      <c r="F72" t="s">
         <v>32</v>
       </c>
-      <c r="C72" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D72">
-        <v>937</v>
-      </c>
-      <c r="G72" s="1"/>
+      <c r="G72" s="1">
+        <v>0.57222222222222219</v>
+      </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>33</v>
-      </c>
-      <c r="B73" t="s">
-        <v>23</v>
-      </c>
-      <c r="C73" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D73">
-        <v>816</v>
-      </c>
-      <c r="G73" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C73" s="1"/>
+      <c r="E73">
+        <v>1468</v>
+      </c>
+      <c r="F73" t="s">
+        <v>27</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0.57638888888888895</v>
+      </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C74" s="1"/>
       <c r="E74">
-        <v>1458</v>
+        <v>1978</v>
       </c>
       <c r="F74" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G74" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.57708333333333328</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C75" s="1"/>
       <c r="E75">
-        <v>380</v>
+        <v>871</v>
       </c>
       <c r="F75" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G75" s="1">
-        <v>0.57222222222222219</v>
+        <v>0.58194444444444449</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="1"/>
-      <c r="E76">
-        <v>1468</v>
-      </c>
-      <c r="F76" t="s">
-        <v>29</v>
-      </c>
-      <c r="G76" s="1">
-        <v>0.57638888888888895</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B76" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" s="1">
+        <v>0.59375</v>
+      </c>
+      <c r="D76">
+        <v>628</v>
+      </c>
+      <c r="G76" s="1"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>30</v>
-      </c>
-      <c r="C77" s="1"/>
-      <c r="E77">
-        <v>1978</v>
-      </c>
-      <c r="F77" t="s">
-        <v>31</v>
-      </c>
-      <c r="G77" s="1">
-        <v>0.57708333333333328</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B77" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77" s="1">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D77">
+        <v>1290</v>
+      </c>
+      <c r="G77" s="1"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>33</v>
-      </c>
-      <c r="C78" s="1"/>
-      <c r="E78">
-        <v>871</v>
-      </c>
-      <c r="F78" t="s">
-        <v>23</v>
-      </c>
-      <c r="G78" s="1">
-        <v>0.58194444444444449</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="D78">
+        <v>557</v>
+      </c>
+      <c r="G78" s="1"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>34</v>
       </c>
-      <c r="B79" t="s">
-        <v>18</v>
-      </c>
-      <c r="C79" s="1">
-        <v>0.59236111111111112</v>
-      </c>
-      <c r="D79">
-        <v>628</v>
-      </c>
-      <c r="G79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="E79">
+        <v>629</v>
+      </c>
+      <c r="F79" t="s">
+        <v>17</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0.64722222222222225</v>
+      </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C80" s="1">
-        <v>0.60416666666666663</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="D80">
-        <v>1290</v>
+        <v>382</v>
       </c>
       <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C81" s="1"/>
       <c r="E81">
-        <v>629</v>
+        <v>1130</v>
       </c>
       <c r="F81" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G81" s="1">
-        <v>0.64722222222222225</v>
+        <v>0.65277777777777779</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -1776,43 +1782,43 @@
         <v>9</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C82" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D82">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="1"/>
-      <c r="E83">
-        <v>1130</v>
-      </c>
-      <c r="F83" t="s">
-        <v>29</v>
-      </c>
-      <c r="G83" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B83" t="s">
+        <v>35</v>
+      </c>
+      <c r="C83" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D83">
+        <v>370</v>
+      </c>
+      <c r="G83" s="1"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C84" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D84">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="G84" s="1"/>
     </row>
@@ -1821,13 +1827,13 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C85" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.68055555555555558</v>
       </c>
       <c r="D85">
-        <v>370</v>
+        <v>441</v>
       </c>
       <c r="G85" s="1"/>
     </row>
@@ -1836,13 +1842,13 @@
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C86" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D86">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="G86" s="1"/>
     </row>
@@ -1851,13 +1857,13 @@
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C87" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.6875</v>
       </c>
       <c r="D87">
-        <v>553</v>
+        <v>311</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1866,13 +1872,13 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C88" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.6875</v>
       </c>
       <c r="D88">
-        <v>441</v>
+        <v>555</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -1881,13 +1887,13 @@
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C89" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.6875</v>
       </c>
       <c r="D89">
-        <v>435</v>
+        <v>610</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -1896,60 +1902,60 @@
         <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C90" s="1">
-        <v>0.6875</v>
+        <v>0.70138888888888884</v>
       </c>
       <c r="D90">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="G90" s="1"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C91" s="1">
-        <v>0.6875</v>
+        <v>0.72777777777777775</v>
       </c>
       <c r="D91">
-        <v>610</v>
+        <v>4327</v>
       </c>
       <c r="G91" s="1"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>12</v>
-      </c>
-      <c r="B92" t="s">
-        <v>29</v>
-      </c>
-      <c r="C92" s="1">
-        <v>0.6958333333333333</v>
-      </c>
-      <c r="D92">
-        <v>4321</v>
-      </c>
-      <c r="G92" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C92" s="1"/>
+      <c r="E92">
+        <v>326</v>
+      </c>
+      <c r="F92" t="s">
+        <v>10</v>
+      </c>
+      <c r="G92" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>9</v>
       </c>
-      <c r="B93" t="s">
-        <v>23</v>
-      </c>
-      <c r="C93" s="1">
-        <v>0.70138888888888884</v>
-      </c>
-      <c r="D93">
-        <v>322</v>
-      </c>
-      <c r="G93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="E93">
+        <v>560</v>
+      </c>
+      <c r="F93" t="s">
+        <v>24</v>
+      </c>
+      <c r="G93" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
@@ -1957,29 +1963,29 @@
       </c>
       <c r="C94" s="1"/>
       <c r="E94">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F94" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G94" s="1">
-        <v>0.72222222222222221</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>12</v>
-      </c>
-      <c r="B95" t="s">
-        <v>29</v>
-      </c>
-      <c r="C95" s="1">
-        <v>0.72777777777777775</v>
-      </c>
-      <c r="D95">
-        <v>4327</v>
-      </c>
-      <c r="G95" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C95" s="1"/>
+      <c r="E95">
+        <v>520</v>
+      </c>
+      <c r="F95" t="s">
+        <v>8</v>
+      </c>
+      <c r="G95" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
@@ -1987,13 +1993,13 @@
       </c>
       <c r="C96" s="1"/>
       <c r="E96">
-        <v>326</v>
+        <v>588</v>
       </c>
       <c r="F96" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G96" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.73611111111111116</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -2002,13 +2008,13 @@
       </c>
       <c r="C97" s="1"/>
       <c r="E97">
-        <v>560</v>
+        <v>448</v>
       </c>
       <c r="F97" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G97" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -2017,28 +2023,28 @@
       </c>
       <c r="C98" s="1"/>
       <c r="E98">
-        <v>313</v>
+        <v>534</v>
       </c>
       <c r="F98" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G98" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>520</v>
+        <v>4308</v>
       </c>
       <c r="F99" t="s">
         <v>8</v>
       </c>
       <c r="G99" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2047,29 +2053,29 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F100" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G100" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.76041666666666663</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>9</v>
-      </c>
-      <c r="C101" s="1"/>
-      <c r="E101">
-        <v>448</v>
-      </c>
-      <c r="F101" t="s">
-        <v>11</v>
-      </c>
-      <c r="G101" s="1">
-        <v>0.74305555555555558</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B101" t="s">
+        <v>18</v>
+      </c>
+      <c r="C101" s="1">
+        <v>0.76736111111111116</v>
+      </c>
+      <c r="D101">
+        <v>222</v>
+      </c>
+      <c r="G101" s="1"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
@@ -2077,57 +2083,57 @@
       </c>
       <c r="C102" s="1"/>
       <c r="E102">
-        <v>534</v>
+        <v>660</v>
       </c>
       <c r="F102" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G102" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>12</v>
-      </c>
-      <c r="C103" s="1"/>
-      <c r="E103">
-        <v>4308</v>
-      </c>
-      <c r="F103" t="s">
-        <v>8</v>
-      </c>
-      <c r="G103" s="1">
-        <v>0.75763888888888886</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B103" t="s">
+        <v>27</v>
+      </c>
+      <c r="C103" s="1">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="D103">
+        <v>742</v>
+      </c>
+      <c r="G103" s="1"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>528</v>
+        <v>4312</v>
       </c>
       <c r="F104" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G104" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.79027777777777775</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="B105" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C105" s="1">
-        <v>0.76736111111111116</v>
+        <v>0.79513888888888884</v>
       </c>
       <c r="D105">
-        <v>222</v>
+        <v>431</v>
       </c>
       <c r="G105" s="1"/>
     </row>
@@ -2137,88 +2143,88 @@
       </c>
       <c r="C106" s="1"/>
       <c r="E106">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="F106" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G106" s="1">
-        <v>0.77083333333333337</v>
+        <v>0.80555555555555558</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>9</v>
       </c>
-      <c r="C107" s="1"/>
-      <c r="E107">
-        <v>558</v>
-      </c>
-      <c r="F107" t="s">
-        <v>25</v>
-      </c>
-      <c r="G107" s="1">
-        <v>0.77777777777777779</v>
-      </c>
+      <c r="B107" t="s">
+        <v>27</v>
+      </c>
+      <c r="C107" s="1">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="D107">
+        <v>425</v>
+      </c>
+      <c r="G107" s="1"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B108" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C108" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="D108">
-        <v>742</v>
+        <v>329</v>
       </c>
       <c r="G108" s="1"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>12</v>
-      </c>
-      <c r="C109" s="1"/>
-      <c r="E109">
-        <v>4312</v>
-      </c>
-      <c r="F109" t="s">
-        <v>13</v>
-      </c>
-      <c r="G109" s="1">
-        <v>0.79027777777777775</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B109" t="s">
+        <v>25</v>
+      </c>
+      <c r="C109" s="1">
+        <v>0.82430555555555551</v>
+      </c>
+      <c r="D109">
+        <v>2657</v>
+      </c>
+      <c r="G109" s="1"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>9</v>
       </c>
       <c r="B110" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C110" s="1">
-        <v>0.79513888888888884</v>
+        <v>0.82638888888888884</v>
       </c>
       <c r="D110">
-        <v>431</v>
+        <v>523</v>
       </c>
       <c r="G110" s="1"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C111" s="1"/>
       <c r="E111">
-        <v>670</v>
+        <v>222</v>
       </c>
       <c r="F111" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="G111" s="1">
-        <v>0.80555555555555558</v>
+        <v>0.82986111111111116</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -2226,28 +2232,28 @@
         <v>9</v>
       </c>
       <c r="B112" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C112" s="1">
-        <v>0.81944444444444442</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D112">
-        <v>425</v>
+        <v>583</v>
       </c>
       <c r="G112" s="1"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C113" s="1">
-        <v>0.82430555555555551</v>
+        <v>0.84375</v>
       </c>
       <c r="D113">
-        <v>2657</v>
+        <v>325</v>
       </c>
       <c r="G113" s="1"/>
     </row>
@@ -2256,133 +2262,133 @@
         <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="C114" s="1">
-        <v>0.82638888888888884</v>
+        <v>0.84375</v>
       </c>
       <c r="D114">
-        <v>523</v>
+        <v>445</v>
       </c>
       <c r="G114" s="1"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>37</v>
-      </c>
-      <c r="C115" s="1"/>
-      <c r="E115">
-        <v>222</v>
-      </c>
-      <c r="F115" t="s">
-        <v>40</v>
-      </c>
-      <c r="G115" s="1">
-        <v>0.82986111111111116</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B115" t="s">
+        <v>19</v>
+      </c>
+      <c r="C115" s="1">
+        <v>0.85069444444444442</v>
+      </c>
+      <c r="D115">
+        <v>393</v>
+      </c>
+      <c r="G115" s="1"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>9</v>
       </c>
-      <c r="B116" t="s">
+      <c r="C116" s="1"/>
+      <c r="E116">
+        <v>590</v>
+      </c>
+      <c r="F116" t="s">
         <v>13</v>
       </c>
-      <c r="C116" s="1">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D116">
-        <v>583</v>
-      </c>
-      <c r="G116" s="1"/>
+      <c r="G116" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>9</v>
       </c>
       <c r="B117" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C117" s="1">
-        <v>0.84375</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D117">
-        <v>325</v>
+        <v>449</v>
       </c>
       <c r="G117" s="1"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B118" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C118" s="1">
-        <v>0.85069444444444442</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D118">
-        <v>393</v>
+        <v>881</v>
       </c>
       <c r="G118" s="1"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>9</v>
-      </c>
-      <c r="C119" s="1"/>
-      <c r="E119">
-        <v>590</v>
-      </c>
-      <c r="F119" t="s">
-        <v>13</v>
-      </c>
-      <c r="G119" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B119" t="s">
+        <v>40</v>
+      </c>
+      <c r="C119" s="1">
+        <v>0.86111111111111116</v>
+      </c>
+      <c r="D119">
+        <v>4323</v>
+      </c>
+      <c r="G119" s="1"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C120" s="1">
-        <v>0.85416666666666663</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D120">
-        <v>449</v>
+        <v>1461</v>
       </c>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B121" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C121" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D121">
-        <v>881</v>
+        <v>563</v>
       </c>
       <c r="G121" s="1"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C122" s="1">
-        <v>0.86736111111111114</v>
+        <v>0.875</v>
       </c>
       <c r="D122">
-        <v>1461</v>
+        <v>535</v>
       </c>
       <c r="G122" s="1"/>
     </row>
@@ -2391,13 +2397,13 @@
         <v>9</v>
       </c>
       <c r="B123" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C123" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D123">
-        <v>443</v>
+        <v>312</v>
       </c>
       <c r="G123" s="1"/>
     </row>
@@ -2406,13 +2412,13 @@
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C124" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D124">
-        <v>563</v>
+        <v>525</v>
       </c>
       <c r="G124" s="1"/>
     </row>
@@ -2421,28 +2427,28 @@
         <v>9</v>
       </c>
       <c r="B125" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C125" s="1">
-        <v>0.87152777777777779</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D125">
-        <v>409</v>
+        <v>589</v>
       </c>
       <c r="G125" s="1"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B126" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C126" s="1">
-        <v>0.875</v>
+        <v>0.89930555555555547</v>
       </c>
       <c r="D126">
-        <v>527</v>
+        <v>1425</v>
       </c>
       <c r="G126" s="1"/>
     </row>
@@ -2451,13 +2457,13 @@
         <v>9</v>
       </c>
       <c r="B127" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C127" s="1">
-        <v>0.875</v>
+        <v>0.91319444444444442</v>
       </c>
       <c r="D127">
-        <v>535</v>
+        <v>585</v>
       </c>
       <c r="G127" s="1"/>
     </row>
@@ -2465,31 +2471,31 @@
       <c r="A128" t="s">
         <v>9</v>
       </c>
-      <c r="B128" t="s">
-        <v>22</v>
-      </c>
-      <c r="C128" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D128">
-        <v>312</v>
-      </c>
-      <c r="G128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="E128">
+        <v>315</v>
+      </c>
+      <c r="F128" t="s">
+        <v>19</v>
+      </c>
+      <c r="G128" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>9</v>
       </c>
-      <c r="B129" t="s">
-        <v>13</v>
-      </c>
-      <c r="C129" s="1">
-        <v>0.91319444444444442</v>
-      </c>
-      <c r="D129">
-        <v>585</v>
-      </c>
-      <c r="G129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="E129">
+        <v>365</v>
+      </c>
+      <c r="F129" t="s">
+        <v>23</v>
+      </c>
+      <c r="G129" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
@@ -2497,10 +2503,10 @@
       </c>
       <c r="C130" s="1"/>
       <c r="E130">
-        <v>315</v>
+        <v>600</v>
       </c>
       <c r="F130" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G130" s="1">
         <v>0.92013888888888884</v>
@@ -2512,13 +2518,13 @@
       </c>
       <c r="C131" s="1"/>
       <c r="E131">
-        <v>365</v>
+        <v>429</v>
       </c>
       <c r="F131" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G131" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.92708333333333337</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -2527,13 +2533,13 @@
       </c>
       <c r="C132" s="1"/>
       <c r="E132">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F132" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G132" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.93055555555555558</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -2542,13 +2548,13 @@
       </c>
       <c r="C133" s="1"/>
       <c r="E133">
-        <v>308</v>
+        <v>627</v>
       </c>
       <c r="F133" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G133" s="1">
-        <v>0.92361111111111116</v>
+        <v>0.93402777777777779</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -2557,13 +2563,13 @@
       </c>
       <c r="C134" s="1"/>
       <c r="E134">
-        <v>429</v>
+        <v>574</v>
       </c>
       <c r="F134" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G134" s="1">
-        <v>0.92708333333333337</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -2572,13 +2578,13 @@
       </c>
       <c r="C135" s="1"/>
       <c r="E135">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="F135" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G135" s="1">
-        <v>0.93055555555555558</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -2587,28 +2593,28 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>627</v>
+        <v>452</v>
       </c>
       <c r="F136" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G136" s="1">
-        <v>0.93402777777777779</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>574</v>
+        <v>339</v>
       </c>
       <c r="F137" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="G137" s="1">
-        <v>0.9375</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -2617,13 +2623,13 @@
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>568</v>
+        <v>317</v>
       </c>
       <c r="F138" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G138" s="1">
-        <v>0.94097222222222221</v>
+        <v>0.95486111111111116</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -2632,13 +2638,13 @@
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F139" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G139" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -2647,59 +2653,44 @@
       </c>
       <c r="C140" s="1"/>
       <c r="E140">
-        <v>317</v>
+        <v>552</v>
       </c>
       <c r="F140" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G140" s="1">
-        <v>0.95486111111111116</v>
+        <v>0.97222222222222221</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>9</v>
       </c>
-      <c r="C141" s="1"/>
-      <c r="E141">
-        <v>457</v>
-      </c>
-      <c r="F141" t="s">
-        <v>16</v>
-      </c>
-      <c r="G141" s="1">
-        <v>0.95833333333333337</v>
-      </c>
+      <c r="B141" t="s">
+        <v>42</v>
+      </c>
+      <c r="C141" s="1">
+        <v>0.97569444444444442</v>
+      </c>
+      <c r="D141">
+        <v>301</v>
+      </c>
+      <c r="G141" s="1"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>9</v>
-      </c>
-      <c r="C142" s="1"/>
-      <c r="E142">
-        <v>556</v>
-      </c>
-      <c r="F142" t="s">
-        <v>19</v>
-      </c>
-      <c r="G142" s="1">
-        <v>0.97222222222222221</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
         <v>33</v>
       </c>
-      <c r="B143" t="s">
-        <v>23</v>
-      </c>
-      <c r="C143" s="1">
+      <c r="B142" t="s">
+        <v>22</v>
+      </c>
+      <c r="C142" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D143">
+      <c r="D142">
         <v>878</v>
       </c>
-      <c r="G143" s="1"/>
+      <c r="G142" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9537AE65-B86F-4977-AB07-AF662CB87675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF77CB06-0748-4CF9-8BB3-CEEAD16A21ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4066A129-BC5A-43F8-B098-DF160A207239}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{33D45D58-5545-4CAC-93DA-EB063451B6E5}"/>
   </bookViews>
   <sheets>
-    <sheet name="14-06" sheetId="1" r:id="rId1"/>
+    <sheet name="15-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="41">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -119,6 +119,12 @@
     <t>KMIA</t>
   </si>
   <si>
+    <t>FFT</t>
+  </si>
+  <si>
+    <t>KDFW</t>
+  </si>
+  <si>
     <t>AAL</t>
   </si>
   <si>
@@ -131,15 +137,6 @@
     <t>KATL</t>
   </si>
   <si>
-    <t>TAG</t>
-  </si>
-  <si>
-    <t>MHRO</t>
-  </si>
-  <si>
-    <t>KDFW</t>
-  </si>
-  <si>
     <t>CMP</t>
   </si>
   <si>
@@ -159,9 +156,6 @@
   </si>
   <si>
     <t>KBOS</t>
-  </si>
-  <si>
-    <t>KOAK</t>
   </si>
   <si>
     <t>KEWR</t>
@@ -542,8 +536,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10682C0A-2E84-47FF-B848-AA473D428D2F}">
-  <dimension ref="A1:G142"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AAFB6C8-5491-4F9B-90EE-0958AB9F17D1}">
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -586,7 +580,7 @@
         <v>2203</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2" s="1">
         <v>5.2083333333333336E-2</v>
@@ -624,7 +618,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
@@ -669,61 +663,61 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1">
-        <v>0.22013888888888888</v>
-      </c>
-      <c r="D8">
-        <v>4313</v>
-      </c>
-      <c r="G8" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="E8">
+        <v>300</v>
+      </c>
+      <c r="F8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.21527777777777779</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1">
-        <v>0.22222222222222221</v>
+        <v>0.22013888888888888</v>
       </c>
       <c r="D9">
-        <v>575</v>
+        <v>4313</v>
       </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1">
-        <v>0.24444444444444444</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="D10">
-        <v>4309</v>
+        <v>575</v>
       </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C11" s="1">
-        <v>0.24652777777777779</v>
+        <v>0.24444444444444444</v>
       </c>
       <c r="D11">
-        <v>456</v>
+        <v>4309</v>
       </c>
       <c r="G11" s="1"/>
     </row>
@@ -732,41 +726,41 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" s="1">
         <v>0.24652777777777779</v>
       </c>
       <c r="D12">
-        <v>661</v>
+        <v>456</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="E13">
-        <v>3154</v>
-      </c>
-      <c r="F13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0.25</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.24652777777777779</v>
+      </c>
+      <c r="D13">
+        <v>661</v>
+      </c>
+      <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C14" s="1"/>
       <c r="E14">
-        <v>1467</v>
+        <v>3154</v>
       </c>
       <c r="F14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G14" s="1">
         <v>0.25</v>
@@ -774,46 +768,46 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15">
-        <v>3154</v>
+        <v>1467</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G15" s="1">
-        <v>0.25069444444444444</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="1">
-        <v>0.25694444444444442</v>
-      </c>
-      <c r="D16">
-        <v>433</v>
-      </c>
-      <c r="G16" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="E16">
+        <v>3154</v>
+      </c>
+      <c r="F16" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0.25069444444444444</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1">
         <v>0.25694444444444442</v>
       </c>
       <c r="D17">
-        <v>579</v>
+        <v>433</v>
       </c>
       <c r="G17" s="1"/>
     </row>
@@ -822,13 +816,13 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C18" s="1">
-        <v>0.26041666666666669</v>
+        <v>0.25694444444444442</v>
       </c>
       <c r="D18">
-        <v>529</v>
+        <v>579</v>
       </c>
       <c r="G18" s="1"/>
     </row>
@@ -837,13 +831,13 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1">
-        <v>0.2638888888888889</v>
+        <v>0.26041666666666669</v>
       </c>
       <c r="D19">
-        <v>314</v>
+        <v>529</v>
       </c>
       <c r="G19" s="1"/>
     </row>
@@ -852,13 +846,13 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" s="1">
-        <v>0.2673611111111111</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="D20">
-        <v>428</v>
+        <v>314</v>
       </c>
       <c r="G20" s="1"/>
     </row>
@@ -867,13 +861,13 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C21" s="1">
         <v>0.2673611111111111</v>
       </c>
       <c r="D21">
-        <v>626</v>
+        <v>428</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -882,13 +876,13 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C22" s="1">
-        <v>0.27083333333333331</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D22">
-        <v>316</v>
+        <v>626</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -897,13 +891,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D23">
-        <v>366</v>
+        <v>316</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -912,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D24">
-        <v>561</v>
+        <v>366</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -927,13 +921,13 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C25" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D25">
-        <v>591</v>
+        <v>561</v>
       </c>
       <c r="G25" s="1"/>
     </row>
@@ -942,13 +936,13 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D26">
-        <v>671</v>
+        <v>591</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -957,30 +951,30 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1">
-        <v>0.29166666666666669</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="D27">
-        <v>521</v>
+        <v>671</v>
       </c>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="1"/>
-      <c r="E28">
-        <v>4326</v>
-      </c>
-      <c r="F28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0.29791666666666666</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="D28">
+        <v>521</v>
+      </c>
+      <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -1021,7 +1015,7 @@
         <v>328</v>
       </c>
       <c r="F31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G31" s="1">
         <v>0.3125</v>
@@ -1044,17 +1038,17 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>310</v>
+        <v>884</v>
       </c>
       <c r="F33" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G33" s="1">
-        <v>0.31597222222222221</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1063,10 +1057,10 @@
       </c>
       <c r="C34" s="1"/>
       <c r="E34">
-        <v>440</v>
+        <v>310</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G34" s="1">
         <v>0.31597222222222221</v>
@@ -1078,10 +1072,10 @@
       </c>
       <c r="C35" s="1"/>
       <c r="E35">
-        <v>536</v>
+        <v>440</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G35" s="1">
         <v>0.31597222222222221</v>
@@ -1096,7 +1090,7 @@
         <v>444</v>
       </c>
       <c r="F36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G36" s="1">
         <v>0.32291666666666669</v>
@@ -1119,17 +1113,17 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C38" s="1"/>
       <c r="E38">
-        <v>4322</v>
+        <v>368</v>
       </c>
       <c r="F38" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G38" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -1138,10 +1132,10 @@
       </c>
       <c r="C39" s="1"/>
       <c r="E39">
-        <v>368</v>
+        <v>522</v>
       </c>
       <c r="F39" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="G39" s="1">
         <v>0.33333333333333331</v>
@@ -1151,29 +1145,29 @@
       <c r="A40" t="s">
         <v>9</v>
       </c>
-      <c r="C40" s="1"/>
-      <c r="E40">
-        <v>522</v>
-      </c>
-      <c r="F40" t="s">
-        <v>8</v>
-      </c>
-      <c r="G40" s="1">
-        <v>0.33333333333333331</v>
-      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="1">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="D40">
+        <v>309</v>
+      </c>
+      <c r="G40" s="1"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C41" s="1">
         <v>0.33680555555555558</v>
       </c>
       <c r="D41">
-        <v>309</v>
+        <v>601</v>
       </c>
       <c r="G41" s="1"/>
     </row>
@@ -1181,16 +1175,16 @@
       <c r="A42" t="s">
         <v>9</v>
       </c>
-      <c r="B42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="1">
+      <c r="C42" s="1"/>
+      <c r="E42">
+        <v>383</v>
+      </c>
+      <c r="F42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" s="1">
         <v>0.33680555555555558</v>
       </c>
-      <c r="D42">
-        <v>581</v>
-      </c>
-      <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -1198,13 +1192,13 @@
       </c>
       <c r="C43" s="1"/>
       <c r="E43">
-        <v>383</v>
+        <v>454</v>
       </c>
       <c r="F43" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G43" s="1">
-        <v>0.33680555555555558</v>
+        <v>0.34027777777777779</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1239,17 +1233,17 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>884</v>
+        <v>422</v>
       </c>
       <c r="F46" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="G46" s="1">
-        <v>0.35347222222222219</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1258,10 +1252,10 @@
       </c>
       <c r="C47" s="1"/>
       <c r="E47">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="F47" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G47" s="1">
         <v>0.36458333333333331</v>
@@ -1273,29 +1267,29 @@
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>430</v>
+        <v>524</v>
       </c>
       <c r="F48" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G48" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.38194444444444442</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>9</v>
       </c>
-      <c r="B49" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="1">
-        <v>0.37847222222222221</v>
-      </c>
-      <c r="D49">
-        <v>559</v>
-      </c>
-      <c r="G49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="E49">
+        <v>369</v>
+      </c>
+      <c r="F49" t="s">
+        <v>34</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0.3888888888888889</v>
+      </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -1303,164 +1297,164 @@
       </c>
       <c r="C50" s="1"/>
       <c r="E50">
-        <v>524</v>
+        <v>582</v>
       </c>
       <c r="F50" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G50" s="1">
-        <v>0.38194444444444442</v>
+        <v>0.39930555555555558</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>9</v>
       </c>
-      <c r="C51" s="1"/>
-      <c r="E51">
-        <v>369</v>
-      </c>
-      <c r="F51" t="s">
-        <v>35</v>
-      </c>
-      <c r="G51" s="1">
-        <v>0.3888888888888889</v>
-      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="D51">
+        <v>569</v>
+      </c>
+      <c r="G51" s="1"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" s="1"/>
-      <c r="E52">
-        <v>582</v>
-      </c>
-      <c r="F52" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="1">
-        <v>0.39930555555555558</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D52">
+        <v>342</v>
+      </c>
+      <c r="G52" s="1"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>9</v>
       </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" s="1">
-        <v>0.41319444444444442</v>
-      </c>
-      <c r="D53">
-        <v>569</v>
-      </c>
-      <c r="G53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="E53">
+        <v>609</v>
+      </c>
+      <c r="F53" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0.4236111111111111</v>
+      </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="1"/>
-      <c r="E54">
-        <v>392</v>
-      </c>
-      <c r="F54" t="s">
-        <v>19</v>
-      </c>
-      <c r="G54" s="1">
-        <v>0.41319444444444442</v>
-      </c>
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="1">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D54">
+        <v>455</v>
+      </c>
+      <c r="G54" s="1"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>9</v>
       </c>
-      <c r="C55" s="1"/>
-      <c r="E55">
-        <v>609</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="B55" t="s">
         <v>21</v>
       </c>
-      <c r="G55" s="1">
-        <v>0.4236111111111111</v>
-      </c>
+      <c r="C55" s="1">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="D55">
+        <v>318</v>
+      </c>
+      <c r="G55" s="1"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C56" s="1">
-        <v>0.42708333333333331</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D56">
-        <v>537</v>
+        <v>384</v>
       </c>
       <c r="G56" s="1"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>9</v>
-      </c>
-      <c r="B57" t="s">
-        <v>21</v>
-      </c>
-      <c r="C57" s="1">
-        <v>0.4548611111111111</v>
-      </c>
-      <c r="D57">
-        <v>318</v>
-      </c>
-      <c r="G57" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="C57" s="1"/>
+      <c r="E57">
+        <v>343</v>
+      </c>
+      <c r="F57" t="s">
+        <v>27</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0.46180555555555558</v>
+      </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B58" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C58" s="1">
-        <v>0.46180555555555558</v>
+        <v>0.47291666666666665</v>
       </c>
       <c r="D58">
-        <v>70</v>
+        <v>495</v>
       </c>
       <c r="G58" s="1"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C59" s="1">
-        <v>0.47291666666666665</v>
+        <v>0.47847222222222219</v>
       </c>
       <c r="D59">
-        <v>495</v>
+        <v>1194</v>
       </c>
       <c r="G59" s="1"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>7</v>
-      </c>
-      <c r="B60" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="1"/>
+      <c r="E60">
+        <v>584</v>
+      </c>
+      <c r="F60" t="s">
         <v>13</v>
       </c>
-      <c r="C60" s="1">
-        <v>0.47847222222222219</v>
-      </c>
-      <c r="D60">
-        <v>1194</v>
-      </c>
-      <c r="G60" s="1"/>
+      <c r="G60" s="1">
+        <v>0.49305555555555558</v>
+      </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
@@ -1468,13 +1462,13 @@
       </c>
       <c r="C61" s="1"/>
       <c r="E61">
-        <v>584</v>
+        <v>385</v>
       </c>
       <c r="F61" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G61" s="1">
-        <v>0.49305555555555558</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -1483,10 +1477,10 @@
       </c>
       <c r="C62" s="1"/>
       <c r="E62">
-        <v>71</v>
+        <v>424</v>
       </c>
       <c r="F62" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G62" s="1">
         <v>0.50347222222222221</v>
@@ -1494,183 +1488,183 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>9</v>
-      </c>
-      <c r="C63" s="1"/>
-      <c r="E63">
-        <v>424</v>
-      </c>
-      <c r="F63" t="s">
-        <v>27</v>
-      </c>
-      <c r="G63" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B63" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63" s="1">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D63">
+        <v>1441</v>
+      </c>
+      <c r="G63" s="1"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>7</v>
-      </c>
-      <c r="B64" t="s">
-        <v>27</v>
-      </c>
-      <c r="C64" s="1">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="D64">
-        <v>1441</v>
-      </c>
-      <c r="G64" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="E64">
+        <v>1508</v>
+      </c>
+      <c r="F64" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0.51597222222222228</v>
+      </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>26</v>
-      </c>
-      <c r="C65" s="1"/>
-      <c r="E65">
-        <v>1508</v>
-      </c>
-      <c r="F65" t="s">
-        <v>25</v>
-      </c>
-      <c r="G65" s="1">
-        <v>0.51597222222222228</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B65" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="1">
+        <v>0.5180555555555556</v>
+      </c>
+      <c r="D65">
+        <v>1910</v>
+      </c>
+      <c r="G65" s="1"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>28</v>
       </c>
       <c r="B66" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C66" s="1">
-        <v>0.5180555555555556</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="D66">
-        <v>1910</v>
+        <v>937</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B67" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C67" s="1">
-        <v>0.52083333333333337</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="D67">
-        <v>420</v>
+        <v>816</v>
       </c>
       <c r="G67" s="1"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>26</v>
-      </c>
-      <c r="B68" t="s">
-        <v>32</v>
-      </c>
-      <c r="C68" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D68">
-        <v>937</v>
-      </c>
-      <c r="G68" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="E68">
+        <v>1458</v>
+      </c>
+      <c r="F68" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0.55555555555555558</v>
+      </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>33</v>
-      </c>
-      <c r="B69" t="s">
-        <v>22</v>
-      </c>
-      <c r="C69" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D69">
-        <v>816</v>
-      </c>
-      <c r="G69" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C69" s="1"/>
+      <c r="E69">
+        <v>380</v>
+      </c>
+      <c r="F69" t="s">
+        <v>27</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0.57222222222222219</v>
+      </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C70" s="1"/>
       <c r="E70">
-        <v>421</v>
+        <v>1468</v>
       </c>
       <c r="F70" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G70" s="1">
-        <v>0.55208333333333337</v>
+        <v>0.57638888888888895</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C71" s="1"/>
       <c r="E71">
-        <v>1458</v>
+        <v>1978</v>
       </c>
       <c r="F71" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G71" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.57708333333333328</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C72" s="1"/>
       <c r="E72">
-        <v>380</v>
+        <v>871</v>
       </c>
       <c r="F72" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G72" s="1">
-        <v>0.57222222222222219</v>
+        <v>0.58194444444444449</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="1"/>
-      <c r="E73">
-        <v>1468</v>
-      </c>
-      <c r="F73" t="s">
-        <v>27</v>
-      </c>
-      <c r="G73" s="1">
-        <v>0.57638888888888895</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B73" t="s">
+        <v>17</v>
+      </c>
+      <c r="C73" s="1">
+        <v>0.59375</v>
+      </c>
+      <c r="D73">
+        <v>628</v>
+      </c>
+      <c r="G73" s="1"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>28</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="E74">
-        <v>1978</v>
-      </c>
-      <c r="F74" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" t="s">
         <v>29</v>
       </c>
-      <c r="G74" s="1">
-        <v>0.57708333333333328</v>
-      </c>
+      <c r="C74" s="1">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D74">
+        <v>1290</v>
+      </c>
+      <c r="G74" s="1"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
@@ -1678,27 +1672,27 @@
       </c>
       <c r="C75" s="1"/>
       <c r="E75">
-        <v>871</v>
+        <v>629</v>
       </c>
       <c r="F75" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G75" s="1">
-        <v>0.58194444444444449</v>
+        <v>0.64722222222222225</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C76" s="1">
-        <v>0.59375</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="D76">
-        <v>628</v>
+        <v>382</v>
       </c>
       <c r="G76" s="1"/>
     </row>
@@ -1706,76 +1700,76 @@
       <c r="A77" t="s">
         <v>7</v>
       </c>
-      <c r="B77" t="s">
-        <v>27</v>
-      </c>
-      <c r="C77" s="1">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D77">
-        <v>1290</v>
-      </c>
-      <c r="G77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="E77">
+        <v>1130</v>
+      </c>
+      <c r="F77" t="s">
+        <v>29</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C78" s="1">
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D78">
-        <v>557</v>
+        <v>367</v>
       </c>
       <c r="G78" s="1"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>9</v>
+      </c>
+      <c r="B79" t="s">
         <v>34</v>
       </c>
-      <c r="C79" s="1"/>
-      <c r="E79">
-        <v>629</v>
-      </c>
-      <c r="F79" t="s">
-        <v>17</v>
-      </c>
-      <c r="G79" s="1">
-        <v>0.64722222222222225</v>
-      </c>
+      <c r="C79" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D79">
+        <v>370</v>
+      </c>
+      <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C80" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D80">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>7</v>
-      </c>
-      <c r="C81" s="1"/>
-      <c r="E81">
-        <v>1130</v>
-      </c>
-      <c r="F81" t="s">
-        <v>27</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B81" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" s="1">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="D81">
+        <v>553</v>
+      </c>
+      <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
@@ -1785,10 +1779,10 @@
         <v>27</v>
       </c>
       <c r="C82" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.68055555555555558</v>
       </c>
       <c r="D82">
-        <v>367</v>
+        <v>441</v>
       </c>
       <c r="G82" s="1"/>
     </row>
@@ -1800,10 +1794,10 @@
         <v>35</v>
       </c>
       <c r="C83" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D83">
-        <v>370</v>
+        <v>423</v>
       </c>
       <c r="G83" s="1"/>
     </row>
@@ -1812,13 +1806,13 @@
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C84" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.6875</v>
       </c>
       <c r="D84">
-        <v>397</v>
+        <v>311</v>
       </c>
       <c r="G84" s="1"/>
     </row>
@@ -1827,13 +1821,13 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C85" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.6875</v>
       </c>
       <c r="D85">
-        <v>441</v>
+        <v>555</v>
       </c>
       <c r="G85" s="1"/>
     </row>
@@ -1842,13 +1836,13 @@
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C86" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.6875</v>
       </c>
       <c r="D86">
-        <v>423</v>
+        <v>610</v>
       </c>
       <c r="G86" s="1"/>
     </row>
@@ -1857,13 +1851,13 @@
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C87" s="1">
-        <v>0.6875</v>
+        <v>0.70138888888888884</v>
       </c>
       <c r="D87">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1871,61 +1865,61 @@
       <c r="A88" t="s">
         <v>9</v>
       </c>
-      <c r="B88" t="s">
-        <v>18</v>
-      </c>
-      <c r="C88" s="1">
-        <v>0.6875</v>
-      </c>
-      <c r="D88">
-        <v>555</v>
-      </c>
-      <c r="G88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="E88">
+        <v>326</v>
+      </c>
+      <c r="F88" t="s">
+        <v>10</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>9</v>
       </c>
-      <c r="B89" t="s">
-        <v>21</v>
-      </c>
-      <c r="C89" s="1">
-        <v>0.6875</v>
-      </c>
-      <c r="D89">
-        <v>610</v>
-      </c>
-      <c r="G89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="E89">
+        <v>560</v>
+      </c>
+      <c r="F89" t="s">
+        <v>24</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>9</v>
       </c>
-      <c r="B90" t="s">
-        <v>22</v>
-      </c>
-      <c r="C90" s="1">
-        <v>0.70138888888888884</v>
-      </c>
-      <c r="D90">
-        <v>322</v>
-      </c>
-      <c r="G90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="E90">
+        <v>313</v>
+      </c>
+      <c r="F90" t="s">
+        <v>21</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>12</v>
-      </c>
-      <c r="B91" t="s">
-        <v>27</v>
-      </c>
-      <c r="C91" s="1">
-        <v>0.72777777777777775</v>
-      </c>
-      <c r="D91">
-        <v>4327</v>
-      </c>
-      <c r="G91" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C91" s="1"/>
+      <c r="E91">
+        <v>450</v>
+      </c>
+      <c r="F91" t="s">
+        <v>19</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
@@ -1933,13 +1927,13 @@
       </c>
       <c r="C92" s="1"/>
       <c r="E92">
-        <v>326</v>
+        <v>520</v>
       </c>
       <c r="F92" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G92" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -1948,13 +1942,13 @@
       </c>
       <c r="C93" s="1"/>
       <c r="E93">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="F93" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G93" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.73611111111111116</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -1963,13 +1957,13 @@
       </c>
       <c r="C94" s="1"/>
       <c r="E94">
-        <v>313</v>
+        <v>448</v>
       </c>
       <c r="F94" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G94" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -1978,43 +1972,43 @@
       </c>
       <c r="C95" s="1"/>
       <c r="E95">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="F95" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G95" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>9</v>
-      </c>
-      <c r="C96" s="1"/>
-      <c r="E96">
-        <v>588</v>
-      </c>
-      <c r="F96" t="s">
+        <v>36</v>
+      </c>
+      <c r="B96" t="s">
         <v>18</v>
       </c>
-      <c r="G96" s="1">
-        <v>0.73611111111111116</v>
-      </c>
+      <c r="C96" s="1">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="D96">
+        <v>224</v>
+      </c>
+      <c r="G96" s="1"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C97" s="1"/>
       <c r="E97">
-        <v>448</v>
+        <v>4308</v>
       </c>
       <c r="F97" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G97" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -2023,103 +2017,103 @@
       </c>
       <c r="C98" s="1"/>
       <c r="E98">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="F98" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G98" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.76041666666666663</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>4308</v>
+        <v>660</v>
       </c>
       <c r="F99" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G99" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>9</v>
-      </c>
-      <c r="C100" s="1"/>
-      <c r="E100">
-        <v>528</v>
-      </c>
-      <c r="F100" t="s">
-        <v>8</v>
-      </c>
-      <c r="G100" s="1">
-        <v>0.76041666666666663</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B100" t="s">
+        <v>29</v>
+      </c>
+      <c r="C100" s="1">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="D100">
+        <v>742</v>
+      </c>
+      <c r="G100" s="1"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>37</v>
-      </c>
-      <c r="B101" t="s">
-        <v>18</v>
-      </c>
-      <c r="C101" s="1">
-        <v>0.76736111111111116</v>
-      </c>
-      <c r="D101">
-        <v>222</v>
-      </c>
-      <c r="G101" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C101" s="1"/>
+      <c r="E101">
+        <v>4312</v>
+      </c>
+      <c r="F101" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" s="1">
+        <v>0.79027777777777775</v>
+      </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>9</v>
       </c>
-      <c r="C102" s="1"/>
-      <c r="E102">
-        <v>660</v>
-      </c>
-      <c r="F102" t="s">
-        <v>16</v>
-      </c>
-      <c r="G102" s="1">
-        <v>0.77083333333333337</v>
-      </c>
+      <c r="B102" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" s="1">
+        <v>0.79513888888888884</v>
+      </c>
+      <c r="D102">
+        <v>431</v>
+      </c>
+      <c r="G102" s="1"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>7</v>
-      </c>
-      <c r="B103" t="s">
-        <v>27</v>
-      </c>
-      <c r="C103" s="1">
-        <v>0.79027777777777775</v>
-      </c>
-      <c r="D103">
-        <v>742</v>
-      </c>
-      <c r="G103" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C103" s="1"/>
+      <c r="E103">
+        <v>670</v>
+      </c>
+      <c r="F103" t="s">
+        <v>16</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0.80555555555555558</v>
+      </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>4312</v>
+        <v>224</v>
       </c>
       <c r="F104" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="G104" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.80902777777777779</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -2127,13 +2121,13 @@
         <v>9</v>
       </c>
       <c r="B105" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C105" s="1">
-        <v>0.79513888888888884</v>
+        <v>0.81944444444444442</v>
       </c>
       <c r="D105">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="G105" s="1"/>
     </row>
@@ -2141,59 +2135,59 @@
       <c r="A106" t="s">
         <v>9</v>
       </c>
-      <c r="C106" s="1"/>
-      <c r="E106">
-        <v>670</v>
-      </c>
-      <c r="F106" t="s">
-        <v>16</v>
-      </c>
-      <c r="G106" s="1">
-        <v>0.80555555555555558</v>
-      </c>
+      <c r="B106" t="s">
+        <v>37</v>
+      </c>
+      <c r="C106" s="1">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D106">
+        <v>329</v>
+      </c>
+      <c r="G106" s="1"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B107" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C107" s="1">
-        <v>0.81944444444444442</v>
+        <v>0.82430555555555551</v>
       </c>
       <c r="D107">
-        <v>425</v>
+        <v>2657</v>
       </c>
       <c r="G107" s="1"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B108" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C108" s="1">
-        <v>0.82291666666666663</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="D108">
-        <v>329</v>
+        <v>2657</v>
       </c>
       <c r="G108" s="1"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B109" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C109" s="1">
-        <v>0.82430555555555551</v>
+        <v>0.82638888888888884</v>
       </c>
       <c r="D109">
-        <v>2657</v>
+        <v>523</v>
       </c>
       <c r="G109" s="1"/>
     </row>
@@ -2202,43 +2196,43 @@
         <v>9</v>
       </c>
       <c r="B110" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C110" s="1">
-        <v>0.82638888888888884</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D110">
-        <v>523</v>
+        <v>583</v>
       </c>
       <c r="G110" s="1"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>37</v>
-      </c>
-      <c r="C111" s="1"/>
-      <c r="E111">
-        <v>222</v>
-      </c>
-      <c r="F111" t="s">
-        <v>42</v>
-      </c>
-      <c r="G111" s="1">
-        <v>0.82986111111111116</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B111" t="s">
+        <v>10</v>
+      </c>
+      <c r="C111" s="1">
+        <v>0.84375</v>
+      </c>
+      <c r="D111">
+        <v>325</v>
+      </c>
+      <c r="G111" s="1"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>9</v>
       </c>
       <c r="B112" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C112" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.84375</v>
       </c>
       <c r="D112">
-        <v>583</v>
+        <v>445</v>
       </c>
       <c r="G112" s="1"/>
     </row>
@@ -2246,119 +2240,119 @@
       <c r="A113" t="s">
         <v>9</v>
       </c>
-      <c r="B113" t="s">
-        <v>10</v>
-      </c>
-      <c r="C113" s="1">
-        <v>0.84375</v>
-      </c>
-      <c r="D113">
-        <v>325</v>
-      </c>
-      <c r="G113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="E113">
+        <v>590</v>
+      </c>
+      <c r="F113" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="C114" s="1">
-        <v>0.84375</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D114">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="G114" s="1"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B115" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C115" s="1">
-        <v>0.85069444444444442</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D115">
-        <v>393</v>
+        <v>881</v>
       </c>
       <c r="G115" s="1"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>9</v>
-      </c>
-      <c r="C116" s="1"/>
-      <c r="E116">
-        <v>590</v>
-      </c>
-      <c r="F116" t="s">
-        <v>13</v>
-      </c>
-      <c r="G116" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B116" t="s">
+        <v>29</v>
+      </c>
+      <c r="C116" s="1">
+        <v>0.86736111111111114</v>
+      </c>
+      <c r="D116">
+        <v>1461</v>
+      </c>
+      <c r="G116" s="1"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>9</v>
       </c>
       <c r="B117" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C117" s="1">
-        <v>0.85416666666666663</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D117">
-        <v>449</v>
+        <v>563</v>
       </c>
       <c r="G117" s="1"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B118" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C118" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.875</v>
       </c>
       <c r="D118">
-        <v>881</v>
+        <v>535</v>
       </c>
       <c r="G118" s="1"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B119" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C119" s="1">
-        <v>0.86111111111111116</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D119">
-        <v>4323</v>
+        <v>312</v>
       </c>
       <c r="G119" s="1"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B120" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C120" s="1">
-        <v>0.86736111111111114</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D120">
-        <v>1461</v>
+        <v>525</v>
       </c>
       <c r="G120" s="1"/>
     </row>
@@ -2367,28 +2361,28 @@
         <v>9</v>
       </c>
       <c r="B121" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C121" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D121">
-        <v>563</v>
+        <v>589</v>
       </c>
       <c r="G121" s="1"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C122" s="1">
-        <v>0.875</v>
+        <v>0.89930555555555547</v>
       </c>
       <c r="D122">
-        <v>535</v>
+        <v>1425</v>
       </c>
       <c r="G122" s="1"/>
     </row>
@@ -2397,13 +2391,13 @@
         <v>9</v>
       </c>
       <c r="B123" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C123" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.91319444444444442</v>
       </c>
       <c r="D123">
-        <v>312</v>
+        <v>585</v>
       </c>
       <c r="G123" s="1"/>
     </row>
@@ -2411,61 +2405,61 @@
       <c r="A124" t="s">
         <v>9</v>
       </c>
-      <c r="B124" t="s">
-        <v>8</v>
-      </c>
-      <c r="C124" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D124">
-        <v>525</v>
-      </c>
-      <c r="G124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="E124">
+        <v>315</v>
+      </c>
+      <c r="F124" t="s">
+        <v>19</v>
+      </c>
+      <c r="G124" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>9</v>
       </c>
-      <c r="B125" t="s">
-        <v>18</v>
-      </c>
-      <c r="C125" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D125">
-        <v>589</v>
-      </c>
-      <c r="G125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="E125">
+        <v>365</v>
+      </c>
+      <c r="F125" t="s">
+        <v>23</v>
+      </c>
+      <c r="G125" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>7</v>
-      </c>
-      <c r="B126" t="s">
-        <v>41</v>
-      </c>
-      <c r="C126" s="1">
-        <v>0.89930555555555547</v>
-      </c>
-      <c r="D126">
-        <v>1425</v>
-      </c>
-      <c r="G126" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C126" s="1"/>
+      <c r="E126">
+        <v>580</v>
+      </c>
+      <c r="F126" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>9</v>
       </c>
-      <c r="B127" t="s">
-        <v>13</v>
-      </c>
-      <c r="C127" s="1">
-        <v>0.91319444444444442</v>
-      </c>
-      <c r="D127">
-        <v>585</v>
-      </c>
-      <c r="G127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="E127">
+        <v>429</v>
+      </c>
+      <c r="F127" t="s">
+        <v>20</v>
+      </c>
+      <c r="G127" s="1">
+        <v>0.92708333333333337</v>
+      </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
@@ -2473,13 +2467,13 @@
       </c>
       <c r="C128" s="1"/>
       <c r="E128">
-        <v>315</v>
+        <v>578</v>
       </c>
       <c r="F128" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G128" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.93055555555555558</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -2488,13 +2482,13 @@
       </c>
       <c r="C129" s="1"/>
       <c r="E129">
-        <v>365</v>
+        <v>627</v>
       </c>
       <c r="F129" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G129" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.93402777777777779</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -2503,13 +2497,13 @@
       </c>
       <c r="C130" s="1"/>
       <c r="E130">
-        <v>600</v>
+        <v>574</v>
       </c>
       <c r="F130" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G130" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -2518,13 +2512,13 @@
       </c>
       <c r="C131" s="1"/>
       <c r="E131">
-        <v>429</v>
+        <v>568</v>
       </c>
       <c r="F131" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G131" s="1">
-        <v>0.92708333333333337</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -2533,43 +2527,43 @@
       </c>
       <c r="C132" s="1"/>
       <c r="E132">
-        <v>578</v>
+        <v>452</v>
       </c>
       <c r="F132" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G132" s="1">
-        <v>0.93055555555555558</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C133" s="1"/>
       <c r="E133">
-        <v>627</v>
+        <v>339</v>
       </c>
       <c r="F133" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="G133" s="1">
-        <v>0.93402777777777779</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C134" s="1"/>
       <c r="E134">
-        <v>574</v>
+        <v>4336</v>
       </c>
       <c r="F134" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="G134" s="1">
-        <v>0.9375</v>
+        <v>0.9506944444444444</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -2578,13 +2572,13 @@
       </c>
       <c r="C135" s="1"/>
       <c r="E135">
-        <v>568</v>
+        <v>317</v>
       </c>
       <c r="F135" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G135" s="1">
-        <v>0.94097222222222221</v>
+        <v>0.95486111111111116</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -2593,28 +2587,28 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="F136" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G136" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>339</v>
+        <v>457</v>
       </c>
       <c r="F137" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="G137" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -2623,74 +2617,29 @@
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>317</v>
+        <v>552</v>
       </c>
       <c r="F138" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G138" s="1">
-        <v>0.95486111111111116</v>
+        <v>0.97222222222222221</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>9</v>
-      </c>
-      <c r="C139" s="1"/>
-      <c r="E139">
-        <v>457</v>
-      </c>
-      <c r="F139" t="s">
-        <v>15</v>
-      </c>
-      <c r="G139" s="1">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>9</v>
-      </c>
-      <c r="C140" s="1"/>
-      <c r="E140">
-        <v>552</v>
-      </c>
-      <c r="F140" t="s">
-        <v>18</v>
-      </c>
-      <c r="G140" s="1">
-        <v>0.97222222222222221</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>9</v>
-      </c>
-      <c r="B141" t="s">
-        <v>42</v>
-      </c>
-      <c r="C141" s="1">
-        <v>0.97569444444444442</v>
-      </c>
-      <c r="D141">
-        <v>301</v>
-      </c>
-      <c r="G141" s="1"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>33</v>
-      </c>
-      <c r="B142" t="s">
+        <v>32</v>
+      </c>
+      <c r="B139" t="s">
         <v>22</v>
       </c>
-      <c r="C142" s="1">
+      <c r="C139" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D142">
+      <c r="D139">
         <v>878</v>
       </c>
-      <c r="G142" s="1"/>
+      <c r="G139" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF77CB06-0748-4CF9-8BB3-CEEAD16A21ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D41FC701-2413-4E14-B1E4-36D8C2B09189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{33D45D58-5545-4CAC-93DA-EB063451B6E5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A4FB302A-4D4C-4C22-B985-C9CF4D20257B}"/>
   </bookViews>
   <sheets>
-    <sheet name="15-06" sheetId="1" r:id="rId1"/>
+    <sheet name="16-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="42">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,9 +83,15 @@
     <t>KIAD</t>
   </si>
   <si>
+    <t>KONT</t>
+  </si>
+  <si>
     <t>MHLM</t>
   </si>
   <si>
+    <t>LEMD</t>
+  </si>
+  <si>
     <t>SEQM</t>
   </si>
   <si>
@@ -116,27 +122,27 @@
     <t>KSFO</t>
   </si>
   <si>
+    <t>KEWR</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
     <t>KMIA</t>
   </si>
   <si>
-    <t>FFT</t>
+    <t>KIAH</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>KATL</t>
   </si>
   <si>
     <t>KDFW</t>
   </si>
   <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>KIAH</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>KATL</t>
-  </si>
-  <si>
     <t>CMP</t>
   </si>
   <si>
@@ -146,22 +152,19 @@
     <t>SKRG</t>
   </si>
   <si>
-    <t>KMCO</t>
+    <t>MMUN</t>
   </si>
   <si>
     <t>IBE</t>
   </si>
   <si>
-    <t>CYUL</t>
-  </si>
-  <si>
     <t>KBOS</t>
   </si>
   <si>
-    <t>KEWR</t>
-  </si>
-  <si>
-    <t>LEMD</t>
+    <t>KORD</t>
+  </si>
+  <si>
+    <t>KLAS</t>
   </si>
 </sst>
 </file>
@@ -536,8 +539,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AAFB6C8-5491-4F9B-90EE-0958AB9F17D1}">
-  <dimension ref="A1:G139"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8EC2223-7985-4DE5-8F00-2BA28A92B126}">
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -580,7 +583,7 @@
         <v>2203</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2" s="1">
         <v>5.2083333333333336E-2</v>
@@ -618,14 +621,14 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
         <v>879</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5" s="1">
         <v>0.20347222222222219</v>
@@ -670,7 +673,7 @@
         <v>300</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G8" s="1">
         <v>0.21527777777777779</v>
@@ -702,22 +705,22 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D10">
-        <v>575</v>
+        <v>531</v>
       </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C11" s="1">
-        <v>0.24444444444444444</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="D11">
-        <v>4309</v>
+        <v>575</v>
       </c>
       <c r="G11" s="1"/>
     </row>
@@ -726,60 +729,60 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1">
-        <v>0.24652777777777779</v>
+        <v>0.22916666666666666</v>
       </c>
       <c r="D12">
-        <v>456</v>
+        <v>301</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C13" s="1">
-        <v>0.24652777777777779</v>
+        <v>0.24444444444444444</v>
       </c>
       <c r="D13">
-        <v>661</v>
+        <v>4309</v>
       </c>
       <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="E14">
-        <v>3154</v>
-      </c>
-      <c r="F14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0.25</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.24652777777777779</v>
+      </c>
+      <c r="D14">
+        <v>456</v>
+      </c>
+      <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="E15">
-        <v>1467</v>
-      </c>
-      <c r="F15" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0.25</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.24652777777777779</v>
+      </c>
+      <c r="D15">
+        <v>661</v>
+      </c>
+      <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -790,54 +793,54 @@
         <v>3154</v>
       </c>
       <c r="F16" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G16" s="1">
-        <v>0.25069444444444444</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="1">
-        <v>0.25694444444444442</v>
-      </c>
-      <c r="D17">
-        <v>433</v>
-      </c>
-      <c r="G17" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="E17">
+        <v>1467</v>
+      </c>
+      <c r="F17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="1">
-        <v>0.25694444444444442</v>
-      </c>
-      <c r="D18">
-        <v>579</v>
-      </c>
-      <c r="G18" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="E18">
+        <v>3154</v>
+      </c>
+      <c r="F18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.25069444444444444</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1">
-        <v>0.26041666666666669</v>
+        <v>0.25694444444444442</v>
       </c>
       <c r="D19">
-        <v>529</v>
+        <v>433</v>
       </c>
       <c r="G19" s="1"/>
     </row>
@@ -846,13 +849,13 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" s="1">
-        <v>0.2638888888888889</v>
+        <v>0.25694444444444442</v>
       </c>
       <c r="D20">
-        <v>314</v>
+        <v>579</v>
       </c>
       <c r="G20" s="1"/>
     </row>
@@ -861,13 +864,13 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C21" s="1">
-        <v>0.2673611111111111</v>
+        <v>0.26041666666666669</v>
       </c>
       <c r="D21">
-        <v>428</v>
+        <v>529</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -879,10 +882,10 @@
         <v>21</v>
       </c>
       <c r="C22" s="1">
-        <v>0.2673611111111111</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="D22">
-        <v>626</v>
+        <v>314</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -894,10 +897,10 @@
         <v>22</v>
       </c>
       <c r="C23" s="1">
-        <v>0.27083333333333331</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D23">
-        <v>316</v>
+        <v>428</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -909,10 +912,10 @@
         <v>23</v>
       </c>
       <c r="C24" s="1">
-        <v>0.27083333333333331</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D24">
-        <v>366</v>
+        <v>626</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -927,7 +930,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D25">
-        <v>561</v>
+        <v>316</v>
       </c>
       <c r="G25" s="1"/>
     </row>
@@ -936,13 +939,13 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C26" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D26">
-        <v>591</v>
+        <v>366</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -951,13 +954,13 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C27" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D27">
-        <v>671</v>
+        <v>561</v>
       </c>
       <c r="G27" s="1"/>
     </row>
@@ -966,13 +969,13 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C28" s="1">
-        <v>0.29166666666666669</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="D28">
-        <v>521</v>
+        <v>591</v>
       </c>
       <c r="G28" s="1"/>
     </row>
@@ -980,45 +983,45 @@
       <c r="A29" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="E29">
-        <v>319</v>
-      </c>
-      <c r="F29" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0.3125</v>
-      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="D29">
+        <v>671</v>
+      </c>
+      <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="1"/>
-      <c r="E30">
-        <v>323</v>
-      </c>
-      <c r="F30" t="s">
-        <v>22</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0.3125</v>
-      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="D30">
+        <v>521</v>
+      </c>
+      <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>328</v>
+        <v>3154</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G31" s="1">
-        <v>0.3125</v>
+        <v>0.29236111111111113</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1027,10 +1030,10 @@
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>396</v>
+        <v>319</v>
       </c>
       <c r="F32" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G32" s="1">
         <v>0.3125</v>
@@ -1038,14 +1041,14 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>884</v>
+        <v>323</v>
       </c>
       <c r="F33" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G33" s="1">
         <v>0.3125</v>
@@ -1057,13 +1060,13 @@
       </c>
       <c r="C34" s="1"/>
       <c r="E34">
-        <v>310</v>
+        <v>396</v>
       </c>
       <c r="F34" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G34" s="1">
-        <v>0.31597222222222221</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1072,10 +1075,10 @@
       </c>
       <c r="C35" s="1"/>
       <c r="E35">
-        <v>440</v>
+        <v>310</v>
       </c>
       <c r="F35" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G35" s="1">
         <v>0.31597222222222221</v>
@@ -1087,13 +1090,13 @@
       </c>
       <c r="C36" s="1"/>
       <c r="E36">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="F36" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G36" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.31597222222222221</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1102,29 +1105,29 @@
       </c>
       <c r="C37" s="1"/>
       <c r="E37">
-        <v>562</v>
+        <v>536</v>
       </c>
       <c r="F37" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G37" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.31597222222222221</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="E38">
-        <v>368</v>
-      </c>
-      <c r="F38" t="s">
-        <v>29</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0.33333333333333331</v>
-      </c>
+      <c r="B38" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="D38">
+        <v>321</v>
+      </c>
+      <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
@@ -1132,44 +1135,44 @@
       </c>
       <c r="C39" s="1"/>
       <c r="E39">
-        <v>522</v>
+        <v>444</v>
       </c>
       <c r="F39" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="G39" s="1">
-        <v>0.33333333333333331</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>9</v>
       </c>
-      <c r="B40" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D40">
-        <v>309</v>
-      </c>
-      <c r="G40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="E40">
+        <v>562</v>
+      </c>
+      <c r="F40" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0.32291666666666669</v>
+      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>9</v>
       </c>
-      <c r="B41" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D41">
-        <v>601</v>
-      </c>
-      <c r="G41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="E41">
+        <v>368</v>
+      </c>
+      <c r="F41" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0.33333333333333331</v>
+      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
@@ -1177,29 +1180,29 @@
       </c>
       <c r="C42" s="1"/>
       <c r="E42">
-        <v>383</v>
+        <v>522</v>
       </c>
       <c r="F42" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G42" s="1">
-        <v>0.33680555555555558</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="C43" s="1"/>
-      <c r="E43">
-        <v>454</v>
-      </c>
-      <c r="F43" t="s">
-        <v>11</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0.34027777777777779</v>
-      </c>
+      <c r="B43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="D43">
+        <v>581</v>
+      </c>
+      <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -1207,13 +1210,13 @@
       </c>
       <c r="C44" s="1"/>
       <c r="E44">
-        <v>324</v>
+        <v>383</v>
       </c>
       <c r="F44" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G44" s="1">
-        <v>0.34375</v>
+        <v>0.33680555555555558</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1222,13 +1225,13 @@
       </c>
       <c r="C45" s="1"/>
       <c r="E45">
-        <v>554</v>
+        <v>454</v>
       </c>
       <c r="F45" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G45" s="1">
-        <v>0.34375</v>
+        <v>0.34027777777777779</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1237,13 +1240,13 @@
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>422</v>
+        <v>324</v>
       </c>
       <c r="F46" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G46" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1252,28 +1255,28 @@
       </c>
       <c r="C47" s="1"/>
       <c r="E47">
-        <v>430</v>
+        <v>572</v>
       </c>
       <c r="F47" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G47" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>524</v>
+        <v>884</v>
       </c>
       <c r="F48" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="G48" s="1">
-        <v>0.38194444444444442</v>
+        <v>0.35347222222222219</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1282,59 +1285,59 @@
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>369</v>
+        <v>430</v>
       </c>
       <c r="F49" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="G49" s="1">
-        <v>0.3888888888888889</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>9</v>
       </c>
-      <c r="C50" s="1"/>
-      <c r="E50">
-        <v>582</v>
-      </c>
-      <c r="F50" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="1">
-        <v>0.39930555555555558</v>
-      </c>
+      <c r="B50" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="D50">
+        <v>451</v>
+      </c>
+      <c r="G50" s="1"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>9</v>
       </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" s="1">
-        <v>0.41319444444444442</v>
-      </c>
-      <c r="D51">
-        <v>569</v>
-      </c>
-      <c r="G51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="E51">
+        <v>526</v>
+      </c>
+      <c r="F51" t="s">
+        <v>41</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.375</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>26</v>
-      </c>
-      <c r="B52" t="s">
-        <v>27</v>
-      </c>
-      <c r="C52" s="1">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D52">
-        <v>342</v>
-      </c>
-      <c r="G52" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="E52">
+        <v>369</v>
+      </c>
+      <c r="F52" t="s">
+        <v>36</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.3888888888888889</v>
+      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -1342,27 +1345,27 @@
       </c>
       <c r="C53" s="1"/>
       <c r="E53">
-        <v>609</v>
+        <v>582</v>
       </c>
       <c r="F53" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G53" s="1">
-        <v>0.4236111111111111</v>
+        <v>0.39930555555555558</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C54" s="1">
-        <v>0.44791666666666669</v>
+        <v>0.40902777777777777</v>
       </c>
       <c r="D54">
-        <v>455</v>
+        <v>4337</v>
       </c>
       <c r="G54" s="1"/>
     </row>
@@ -1371,13 +1374,13 @@
         <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C55" s="1">
-        <v>0.4548611111111111</v>
+        <v>0.41319444444444442</v>
       </c>
       <c r="D55">
-        <v>318</v>
+        <v>569</v>
       </c>
       <c r="G55" s="1"/>
     </row>
@@ -1385,59 +1388,59 @@
       <c r="A56" t="s">
         <v>9</v>
       </c>
-      <c r="B56" t="s">
-        <v>23</v>
-      </c>
-      <c r="C56" s="1">
-        <v>0.46180555555555558</v>
-      </c>
-      <c r="D56">
-        <v>384</v>
-      </c>
-      <c r="G56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="E56">
+        <v>392</v>
+      </c>
+      <c r="F56" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0.41319444444444442</v>
+      </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C57" s="1"/>
       <c r="E57">
-        <v>343</v>
+        <v>408</v>
       </c>
       <c r="F57" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G57" s="1">
-        <v>0.46180555555555558</v>
+        <v>0.41319444444444442</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>28</v>
-      </c>
-      <c r="B58" t="s">
-        <v>25</v>
-      </c>
-      <c r="C58" s="1">
-        <v>0.47291666666666665</v>
-      </c>
-      <c r="D58">
-        <v>495</v>
-      </c>
-      <c r="G58" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C58" s="1"/>
+      <c r="E58">
+        <v>609</v>
+      </c>
+      <c r="F58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0.4236111111111111</v>
+      </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C59" s="1">
-        <v>0.47847222222222219</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="D59">
-        <v>1194</v>
+        <v>537</v>
       </c>
       <c r="G59" s="1"/>
     </row>
@@ -1445,59 +1448,59 @@
       <c r="A60" t="s">
         <v>9</v>
       </c>
-      <c r="C60" s="1"/>
-      <c r="E60">
-        <v>584</v>
-      </c>
-      <c r="F60" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" s="1">
-        <v>0.49305555555555558</v>
-      </c>
+      <c r="B60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="1">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D60">
+        <v>455</v>
+      </c>
+      <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>9</v>
       </c>
-      <c r="C61" s="1"/>
-      <c r="E61">
-        <v>385</v>
-      </c>
-      <c r="F61" t="s">
-        <v>23</v>
-      </c>
-      <c r="G61" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+      <c r="B61" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="1">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="D61">
+        <v>573</v>
+      </c>
+      <c r="G61" s="1"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>9</v>
       </c>
-      <c r="C62" s="1"/>
-      <c r="E62">
-        <v>424</v>
-      </c>
-      <c r="F62" t="s">
-        <v>29</v>
-      </c>
-      <c r="G62" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+      <c r="B62" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62" s="1">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="D62">
+        <v>318</v>
+      </c>
+      <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B63" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C63" s="1">
-        <v>0.51041666666666663</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D63">
-        <v>1441</v>
+        <v>384</v>
       </c>
       <c r="G63" s="1"/>
     </row>
@@ -1505,301 +1508,301 @@
       <c r="A64" t="s">
         <v>28</v>
       </c>
-      <c r="C64" s="1"/>
-      <c r="E64">
-        <v>1508</v>
-      </c>
-      <c r="F64" t="s">
-        <v>25</v>
-      </c>
-      <c r="G64" s="1">
-        <v>0.51597222222222228</v>
-      </c>
+      <c r="B64" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" s="1">
+        <v>0.47291666666666665</v>
+      </c>
+      <c r="D64">
+        <v>495</v>
+      </c>
+      <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C65" s="1">
-        <v>0.5180555555555556</v>
+        <v>0.47847222222222219</v>
       </c>
       <c r="D65">
-        <v>1910</v>
+        <v>1194</v>
       </c>
       <c r="G65" s="1"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>28</v>
-      </c>
-      <c r="B66" t="s">
-        <v>27</v>
-      </c>
-      <c r="C66" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D66">
-        <v>937</v>
-      </c>
-      <c r="G66" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="E66">
+        <v>584</v>
+      </c>
+      <c r="F66" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0.49305555555555558</v>
+      </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>32</v>
-      </c>
-      <c r="B67" t="s">
-        <v>22</v>
-      </c>
-      <c r="C67" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D67">
-        <v>816</v>
-      </c>
-      <c r="G67" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C67" s="1"/>
+      <c r="E67">
+        <v>434</v>
+      </c>
+      <c r="F67" t="s">
+        <v>37</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0.49652777777777779</v>
+      </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C68" s="1"/>
       <c r="E68">
-        <v>1458</v>
+        <v>385</v>
       </c>
       <c r="F68" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G68" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C69" s="1"/>
       <c r="E69">
-        <v>380</v>
+        <v>424</v>
       </c>
       <c r="F69" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G69" s="1">
-        <v>0.57222222222222219</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C70" s="1"/>
       <c r="E70">
-        <v>1468</v>
+        <v>442</v>
       </c>
       <c r="F70" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G70" s="1">
-        <v>0.57638888888888895</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" t="s">
         <v>30</v>
       </c>
-      <c r="C71" s="1"/>
-      <c r="E71">
-        <v>1978</v>
-      </c>
-      <c r="F71" t="s">
-        <v>31</v>
-      </c>
-      <c r="G71" s="1">
-        <v>0.57708333333333328</v>
-      </c>
+      <c r="C71" s="1">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D71">
+        <v>1441</v>
+      </c>
+      <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C72" s="1"/>
       <c r="E72">
-        <v>871</v>
+        <v>1508</v>
       </c>
       <c r="F72" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G72" s="1">
-        <v>0.58194444444444449</v>
+        <v>0.51597222222222228</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B73" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C73" s="1">
-        <v>0.59375</v>
+        <v>0.5180555555555556</v>
       </c>
       <c r="D73">
-        <v>628</v>
+        <v>1910</v>
       </c>
       <c r="G73" s="1"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B74" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C74" s="1">
-        <v>0.60416666666666663</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="D74">
-        <v>1290</v>
+        <v>937</v>
       </c>
       <c r="G74" s="1"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>33</v>
-      </c>
-      <c r="C75" s="1"/>
-      <c r="E75">
-        <v>629</v>
-      </c>
-      <c r="F75" t="s">
-        <v>17</v>
-      </c>
-      <c r="G75" s="1">
-        <v>0.64722222222222225</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B75" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D75">
+        <v>816</v>
+      </c>
+      <c r="G75" s="1"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>9</v>
-      </c>
-      <c r="B76" t="s">
-        <v>23</v>
-      </c>
-      <c r="C76" s="1">
-        <v>0.65277777777777779</v>
-      </c>
-      <c r="D76">
-        <v>382</v>
-      </c>
-      <c r="G76" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="E76">
+        <v>1458</v>
+      </c>
+      <c r="F76" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0.55555555555555558</v>
+      </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C77" s="1"/>
       <c r="E77">
-        <v>1130</v>
+        <v>380</v>
       </c>
       <c r="F77" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G77" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.57222222222222219</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>9</v>
-      </c>
-      <c r="B78" t="s">
-        <v>29</v>
-      </c>
-      <c r="C78" s="1">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D78">
-        <v>367</v>
-      </c>
-      <c r="G78" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="E78">
+        <v>1468</v>
+      </c>
+      <c r="F78" t="s">
+        <v>30</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0.57638888888888895</v>
+      </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>9</v>
-      </c>
-      <c r="B79" t="s">
-        <v>34</v>
-      </c>
-      <c r="C79" s="1">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D79">
-        <v>370</v>
-      </c>
-      <c r="G79" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="E79">
+        <v>1978</v>
+      </c>
+      <c r="F79" t="s">
+        <v>32</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0.57708333333333328</v>
+      </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>9</v>
-      </c>
-      <c r="B80" t="s">
-        <v>19</v>
-      </c>
-      <c r="C80" s="1">
-        <v>0.67361111111111116</v>
-      </c>
-      <c r="D80">
-        <v>397</v>
-      </c>
-      <c r="G80" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="E80">
+        <v>871</v>
+      </c>
+      <c r="F80" t="s">
+        <v>24</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0.58194444444444449</v>
+      </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B81" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C81" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.59236111111111112</v>
       </c>
       <c r="D81">
-        <v>553</v>
+        <v>628</v>
       </c>
       <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B82" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C82" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D82">
-        <v>441</v>
+        <v>1290</v>
       </c>
       <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>9</v>
-      </c>
-      <c r="B83" t="s">
         <v>35</v>
       </c>
-      <c r="C83" s="1">
-        <v>0.68402777777777779</v>
-      </c>
-      <c r="D83">
-        <v>423</v>
-      </c>
-      <c r="G83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="E83">
+        <v>629</v>
+      </c>
+      <c r="F83" t="s">
+        <v>19</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0.64722222222222225</v>
+      </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
@@ -1809,40 +1812,40 @@
         <v>25</v>
       </c>
       <c r="C84" s="1">
-        <v>0.6875</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="D84">
-        <v>311</v>
+        <v>382</v>
       </c>
       <c r="G84" s="1"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>9</v>
-      </c>
-      <c r="B85" t="s">
-        <v>18</v>
-      </c>
-      <c r="C85" s="1">
-        <v>0.6875</v>
-      </c>
-      <c r="D85">
-        <v>555</v>
-      </c>
-      <c r="G85" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C85" s="1"/>
+      <c r="E85">
+        <v>1130</v>
+      </c>
+      <c r="F85" t="s">
+        <v>30</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C86" s="1">
-        <v>0.6875</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D86">
-        <v>610</v>
+        <v>367</v>
       </c>
       <c r="G86" s="1"/>
     </row>
@@ -1851,13 +1854,13 @@
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C87" s="1">
-        <v>0.70138888888888884</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D87">
-        <v>322</v>
+        <v>370</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1865,106 +1868,106 @@
       <c r="A88" t="s">
         <v>9</v>
       </c>
-      <c r="C88" s="1"/>
-      <c r="E88">
-        <v>326</v>
-      </c>
-      <c r="F88" t="s">
-        <v>10</v>
-      </c>
-      <c r="G88" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+      <c r="B88" t="s">
+        <v>21</v>
+      </c>
+      <c r="C88" s="1">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="D88">
+        <v>397</v>
+      </c>
+      <c r="G88" s="1"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>9</v>
       </c>
-      <c r="C89" s="1"/>
-      <c r="E89">
-        <v>560</v>
-      </c>
-      <c r="F89" t="s">
-        <v>24</v>
-      </c>
-      <c r="G89" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+      <c r="B89" t="s">
+        <v>20</v>
+      </c>
+      <c r="C89" s="1">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="D89">
+        <v>553</v>
+      </c>
+      <c r="G89" s="1"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>9</v>
       </c>
-      <c r="C90" s="1"/>
-      <c r="E90">
-        <v>313</v>
-      </c>
-      <c r="F90" t="s">
-        <v>21</v>
-      </c>
-      <c r="G90" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+      <c r="B90" t="s">
+        <v>33</v>
+      </c>
+      <c r="C90" s="1">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="D90">
+        <v>441</v>
+      </c>
+      <c r="G90" s="1"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>9</v>
       </c>
-      <c r="C91" s="1"/>
-      <c r="E91">
-        <v>450</v>
-      </c>
-      <c r="F91" t="s">
-        <v>19</v>
-      </c>
-      <c r="G91" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+      <c r="B91" t="s">
+        <v>37</v>
+      </c>
+      <c r="C91" s="1">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="D91">
+        <v>435</v>
+      </c>
+      <c r="G91" s="1"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>9</v>
       </c>
-      <c r="C92" s="1"/>
-      <c r="E92">
-        <v>520</v>
-      </c>
-      <c r="F92" t="s">
-        <v>8</v>
-      </c>
-      <c r="G92" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+      <c r="B92" t="s">
+        <v>29</v>
+      </c>
+      <c r="C92" s="1">
+        <v>0.6875</v>
+      </c>
+      <c r="D92">
+        <v>311</v>
+      </c>
+      <c r="G92" s="1"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>9</v>
       </c>
-      <c r="C93" s="1"/>
-      <c r="E93">
-        <v>588</v>
-      </c>
-      <c r="F93" t="s">
-        <v>18</v>
-      </c>
-      <c r="G93" s="1">
-        <v>0.73611111111111116</v>
-      </c>
+      <c r="B93" t="s">
+        <v>23</v>
+      </c>
+      <c r="C93" s="1">
+        <v>0.6875</v>
+      </c>
+      <c r="D93">
+        <v>610</v>
+      </c>
+      <c r="G93" s="1"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>9</v>
       </c>
-      <c r="C94" s="1"/>
-      <c r="E94">
-        <v>448</v>
-      </c>
-      <c r="F94" t="s">
-        <v>11</v>
-      </c>
-      <c r="G94" s="1">
-        <v>0.74305555555555558</v>
-      </c>
+      <c r="B94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C94" s="1">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="D94">
+        <v>322</v>
+      </c>
+      <c r="G94" s="1"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
@@ -1972,43 +1975,43 @@
       </c>
       <c r="C95" s="1"/>
       <c r="E95">
-        <v>534</v>
+        <v>320</v>
       </c>
       <c r="F95" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G95" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.72222222222222221</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>36</v>
-      </c>
-      <c r="B96" t="s">
-        <v>18</v>
-      </c>
-      <c r="C96" s="1">
-        <v>0.74652777777777779</v>
-      </c>
-      <c r="D96">
-        <v>224</v>
-      </c>
-      <c r="G96" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C96" s="1"/>
+      <c r="E96">
+        <v>326</v>
+      </c>
+      <c r="F96" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C97" s="1"/>
       <c r="E97">
-        <v>4308</v>
+        <v>560</v>
       </c>
       <c r="F97" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="G97" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -2017,13 +2020,13 @@
       </c>
       <c r="C98" s="1"/>
       <c r="E98">
-        <v>528</v>
+        <v>313</v>
       </c>
       <c r="F98" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G98" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -2032,144 +2035,144 @@
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>660</v>
+        <v>520</v>
       </c>
       <c r="F99" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G99" s="1">
-        <v>0.77083333333333337</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>7</v>
-      </c>
-      <c r="B100" t="s">
-        <v>29</v>
-      </c>
-      <c r="C100" s="1">
-        <v>0.79027777777777775</v>
-      </c>
-      <c r="D100">
-        <v>742</v>
-      </c>
-      <c r="G100" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C100" s="1"/>
+      <c r="E100">
+        <v>530</v>
+      </c>
+      <c r="F100" t="s">
+        <v>14</v>
+      </c>
+      <c r="G100" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C101" s="1"/>
       <c r="E101">
-        <v>4312</v>
+        <v>588</v>
       </c>
       <c r="F101" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G101" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.73611111111111116</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>9</v>
       </c>
-      <c r="B102" t="s">
-        <v>17</v>
-      </c>
-      <c r="C102" s="1">
-        <v>0.79513888888888884</v>
-      </c>
-      <c r="D102">
-        <v>431</v>
-      </c>
-      <c r="G102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="E102">
+        <v>534</v>
+      </c>
+      <c r="F102" t="s">
+        <v>15</v>
+      </c>
+      <c r="G102" s="1">
+        <v>0.74305555555555558</v>
+      </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>9</v>
-      </c>
-      <c r="C103" s="1"/>
-      <c r="E103">
-        <v>670</v>
-      </c>
-      <c r="F103" t="s">
-        <v>16</v>
-      </c>
-      <c r="G103" s="1">
-        <v>0.80555555555555558</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B103" t="s">
+        <v>20</v>
+      </c>
+      <c r="C103" s="1">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="D103">
+        <v>222</v>
+      </c>
+      <c r="G103" s="1"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>224</v>
+        <v>4308</v>
       </c>
       <c r="F104" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G104" s="1">
-        <v>0.80902777777777779</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>9</v>
       </c>
-      <c r="B105" t="s">
-        <v>29</v>
-      </c>
-      <c r="C105" s="1">
-        <v>0.81944444444444442</v>
-      </c>
-      <c r="D105">
-        <v>425</v>
-      </c>
-      <c r="G105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="E105">
+        <v>528</v>
+      </c>
+      <c r="F105" t="s">
+        <v>8</v>
+      </c>
+      <c r="G105" s="1">
+        <v>0.76041666666666663</v>
+      </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>9</v>
       </c>
-      <c r="B106" t="s">
-        <v>37</v>
-      </c>
-      <c r="C106" s="1">
-        <v>0.82291666666666663</v>
-      </c>
-      <c r="D106">
-        <v>329</v>
-      </c>
-      <c r="G106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="E106">
+        <v>660</v>
+      </c>
+      <c r="F106" t="s">
+        <v>18</v>
+      </c>
+      <c r="G106" s="1">
+        <v>0.77083333333333337</v>
+      </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>28</v>
-      </c>
-      <c r="B107" t="s">
-        <v>25</v>
-      </c>
-      <c r="C107" s="1">
-        <v>0.82430555555555551</v>
-      </c>
-      <c r="D107">
-        <v>2657</v>
-      </c>
-      <c r="G107" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C107" s="1"/>
+      <c r="E107">
+        <v>558</v>
+      </c>
+      <c r="F107" t="s">
+        <v>26</v>
+      </c>
+      <c r="G107" s="1">
+        <v>0.77777777777777779</v>
+      </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>28</v>
       </c>
       <c r="B108" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C108" s="1">
-        <v>0.82499999999999996</v>
+        <v>0.77847222222222223</v>
       </c>
       <c r="D108">
         <v>2657</v>
@@ -2178,46 +2181,46 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B109" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C109" s="1">
-        <v>0.82638888888888884</v>
+        <v>0.79027777777777775</v>
       </c>
       <c r="D109">
-        <v>523</v>
+        <v>742</v>
       </c>
       <c r="G109" s="1"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>9</v>
-      </c>
-      <c r="B110" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" s="1"/>
+      <c r="E110">
+        <v>4312</v>
+      </c>
+      <c r="F110" t="s">
         <v>13</v>
       </c>
-      <c r="C110" s="1">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D110">
-        <v>583</v>
-      </c>
-      <c r="G110" s="1"/>
+      <c r="G110" s="1">
+        <v>0.79027777777777775</v>
+      </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C111" s="1">
-        <v>0.84375</v>
+        <v>0.79513888888888884</v>
       </c>
       <c r="D111">
-        <v>325</v>
+        <v>431</v>
       </c>
       <c r="G111" s="1"/>
     </row>
@@ -2225,74 +2228,74 @@
       <c r="A112" t="s">
         <v>9</v>
       </c>
-      <c r="B112" t="s">
-        <v>38</v>
-      </c>
-      <c r="C112" s="1">
-        <v>0.84375</v>
-      </c>
-      <c r="D112">
-        <v>445</v>
-      </c>
-      <c r="G112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="E112">
+        <v>670</v>
+      </c>
+      <c r="F112" t="s">
+        <v>18</v>
+      </c>
+      <c r="G112" s="1">
+        <v>0.80555555555555558</v>
+      </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C113" s="1"/>
       <c r="E113">
-        <v>590</v>
+        <v>222</v>
       </c>
       <c r="F113" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G113" s="1">
-        <v>0.85069444444444442</v>
+        <v>0.80902777777777779</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>9</v>
-      </c>
-      <c r="B114" t="s">
-        <v>11</v>
-      </c>
-      <c r="C114" s="1">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="D114">
-        <v>449</v>
-      </c>
-      <c r="G114" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C114" s="1"/>
+      <c r="E114">
+        <v>4300</v>
+      </c>
+      <c r="F114" t="s">
+        <v>19</v>
+      </c>
+      <c r="G114" s="1">
+        <v>0.81388888888888888</v>
+      </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C115" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.81944444444444442</v>
       </c>
       <c r="D115">
-        <v>881</v>
+        <v>425</v>
       </c>
       <c r="G115" s="1"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B116" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C116" s="1">
-        <v>0.86736111111111114</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D116">
-        <v>1461</v>
+        <v>583</v>
       </c>
       <c r="G116" s="1"/>
     </row>
@@ -2301,13 +2304,13 @@
         <v>9</v>
       </c>
       <c r="B117" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C117" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.84375</v>
       </c>
       <c r="D117">
-        <v>563</v>
+        <v>325</v>
       </c>
       <c r="G117" s="1"/>
     </row>
@@ -2316,13 +2319,13 @@
         <v>9</v>
       </c>
       <c r="B118" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C118" s="1">
-        <v>0.875</v>
+        <v>0.84375</v>
       </c>
       <c r="D118">
-        <v>535</v>
+        <v>445</v>
       </c>
       <c r="G118" s="1"/>
     </row>
@@ -2334,10 +2337,10 @@
         <v>21</v>
       </c>
       <c r="C119" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.85069444444444442</v>
       </c>
       <c r="D119">
-        <v>312</v>
+        <v>393</v>
       </c>
       <c r="G119" s="1"/>
     </row>
@@ -2345,59 +2348,59 @@
       <c r="A120" t="s">
         <v>9</v>
       </c>
-      <c r="B120" t="s">
-        <v>8</v>
-      </c>
-      <c r="C120" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D120">
-        <v>525</v>
-      </c>
-      <c r="G120" s="1"/>
+      <c r="C120" s="1"/>
+      <c r="E120">
+        <v>590</v>
+      </c>
+      <c r="F120" t="s">
+        <v>13</v>
+      </c>
+      <c r="G120" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B121" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C121" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D121">
-        <v>589</v>
+        <v>881</v>
       </c>
       <c r="G121" s="1"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="C122" s="1">
-        <v>0.89930555555555547</v>
+        <v>0.86111111111111116</v>
       </c>
       <c r="D122">
-        <v>1425</v>
+        <v>523</v>
       </c>
       <c r="G122" s="1"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C123" s="1">
-        <v>0.91319444444444442</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D123">
-        <v>585</v>
+        <v>1461</v>
       </c>
       <c r="G123" s="1"/>
     </row>
@@ -2405,165 +2408,165 @@
       <c r="A124" t="s">
         <v>9</v>
       </c>
-      <c r="C124" s="1"/>
-      <c r="E124">
-        <v>315</v>
-      </c>
-      <c r="F124" t="s">
-        <v>19</v>
-      </c>
-      <c r="G124" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B124" t="s">
+        <v>33</v>
+      </c>
+      <c r="C124" s="1">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="D124">
+        <v>443</v>
+      </c>
+      <c r="G124" s="1"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>9</v>
       </c>
-      <c r="C125" s="1"/>
-      <c r="E125">
-        <v>365</v>
-      </c>
-      <c r="F125" t="s">
-        <v>23</v>
-      </c>
-      <c r="G125" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B125" t="s">
+        <v>26</v>
+      </c>
+      <c r="C125" s="1">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="D125">
+        <v>563</v>
+      </c>
+      <c r="G125" s="1"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>9</v>
       </c>
-      <c r="C126" s="1"/>
-      <c r="E126">
-        <v>580</v>
-      </c>
-      <c r="F126" t="s">
-        <v>13</v>
-      </c>
-      <c r="G126" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B126" t="s">
+        <v>40</v>
+      </c>
+      <c r="C126" s="1">
+        <v>0.87152777777777779</v>
+      </c>
+      <c r="D126">
+        <v>409</v>
+      </c>
+      <c r="G126" s="1"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>9</v>
       </c>
-      <c r="C127" s="1"/>
-      <c r="E127">
-        <v>429</v>
-      </c>
-      <c r="F127" t="s">
-        <v>20</v>
-      </c>
-      <c r="G127" s="1">
-        <v>0.92708333333333337</v>
-      </c>
+      <c r="B127" t="s">
+        <v>41</v>
+      </c>
+      <c r="C127" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="D127">
+        <v>527</v>
+      </c>
+      <c r="G127" s="1"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>9</v>
       </c>
-      <c r="C128" s="1"/>
-      <c r="E128">
-        <v>578</v>
-      </c>
-      <c r="F128" t="s">
-        <v>18</v>
-      </c>
-      <c r="G128" s="1">
-        <v>0.93055555555555558</v>
-      </c>
+      <c r="B128" t="s">
+        <v>15</v>
+      </c>
+      <c r="C128" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="D128">
+        <v>535</v>
+      </c>
+      <c r="G128" s="1"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>9</v>
       </c>
-      <c r="C129" s="1"/>
-      <c r="E129">
-        <v>627</v>
-      </c>
-      <c r="F129" t="s">
-        <v>21</v>
-      </c>
-      <c r="G129" s="1">
-        <v>0.93402777777777779</v>
-      </c>
+      <c r="B129" t="s">
+        <v>23</v>
+      </c>
+      <c r="C129" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D129">
+        <v>312</v>
+      </c>
+      <c r="G129" s="1"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>9</v>
       </c>
-      <c r="C130" s="1"/>
-      <c r="E130">
-        <v>574</v>
-      </c>
-      <c r="F130" t="s">
-        <v>14</v>
-      </c>
-      <c r="G130" s="1">
-        <v>0.9375</v>
-      </c>
+      <c r="B130" t="s">
+        <v>20</v>
+      </c>
+      <c r="C130" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D130">
+        <v>589</v>
+      </c>
+      <c r="G130" s="1"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>9</v>
-      </c>
-      <c r="C131" s="1"/>
-      <c r="E131">
-        <v>568</v>
-      </c>
-      <c r="F131" t="s">
-        <v>16</v>
-      </c>
-      <c r="G131" s="1">
-        <v>0.94097222222222221</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B131" t="s">
+        <v>27</v>
+      </c>
+      <c r="C131" s="1">
+        <v>0.89930555555555547</v>
+      </c>
+      <c r="D131">
+        <v>1425</v>
+      </c>
+      <c r="G131" s="1"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>9</v>
       </c>
-      <c r="C132" s="1"/>
-      <c r="E132">
-        <v>452</v>
-      </c>
-      <c r="F132" t="s">
-        <v>11</v>
-      </c>
-      <c r="G132" s="1">
-        <v>0.94791666666666663</v>
-      </c>
+      <c r="B132" t="s">
+        <v>13</v>
+      </c>
+      <c r="C132" s="1">
+        <v>0.91319444444444442</v>
+      </c>
+      <c r="D132">
+        <v>585</v>
+      </c>
+      <c r="G132" s="1"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C133" s="1"/>
       <c r="E133">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="F133" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="G133" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C134" s="1"/>
       <c r="E134">
-        <v>4336</v>
+        <v>365</v>
       </c>
       <c r="F134" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G134" s="1">
-        <v>0.9506944444444444</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -2572,13 +2575,13 @@
       </c>
       <c r="C135" s="1"/>
       <c r="E135">
-        <v>317</v>
+        <v>580</v>
       </c>
       <c r="F135" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G135" s="1">
-        <v>0.95486111111111116</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -2587,13 +2590,13 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>432</v>
+        <v>308</v>
       </c>
       <c r="F136" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G136" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.92361111111111116</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -2602,13 +2605,13 @@
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>457</v>
+        <v>429</v>
       </c>
       <c r="F137" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G137" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.92708333333333337</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -2617,29 +2620,164 @@
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>552</v>
+        <v>578</v>
       </c>
       <c r="F138" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G138" s="1">
-        <v>0.97222222222222221</v>
+        <v>0.93055555555555558</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>32</v>
-      </c>
-      <c r="B139" t="s">
-        <v>22</v>
-      </c>
-      <c r="C139" s="1">
+        <v>9</v>
+      </c>
+      <c r="C139" s="1"/>
+      <c r="E139">
+        <v>627</v>
+      </c>
+      <c r="F139" t="s">
+        <v>23</v>
+      </c>
+      <c r="G139" s="1">
+        <v>0.93402777777777779</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>9</v>
+      </c>
+      <c r="C140" s="1"/>
+      <c r="E140">
+        <v>574</v>
+      </c>
+      <c r="F140" t="s">
+        <v>15</v>
+      </c>
+      <c r="G140" s="1">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>9</v>
+      </c>
+      <c r="C141" s="1"/>
+      <c r="E141">
+        <v>568</v>
+      </c>
+      <c r="F141" t="s">
+        <v>18</v>
+      </c>
+      <c r="G141" s="1">
+        <v>0.94097222222222221</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="1"/>
+      <c r="E142">
+        <v>452</v>
+      </c>
+      <c r="F142" t="s">
+        <v>11</v>
+      </c>
+      <c r="G142" s="1">
+        <v>0.94791666666666663</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>7</v>
+      </c>
+      <c r="C143" s="1"/>
+      <c r="E143">
+        <v>339</v>
+      </c>
+      <c r="F143" t="s">
+        <v>27</v>
+      </c>
+      <c r="G143" s="1">
+        <v>0.94791666666666663</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>9</v>
+      </c>
+      <c r="C144" s="1"/>
+      <c r="E144">
+        <v>317</v>
+      </c>
+      <c r="F144" t="s">
+        <v>24</v>
+      </c>
+      <c r="G144" s="1">
+        <v>0.95486111111111116</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145" s="1"/>
+      <c r="E145">
+        <v>457</v>
+      </c>
+      <c r="F145" t="s">
+        <v>17</v>
+      </c>
+      <c r="G145" s="1">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="1"/>
+      <c r="E146">
+        <v>300</v>
+      </c>
+      <c r="F146" t="s">
+        <v>16</v>
+      </c>
+      <c r="G146" s="1">
+        <v>0.96180555555555558</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>9</v>
+      </c>
+      <c r="C147" s="1"/>
+      <c r="E147">
+        <v>556</v>
+      </c>
+      <c r="F147" t="s">
+        <v>20</v>
+      </c>
+      <c r="G147" s="1">
+        <v>0.97222222222222221</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>34</v>
+      </c>
+      <c r="B148" t="s">
+        <v>24</v>
+      </c>
+      <c r="C148" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D139">
+      <c r="D148">
         <v>878</v>
       </c>
-      <c r="G139" s="1"/>
+      <c r="G148" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D41FC701-2413-4E14-B1E4-36D8C2B09189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8DDA7D1-4E01-48F1-A857-A04C83A2AEEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A4FB302A-4D4C-4C22-B985-C9CF4D20257B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D3A8D63C-1D19-4F43-9B70-0AD0C179CD7A}"/>
   </bookViews>
   <sheets>
-    <sheet name="16-06" sheetId="1" r:id="rId1"/>
+    <sheet name="17-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="41">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,9 +83,6 @@
     <t>KIAD</t>
   </si>
   <si>
-    <t>KONT</t>
-  </si>
-  <si>
     <t>MHLM</t>
   </si>
   <si>
@@ -122,49 +119,49 @@
     <t>KSFO</t>
   </si>
   <si>
+    <t>KMIA</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
+    <t>KIAH</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>KATL</t>
+  </si>
+  <si>
+    <t>KDFW</t>
+  </si>
+  <si>
+    <t>CMP</t>
+  </si>
+  <si>
+    <t>AMX</t>
+  </si>
+  <si>
+    <t>SKRG</t>
+  </si>
+  <si>
+    <t>KMCO</t>
+  </si>
+  <si>
+    <t>IBE</t>
+  </si>
+  <si>
+    <t>CYUL</t>
+  </si>
+  <si>
+    <t>KBOS</t>
+  </si>
+  <si>
+    <t>KOAK</t>
+  </si>
+  <si>
     <t>KEWR</t>
-  </si>
-  <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>KMIA</t>
-  </si>
-  <si>
-    <t>KIAH</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>KATL</t>
-  </si>
-  <si>
-    <t>KDFW</t>
-  </si>
-  <si>
-    <t>CMP</t>
-  </si>
-  <si>
-    <t>AMX</t>
-  </si>
-  <si>
-    <t>SKRG</t>
-  </si>
-  <si>
-    <t>MMUN</t>
-  </si>
-  <si>
-    <t>IBE</t>
-  </si>
-  <si>
-    <t>KBOS</t>
-  </si>
-  <si>
-    <t>KORD</t>
-  </si>
-  <si>
-    <t>KLAS</t>
   </si>
 </sst>
 </file>
@@ -539,8 +536,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8EC2223-7985-4DE5-8F00-2BA28A92B126}">
-  <dimension ref="A1:G148"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{639CD107-C239-43B7-A607-5137B08D2A5B}">
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -583,7 +580,7 @@
         <v>2203</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G2" s="1">
         <v>5.2083333333333336E-2</v>
@@ -621,14 +618,14 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
         <v>879</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1">
         <v>0.20347222222222219</v>
@@ -673,7 +670,7 @@
         <v>300</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1">
         <v>0.21527777777777779</v>
@@ -705,7 +702,7 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D10">
-        <v>531</v>
+        <v>575</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -717,40 +714,40 @@
         <v>15</v>
       </c>
       <c r="C11" s="1">
-        <v>0.22222222222222221</v>
+        <v>0.22916666666666666</v>
       </c>
       <c r="D11">
-        <v>575</v>
+        <v>301</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1">
-        <v>0.22916666666666666</v>
+        <v>0.24444444444444444</v>
       </c>
       <c r="D12">
-        <v>301</v>
+        <v>4309</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C13" s="1">
-        <v>0.24444444444444444</v>
+        <v>0.24652777777777779</v>
       </c>
       <c r="D13">
-        <v>4309</v>
+        <v>456</v>
       </c>
       <c r="G13" s="1"/>
     </row>
@@ -765,35 +762,35 @@
         <v>0.24652777777777779</v>
       </c>
       <c r="D14">
-        <v>456</v>
+        <v>661</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0.24652777777777779</v>
-      </c>
-      <c r="D15">
-        <v>661</v>
-      </c>
-      <c r="G15" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="E15">
+        <v>3154</v>
+      </c>
+      <c r="F15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C16" s="1"/>
       <c r="E16">
-        <v>3154</v>
+        <v>1467</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G16" s="1">
         <v>0.25</v>
@@ -801,33 +798,33 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C17" s="1"/>
       <c r="E17">
-        <v>1467</v>
+        <v>3154</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G17" s="1">
-        <v>0.25</v>
+        <v>0.25069444444444444</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="E18">
-        <v>3154</v>
-      </c>
-      <c r="F18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0.25069444444444444</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.25694444444444442</v>
+      </c>
+      <c r="D18">
+        <v>433</v>
+      </c>
+      <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -840,7 +837,7 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="D19">
-        <v>433</v>
+        <v>579</v>
       </c>
       <c r="G19" s="1"/>
     </row>
@@ -849,13 +846,13 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C20" s="1">
-        <v>0.25694444444444442</v>
+        <v>0.26041666666666669</v>
       </c>
       <c r="D20">
-        <v>579</v>
+        <v>529</v>
       </c>
       <c r="G20" s="1"/>
     </row>
@@ -864,13 +861,13 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" s="1">
-        <v>0.26041666666666669</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="D21">
-        <v>529</v>
+        <v>314</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -882,10 +879,10 @@
         <v>21</v>
       </c>
       <c r="C22" s="1">
-        <v>0.2638888888888889</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D22">
-        <v>314</v>
+        <v>428</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -900,7 +897,7 @@
         <v>0.2673611111111111</v>
       </c>
       <c r="D23">
-        <v>428</v>
+        <v>626</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -912,10 +909,10 @@
         <v>23</v>
       </c>
       <c r="C24" s="1">
-        <v>0.2673611111111111</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="D24">
-        <v>626</v>
+        <v>316</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -930,7 +927,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D25">
-        <v>316</v>
+        <v>366</v>
       </c>
       <c r="G25" s="1"/>
     </row>
@@ -945,7 +942,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D26">
-        <v>366</v>
+        <v>561</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -954,13 +951,13 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C27" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D27">
-        <v>561</v>
+        <v>591</v>
       </c>
       <c r="G27" s="1"/>
     </row>
@@ -969,13 +966,13 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D28">
-        <v>591</v>
+        <v>671</v>
       </c>
       <c r="G28" s="1"/>
     </row>
@@ -984,44 +981,44 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C29" s="1">
-        <v>0.27083333333333331</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="D29">
-        <v>671</v>
+        <v>521</v>
       </c>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="D30">
-        <v>521</v>
-      </c>
-      <c r="G30" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="E30">
+        <v>3154</v>
+      </c>
+      <c r="F30" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0.29236111111111113</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>3154</v>
+        <v>319</v>
       </c>
       <c r="F31" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G31" s="1">
-        <v>0.29236111111111113</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1030,7 +1027,7 @@
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F32" t="s">
         <v>23</v>
@@ -1045,10 +1042,10 @@
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="F33" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="G33" s="1">
         <v>0.3125</v>
@@ -1063,7 +1060,7 @@
         <v>396</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G34" s="1">
         <v>0.3125</v>
@@ -1078,7 +1075,7 @@
         <v>310</v>
       </c>
       <c r="F35" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G35" s="1">
         <v>0.31597222222222221</v>
@@ -1093,7 +1090,7 @@
         <v>440</v>
       </c>
       <c r="F36" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G36" s="1">
         <v>0.31597222222222221</v>
@@ -1108,7 +1105,7 @@
         <v>536</v>
       </c>
       <c r="F37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G37" s="1">
         <v>0.31597222222222221</v>
@@ -1118,16 +1115,16 @@
       <c r="A38" t="s">
         <v>9</v>
       </c>
-      <c r="B38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="1">
-        <v>0.31944444444444442</v>
-      </c>
-      <c r="D38">
-        <v>321</v>
-      </c>
-      <c r="G38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="E38">
+        <v>444</v>
+      </c>
+      <c r="F38" t="s">
+        <v>38</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0.32291666666666669</v>
+      </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
@@ -1135,10 +1132,10 @@
       </c>
       <c r="C39" s="1"/>
       <c r="E39">
-        <v>444</v>
+        <v>562</v>
       </c>
       <c r="F39" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G39" s="1">
         <v>0.32291666666666669</v>
@@ -1146,14 +1143,14 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C40" s="1"/>
       <c r="E40">
-        <v>562</v>
+        <v>4322</v>
       </c>
       <c r="F40" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="G40" s="1">
         <v>0.32291666666666669</v>
@@ -1168,7 +1165,7 @@
         <v>368</v>
       </c>
       <c r="F41" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G41" s="1">
         <v>0.33333333333333331</v>
@@ -1194,13 +1191,13 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C43" s="1">
         <v>0.33680555555555558</v>
       </c>
       <c r="D43">
-        <v>581</v>
+        <v>309</v>
       </c>
       <c r="G43" s="1"/>
     </row>
@@ -1208,16 +1205,16 @@
       <c r="A44" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="1"/>
-      <c r="E44">
-        <v>383</v>
-      </c>
-      <c r="F44" t="s">
-        <v>25</v>
-      </c>
-      <c r="G44" s="1">
+      <c r="B44" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="1">
         <v>0.33680555555555558</v>
       </c>
+      <c r="D44">
+        <v>581</v>
+      </c>
+      <c r="G44" s="1"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -1225,13 +1222,13 @@
       </c>
       <c r="C45" s="1"/>
       <c r="E45">
-        <v>454</v>
+        <v>383</v>
       </c>
       <c r="F45" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G45" s="1">
-        <v>0.34027777777777779</v>
+        <v>0.33680555555555558</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1240,13 +1237,13 @@
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>324</v>
+        <v>454</v>
       </c>
       <c r="F46" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G46" s="1">
-        <v>0.34375</v>
+        <v>0.34027777777777779</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1255,10 +1252,10 @@
       </c>
       <c r="C47" s="1"/>
       <c r="E47">
-        <v>572</v>
+        <v>324</v>
       </c>
       <c r="F47" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G47" s="1">
         <v>0.34375</v>
@@ -1266,48 +1263,48 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>884</v>
+        <v>554</v>
       </c>
       <c r="F48" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G48" s="1">
-        <v>0.35347222222222219</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>430</v>
+        <v>884</v>
       </c>
       <c r="F49" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G49" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.35347222222222219</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>9</v>
       </c>
-      <c r="B50" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50" s="1">
-        <v>0.37152777777777779</v>
-      </c>
-      <c r="D50">
-        <v>451</v>
-      </c>
-      <c r="G50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="E50">
+        <v>422</v>
+      </c>
+      <c r="F50" t="s">
+        <v>35</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0.36458333333333331</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
@@ -1315,29 +1312,29 @@
       </c>
       <c r="C51" s="1"/>
       <c r="E51">
-        <v>526</v>
+        <v>430</v>
       </c>
       <c r="F51" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="G51" s="1">
-        <v>0.375</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="1"/>
-      <c r="E52">
-        <v>369</v>
-      </c>
-      <c r="F52" t="s">
-        <v>36</v>
-      </c>
-      <c r="G52" s="1">
-        <v>0.3888888888888889</v>
-      </c>
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.37847222222222221</v>
+      </c>
+      <c r="D52">
+        <v>559</v>
+      </c>
+      <c r="G52" s="1"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -1345,59 +1342,59 @@
       </c>
       <c r="C53" s="1"/>
       <c r="E53">
-        <v>582</v>
+        <v>524</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G53" s="1">
-        <v>0.39930555555555558</v>
+        <v>0.38194444444444442</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>12</v>
-      </c>
-      <c r="B54" t="s">
-        <v>27</v>
-      </c>
-      <c r="C54" s="1">
-        <v>0.40902777777777777</v>
-      </c>
-      <c r="D54">
-        <v>4337</v>
-      </c>
-      <c r="G54" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="E54">
+        <v>369</v>
+      </c>
+      <c r="F54" t="s">
+        <v>34</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0.3888888888888889</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>9</v>
       </c>
-      <c r="B55" t="s">
-        <v>18</v>
-      </c>
-      <c r="C55" s="1">
-        <v>0.41319444444444442</v>
-      </c>
-      <c r="D55">
-        <v>569</v>
-      </c>
-      <c r="G55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="E55">
+        <v>582</v>
+      </c>
+      <c r="F55" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0.39930555555555558</v>
+      </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
-      <c r="C56" s="1"/>
-      <c r="E56">
-        <v>392</v>
-      </c>
-      <c r="F56" t="s">
-        <v>21</v>
-      </c>
-      <c r="G56" s="1">
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" s="1">
         <v>0.41319444444444442</v>
       </c>
+      <c r="D56">
+        <v>569</v>
+      </c>
+      <c r="G56" s="1"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
@@ -1405,42 +1402,42 @@
       </c>
       <c r="C57" s="1"/>
       <c r="E57">
-        <v>408</v>
+        <v>609</v>
       </c>
       <c r="F57" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G57" s="1">
-        <v>0.41319444444444442</v>
+        <v>0.4236111111111111</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>9</v>
       </c>
-      <c r="C58" s="1"/>
-      <c r="E58">
-        <v>609</v>
-      </c>
-      <c r="F58" t="s">
-        <v>23</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0.4236111111111111</v>
-      </c>
+      <c r="B58" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="1">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D58">
+        <v>537</v>
+      </c>
+      <c r="G58" s="1"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C59" s="1">
-        <v>0.42708333333333331</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="D59">
-        <v>537</v>
+        <v>455</v>
       </c>
       <c r="G59" s="1"/>
     </row>
@@ -1449,13 +1446,13 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C60" s="1">
-        <v>0.44791666666666669</v>
+        <v>0.4548611111111111</v>
       </c>
       <c r="D60">
-        <v>455</v>
+        <v>318</v>
       </c>
       <c r="G60" s="1"/>
     </row>
@@ -1464,73 +1461,73 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C61" s="1">
-        <v>0.4513888888888889</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D61">
-        <v>573</v>
+        <v>384</v>
       </c>
       <c r="G61" s="1"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C62" s="1">
-        <v>0.4548611111111111</v>
+        <v>0.47291666666666665</v>
       </c>
       <c r="D62">
-        <v>318</v>
+        <v>495</v>
       </c>
       <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B63" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C63" s="1">
-        <v>0.46180555555555558</v>
+        <v>0.47847222222222219</v>
       </c>
       <c r="D63">
-        <v>384</v>
+        <v>1194</v>
       </c>
       <c r="G63" s="1"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>28</v>
-      </c>
-      <c r="B64" t="s">
-        <v>29</v>
-      </c>
-      <c r="C64" s="1">
-        <v>0.47291666666666665</v>
-      </c>
-      <c r="D64">
-        <v>495</v>
-      </c>
-      <c r="G64" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="E64">
+        <v>584</v>
+      </c>
+      <c r="F64" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0.49305555555555558</v>
+      </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C65" s="1">
-        <v>0.47847222222222219</v>
+        <v>0.49444444444444446</v>
       </c>
       <c r="D65">
-        <v>1194</v>
+        <v>4301</v>
       </c>
       <c r="G65" s="1"/>
     </row>
@@ -1540,13 +1537,13 @@
       </c>
       <c r="C66" s="1"/>
       <c r="E66">
-        <v>584</v>
+        <v>385</v>
       </c>
       <c r="F66" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G66" s="1">
-        <v>0.49305555555555558</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -1555,253 +1552,253 @@
       </c>
       <c r="C67" s="1"/>
       <c r="E67">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="F67" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G67" s="1">
-        <v>0.49652777777777779</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" s="1"/>
-      <c r="E68">
-        <v>385</v>
-      </c>
-      <c r="F68" t="s">
-        <v>25</v>
-      </c>
-      <c r="G68" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B68" t="s">
+        <v>28</v>
+      </c>
+      <c r="C68" s="1">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D68">
+        <v>1441</v>
+      </c>
+      <c r="G68" s="1"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C69" s="1"/>
       <c r="E69">
-        <v>424</v>
+        <v>1508</v>
       </c>
       <c r="F69" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G69" s="1">
-        <v>0.50347222222222221</v>
+        <v>0.51597222222222228</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>9</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="E70">
-        <v>442</v>
-      </c>
-      <c r="F70" t="s">
-        <v>33</v>
-      </c>
-      <c r="G70" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B70" t="s">
+        <v>30</v>
+      </c>
+      <c r="C70" s="1">
+        <v>0.5180555555555556</v>
+      </c>
+      <c r="D70">
+        <v>1910</v>
+      </c>
+      <c r="G70" s="1"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B71" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C71" s="1">
-        <v>0.51041666666666663</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="D71">
-        <v>1441</v>
+        <v>937</v>
       </c>
       <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>28</v>
-      </c>
-      <c r="C72" s="1"/>
-      <c r="E72">
-        <v>1508</v>
-      </c>
-      <c r="F72" t="s">
-        <v>29</v>
-      </c>
-      <c r="G72" s="1">
-        <v>0.51597222222222228</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B72" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D72">
+        <v>816</v>
+      </c>
+      <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>31</v>
-      </c>
-      <c r="B73" t="s">
-        <v>32</v>
-      </c>
-      <c r="C73" s="1">
-        <v>0.5180555555555556</v>
-      </c>
-      <c r="D73">
-        <v>1910</v>
-      </c>
-      <c r="G73" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C73" s="1"/>
+      <c r="E73">
+        <v>1458</v>
+      </c>
+      <c r="F73" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0.55555555555555558</v>
+      </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>28</v>
-      </c>
-      <c r="B74" t="s">
-        <v>33</v>
-      </c>
-      <c r="C74" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D74">
-        <v>937</v>
-      </c>
-      <c r="G74" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="E74">
+        <v>380</v>
+      </c>
+      <c r="F74" t="s">
+        <v>31</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0.57222222222222219</v>
+      </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>34</v>
-      </c>
-      <c r="B75" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D75">
-        <v>816</v>
-      </c>
-      <c r="G75" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="E75">
+        <v>1468</v>
+      </c>
+      <c r="F75" t="s">
+        <v>28</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0.57638888888888895</v>
+      </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C76" s="1"/>
       <c r="E76">
-        <v>1458</v>
+        <v>1978</v>
       </c>
       <c r="F76" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G76" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.57708333333333328</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C77" s="1"/>
       <c r="E77">
-        <v>380</v>
+        <v>871</v>
       </c>
       <c r="F77" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G77" s="1">
-        <v>0.57222222222222219</v>
+        <v>0.58194444444444449</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="1"/>
-      <c r="E78">
-        <v>1468</v>
-      </c>
-      <c r="F78" t="s">
-        <v>30</v>
-      </c>
-      <c r="G78" s="1">
-        <v>0.57638888888888895</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" s="1">
+        <v>0.59236111111111112</v>
+      </c>
+      <c r="D78">
+        <v>628</v>
+      </c>
+      <c r="G78" s="1"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="1"/>
-      <c r="E79">
-        <v>1978</v>
-      </c>
-      <c r="F79" t="s">
-        <v>32</v>
-      </c>
-      <c r="G79" s="1">
-        <v>0.57708333333333328</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B79" t="s">
+        <v>28</v>
+      </c>
+      <c r="C79" s="1">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D79">
+        <v>1290</v>
+      </c>
+      <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>34</v>
-      </c>
-      <c r="C80" s="1"/>
-      <c r="E80">
-        <v>871</v>
-      </c>
-      <c r="F80" t="s">
-        <v>24</v>
-      </c>
-      <c r="G80" s="1">
-        <v>0.58194444444444449</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="D80">
+        <v>557</v>
+      </c>
+      <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>35</v>
-      </c>
-      <c r="B81" t="s">
-        <v>19</v>
-      </c>
-      <c r="C81" s="1">
-        <v>0.59236111111111112</v>
-      </c>
-      <c r="D81">
-        <v>628</v>
-      </c>
-      <c r="G81" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="E81">
+        <v>629</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0.64722222222222225</v>
+      </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B82" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C82" s="1">
-        <v>0.60416666666666663</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="D82">
-        <v>1290</v>
+        <v>382</v>
       </c>
       <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C83" s="1"/>
       <c r="E83">
-        <v>629</v>
+        <v>1130</v>
       </c>
       <c r="F83" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G83" s="1">
-        <v>0.64722222222222225</v>
+        <v>0.65277777777777779</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -1809,43 +1806,43 @@
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C84" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D84">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="G84" s="1"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>7</v>
-      </c>
-      <c r="C85" s="1"/>
-      <c r="E85">
-        <v>1130</v>
-      </c>
-      <c r="F85" t="s">
-        <v>30</v>
-      </c>
-      <c r="G85" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B85" t="s">
+        <v>34</v>
+      </c>
+      <c r="C85" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D85">
+        <v>370</v>
+      </c>
+      <c r="G85" s="1"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C86" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D86">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="G86" s="1"/>
     </row>
@@ -1854,13 +1851,13 @@
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C87" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.68055555555555558</v>
       </c>
       <c r="D87">
-        <v>370</v>
+        <v>441</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1869,13 +1866,13 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C88" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D88">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -1884,13 +1881,13 @@
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C89" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.6875</v>
       </c>
       <c r="D89">
-        <v>553</v>
+        <v>311</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -1899,13 +1896,13 @@
         <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C90" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.6875</v>
       </c>
       <c r="D90">
-        <v>441</v>
+        <v>555</v>
       </c>
       <c r="G90" s="1"/>
     </row>
@@ -1914,13 +1911,13 @@
         <v>9</v>
       </c>
       <c r="B91" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C91" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.6875</v>
       </c>
       <c r="D91">
-        <v>435</v>
+        <v>610</v>
       </c>
       <c r="G91" s="1"/>
     </row>
@@ -1929,13 +1926,13 @@
         <v>9</v>
       </c>
       <c r="B92" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C92" s="1">
-        <v>0.6875</v>
+        <v>0.70138888888888884</v>
       </c>
       <c r="D92">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="G92" s="1"/>
     </row>
@@ -1943,31 +1940,31 @@
       <c r="A93" t="s">
         <v>9</v>
       </c>
-      <c r="B93" t="s">
-        <v>23</v>
-      </c>
-      <c r="C93" s="1">
-        <v>0.6875</v>
-      </c>
-      <c r="D93">
-        <v>610</v>
-      </c>
-      <c r="G93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="E93">
+        <v>326</v>
+      </c>
+      <c r="F93" t="s">
+        <v>10</v>
+      </c>
+      <c r="G93" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>9</v>
       </c>
-      <c r="B94" t="s">
-        <v>24</v>
-      </c>
-      <c r="C94" s="1">
-        <v>0.70138888888888884</v>
-      </c>
-      <c r="D94">
-        <v>322</v>
-      </c>
-      <c r="G94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="E94">
+        <v>560</v>
+      </c>
+      <c r="F94" t="s">
+        <v>25</v>
+      </c>
+      <c r="G94" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
@@ -1975,13 +1972,13 @@
       </c>
       <c r="C95" s="1"/>
       <c r="E95">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F95" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G95" s="1">
-        <v>0.72222222222222221</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -1990,13 +1987,13 @@
       </c>
       <c r="C96" s="1"/>
       <c r="E96">
-        <v>326</v>
+        <v>450</v>
       </c>
       <c r="F96" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G96" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -2005,13 +2002,13 @@
       </c>
       <c r="C97" s="1"/>
       <c r="E97">
-        <v>560</v>
+        <v>520</v>
       </c>
       <c r="F97" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G97" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -2020,13 +2017,13 @@
       </c>
       <c r="C98" s="1"/>
       <c r="E98">
-        <v>313</v>
+        <v>588</v>
       </c>
       <c r="F98" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G98" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.73611111111111116</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -2035,13 +2032,13 @@
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>520</v>
+        <v>448</v>
       </c>
       <c r="F99" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G99" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2050,237 +2047,237 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F100" t="s">
         <v>14</v>
       </c>
       <c r="G100" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>9</v>
-      </c>
-      <c r="C101" s="1"/>
-      <c r="E101">
-        <v>588</v>
-      </c>
-      <c r="F101" t="s">
-        <v>20</v>
-      </c>
-      <c r="G101" s="1">
-        <v>0.73611111111111116</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B101" t="s">
+        <v>19</v>
+      </c>
+      <c r="C101" s="1">
+        <v>0.75694444444444442</v>
+      </c>
+      <c r="D101">
+        <v>222</v>
+      </c>
+      <c r="G101" s="1"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C102" s="1"/>
       <c r="E102">
-        <v>534</v>
+        <v>4308</v>
       </c>
       <c r="F102" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G102" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>38</v>
-      </c>
-      <c r="B103" t="s">
-        <v>20</v>
-      </c>
-      <c r="C103" s="1">
-        <v>0.74652777777777779</v>
-      </c>
-      <c r="D103">
-        <v>222</v>
-      </c>
-      <c r="G103" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C103" s="1"/>
+      <c r="E103">
+        <v>528</v>
+      </c>
+      <c r="F103" t="s">
+        <v>8</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0.76041666666666663</v>
+      </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>4308</v>
+        <v>660</v>
       </c>
       <c r="F104" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G104" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>9</v>
-      </c>
-      <c r="C105" s="1"/>
-      <c r="E105">
-        <v>528</v>
-      </c>
-      <c r="F105" t="s">
-        <v>8</v>
-      </c>
-      <c r="G105" s="1">
-        <v>0.76041666666666663</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B105" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" s="1">
+        <v>0.77847222222222223</v>
+      </c>
+      <c r="D105">
+        <v>2657</v>
+      </c>
+      <c r="G105" s="1"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>9</v>
-      </c>
-      <c r="C106" s="1"/>
-      <c r="E106">
-        <v>660</v>
-      </c>
-      <c r="F106" t="s">
-        <v>18</v>
-      </c>
-      <c r="G106" s="1">
-        <v>0.77083333333333337</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B106" t="s">
+        <v>28</v>
+      </c>
+      <c r="C106" s="1">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="D106">
+        <v>742</v>
+      </c>
+      <c r="G106" s="1"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C107" s="1"/>
       <c r="E107">
-        <v>558</v>
+        <v>4312</v>
       </c>
       <c r="F107" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G107" s="1">
-        <v>0.77777777777777779</v>
+        <v>0.79027777777777775</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B108" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C108" s="1">
-        <v>0.77847222222222223</v>
+        <v>0.79513888888888884</v>
       </c>
       <c r="D108">
-        <v>2657</v>
+        <v>431</v>
       </c>
       <c r="G108" s="1"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>7</v>
-      </c>
-      <c r="B109" t="s">
-        <v>30</v>
-      </c>
-      <c r="C109" s="1">
-        <v>0.79027777777777775</v>
-      </c>
-      <c r="D109">
-        <v>742</v>
-      </c>
-      <c r="G109" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C109" s="1"/>
+      <c r="E109">
+        <v>670</v>
+      </c>
+      <c r="F109" t="s">
+        <v>17</v>
+      </c>
+      <c r="G109" s="1">
+        <v>0.80555555555555558</v>
+      </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>12</v>
-      </c>
-      <c r="C110" s="1"/>
-      <c r="E110">
-        <v>4312</v>
-      </c>
-      <c r="F110" t="s">
-        <v>13</v>
-      </c>
-      <c r="G110" s="1">
-        <v>0.79027777777777775</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B110" t="s">
+        <v>28</v>
+      </c>
+      <c r="C110" s="1">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="D110">
+        <v>425</v>
+      </c>
+      <c r="G110" s="1"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>9</v>
-      </c>
-      <c r="B111" t="s">
-        <v>19</v>
-      </c>
-      <c r="C111" s="1">
-        <v>0.79513888888888884</v>
-      </c>
-      <c r="D111">
-        <v>431</v>
-      </c>
-      <c r="G111" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="C111" s="1"/>
+      <c r="E111">
+        <v>222</v>
+      </c>
+      <c r="F111" t="s">
+        <v>15</v>
+      </c>
+      <c r="G111" s="1">
+        <v>0.81944444444444442</v>
+      </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>9</v>
       </c>
-      <c r="C112" s="1"/>
-      <c r="E112">
-        <v>670</v>
-      </c>
-      <c r="F112" t="s">
-        <v>18</v>
-      </c>
-      <c r="G112" s="1">
-        <v>0.80555555555555558</v>
-      </c>
+      <c r="B112" t="s">
+        <v>37</v>
+      </c>
+      <c r="C112" s="1">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D112">
+        <v>329</v>
+      </c>
+      <c r="G112" s="1"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>38</v>
-      </c>
-      <c r="C113" s="1"/>
-      <c r="E113">
-        <v>222</v>
-      </c>
-      <c r="F113" t="s">
-        <v>16</v>
-      </c>
-      <c r="G113" s="1">
-        <v>0.80902777777777779</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B113" t="s">
+        <v>8</v>
+      </c>
+      <c r="C113" s="1">
+        <v>0.82638888888888884</v>
+      </c>
+      <c r="D113">
+        <v>523</v>
+      </c>
+      <c r="G113" s="1"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>12</v>
-      </c>
-      <c r="C114" s="1"/>
-      <c r="E114">
-        <v>4300</v>
-      </c>
-      <c r="F114" t="s">
-        <v>19</v>
-      </c>
-      <c r="G114" s="1">
-        <v>0.81388888888888888</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B114" t="s">
+        <v>13</v>
+      </c>
+      <c r="C114" s="1">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D114">
+        <v>583</v>
+      </c>
+      <c r="G114" s="1"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C115" s="1">
-        <v>0.81944444444444442</v>
+        <v>0.84375</v>
       </c>
       <c r="D115">
-        <v>425</v>
+        <v>325</v>
       </c>
       <c r="G115" s="1"/>
     </row>
@@ -2289,13 +2286,13 @@
         <v>9</v>
       </c>
       <c r="B116" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C116" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.84375</v>
       </c>
       <c r="D116">
-        <v>583</v>
+        <v>445</v>
       </c>
       <c r="G116" s="1"/>
     </row>
@@ -2303,74 +2300,74 @@
       <c r="A117" t="s">
         <v>9</v>
       </c>
-      <c r="B117" t="s">
-        <v>10</v>
-      </c>
-      <c r="C117" s="1">
-        <v>0.84375</v>
-      </c>
-      <c r="D117">
-        <v>325</v>
-      </c>
-      <c r="G117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="E117">
+        <v>590</v>
+      </c>
+      <c r="F117" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>9</v>
       </c>
       <c r="B118" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="C118" s="1">
-        <v>0.84375</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D118">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="G118" s="1"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B119" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C119" s="1">
-        <v>0.85069444444444442</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D119">
-        <v>393</v>
+        <v>881</v>
       </c>
       <c r="G119" s="1"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>9</v>
-      </c>
-      <c r="C120" s="1"/>
-      <c r="E120">
-        <v>590</v>
-      </c>
-      <c r="F120" t="s">
-        <v>13</v>
-      </c>
-      <c r="G120" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B120" t="s">
+        <v>39</v>
+      </c>
+      <c r="C120" s="1">
+        <v>0.86111111111111116</v>
+      </c>
+      <c r="D120">
+        <v>4323</v>
+      </c>
+      <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C121" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D121">
-        <v>881</v>
+        <v>1461</v>
       </c>
       <c r="G121" s="1"/>
     </row>
@@ -2379,28 +2376,28 @@
         <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C122" s="1">
-        <v>0.86111111111111116</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D122">
-        <v>523</v>
+        <v>563</v>
       </c>
       <c r="G122" s="1"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B123" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C123" s="1">
-        <v>0.86736111111111114</v>
+        <v>0.875</v>
       </c>
       <c r="D123">
-        <v>1461</v>
+        <v>535</v>
       </c>
       <c r="G123" s="1"/>
     </row>
@@ -2409,13 +2406,13 @@
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C124" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D124">
-        <v>443</v>
+        <v>312</v>
       </c>
       <c r="G124" s="1"/>
     </row>
@@ -2424,13 +2421,13 @@
         <v>9</v>
       </c>
       <c r="B125" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C125" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D125">
-        <v>563</v>
+        <v>525</v>
       </c>
       <c r="G125" s="1"/>
     </row>
@@ -2439,28 +2436,28 @@
         <v>9</v>
       </c>
       <c r="B126" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C126" s="1">
-        <v>0.87152777777777779</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D126">
-        <v>409</v>
+        <v>589</v>
       </c>
       <c r="G126" s="1"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C127" s="1">
-        <v>0.875</v>
+        <v>0.89930555555555547</v>
       </c>
       <c r="D127">
-        <v>527</v>
+        <v>1425</v>
       </c>
       <c r="G127" s="1"/>
     </row>
@@ -2469,13 +2466,13 @@
         <v>9</v>
       </c>
       <c r="B128" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C128" s="1">
-        <v>0.875</v>
+        <v>0.91319444444444442</v>
       </c>
       <c r="D128">
-        <v>535</v>
+        <v>585</v>
       </c>
       <c r="G128" s="1"/>
     </row>
@@ -2483,61 +2480,61 @@
       <c r="A129" t="s">
         <v>9</v>
       </c>
-      <c r="B129" t="s">
-        <v>23</v>
-      </c>
-      <c r="C129" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D129">
-        <v>312</v>
-      </c>
-      <c r="G129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="E129">
+        <v>315</v>
+      </c>
+      <c r="F129" t="s">
+        <v>20</v>
+      </c>
+      <c r="G129" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>9</v>
       </c>
-      <c r="B130" t="s">
-        <v>20</v>
-      </c>
-      <c r="C130" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D130">
-        <v>589</v>
-      </c>
-      <c r="G130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="E130">
+        <v>365</v>
+      </c>
+      <c r="F130" t="s">
+        <v>24</v>
+      </c>
+      <c r="G130" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>7</v>
-      </c>
-      <c r="B131" t="s">
-        <v>27</v>
-      </c>
-      <c r="C131" s="1">
-        <v>0.89930555555555547</v>
-      </c>
-      <c r="D131">
-        <v>1425</v>
-      </c>
-      <c r="G131" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C131" s="1"/>
+      <c r="E131">
+        <v>600</v>
+      </c>
+      <c r="F131" t="s">
+        <v>13</v>
+      </c>
+      <c r="G131" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>9</v>
       </c>
-      <c r="B132" t="s">
-        <v>13</v>
-      </c>
-      <c r="C132" s="1">
-        <v>0.91319444444444442</v>
-      </c>
-      <c r="D132">
-        <v>585</v>
-      </c>
-      <c r="G132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="E132">
+        <v>429</v>
+      </c>
+      <c r="F132" t="s">
+        <v>21</v>
+      </c>
+      <c r="G132" s="1">
+        <v>0.92708333333333337</v>
+      </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
@@ -2545,13 +2542,13 @@
       </c>
       <c r="C133" s="1"/>
       <c r="E133">
-        <v>315</v>
+        <v>578</v>
       </c>
       <c r="F133" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G133" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.93055555555555558</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -2560,13 +2557,13 @@
       </c>
       <c r="C134" s="1"/>
       <c r="E134">
-        <v>365</v>
+        <v>627</v>
       </c>
       <c r="F134" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G134" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.93402777777777779</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -2575,13 +2572,13 @@
       </c>
       <c r="C135" s="1"/>
       <c r="E135">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="F135" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G135" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -2590,43 +2587,43 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>308</v>
+        <v>452</v>
       </c>
       <c r="F136" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G136" s="1">
-        <v>0.92361111111111116</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>429</v>
+        <v>339</v>
       </c>
       <c r="F137" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G137" s="1">
-        <v>0.92708333333333337</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>578</v>
+        <v>4336</v>
       </c>
       <c r="F138" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G138" s="1">
-        <v>0.93055555555555558</v>
+        <v>0.9506944444444444</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -2635,13 +2632,13 @@
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>627</v>
+        <v>317</v>
       </c>
       <c r="F139" t="s">
         <v>23</v>
       </c>
       <c r="G139" s="1">
-        <v>0.93402777777777779</v>
+        <v>0.95486111111111116</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -2650,13 +2647,13 @@
       </c>
       <c r="C140" s="1"/>
       <c r="E140">
-        <v>574</v>
+        <v>432</v>
       </c>
       <c r="F140" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G140" s="1">
-        <v>0.9375</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -2665,13 +2662,13 @@
       </c>
       <c r="C141" s="1"/>
       <c r="E141">
-        <v>568</v>
+        <v>457</v>
       </c>
       <c r="F141" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G141" s="1">
-        <v>0.94097222222222221</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -2680,104 +2677,29 @@
       </c>
       <c r="C142" s="1"/>
       <c r="E142">
-        <v>452</v>
+        <v>552</v>
       </c>
       <c r="F142" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G142" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.97222222222222221</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>7</v>
-      </c>
-      <c r="C143" s="1"/>
-      <c r="E143">
-        <v>339</v>
-      </c>
-      <c r="F143" t="s">
-        <v>27</v>
-      </c>
-      <c r="G143" s="1">
-        <v>0.94791666666666663</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>9</v>
-      </c>
-      <c r="C144" s="1"/>
-      <c r="E144">
-        <v>317</v>
-      </c>
-      <c r="F144" t="s">
-        <v>24</v>
-      </c>
-      <c r="G144" s="1">
-        <v>0.95486111111111116</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>9</v>
-      </c>
-      <c r="C145" s="1"/>
-      <c r="E145">
-        <v>457</v>
-      </c>
-      <c r="F145" t="s">
-        <v>17</v>
-      </c>
-      <c r="G145" s="1">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>9</v>
-      </c>
-      <c r="C146" s="1"/>
-      <c r="E146">
-        <v>300</v>
-      </c>
-      <c r="F146" t="s">
-        <v>16</v>
-      </c>
-      <c r="G146" s="1">
-        <v>0.96180555555555558</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>9</v>
-      </c>
-      <c r="C147" s="1"/>
-      <c r="E147">
-        <v>556</v>
-      </c>
-      <c r="F147" t="s">
-        <v>20</v>
-      </c>
-      <c r="G147" s="1">
-        <v>0.97222222222222221</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>34</v>
-      </c>
-      <c r="B148" t="s">
-        <v>24</v>
-      </c>
-      <c r="C148" s="1">
+        <v>32</v>
+      </c>
+      <c r="B143" t="s">
+        <v>23</v>
+      </c>
+      <c r="C143" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D148">
+      <c r="D143">
         <v>878</v>
       </c>
-      <c r="G148" s="1"/>
+      <c r="G143" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8DDA7D1-4E01-48F1-A857-A04C83A2AEEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEFC8E11-4056-417E-A6BE-372DA3315DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D3A8D63C-1D19-4F43-9B70-0AD0C179CD7A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7A3D3D8B-5B9D-4A78-9D52-130611081818}"/>
   </bookViews>
   <sheets>
-    <sheet name="17-06" sheetId="1" r:id="rId1"/>
+    <sheet name="18-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="44">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,48 +83,54 @@
     <t>KIAD</t>
   </si>
   <si>
+    <t>KONT</t>
+  </si>
+  <si>
+    <t>LEMD</t>
+  </si>
+  <si>
+    <t>SEQM</t>
+  </si>
+  <si>
+    <t>KJFK</t>
+  </si>
+  <si>
+    <t>MMMX</t>
+  </si>
+  <si>
+    <t>MGGT</t>
+  </si>
+  <si>
+    <t>MNMG</t>
+  </si>
+  <si>
+    <t>SPJC</t>
+  </si>
+  <si>
+    <t>MROC</t>
+  </si>
+  <si>
+    <t>MPTO</t>
+  </si>
+  <si>
+    <t>SKBO</t>
+  </si>
+  <si>
+    <t>KSFO</t>
+  </si>
+  <si>
+    <t>KEWR</t>
+  </si>
+  <si>
     <t>MHLM</t>
   </si>
   <si>
-    <t>LEMD</t>
-  </si>
-  <si>
-    <t>SEQM</t>
-  </si>
-  <si>
-    <t>KJFK</t>
-  </si>
-  <si>
-    <t>MMMX</t>
-  </si>
-  <si>
-    <t>MGGT</t>
-  </si>
-  <si>
-    <t>MNMG</t>
-  </si>
-  <si>
-    <t>SPJC</t>
-  </si>
-  <si>
-    <t>MROC</t>
-  </si>
-  <si>
-    <t>MPTO</t>
-  </si>
-  <si>
-    <t>SKBO</t>
-  </si>
-  <si>
-    <t>KSFO</t>
+    <t>AAL</t>
   </si>
   <si>
     <t>KMIA</t>
   </si>
   <si>
-    <t>AAL</t>
-  </si>
-  <si>
     <t>KIAH</t>
   </si>
   <si>
@@ -134,6 +140,12 @@
     <t>KATL</t>
   </si>
   <si>
+    <t>TAG</t>
+  </si>
+  <si>
+    <t>MHRO</t>
+  </si>
+  <si>
     <t>KDFW</t>
   </si>
   <si>
@@ -146,22 +158,19 @@
     <t>SKRG</t>
   </si>
   <si>
-    <t>KMCO</t>
+    <t>MMUN</t>
   </si>
   <si>
     <t>IBE</t>
   </si>
   <si>
-    <t>CYUL</t>
-  </si>
-  <si>
     <t>KBOS</t>
   </si>
   <si>
-    <t>KOAK</t>
-  </si>
-  <si>
-    <t>KEWR</t>
+    <t>KORD</t>
+  </si>
+  <si>
+    <t>KLAS</t>
   </si>
 </sst>
 </file>
@@ -536,8 +545,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{639CD107-C239-43B7-A607-5137B08D2A5B}">
-  <dimension ref="A1:G143"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{175611BB-4E45-4BD4-8461-1BF04AF30F76}">
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -580,7 +589,7 @@
         <v>2203</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2" s="1">
         <v>5.2083333333333336E-2</v>
@@ -618,7 +627,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
@@ -702,7 +711,7 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D10">
-        <v>575</v>
+        <v>531</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -768,14 +777,14 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15">
         <v>3154</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G15" s="1">
         <v>0.25</v>
@@ -790,7 +799,7 @@
         <v>1467</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G16" s="1">
         <v>0.25</v>
@@ -798,14 +807,14 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1"/>
       <c r="E17">
         <v>3154</v>
       </c>
       <c r="F17" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G17" s="1">
         <v>0.25069444444444444</v>
@@ -993,17 +1002,17 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C30" s="1"/>
       <c r="E30">
-        <v>3154</v>
+        <v>319</v>
       </c>
       <c r="F30" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G30" s="1">
-        <v>0.29236111111111113</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1012,10 +1021,10 @@
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G31" s="1">
         <v>0.3125</v>
@@ -1027,10 +1036,10 @@
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>323</v>
+        <v>396</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G32" s="1">
         <v>0.3125</v>
@@ -1038,14 +1047,14 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>328</v>
+        <v>884</v>
       </c>
       <c r="F33" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G33" s="1">
         <v>0.3125</v>
@@ -1057,13 +1066,13 @@
       </c>
       <c r="C34" s="1"/>
       <c r="E34">
-        <v>396</v>
+        <v>310</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G34" s="1">
-        <v>0.3125</v>
+        <v>0.31597222222222221</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1072,10 +1081,10 @@
       </c>
       <c r="C35" s="1"/>
       <c r="E35">
-        <v>310</v>
+        <v>440</v>
       </c>
       <c r="F35" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G35" s="1">
         <v>0.31597222222222221</v>
@@ -1087,10 +1096,10 @@
       </c>
       <c r="C36" s="1"/>
       <c r="E36">
-        <v>440</v>
+        <v>536</v>
       </c>
       <c r="F36" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G36" s="1">
         <v>0.31597222222222221</v>
@@ -1100,16 +1109,16 @@
       <c r="A37" t="s">
         <v>9</v>
       </c>
-      <c r="C37" s="1"/>
-      <c r="E37">
-        <v>536</v>
-      </c>
-      <c r="F37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0.31597222222222221</v>
-      </c>
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="D37">
+        <v>321</v>
+      </c>
+      <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
@@ -1120,7 +1129,7 @@
         <v>444</v>
       </c>
       <c r="F38" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G38" s="1">
         <v>0.32291666666666669</v>
@@ -1143,17 +1152,17 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C40" s="1"/>
       <c r="E40">
-        <v>4322</v>
+        <v>368</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G40" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1162,10 +1171,10 @@
       </c>
       <c r="C41" s="1"/>
       <c r="E41">
-        <v>368</v>
+        <v>522</v>
       </c>
       <c r="F41" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G41" s="1">
         <v>0.33333333333333331</v>
@@ -1175,46 +1184,46 @@
       <c r="A42" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="1"/>
-      <c r="E42">
-        <v>522</v>
-      </c>
-      <c r="F42" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0.33333333333333331</v>
-      </c>
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="D42">
+        <v>601</v>
+      </c>
+      <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="B43" t="s">
-        <v>26</v>
-      </c>
-      <c r="C43" s="1">
+      <c r="C43" s="1"/>
+      <c r="E43">
+        <v>383</v>
+      </c>
+      <c r="F43" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" s="1">
         <v>0.33680555555555558</v>
       </c>
-      <c r="D43">
-        <v>309</v>
-      </c>
-      <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>9</v>
       </c>
-      <c r="B44" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D44">
-        <v>581</v>
-      </c>
-      <c r="G44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="E44">
+        <v>454</v>
+      </c>
+      <c r="F44" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0.34027777777777779</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -1222,13 +1231,13 @@
       </c>
       <c r="C45" s="1"/>
       <c r="E45">
-        <v>383</v>
+        <v>324</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G45" s="1">
-        <v>0.33680555555555558</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1237,13 +1246,13 @@
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>454</v>
+        <v>572</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G46" s="1">
-        <v>0.34027777777777779</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1252,10 +1261,10 @@
       </c>
       <c r="C47" s="1"/>
       <c r="E47">
-        <v>324</v>
+        <v>744</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G47" s="1">
         <v>0.34375</v>
@@ -1267,29 +1276,29 @@
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>554</v>
+        <v>430</v>
       </c>
       <c r="F48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G48" s="1">
-        <v>0.34375</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>32</v>
-      </c>
-      <c r="C49" s="1"/>
-      <c r="E49">
-        <v>884</v>
-      </c>
-      <c r="F49" t="s">
-        <v>23</v>
-      </c>
-      <c r="G49" s="1">
-        <v>0.35347222222222219</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B49" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="1">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="D49">
+        <v>451</v>
+      </c>
+      <c r="G49" s="1"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -1297,44 +1306,44 @@
       </c>
       <c r="C50" s="1"/>
       <c r="E50">
-        <v>422</v>
+        <v>526</v>
       </c>
       <c r="F50" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G50" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C51" s="1"/>
       <c r="E51">
-        <v>430</v>
+        <v>4320</v>
       </c>
       <c r="F51" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G51" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.38333333333333336</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>9</v>
       </c>
-      <c r="B52" t="s">
-        <v>25</v>
-      </c>
-      <c r="C52" s="1">
-        <v>0.37847222222222221</v>
-      </c>
-      <c r="D52">
-        <v>559</v>
-      </c>
-      <c r="G52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="E52">
+        <v>369</v>
+      </c>
+      <c r="F52" t="s">
+        <v>38</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.3888888888888889</v>
+      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -1342,59 +1351,59 @@
       </c>
       <c r="C53" s="1"/>
       <c r="E53">
-        <v>524</v>
+        <v>582</v>
       </c>
       <c r="F53" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G53" s="1">
-        <v>0.38194444444444442</v>
+        <v>0.39930555555555558</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" s="1"/>
-      <c r="E54">
-        <v>369</v>
-      </c>
-      <c r="F54" t="s">
-        <v>34</v>
-      </c>
-      <c r="G54" s="1">
-        <v>0.3888888888888889</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B54" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" s="1">
+        <v>0.40902777777777777</v>
+      </c>
+      <c r="D54">
+        <v>4337</v>
+      </c>
+      <c r="G54" s="1"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>9</v>
       </c>
-      <c r="C55" s="1"/>
-      <c r="E55">
-        <v>582</v>
-      </c>
-      <c r="F55" t="s">
-        <v>13</v>
-      </c>
-      <c r="G55" s="1">
-        <v>0.39930555555555558</v>
-      </c>
+      <c r="B55" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="1">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="D55">
+        <v>569</v>
+      </c>
+      <c r="G55" s="1"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
-      <c r="B56" t="s">
-        <v>17</v>
-      </c>
-      <c r="C56" s="1">
+      <c r="C56" s="1"/>
+      <c r="E56">
+        <v>392</v>
+      </c>
+      <c r="F56" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" s="1">
         <v>0.41319444444444442</v>
       </c>
-      <c r="D56">
-        <v>569</v>
-      </c>
-      <c r="G56" s="1"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
@@ -1402,42 +1411,42 @@
       </c>
       <c r="C57" s="1"/>
       <c r="E57">
-        <v>609</v>
+        <v>408</v>
       </c>
       <c r="F57" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G57" s="1">
-        <v>0.4236111111111111</v>
+        <v>0.41319444444444442</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>9</v>
       </c>
-      <c r="B58" t="s">
-        <v>14</v>
-      </c>
-      <c r="C58" s="1">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="D58">
-        <v>537</v>
-      </c>
-      <c r="G58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="E58">
+        <v>609</v>
+      </c>
+      <c r="F58" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0.4236111111111111</v>
+      </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C59" s="1">
-        <v>0.44791666666666669</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="D59">
-        <v>455</v>
+        <v>537</v>
       </c>
       <c r="G59" s="1"/>
     </row>
@@ -1446,13 +1455,13 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C60" s="1">
-        <v>0.4548611111111111</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="D60">
-        <v>318</v>
+        <v>455</v>
       </c>
       <c r="G60" s="1"/>
     </row>
@@ -1461,43 +1470,43 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C61" s="1">
-        <v>0.46180555555555558</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="D61">
-        <v>384</v>
+        <v>573</v>
       </c>
       <c r="G61" s="1"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C62" s="1">
-        <v>0.47291666666666665</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="D62">
-        <v>495</v>
+        <v>745</v>
       </c>
       <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C63" s="1">
-        <v>0.47847222222222219</v>
+        <v>0.4548611111111111</v>
       </c>
       <c r="D63">
-        <v>1194</v>
+        <v>318</v>
       </c>
       <c r="G63" s="1"/>
     </row>
@@ -1505,46 +1514,46 @@
       <c r="A64" t="s">
         <v>9</v>
       </c>
-      <c r="C64" s="1"/>
-      <c r="E64">
-        <v>584</v>
-      </c>
-      <c r="F64" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" s="1">
-        <v>0.49305555555555558</v>
-      </c>
+      <c r="B64" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="1">
+        <v>0.46180555555555558</v>
+      </c>
+      <c r="D64">
+        <v>384</v>
+      </c>
+      <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B65" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C65" s="1">
-        <v>0.49444444444444446</v>
+        <v>0.47291666666666665</v>
       </c>
       <c r="D65">
-        <v>4301</v>
+        <v>495</v>
       </c>
       <c r="G65" s="1"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>9</v>
-      </c>
-      <c r="C66" s="1"/>
-      <c r="E66">
-        <v>385</v>
-      </c>
-      <c r="F66" t="s">
-        <v>24</v>
-      </c>
-      <c r="G66" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B66" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="1">
+        <v>0.47847222222222219</v>
+      </c>
+      <c r="D66">
+        <v>1194</v>
+      </c>
+      <c r="G66" s="1"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
@@ -1552,342 +1561,342 @@
       </c>
       <c r="C67" s="1"/>
       <c r="E67">
-        <v>424</v>
+        <v>584</v>
       </c>
       <c r="F67" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G67" s="1">
-        <v>0.50347222222222221</v>
+        <v>0.49305555555555558</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>7</v>
-      </c>
-      <c r="B68" t="s">
-        <v>28</v>
-      </c>
-      <c r="C68" s="1">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="D68">
-        <v>1441</v>
-      </c>
-      <c r="G68" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="E68">
+        <v>434</v>
+      </c>
+      <c r="F68" t="s">
+        <v>39</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0.49652777777777779</v>
+      </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C69" s="1"/>
       <c r="E69">
-        <v>1508</v>
+        <v>385</v>
       </c>
       <c r="F69" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G69" s="1">
-        <v>0.51597222222222228</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>29</v>
-      </c>
-      <c r="B70" t="s">
+        <v>9</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="E70">
+        <v>424</v>
+      </c>
+      <c r="F70" t="s">
         <v>30</v>
       </c>
-      <c r="C70" s="1">
-        <v>0.5180555555555556</v>
-      </c>
-      <c r="D70">
-        <v>1910</v>
-      </c>
-      <c r="G70" s="1"/>
+      <c r="G70" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>27</v>
-      </c>
-      <c r="B71" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D71">
-        <v>937</v>
-      </c>
-      <c r="G71" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C71" s="1"/>
+      <c r="E71">
+        <v>442</v>
+      </c>
+      <c r="F71" t="s">
+        <v>35</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C72" s="1">
-        <v>0.52916666666666667</v>
+        <v>0.51041666666666663</v>
       </c>
       <c r="D72">
-        <v>816</v>
+        <v>1441</v>
       </c>
       <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C73" s="1"/>
       <c r="E73">
-        <v>1458</v>
+        <v>1508</v>
       </c>
       <c r="F73" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G73" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.51597222222222228</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>27</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="E74">
-        <v>380</v>
-      </c>
-      <c r="F74" t="s">
         <v>31</v>
       </c>
-      <c r="G74" s="1">
-        <v>0.57222222222222219</v>
-      </c>
+      <c r="B74" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" s="1">
+        <v>0.5180555555555556</v>
+      </c>
+      <c r="D74">
+        <v>1910</v>
+      </c>
+      <c r="G74" s="1"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" s="1"/>
-      <c r="E75">
-        <v>1468</v>
-      </c>
-      <c r="F75" t="s">
-        <v>28</v>
-      </c>
-      <c r="G75" s="1">
-        <v>0.57638888888888895</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B75" t="s">
+        <v>34</v>
+      </c>
+      <c r="C75" s="1">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D75">
+        <v>420</v>
+      </c>
+      <c r="G75" s="1"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>29</v>
-      </c>
-      <c r="C76" s="1"/>
-      <c r="E76">
-        <v>1978</v>
-      </c>
-      <c r="F76" t="s">
-        <v>30</v>
-      </c>
-      <c r="G76" s="1">
-        <v>0.57708333333333328</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B76" t="s">
+        <v>35</v>
+      </c>
+      <c r="C76" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D76">
+        <v>937</v>
+      </c>
+      <c r="G76" s="1"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>32</v>
-      </c>
-      <c r="C77" s="1"/>
-      <c r="E77">
-        <v>871</v>
-      </c>
-      <c r="F77" t="s">
+        <v>36</v>
+      </c>
+      <c r="B77" t="s">
         <v>23</v>
       </c>
-      <c r="G77" s="1">
-        <v>0.58194444444444449</v>
-      </c>
+      <c r="C77" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D77">
+        <v>816</v>
+      </c>
+      <c r="G77" s="1"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>33</v>
       </c>
-      <c r="B78" t="s">
-        <v>18</v>
-      </c>
-      <c r="C78" s="1">
-        <v>0.59236111111111112</v>
-      </c>
-      <c r="D78">
-        <v>628</v>
-      </c>
-      <c r="G78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="E78">
+        <v>421</v>
+      </c>
+      <c r="F78" t="s">
+        <v>34</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0.55208333333333337</v>
+      </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>7</v>
       </c>
-      <c r="B79" t="s">
-        <v>28</v>
-      </c>
-      <c r="C79" s="1">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D79">
-        <v>1290</v>
-      </c>
-      <c r="G79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="E79">
+        <v>1458</v>
+      </c>
+      <c r="F79" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0.55555555555555558</v>
+      </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>9</v>
-      </c>
-      <c r="B80" t="s">
-        <v>19</v>
-      </c>
-      <c r="C80" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="D80">
-        <v>557</v>
-      </c>
-      <c r="G80" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="E80">
+        <v>380</v>
+      </c>
+      <c r="F80" t="s">
+        <v>35</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0.57222222222222219</v>
+      </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C81" s="1"/>
       <c r="E81">
-        <v>629</v>
+        <v>1468</v>
       </c>
       <c r="F81" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G81" s="1">
-        <v>0.64722222222222225</v>
+        <v>0.57638888888888895</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>9</v>
-      </c>
-      <c r="B82" t="s">
-        <v>24</v>
-      </c>
-      <c r="C82" s="1">
-        <v>0.65277777777777779</v>
-      </c>
-      <c r="D82">
-        <v>382</v>
-      </c>
-      <c r="G82" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="E82">
+        <v>1978</v>
+      </c>
+      <c r="F82" t="s">
+        <v>32</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0.57708333333333328</v>
+      </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="C83" s="1"/>
       <c r="E83">
-        <v>1130</v>
+        <v>871</v>
       </c>
       <c r="F83" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G83" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.58194444444444449</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C84" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.59375</v>
       </c>
       <c r="D84">
-        <v>367</v>
+        <v>628</v>
       </c>
       <c r="G84" s="1"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B85" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C85" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D85">
-        <v>370</v>
+        <v>1290</v>
       </c>
       <c r="G85" s="1"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>9</v>
-      </c>
-      <c r="B86" t="s">
-        <v>20</v>
-      </c>
-      <c r="C86" s="1">
-        <v>0.67361111111111116</v>
-      </c>
-      <c r="D86">
-        <v>397</v>
-      </c>
-      <c r="G86" s="1"/>
+        <v>37</v>
+      </c>
+      <c r="C86" s="1"/>
+      <c r="E86">
+        <v>629</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0.64722222222222225</v>
+      </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C87" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="D87">
-        <v>441</v>
+        <v>382</v>
       </c>
       <c r="G87" s="1"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>9</v>
-      </c>
-      <c r="B88" t="s">
-        <v>35</v>
-      </c>
-      <c r="C88" s="1">
-        <v>0.68402777777777779</v>
-      </c>
-      <c r="D88">
-        <v>423</v>
-      </c>
-      <c r="G88" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C88" s="1"/>
+      <c r="E88">
+        <v>1130</v>
+      </c>
+      <c r="F88" t="s">
+        <v>30</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C89" s="1">
-        <v>0.6875</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D89">
-        <v>311</v>
+        <v>367</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -1896,13 +1905,13 @@
         <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C90" s="1">
-        <v>0.6875</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D90">
-        <v>555</v>
+        <v>370</v>
       </c>
       <c r="G90" s="1"/>
     </row>
@@ -1911,13 +1920,13 @@
         <v>9</v>
       </c>
       <c r="B91" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C91" s="1">
-        <v>0.6875</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D91">
-        <v>610</v>
+        <v>397</v>
       </c>
       <c r="G91" s="1"/>
     </row>
@@ -1926,13 +1935,13 @@
         <v>9</v>
       </c>
       <c r="B92" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C92" s="1">
-        <v>0.70138888888888884</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D92">
-        <v>322</v>
+        <v>553</v>
       </c>
       <c r="G92" s="1"/>
     </row>
@@ -1940,91 +1949,91 @@
       <c r="A93" t="s">
         <v>9</v>
       </c>
-      <c r="C93" s="1"/>
-      <c r="E93">
-        <v>326</v>
-      </c>
-      <c r="F93" t="s">
-        <v>10</v>
-      </c>
-      <c r="G93" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+      <c r="B93" t="s">
+        <v>35</v>
+      </c>
+      <c r="C93" s="1">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="D93">
+        <v>441</v>
+      </c>
+      <c r="G93" s="1"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>9</v>
       </c>
-      <c r="C94" s="1"/>
-      <c r="E94">
-        <v>560</v>
-      </c>
-      <c r="F94" t="s">
-        <v>25</v>
-      </c>
-      <c r="G94" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+      <c r="B94" t="s">
+        <v>39</v>
+      </c>
+      <c r="C94" s="1">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="D94">
+        <v>435</v>
+      </c>
+      <c r="G94" s="1"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>9</v>
       </c>
-      <c r="C95" s="1"/>
-      <c r="E95">
-        <v>313</v>
-      </c>
-      <c r="F95" t="s">
-        <v>22</v>
-      </c>
-      <c r="G95" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+      <c r="B95" t="s">
+        <v>29</v>
+      </c>
+      <c r="C95" s="1">
+        <v>0.6875</v>
+      </c>
+      <c r="D95">
+        <v>311</v>
+      </c>
+      <c r="G95" s="1"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>9</v>
       </c>
-      <c r="C96" s="1"/>
-      <c r="E96">
-        <v>450</v>
-      </c>
-      <c r="F96" t="s">
-        <v>20</v>
-      </c>
-      <c r="G96" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+      <c r="B96" t="s">
+        <v>22</v>
+      </c>
+      <c r="C96" s="1">
+        <v>0.6875</v>
+      </c>
+      <c r="D96">
+        <v>610</v>
+      </c>
+      <c r="G96" s="1"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>9</v>
-      </c>
-      <c r="C97" s="1"/>
-      <c r="E97">
-        <v>520</v>
-      </c>
-      <c r="F97" t="s">
-        <v>8</v>
-      </c>
-      <c r="G97" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B97" t="s">
+        <v>30</v>
+      </c>
+      <c r="C97" s="1">
+        <v>0.6958333333333333</v>
+      </c>
+      <c r="D97">
+        <v>4321</v>
+      </c>
+      <c r="G97" s="1"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>9</v>
       </c>
-      <c r="C98" s="1"/>
-      <c r="E98">
-        <v>588</v>
-      </c>
-      <c r="F98" t="s">
-        <v>19</v>
-      </c>
-      <c r="G98" s="1">
-        <v>0.73611111111111116</v>
-      </c>
+      <c r="B98" t="s">
+        <v>23</v>
+      </c>
+      <c r="C98" s="1">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="D98">
+        <v>322</v>
+      </c>
+      <c r="G98" s="1"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
@@ -2032,13 +2041,13 @@
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>448</v>
+        <v>320</v>
       </c>
       <c r="F99" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G99" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.72222222222222221</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2047,43 +2056,43 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>534</v>
+        <v>326</v>
       </c>
       <c r="F100" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G100" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>36</v>
-      </c>
-      <c r="B101" t="s">
-        <v>19</v>
-      </c>
-      <c r="C101" s="1">
-        <v>0.75694444444444442</v>
-      </c>
-      <c r="D101">
-        <v>222</v>
-      </c>
-      <c r="G101" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C101" s="1"/>
+      <c r="E101">
+        <v>560</v>
+      </c>
+      <c r="F101" t="s">
+        <v>25</v>
+      </c>
+      <c r="G101" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C102" s="1"/>
       <c r="E102">
-        <v>4308</v>
+        <v>313</v>
       </c>
       <c r="F102" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="G102" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -2092,13 +2101,13 @@
       </c>
       <c r="C103" s="1"/>
       <c r="E103">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="F103" t="s">
         <v>8</v>
       </c>
       <c r="G103" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -2107,177 +2116,177 @@
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>660</v>
+        <v>530</v>
       </c>
       <c r="F104" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G104" s="1">
-        <v>0.77083333333333337</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>27</v>
-      </c>
-      <c r="B105" t="s">
-        <v>26</v>
-      </c>
-      <c r="C105" s="1">
-        <v>0.77847222222222223</v>
-      </c>
-      <c r="D105">
-        <v>2657</v>
-      </c>
-      <c r="G105" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C105" s="1"/>
+      <c r="E105">
+        <v>588</v>
+      </c>
+      <c r="F105" t="s">
+        <v>19</v>
+      </c>
+      <c r="G105" s="1">
+        <v>0.73611111111111116</v>
+      </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>7</v>
-      </c>
-      <c r="B106" t="s">
-        <v>28</v>
-      </c>
-      <c r="C106" s="1">
-        <v>0.79027777777777775</v>
-      </c>
-      <c r="D106">
-        <v>742</v>
-      </c>
-      <c r="G106" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C106" s="1"/>
+      <c r="E106">
+        <v>448</v>
+      </c>
+      <c r="F106" t="s">
+        <v>11</v>
+      </c>
+      <c r="G106" s="1">
+        <v>0.74305555555555558</v>
+      </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C107" s="1"/>
       <c r="E107">
-        <v>4312</v>
+        <v>534</v>
       </c>
       <c r="F107" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G107" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="B108" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C108" s="1">
-        <v>0.79513888888888884</v>
+        <v>0.75694444444444442</v>
       </c>
       <c r="D108">
-        <v>431</v>
+        <v>222</v>
       </c>
       <c r="G108" s="1"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C109" s="1"/>
       <c r="E109">
-        <v>670</v>
+        <v>4308</v>
       </c>
       <c r="F109" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G109" s="1">
-        <v>0.80555555555555558</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>9</v>
       </c>
-      <c r="B110" t="s">
-        <v>28</v>
-      </c>
-      <c r="C110" s="1">
-        <v>0.81944444444444442</v>
-      </c>
-      <c r="D110">
-        <v>425</v>
-      </c>
-      <c r="G110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="E110">
+        <v>528</v>
+      </c>
+      <c r="F110" t="s">
+        <v>8</v>
+      </c>
+      <c r="G110" s="1">
+        <v>0.76041666666666663</v>
+      </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C111" s="1"/>
       <c r="E111">
-        <v>222</v>
+        <v>660</v>
       </c>
       <c r="F111" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G111" s="1">
-        <v>0.81944444444444442</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>9</v>
       </c>
-      <c r="B112" t="s">
-        <v>37</v>
-      </c>
-      <c r="C112" s="1">
-        <v>0.82291666666666663</v>
-      </c>
-      <c r="D112">
-        <v>329</v>
-      </c>
-      <c r="G112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="E112">
+        <v>558</v>
+      </c>
+      <c r="F112" t="s">
+        <v>25</v>
+      </c>
+      <c r="G112" s="1">
+        <v>0.77777777777777779</v>
+      </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B113" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C113" s="1">
-        <v>0.82638888888888884</v>
+        <v>0.79027777777777775</v>
       </c>
       <c r="D113">
-        <v>523</v>
+        <v>742</v>
       </c>
       <c r="G113" s="1"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>9</v>
-      </c>
-      <c r="B114" t="s">
+        <v>12</v>
+      </c>
+      <c r="C114" s="1"/>
+      <c r="E114">
+        <v>4312</v>
+      </c>
+      <c r="F114" t="s">
         <v>13</v>
       </c>
-      <c r="C114" s="1">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D114">
-        <v>583</v>
-      </c>
-      <c r="G114" s="1"/>
+      <c r="G114" s="1">
+        <v>0.79027777777777775</v>
+      </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C115" s="1">
-        <v>0.84375</v>
+        <v>0.79513888888888884</v>
       </c>
       <c r="D115">
-        <v>325</v>
+        <v>431</v>
       </c>
       <c r="G115" s="1"/>
     </row>
@@ -2285,89 +2294,89 @@
       <c r="A116" t="s">
         <v>9</v>
       </c>
-      <c r="B116" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="1">
-        <v>0.84375</v>
-      </c>
-      <c r="D116">
-        <v>445</v>
-      </c>
-      <c r="G116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="E116">
+        <v>670</v>
+      </c>
+      <c r="F116" t="s">
+        <v>17</v>
+      </c>
+      <c r="G116" s="1">
+        <v>0.80555555555555558</v>
+      </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>9</v>
       </c>
-      <c r="C117" s="1"/>
-      <c r="E117">
-        <v>590</v>
-      </c>
-      <c r="F117" t="s">
-        <v>13</v>
-      </c>
-      <c r="G117" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+      <c r="B117" t="s">
+        <v>30</v>
+      </c>
+      <c r="C117" s="1">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="D117">
+        <v>425</v>
+      </c>
+      <c r="G117" s="1"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>9</v>
-      </c>
-      <c r="B118" t="s">
-        <v>11</v>
-      </c>
-      <c r="C118" s="1">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="D118">
-        <v>449</v>
-      </c>
-      <c r="G118" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="C118" s="1"/>
+      <c r="E118">
+        <v>222</v>
+      </c>
+      <c r="F118" t="s">
+        <v>15</v>
+      </c>
+      <c r="G118" s="1">
+        <v>0.81944444444444442</v>
+      </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B119" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C119" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.82430555555555551</v>
       </c>
       <c r="D119">
-        <v>881</v>
+        <v>2657</v>
       </c>
       <c r="G119" s="1"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B120" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C120" s="1">
-        <v>0.86111111111111116</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D120">
-        <v>4323</v>
+        <v>583</v>
       </c>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B121" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C121" s="1">
-        <v>0.86736111111111114</v>
+        <v>0.84375</v>
       </c>
       <c r="D121">
-        <v>1461</v>
+        <v>325</v>
       </c>
       <c r="G121" s="1"/>
     </row>
@@ -2376,13 +2385,13 @@
         <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C122" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.84375</v>
       </c>
       <c r="D122">
-        <v>563</v>
+        <v>445</v>
       </c>
       <c r="G122" s="1"/>
     </row>
@@ -2391,13 +2400,13 @@
         <v>9</v>
       </c>
       <c r="B123" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C123" s="1">
-        <v>0.875</v>
+        <v>0.85069444444444442</v>
       </c>
       <c r="D123">
-        <v>535</v>
+        <v>393</v>
       </c>
       <c r="G123" s="1"/>
     </row>
@@ -2405,74 +2414,74 @@
       <c r="A124" t="s">
         <v>9</v>
       </c>
-      <c r="B124" t="s">
-        <v>22</v>
-      </c>
-      <c r="C124" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D124">
-        <v>312</v>
-      </c>
-      <c r="G124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="E124">
+        <v>590</v>
+      </c>
+      <c r="F124" t="s">
+        <v>13</v>
+      </c>
+      <c r="G124" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>9</v>
       </c>
       <c r="B125" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C125" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D125">
-        <v>525</v>
+        <v>449</v>
       </c>
       <c r="G125" s="1"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B126" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C126" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D126">
-        <v>589</v>
+        <v>881</v>
       </c>
       <c r="G126" s="1"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B127" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C127" s="1">
-        <v>0.89930555555555547</v>
+        <v>0.86111111111111116</v>
       </c>
       <c r="D127">
-        <v>1425</v>
+        <v>523</v>
       </c>
       <c r="G127" s="1"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B128" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C128" s="1">
-        <v>0.91319444444444442</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D128">
-        <v>585</v>
+        <v>1461</v>
       </c>
       <c r="G128" s="1"/>
     </row>
@@ -2480,150 +2489,150 @@
       <c r="A129" t="s">
         <v>9</v>
       </c>
-      <c r="C129" s="1"/>
-      <c r="E129">
-        <v>315</v>
-      </c>
-      <c r="F129" t="s">
-        <v>20</v>
-      </c>
-      <c r="G129" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B129" t="s">
+        <v>35</v>
+      </c>
+      <c r="C129" s="1">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="D129">
+        <v>443</v>
+      </c>
+      <c r="G129" s="1"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>9</v>
       </c>
-      <c r="C130" s="1"/>
-      <c r="E130">
-        <v>365</v>
-      </c>
-      <c r="F130" t="s">
-        <v>24</v>
-      </c>
-      <c r="G130" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B130" t="s">
+        <v>25</v>
+      </c>
+      <c r="C130" s="1">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="D130">
+        <v>563</v>
+      </c>
+      <c r="G130" s="1"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>9</v>
       </c>
-      <c r="C131" s="1"/>
-      <c r="E131">
-        <v>600</v>
-      </c>
-      <c r="F131" t="s">
-        <v>13</v>
-      </c>
-      <c r="G131" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B131" t="s">
+        <v>42</v>
+      </c>
+      <c r="C131" s="1">
+        <v>0.87152777777777779</v>
+      </c>
+      <c r="D131">
+        <v>409</v>
+      </c>
+      <c r="G131" s="1"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>9</v>
       </c>
-      <c r="C132" s="1"/>
-      <c r="E132">
-        <v>429</v>
-      </c>
-      <c r="F132" t="s">
-        <v>21</v>
-      </c>
-      <c r="G132" s="1">
-        <v>0.92708333333333337</v>
-      </c>
+      <c r="B132" t="s">
+        <v>43</v>
+      </c>
+      <c r="C132" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="D132">
+        <v>527</v>
+      </c>
+      <c r="G132" s="1"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>9</v>
       </c>
-      <c r="C133" s="1"/>
-      <c r="E133">
-        <v>578</v>
-      </c>
-      <c r="F133" t="s">
-        <v>19</v>
-      </c>
-      <c r="G133" s="1">
-        <v>0.93055555555555558</v>
-      </c>
+      <c r="B133" t="s">
+        <v>27</v>
+      </c>
+      <c r="C133" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="D133">
+        <v>535</v>
+      </c>
+      <c r="G133" s="1"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>9</v>
       </c>
-      <c r="C134" s="1"/>
-      <c r="E134">
-        <v>627</v>
-      </c>
-      <c r="F134" t="s">
+      <c r="B134" t="s">
         <v>22</v>
       </c>
-      <c r="G134" s="1">
-        <v>0.93402777777777779</v>
-      </c>
+      <c r="C134" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D134">
+        <v>312</v>
+      </c>
+      <c r="G134" s="1"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>9</v>
       </c>
-      <c r="C135" s="1"/>
-      <c r="E135">
-        <v>568</v>
-      </c>
-      <c r="F135" t="s">
-        <v>17</v>
-      </c>
-      <c r="G135" s="1">
-        <v>0.94097222222222221</v>
-      </c>
+      <c r="B135" t="s">
+        <v>19</v>
+      </c>
+      <c r="C135" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D135">
+        <v>589</v>
+      </c>
+      <c r="G135" s="1"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>9</v>
       </c>
-      <c r="C136" s="1"/>
-      <c r="E136">
-        <v>452</v>
-      </c>
-      <c r="F136" t="s">
-        <v>11</v>
-      </c>
-      <c r="G136" s="1">
-        <v>0.94791666666666663</v>
-      </c>
+      <c r="B136" t="s">
+        <v>13</v>
+      </c>
+      <c r="C136" s="1">
+        <v>0.91319444444444442</v>
+      </c>
+      <c r="D136">
+        <v>585</v>
+      </c>
+      <c r="G136" s="1"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="F137" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G137" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>4336</v>
+        <v>365</v>
       </c>
       <c r="F138" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="G138" s="1">
-        <v>0.9506944444444444</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -2632,13 +2641,13 @@
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>317</v>
+        <v>580</v>
       </c>
       <c r="F139" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G139" s="1">
-        <v>0.95486111111111116</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -2647,13 +2656,13 @@
       </c>
       <c r="C140" s="1"/>
       <c r="E140">
-        <v>432</v>
+        <v>308</v>
       </c>
       <c r="F140" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G140" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.92361111111111116</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -2662,13 +2671,13 @@
       </c>
       <c r="C141" s="1"/>
       <c r="E141">
-        <v>457</v>
+        <v>429</v>
       </c>
       <c r="F141" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G141" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.92708333333333337</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -2677,29 +2686,149 @@
       </c>
       <c r="C142" s="1"/>
       <c r="E142">
-        <v>552</v>
+        <v>578</v>
       </c>
       <c r="F142" t="s">
         <v>19</v>
       </c>
       <c r="G142" s="1">
-        <v>0.97222222222222221</v>
+        <v>0.93055555555555558</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>32</v>
-      </c>
-      <c r="B143" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143" s="1"/>
+      <c r="E143">
+        <v>627</v>
+      </c>
+      <c r="F143" t="s">
+        <v>22</v>
+      </c>
+      <c r="G143" s="1">
+        <v>0.93402777777777779</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>9</v>
+      </c>
+      <c r="C144" s="1"/>
+      <c r="E144">
+        <v>574</v>
+      </c>
+      <c r="F144" t="s">
+        <v>27</v>
+      </c>
+      <c r="G144" s="1">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145" s="1"/>
+      <c r="E145">
+        <v>568</v>
+      </c>
+      <c r="F145" t="s">
+        <v>17</v>
+      </c>
+      <c r="G145" s="1">
+        <v>0.94097222222222221</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="1"/>
+      <c r="E146">
+        <v>452</v>
+      </c>
+      <c r="F146" t="s">
+        <v>11</v>
+      </c>
+      <c r="G146" s="1">
+        <v>0.94791666666666663</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>9</v>
+      </c>
+      <c r="C147" s="1"/>
+      <c r="E147">
+        <v>317</v>
+      </c>
+      <c r="F147" t="s">
         <v>23</v>
       </c>
-      <c r="C143" s="1">
+      <c r="G147" s="1">
+        <v>0.95486111111111116</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>9</v>
+      </c>
+      <c r="C148" s="1"/>
+      <c r="E148">
+        <v>457</v>
+      </c>
+      <c r="F148" t="s">
+        <v>16</v>
+      </c>
+      <c r="G148" s="1">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>9</v>
+      </c>
+      <c r="C149" s="1"/>
+      <c r="E149">
+        <v>300</v>
+      </c>
+      <c r="F149" t="s">
+        <v>15</v>
+      </c>
+      <c r="G149" s="1">
+        <v>0.96180555555555558</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>9</v>
+      </c>
+      <c r="C150" s="1"/>
+      <c r="E150">
+        <v>556</v>
+      </c>
+      <c r="F150" t="s">
+        <v>19</v>
+      </c>
+      <c r="G150" s="1">
+        <v>0.97222222222222221</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>36</v>
+      </c>
+      <c r="B151" t="s">
+        <v>23</v>
+      </c>
+      <c r="C151" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D143">
+      <c r="D151">
         <v>878</v>
       </c>
-      <c r="G143" s="1"/>
+      <c r="G151" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEFC8E11-4056-417E-A6BE-372DA3315DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C18C9BB8-0D31-482D-B7E1-CB4649578DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7A3D3D8B-5B9D-4A78-9D52-130611081818}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2D26AC11-2CBB-4156-B221-07E64A87076B}"/>
   </bookViews>
   <sheets>
-    <sheet name="18-06" sheetId="1" r:id="rId1"/>
+    <sheet name="19-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="42">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,7 +83,7 @@
     <t>KIAD</t>
   </si>
   <si>
-    <t>KONT</t>
+    <t>MHLM</t>
   </si>
   <si>
     <t>LEMD</t>
@@ -119,58 +119,52 @@
     <t>KSFO</t>
   </si>
   <si>
+    <t>KMIA</t>
+  </si>
+  <si>
+    <t>FFT</t>
+  </si>
+  <si>
+    <t>KDFW</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
+    <t>KIAH</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>KATL</t>
+  </si>
+  <si>
+    <t>CMP</t>
+  </si>
+  <si>
+    <t>AMX</t>
+  </si>
+  <si>
+    <t>SKRG</t>
+  </si>
+  <si>
+    <t>KMCO</t>
+  </si>
+  <si>
+    <t>IBE</t>
+  </si>
+  <si>
+    <t>CYUL</t>
+  </si>
+  <si>
+    <t>KBOS</t>
+  </si>
+  <si>
+    <t>KOAK</t>
+  </si>
+  <si>
     <t>KEWR</t>
-  </si>
-  <si>
-    <t>MHLM</t>
-  </si>
-  <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>KMIA</t>
-  </si>
-  <si>
-    <t>KIAH</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>KATL</t>
-  </si>
-  <si>
-    <t>TAG</t>
-  </si>
-  <si>
-    <t>MHRO</t>
-  </si>
-  <si>
-    <t>KDFW</t>
-  </si>
-  <si>
-    <t>CMP</t>
-  </si>
-  <si>
-    <t>AMX</t>
-  </si>
-  <si>
-    <t>SKRG</t>
-  </si>
-  <si>
-    <t>MMUN</t>
-  </si>
-  <si>
-    <t>IBE</t>
-  </si>
-  <si>
-    <t>KBOS</t>
-  </si>
-  <si>
-    <t>KORD</t>
-  </si>
-  <si>
-    <t>KLAS</t>
   </si>
 </sst>
 </file>
@@ -545,8 +539,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{175611BB-4E45-4BD4-8461-1BF04AF30F76}">
-  <dimension ref="A1:G151"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{508C324D-6636-4368-830D-49D95E85D773}">
+  <dimension ref="A1:G146"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -627,7 +621,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
@@ -711,7 +705,7 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D10">
-        <v>531</v>
+        <v>575</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -777,14 +771,14 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15">
         <v>3154</v>
       </c>
       <c r="F15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G15" s="1">
         <v>0.25</v>
@@ -807,14 +801,14 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" s="1"/>
       <c r="E17">
         <v>3154</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G17" s="1">
         <v>0.25069444444444444</v>
@@ -1002,17 +996,17 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C30" s="1"/>
       <c r="E30">
-        <v>319</v>
+        <v>4326</v>
       </c>
       <c r="F30" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G30" s="1">
-        <v>0.3125</v>
+        <v>0.29791666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1021,10 +1015,10 @@
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G31" s="1">
         <v>0.3125</v>
@@ -1036,10 +1030,10 @@
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>396</v>
+        <v>323</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G32" s="1">
         <v>0.3125</v>
@@ -1047,14 +1041,14 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>884</v>
+        <v>328</v>
       </c>
       <c r="F33" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G33" s="1">
         <v>0.3125</v>
@@ -1066,13 +1060,13 @@
       </c>
       <c r="C34" s="1"/>
       <c r="E34">
-        <v>310</v>
+        <v>396</v>
       </c>
       <c r="F34" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G34" s="1">
-        <v>0.31597222222222221</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1081,10 +1075,10 @@
       </c>
       <c r="C35" s="1"/>
       <c r="E35">
-        <v>440</v>
+        <v>310</v>
       </c>
       <c r="F35" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G35" s="1">
         <v>0.31597222222222221</v>
@@ -1096,10 +1090,10 @@
       </c>
       <c r="C36" s="1"/>
       <c r="E36">
-        <v>536</v>
+        <v>440</v>
       </c>
       <c r="F36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G36" s="1">
         <v>0.31597222222222221</v>
@@ -1109,16 +1103,16 @@
       <c r="A37" t="s">
         <v>9</v>
       </c>
-      <c r="B37" t="s">
-        <v>19</v>
-      </c>
-      <c r="C37" s="1">
-        <v>0.31944444444444442</v>
-      </c>
-      <c r="D37">
-        <v>321</v>
-      </c>
-      <c r="G37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="E37">
+        <v>536</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.31597222222222221</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
@@ -1129,7 +1123,7 @@
         <v>444</v>
       </c>
       <c r="F38" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G38" s="1">
         <v>0.32291666666666669</v>
@@ -1152,17 +1146,17 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C40" s="1"/>
       <c r="E40">
-        <v>368</v>
+        <v>4322</v>
       </c>
       <c r="F40" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G40" s="1">
-        <v>0.33333333333333331</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1171,10 +1165,10 @@
       </c>
       <c r="C41" s="1"/>
       <c r="E41">
-        <v>522</v>
+        <v>368</v>
       </c>
       <c r="F41" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G41" s="1">
         <v>0.33333333333333331</v>
@@ -1184,46 +1178,46 @@
       <c r="A42" t="s">
         <v>9</v>
       </c>
-      <c r="B42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D42">
-        <v>601</v>
-      </c>
-      <c r="G42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="E42">
+        <v>522</v>
+      </c>
+      <c r="F42" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.33333333333333331</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="C43" s="1"/>
-      <c r="E43">
-        <v>383</v>
-      </c>
-      <c r="F43" t="s">
-        <v>24</v>
-      </c>
-      <c r="G43" s="1">
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" s="1">
         <v>0.33680555555555558</v>
       </c>
+      <c r="D43">
+        <v>309</v>
+      </c>
+      <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="1"/>
-      <c r="E44">
-        <v>454</v>
-      </c>
-      <c r="F44" t="s">
-        <v>11</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0.34027777777777779</v>
-      </c>
+      <c r="B44" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="1">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="D44">
+        <v>581</v>
+      </c>
+      <c r="G44" s="1"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -1231,13 +1225,13 @@
       </c>
       <c r="C45" s="1"/>
       <c r="E45">
-        <v>324</v>
+        <v>383</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G45" s="1">
-        <v>0.34375</v>
+        <v>0.33680555555555558</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1246,13 +1240,13 @@
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>572</v>
+        <v>454</v>
       </c>
       <c r="F46" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G46" s="1">
-        <v>0.34375</v>
+        <v>0.34027777777777779</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1261,10 +1255,10 @@
       </c>
       <c r="C47" s="1"/>
       <c r="E47">
-        <v>744</v>
+        <v>324</v>
       </c>
       <c r="F47" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G47" s="1">
         <v>0.34375</v>
@@ -1276,29 +1270,29 @@
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>430</v>
+        <v>554</v>
       </c>
       <c r="F48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G48" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>9</v>
-      </c>
-      <c r="B49" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="1">
-        <v>0.37152777777777779</v>
-      </c>
-      <c r="D49">
-        <v>451</v>
-      </c>
-      <c r="G49" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="C49" s="1"/>
+      <c r="E49">
+        <v>884</v>
+      </c>
+      <c r="F49" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0.35347222222222219</v>
+      </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -1306,44 +1300,44 @@
       </c>
       <c r="C50" s="1"/>
       <c r="E50">
-        <v>526</v>
+        <v>422</v>
       </c>
       <c r="F50" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G50" s="1">
-        <v>0.375</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C51" s="1"/>
       <c r="E51">
-        <v>4320</v>
+        <v>430</v>
       </c>
       <c r="F51" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G51" s="1">
-        <v>0.38333333333333336</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="1"/>
-      <c r="E52">
-        <v>369</v>
-      </c>
-      <c r="F52" t="s">
-        <v>38</v>
-      </c>
-      <c r="G52" s="1">
-        <v>0.3888888888888889</v>
-      </c>
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.37847222222222221</v>
+      </c>
+      <c r="D52">
+        <v>559</v>
+      </c>
+      <c r="G52" s="1"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -1351,74 +1345,74 @@
       </c>
       <c r="C53" s="1"/>
       <c r="E53">
-        <v>582</v>
+        <v>524</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G53" s="1">
-        <v>0.39930555555555558</v>
+        <v>0.38194444444444442</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>12</v>
-      </c>
-      <c r="B54" t="s">
-        <v>26</v>
-      </c>
-      <c r="C54" s="1">
-        <v>0.40902777777777777</v>
-      </c>
-      <c r="D54">
-        <v>4337</v>
-      </c>
-      <c r="G54" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="E54">
+        <v>369</v>
+      </c>
+      <c r="F54" t="s">
+        <v>35</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0.3888888888888889</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>9</v>
       </c>
-      <c r="B55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C55" s="1">
-        <v>0.41319444444444442</v>
-      </c>
-      <c r="D55">
-        <v>569</v>
-      </c>
-      <c r="G55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="E55">
+        <v>582</v>
+      </c>
+      <c r="F55" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0.39930555555555558</v>
+      </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
-      <c r="C56" s="1"/>
-      <c r="E56">
-        <v>392</v>
-      </c>
-      <c r="F56" t="s">
-        <v>20</v>
-      </c>
-      <c r="G56" s="1">
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" s="1">
         <v>0.41319444444444442</v>
       </c>
+      <c r="D56">
+        <v>569</v>
+      </c>
+      <c r="G56" s="1"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>9</v>
-      </c>
-      <c r="C57" s="1"/>
-      <c r="E57">
-        <v>408</v>
-      </c>
-      <c r="F57" t="s">
-        <v>42</v>
-      </c>
-      <c r="G57" s="1">
-        <v>0.41319444444444442</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B57" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D57">
+        <v>342</v>
+      </c>
+      <c r="G57" s="1"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -1440,7 +1434,7 @@
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C59" s="1">
         <v>0.42708333333333331</v>
@@ -1470,13 +1464,13 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C61" s="1">
-        <v>0.4513888888888889</v>
+        <v>0.4548611111111111</v>
       </c>
       <c r="D61">
-        <v>573</v>
+        <v>318</v>
       </c>
       <c r="G61" s="1"/>
     </row>
@@ -1485,75 +1479,75 @@
         <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C62" s="1">
-        <v>0.4513888888888889</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D62">
-        <v>745</v>
+        <v>384</v>
       </c>
       <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B63" t="s">
-        <v>22</v>
-      </c>
-      <c r="C63" s="1">
-        <v>0.4548611111111111</v>
-      </c>
-      <c r="D63">
-        <v>318</v>
-      </c>
-      <c r="G63" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C63" s="1"/>
+      <c r="E63">
+        <v>343</v>
+      </c>
+      <c r="F63" t="s">
+        <v>28</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0.46180555555555558</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C64" s="1">
-        <v>0.46180555555555558</v>
+        <v>0.47291666666666665</v>
       </c>
       <c r="D64">
-        <v>384</v>
+        <v>495</v>
       </c>
       <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C65" s="1">
-        <v>0.47291666666666665</v>
+        <v>0.47847222222222219</v>
       </c>
       <c r="D65">
-        <v>495</v>
+        <v>1194</v>
       </c>
       <c r="G65" s="1"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>7</v>
-      </c>
-      <c r="B66" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="E66">
+        <v>584</v>
+      </c>
+      <c r="F66" t="s">
         <v>13</v>
       </c>
-      <c r="C66" s="1">
-        <v>0.47847222222222219</v>
-      </c>
-      <c r="D66">
-        <v>1194</v>
-      </c>
-      <c r="G66" s="1"/>
+      <c r="G66" s="1">
+        <v>0.49305555555555558</v>
+      </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
@@ -1561,13 +1555,13 @@
       </c>
       <c r="C67" s="1"/>
       <c r="E67">
-        <v>584</v>
+        <v>385</v>
       </c>
       <c r="F67" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G67" s="1">
-        <v>0.49305555555555558</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -1576,149 +1570,149 @@
       </c>
       <c r="C68" s="1"/>
       <c r="E68">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="F68" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G68" s="1">
-        <v>0.49652777777777779</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69" s="1"/>
-      <c r="E69">
-        <v>385</v>
-      </c>
-      <c r="F69" t="s">
-        <v>24</v>
-      </c>
-      <c r="G69" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B69" t="s">
+        <v>30</v>
+      </c>
+      <c r="C69" s="1">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D69">
+        <v>1441</v>
+      </c>
+      <c r="G69" s="1"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C70" s="1"/>
       <c r="E70">
-        <v>424</v>
+        <v>1508</v>
       </c>
       <c r="F70" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G70" s="1">
-        <v>0.50347222222222221</v>
+        <v>0.51597222222222228</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>9</v>
-      </c>
-      <c r="C71" s="1"/>
-      <c r="E71">
-        <v>442</v>
-      </c>
-      <c r="F71" t="s">
-        <v>35</v>
-      </c>
-      <c r="G71" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B71" t="s">
+        <v>32</v>
+      </c>
+      <c r="C71" s="1">
+        <v>0.5180555555555556</v>
+      </c>
+      <c r="D71">
+        <v>1910</v>
+      </c>
+      <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C72" s="1">
-        <v>0.51041666666666663</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="D72">
-        <v>1441</v>
+        <v>937</v>
       </c>
       <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>28</v>
-      </c>
-      <c r="C73" s="1"/>
-      <c r="E73">
-        <v>1508</v>
-      </c>
-      <c r="F73" t="s">
-        <v>29</v>
-      </c>
-      <c r="G73" s="1">
-        <v>0.51597222222222228</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B73" t="s">
+        <v>23</v>
+      </c>
+      <c r="C73" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D73">
+        <v>816</v>
+      </c>
+      <c r="G73" s="1"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>31</v>
-      </c>
-      <c r="B74" t="s">
-        <v>32</v>
-      </c>
-      <c r="C74" s="1">
-        <v>0.5180555555555556</v>
-      </c>
-      <c r="D74">
-        <v>1910</v>
-      </c>
-      <c r="G74" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="E74">
+        <v>1458</v>
+      </c>
+      <c r="F74" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0.55555555555555558</v>
+      </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>33</v>
-      </c>
-      <c r="B75" t="s">
-        <v>34</v>
-      </c>
-      <c r="C75" s="1">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D75">
-        <v>420</v>
-      </c>
-      <c r="G75" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="E75">
+        <v>380</v>
+      </c>
+      <c r="F75" t="s">
+        <v>28</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0.57222222222222219</v>
+      </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>28</v>
-      </c>
-      <c r="B76" t="s">
-        <v>35</v>
-      </c>
-      <c r="C76" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D76">
-        <v>937</v>
-      </c>
-      <c r="G76" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="E76">
+        <v>1468</v>
+      </c>
+      <c r="F76" t="s">
+        <v>30</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0.57638888888888895</v>
+      </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>36</v>
-      </c>
-      <c r="B77" t="s">
-        <v>23</v>
-      </c>
-      <c r="C77" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D77">
-        <v>816</v>
-      </c>
-      <c r="G77" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="E77">
+        <v>1978</v>
+      </c>
+      <c r="F77" t="s">
+        <v>32</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0.57708333333333328</v>
+      </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
@@ -1726,177 +1720,177 @@
       </c>
       <c r="C78" s="1"/>
       <c r="E78">
-        <v>421</v>
+        <v>871</v>
       </c>
       <c r="F78" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G78" s="1">
-        <v>0.55208333333333337</v>
+        <v>0.58194444444444449</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="1"/>
-      <c r="E79">
-        <v>1458</v>
-      </c>
-      <c r="F79" t="s">
-        <v>13</v>
-      </c>
-      <c r="G79" s="1">
-        <v>0.55555555555555558</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="1">
+        <v>0.59375</v>
+      </c>
+      <c r="D79">
+        <v>628</v>
+      </c>
+      <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>28</v>
-      </c>
-      <c r="C80" s="1"/>
-      <c r="E80">
-        <v>380</v>
-      </c>
-      <c r="F80" t="s">
-        <v>35</v>
-      </c>
-      <c r="G80" s="1">
-        <v>0.57222222222222219</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B80" t="s">
+        <v>30</v>
+      </c>
+      <c r="C80" s="1">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D80">
+        <v>1290</v>
+      </c>
+      <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>7</v>
-      </c>
-      <c r="C81" s="1"/>
-      <c r="E81">
-        <v>1468</v>
-      </c>
-      <c r="F81" t="s">
-        <v>30</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0.57638888888888895</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B81" t="s">
+        <v>19</v>
+      </c>
+      <c r="C81" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="D81">
+        <v>557</v>
+      </c>
+      <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C82" s="1"/>
       <c r="E82">
-        <v>1978</v>
+        <v>629</v>
       </c>
       <c r="F82" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G82" s="1">
-        <v>0.57708333333333328</v>
+        <v>0.64722222222222225</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>36</v>
-      </c>
-      <c r="C83" s="1"/>
-      <c r="E83">
-        <v>871</v>
-      </c>
-      <c r="F83" t="s">
-        <v>23</v>
-      </c>
-      <c r="G83" s="1">
-        <v>0.58194444444444449</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B83" t="s">
+        <v>24</v>
+      </c>
+      <c r="C83" s="1">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D83">
+        <v>382</v>
+      </c>
+      <c r="G83" s="1"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>37</v>
-      </c>
-      <c r="B84" t="s">
-        <v>18</v>
-      </c>
-      <c r="C84" s="1">
-        <v>0.59375</v>
-      </c>
-      <c r="D84">
-        <v>628</v>
-      </c>
-      <c r="G84" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C84" s="1"/>
+      <c r="E84">
+        <v>1130</v>
+      </c>
+      <c r="F84" t="s">
+        <v>30</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B85" t="s">
         <v>30</v>
       </c>
       <c r="C85" s="1">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D85">
-        <v>1290</v>
+        <v>367</v>
       </c>
       <c r="G85" s="1"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>37</v>
-      </c>
-      <c r="C86" s="1"/>
-      <c r="E86">
-        <v>629</v>
-      </c>
-      <c r="F86" t="s">
-        <v>18</v>
-      </c>
-      <c r="G86" s="1">
-        <v>0.64722222222222225</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B86" t="s">
+        <v>35</v>
+      </c>
+      <c r="C86" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D86">
+        <v>370</v>
+      </c>
+      <c r="G86" s="1"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C87" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D87">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="G87" s="1"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>7</v>
-      </c>
-      <c r="C88" s="1"/>
-      <c r="E88">
-        <v>1130</v>
-      </c>
-      <c r="F88" t="s">
-        <v>30</v>
-      </c>
-      <c r="G88" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B88" t="s">
+        <v>28</v>
+      </c>
+      <c r="C88" s="1">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="D88">
+        <v>441</v>
+      </c>
+      <c r="G88" s="1"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C89" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D89">
-        <v>367</v>
+        <v>423</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -1905,13 +1899,13 @@
         <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C90" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.6875</v>
       </c>
       <c r="D90">
-        <v>370</v>
+        <v>311</v>
       </c>
       <c r="G90" s="1"/>
     </row>
@@ -1920,13 +1914,13 @@
         <v>9</v>
       </c>
       <c r="B91" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C91" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.6875</v>
       </c>
       <c r="D91">
-        <v>397</v>
+        <v>555</v>
       </c>
       <c r="G91" s="1"/>
     </row>
@@ -1935,13 +1929,13 @@
         <v>9</v>
       </c>
       <c r="B92" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C92" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.6875</v>
       </c>
       <c r="D92">
-        <v>553</v>
+        <v>610</v>
       </c>
       <c r="G92" s="1"/>
     </row>
@@ -1950,28 +1944,28 @@
         <v>9</v>
       </c>
       <c r="B93" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C93" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.70138888888888884</v>
       </c>
       <c r="D93">
-        <v>441</v>
+        <v>322</v>
       </c>
       <c r="G93" s="1"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C94" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.72777777777777775</v>
       </c>
       <c r="D94">
-        <v>435</v>
+        <v>4327</v>
       </c>
       <c r="G94" s="1"/>
     </row>
@@ -1979,61 +1973,61 @@
       <c r="A95" t="s">
         <v>9</v>
       </c>
-      <c r="B95" t="s">
-        <v>29</v>
-      </c>
-      <c r="C95" s="1">
-        <v>0.6875</v>
-      </c>
-      <c r="D95">
-        <v>311</v>
-      </c>
-      <c r="G95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="E95">
+        <v>326</v>
+      </c>
+      <c r="F95" t="s">
+        <v>10</v>
+      </c>
+      <c r="G95" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>9</v>
       </c>
-      <c r="B96" t="s">
-        <v>22</v>
-      </c>
-      <c r="C96" s="1">
-        <v>0.6875</v>
-      </c>
-      <c r="D96">
-        <v>610</v>
-      </c>
-      <c r="G96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="E96">
+        <v>560</v>
+      </c>
+      <c r="F96" t="s">
+        <v>25</v>
+      </c>
+      <c r="G96" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>12</v>
-      </c>
-      <c r="B97" t="s">
-        <v>30</v>
-      </c>
-      <c r="C97" s="1">
-        <v>0.6958333333333333</v>
-      </c>
-      <c r="D97">
-        <v>4321</v>
-      </c>
-      <c r="G97" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C97" s="1"/>
+      <c r="E97">
+        <v>313</v>
+      </c>
+      <c r="F97" t="s">
+        <v>22</v>
+      </c>
+      <c r="G97" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>9</v>
       </c>
-      <c r="B98" t="s">
-        <v>23</v>
-      </c>
-      <c r="C98" s="1">
-        <v>0.70138888888888884</v>
-      </c>
-      <c r="D98">
-        <v>322</v>
-      </c>
-      <c r="G98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="E98">
+        <v>450</v>
+      </c>
+      <c r="F98" t="s">
+        <v>20</v>
+      </c>
+      <c r="G98" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
@@ -2041,13 +2035,13 @@
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>320</v>
+        <v>520</v>
       </c>
       <c r="F99" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G99" s="1">
-        <v>0.72222222222222221</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2056,13 +2050,13 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>326</v>
+        <v>588</v>
       </c>
       <c r="F100" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G100" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.73611111111111116</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -2071,13 +2065,13 @@
       </c>
       <c r="C101" s="1"/>
       <c r="E101">
-        <v>560</v>
+        <v>448</v>
       </c>
       <c r="F101" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G101" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -2086,43 +2080,43 @@
       </c>
       <c r="C102" s="1"/>
       <c r="E102">
-        <v>313</v>
+        <v>534</v>
       </c>
       <c r="F102" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G102" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>9</v>
-      </c>
-      <c r="C103" s="1"/>
-      <c r="E103">
-        <v>520</v>
-      </c>
-      <c r="F103" t="s">
-        <v>8</v>
-      </c>
-      <c r="G103" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B103" t="s">
+        <v>19</v>
+      </c>
+      <c r="C103" s="1">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="D103">
+        <v>222</v>
+      </c>
+      <c r="G103" s="1"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>530</v>
+        <v>4308</v>
       </c>
       <c r="F104" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G104" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -2131,13 +2125,13 @@
       </c>
       <c r="C105" s="1"/>
       <c r="E105">
-        <v>588</v>
+        <v>528</v>
       </c>
       <c r="F105" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G105" s="1">
-        <v>0.73611111111111116</v>
+        <v>0.76041666666666663</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -2146,59 +2140,59 @@
       </c>
       <c r="C106" s="1"/>
       <c r="E106">
-        <v>448</v>
+        <v>660</v>
       </c>
       <c r="F106" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G106" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>9</v>
-      </c>
-      <c r="C107" s="1"/>
-      <c r="E107">
-        <v>534</v>
-      </c>
-      <c r="F107" t="s">
-        <v>27</v>
-      </c>
-      <c r="G107" s="1">
-        <v>0.74305555555555558</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B107" t="s">
+        <v>30</v>
+      </c>
+      <c r="C107" s="1">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="D107">
+        <v>742</v>
+      </c>
+      <c r="G107" s="1"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>40</v>
-      </c>
-      <c r="B108" t="s">
-        <v>19</v>
-      </c>
-      <c r="C108" s="1">
-        <v>0.75694444444444442</v>
-      </c>
-      <c r="D108">
-        <v>222</v>
-      </c>
-      <c r="G108" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C108" s="1"/>
+      <c r="E108">
+        <v>4312</v>
+      </c>
+      <c r="F108" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" s="1">
+        <v>0.79027777777777775</v>
+      </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>12</v>
-      </c>
-      <c r="C109" s="1"/>
-      <c r="E109">
-        <v>4308</v>
-      </c>
-      <c r="F109" t="s">
-        <v>8</v>
-      </c>
-      <c r="G109" s="1">
-        <v>0.75763888888888886</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B109" t="s">
+        <v>18</v>
+      </c>
+      <c r="C109" s="1">
+        <v>0.79513888888888884</v>
+      </c>
+      <c r="D109">
+        <v>431</v>
+      </c>
+      <c r="G109" s="1"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -2206,87 +2200,87 @@
       </c>
       <c r="C110" s="1"/>
       <c r="E110">
-        <v>528</v>
+        <v>670</v>
       </c>
       <c r="F110" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G110" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.80555555555555558</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C111" s="1"/>
       <c r="E111">
-        <v>660</v>
+        <v>222</v>
       </c>
       <c r="F111" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G111" s="1">
-        <v>0.77083333333333337</v>
+        <v>0.80902777777777779</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>9</v>
       </c>
-      <c r="C112" s="1"/>
-      <c r="E112">
-        <v>558</v>
-      </c>
-      <c r="F112" t="s">
-        <v>25</v>
-      </c>
-      <c r="G112" s="1">
-        <v>0.77777777777777779</v>
-      </c>
+      <c r="B112" t="s">
+        <v>30</v>
+      </c>
+      <c r="C112" s="1">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="D112">
+        <v>425</v>
+      </c>
+      <c r="G112" s="1"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C113" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="D113">
-        <v>742</v>
+        <v>329</v>
       </c>
       <c r="G113" s="1"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>12</v>
-      </c>
-      <c r="C114" s="1"/>
-      <c r="E114">
-        <v>4312</v>
-      </c>
-      <c r="F114" t="s">
-        <v>13</v>
-      </c>
-      <c r="G114" s="1">
-        <v>0.79027777777777775</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B114" t="s">
+        <v>26</v>
+      </c>
+      <c r="C114" s="1">
+        <v>0.82430555555555551</v>
+      </c>
+      <c r="D114">
+        <v>2657</v>
+      </c>
+      <c r="G114" s="1"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C115" s="1">
-        <v>0.79513888888888884</v>
+        <v>0.82638888888888884</v>
       </c>
       <c r="D115">
-        <v>431</v>
+        <v>523</v>
       </c>
       <c r="G115" s="1"/>
     </row>
@@ -2294,119 +2288,119 @@
       <c r="A116" t="s">
         <v>9</v>
       </c>
-      <c r="C116" s="1"/>
-      <c r="E116">
-        <v>670</v>
-      </c>
-      <c r="F116" t="s">
-        <v>17</v>
-      </c>
-      <c r="G116" s="1">
-        <v>0.80555555555555558</v>
-      </c>
+      <c r="B116" t="s">
+        <v>13</v>
+      </c>
+      <c r="C116" s="1">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D116">
+        <v>583</v>
+      </c>
+      <c r="G116" s="1"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>9</v>
       </c>
       <c r="B117" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C117" s="1">
-        <v>0.81944444444444442</v>
+        <v>0.84375</v>
       </c>
       <c r="D117">
-        <v>425</v>
+        <v>325</v>
       </c>
       <c r="G117" s="1"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>40</v>
-      </c>
-      <c r="C118" s="1"/>
-      <c r="E118">
-        <v>222</v>
-      </c>
-      <c r="F118" t="s">
-        <v>15</v>
-      </c>
-      <c r="G118" s="1">
-        <v>0.81944444444444442</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B118" t="s">
+        <v>39</v>
+      </c>
+      <c r="C118" s="1">
+        <v>0.84375</v>
+      </c>
+      <c r="D118">
+        <v>445</v>
+      </c>
+      <c r="G118" s="1"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>28</v>
-      </c>
-      <c r="B119" t="s">
-        <v>29</v>
-      </c>
-      <c r="C119" s="1">
-        <v>0.82430555555555551</v>
-      </c>
-      <c r="D119">
-        <v>2657</v>
-      </c>
-      <c r="G119" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C119" s="1"/>
+      <c r="E119">
+        <v>590</v>
+      </c>
+      <c r="F119" t="s">
+        <v>13</v>
+      </c>
+      <c r="G119" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>9</v>
       </c>
       <c r="B120" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C120" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D120">
-        <v>583</v>
+        <v>449</v>
       </c>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B121" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C121" s="1">
-        <v>0.84375</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D121">
-        <v>325</v>
+        <v>881</v>
       </c>
       <c r="G121" s="1"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C122" s="1">
-        <v>0.84375</v>
+        <v>0.86111111111111116</v>
       </c>
       <c r="D122">
-        <v>445</v>
+        <v>4323</v>
       </c>
       <c r="G122" s="1"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C123" s="1">
-        <v>0.85069444444444442</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D123">
-        <v>393</v>
+        <v>1461</v>
       </c>
       <c r="G123" s="1"/>
     </row>
@@ -2414,44 +2408,44 @@
       <c r="A124" t="s">
         <v>9</v>
       </c>
-      <c r="C124" s="1"/>
-      <c r="E124">
-        <v>590</v>
-      </c>
-      <c r="F124" t="s">
-        <v>13</v>
-      </c>
-      <c r="G124" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+      <c r="B124" t="s">
+        <v>25</v>
+      </c>
+      <c r="C124" s="1">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="D124">
+        <v>563</v>
+      </c>
+      <c r="G124" s="1"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>9</v>
       </c>
       <c r="B125" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C125" s="1">
-        <v>0.85416666666666663</v>
+        <v>0.875</v>
       </c>
       <c r="D125">
-        <v>449</v>
+        <v>535</v>
       </c>
       <c r="G125" s="1"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B126" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C126" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D126">
-        <v>881</v>
+        <v>312</v>
       </c>
       <c r="G126" s="1"/>
     </row>
@@ -2463,40 +2457,40 @@
         <v>8</v>
       </c>
       <c r="C127" s="1">
-        <v>0.86111111111111116</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D127">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G127" s="1"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B128" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C128" s="1">
-        <v>0.86736111111111114</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D128">
-        <v>1461</v>
+        <v>589</v>
       </c>
       <c r="G128" s="1"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B129" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C129" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.89930555555555547</v>
       </c>
       <c r="D129">
-        <v>443</v>
+        <v>1425</v>
       </c>
       <c r="G129" s="1"/>
     </row>
@@ -2505,13 +2499,13 @@
         <v>9</v>
       </c>
       <c r="B130" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C130" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.91319444444444442</v>
       </c>
       <c r="D130">
-        <v>563</v>
+        <v>585</v>
       </c>
       <c r="G130" s="1"/>
     </row>
@@ -2519,91 +2513,91 @@
       <c r="A131" t="s">
         <v>9</v>
       </c>
-      <c r="B131" t="s">
-        <v>42</v>
-      </c>
-      <c r="C131" s="1">
-        <v>0.87152777777777779</v>
-      </c>
-      <c r="D131">
-        <v>409</v>
-      </c>
-      <c r="G131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="E131">
+        <v>315</v>
+      </c>
+      <c r="F131" t="s">
+        <v>20</v>
+      </c>
+      <c r="G131" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>9</v>
       </c>
-      <c r="B132" t="s">
-        <v>43</v>
-      </c>
-      <c r="C132" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="D132">
-        <v>527</v>
-      </c>
-      <c r="G132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="E132">
+        <v>365</v>
+      </c>
+      <c r="F132" t="s">
+        <v>24</v>
+      </c>
+      <c r="G132" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>9</v>
       </c>
-      <c r="B133" t="s">
-        <v>27</v>
-      </c>
-      <c r="C133" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="D133">
-        <v>535</v>
-      </c>
-      <c r="G133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="E133">
+        <v>600</v>
+      </c>
+      <c r="F133" t="s">
+        <v>13</v>
+      </c>
+      <c r="G133" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>9</v>
       </c>
-      <c r="B134" t="s">
-        <v>22</v>
-      </c>
-      <c r="C134" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D134">
-        <v>312</v>
-      </c>
-      <c r="G134" s="1"/>
+      <c r="C134" s="1"/>
+      <c r="E134">
+        <v>429</v>
+      </c>
+      <c r="F134" t="s">
+        <v>21</v>
+      </c>
+      <c r="G134" s="1">
+        <v>0.92708333333333337</v>
+      </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>9</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C135" s="1"/>
+      <c r="E135">
+        <v>578</v>
+      </c>
+      <c r="F135" t="s">
         <v>19</v>
       </c>
-      <c r="C135" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D135">
-        <v>589</v>
-      </c>
-      <c r="G135" s="1"/>
+      <c r="G135" s="1">
+        <v>0.93055555555555558</v>
+      </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>9</v>
       </c>
-      <c r="B136" t="s">
-        <v>13</v>
-      </c>
-      <c r="C136" s="1">
-        <v>0.91319444444444442</v>
-      </c>
-      <c r="D136">
-        <v>585</v>
-      </c>
-      <c r="G136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="E136">
+        <v>627</v>
+      </c>
+      <c r="F136" t="s">
+        <v>22</v>
+      </c>
+      <c r="G136" s="1">
+        <v>0.93402777777777779</v>
+      </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
@@ -2611,13 +2605,13 @@
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>315</v>
+        <v>574</v>
       </c>
       <c r="F137" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G137" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -2626,13 +2620,13 @@
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>365</v>
+        <v>568</v>
       </c>
       <c r="F138" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G138" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -2641,43 +2635,43 @@
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>580</v>
+        <v>452</v>
       </c>
       <c r="F139" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G139" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C140" s="1"/>
       <c r="E140">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="F140" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G140" s="1">
-        <v>0.92361111111111116</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C141" s="1"/>
       <c r="E141">
-        <v>429</v>
+        <v>4336</v>
       </c>
       <c r="F141" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="G141" s="1">
-        <v>0.92708333333333337</v>
+        <v>0.9506944444444444</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -2686,13 +2680,13 @@
       </c>
       <c r="C142" s="1"/>
       <c r="E142">
-        <v>578</v>
+        <v>317</v>
       </c>
       <c r="F142" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G142" s="1">
-        <v>0.93055555555555558</v>
+        <v>0.95486111111111116</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -2701,13 +2695,13 @@
       </c>
       <c r="C143" s="1"/>
       <c r="E143">
-        <v>627</v>
+        <v>432</v>
       </c>
       <c r="F143" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G143" s="1">
-        <v>0.93402777777777779</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -2716,13 +2710,13 @@
       </c>
       <c r="C144" s="1"/>
       <c r="E144">
-        <v>574</v>
+        <v>457</v>
       </c>
       <c r="F144" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G144" s="1">
-        <v>0.9375</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -2731,104 +2725,29 @@
       </c>
       <c r="C145" s="1"/>
       <c r="E145">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="F145" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G145" s="1">
-        <v>0.94097222222222221</v>
+        <v>0.97222222222222221</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>9</v>
-      </c>
-      <c r="C146" s="1"/>
-      <c r="E146">
-        <v>452</v>
-      </c>
-      <c r="F146" t="s">
-        <v>11</v>
-      </c>
-      <c r="G146" s="1">
-        <v>0.94791666666666663</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>9</v>
-      </c>
-      <c r="C147" s="1"/>
-      <c r="E147">
-        <v>317</v>
-      </c>
-      <c r="F147" t="s">
+        <v>33</v>
+      </c>
+      <c r="B146" t="s">
         <v>23</v>
       </c>
-      <c r="G147" s="1">
-        <v>0.95486111111111116</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>9</v>
-      </c>
-      <c r="C148" s="1"/>
-      <c r="E148">
-        <v>457</v>
-      </c>
-      <c r="F148" t="s">
-        <v>16</v>
-      </c>
-      <c r="G148" s="1">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>9</v>
-      </c>
-      <c r="C149" s="1"/>
-      <c r="E149">
-        <v>300</v>
-      </c>
-      <c r="F149" t="s">
-        <v>15</v>
-      </c>
-      <c r="G149" s="1">
-        <v>0.96180555555555558</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>9</v>
-      </c>
-      <c r="C150" s="1"/>
-      <c r="E150">
-        <v>556</v>
-      </c>
-      <c r="F150" t="s">
-        <v>19</v>
-      </c>
-      <c r="G150" s="1">
-        <v>0.97222222222222221</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>36</v>
-      </c>
-      <c r="B151" t="s">
-        <v>23</v>
-      </c>
-      <c r="C151" s="1">
+      <c r="C146" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D151">
+      <c r="D146">
         <v>878</v>
       </c>
-      <c r="G151" s="1"/>
+      <c r="G146" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C18C9BB8-0D31-482D-B7E1-CB4649578DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21B5230F-6451-484E-9219-EC117ED0A7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2D26AC11-2CBB-4156-B221-07E64A87076B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{87A6EB5F-1EEE-4D76-9157-B48DE173843C}"/>
   </bookViews>
   <sheets>
-    <sheet name="19-06" sheetId="1" r:id="rId1"/>
+    <sheet name="20-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="42">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,6 +83,9 @@
     <t>KIAD</t>
   </si>
   <si>
+    <t>KONT</t>
+  </si>
+  <si>
     <t>MHLM</t>
   </si>
   <si>
@@ -119,27 +122,27 @@
     <t>KSFO</t>
   </si>
   <si>
+    <t>KEWR</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
     <t>KMIA</t>
   </si>
   <si>
-    <t>FFT</t>
+    <t>KIAH</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>KATL</t>
   </si>
   <si>
     <t>KDFW</t>
   </si>
   <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>KIAH</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>KATL</t>
-  </si>
-  <si>
     <t>CMP</t>
   </si>
   <si>
@@ -149,22 +152,19 @@
     <t>SKRG</t>
   </si>
   <si>
-    <t>KMCO</t>
+    <t>MMUN</t>
   </si>
   <si>
     <t>IBE</t>
   </si>
   <si>
-    <t>CYUL</t>
-  </si>
-  <si>
     <t>KBOS</t>
   </si>
   <si>
-    <t>KOAK</t>
-  </si>
-  <si>
-    <t>KEWR</t>
+    <t>KORD</t>
+  </si>
+  <si>
+    <t>KLAS</t>
   </si>
 </sst>
 </file>
@@ -539,8 +539,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{508C324D-6636-4368-830D-49D95E85D773}">
-  <dimension ref="A1:G146"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{994D9681-FB34-4BD8-AD6F-8E5224EAAA3E}">
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -621,14 +621,14 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
         <v>879</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5" s="1">
         <v>0.20347222222222219</v>
@@ -673,7 +673,7 @@
         <v>300</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" s="1">
         <v>0.21527777777777779</v>
@@ -705,7 +705,7 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D10">
-        <v>575</v>
+        <v>531</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -717,40 +717,40 @@
         <v>15</v>
       </c>
       <c r="C11" s="1">
-        <v>0.22916666666666666</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="D11">
-        <v>301</v>
+        <v>575</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1">
-        <v>0.24444444444444444</v>
+        <v>0.22916666666666666</v>
       </c>
       <c r="D12">
-        <v>4309</v>
+        <v>301</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C13" s="1">
-        <v>0.24652777777777779</v>
+        <v>0.24444444444444444</v>
       </c>
       <c r="D13">
-        <v>456</v>
+        <v>4309</v>
       </c>
       <c r="G13" s="1"/>
     </row>
@@ -765,35 +765,35 @@
         <v>0.24652777777777779</v>
       </c>
       <c r="D14">
-        <v>661</v>
+        <v>456</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="E15">
-        <v>3154</v>
-      </c>
-      <c r="F15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0.25</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.24652777777777779</v>
+      </c>
+      <c r="D15">
+        <v>661</v>
+      </c>
+      <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C16" s="1"/>
       <c r="E16">
-        <v>1467</v>
+        <v>3154</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G16" s="1">
         <v>0.25</v>
@@ -801,33 +801,33 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1"/>
       <c r="E17">
-        <v>3154</v>
+        <v>1467</v>
       </c>
       <c r="F17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G17" s="1">
-        <v>0.25069444444444444</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="1">
-        <v>0.25694444444444442</v>
-      </c>
-      <c r="D18">
-        <v>433</v>
-      </c>
-      <c r="G18" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="E18">
+        <v>3154</v>
+      </c>
+      <c r="F18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.25069444444444444</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -840,7 +840,7 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="D19">
-        <v>579</v>
+        <v>433</v>
       </c>
       <c r="G19" s="1"/>
     </row>
@@ -849,13 +849,13 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C20" s="1">
-        <v>0.26041666666666669</v>
+        <v>0.25694444444444442</v>
       </c>
       <c r="D20">
-        <v>529</v>
+        <v>579</v>
       </c>
       <c r="G20" s="1"/>
     </row>
@@ -864,13 +864,13 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C21" s="1">
-        <v>0.2638888888888889</v>
+        <v>0.26041666666666669</v>
       </c>
       <c r="D21">
-        <v>314</v>
+        <v>529</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -882,10 +882,10 @@
         <v>21</v>
       </c>
       <c r="C22" s="1">
-        <v>0.2673611111111111</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="D22">
-        <v>428</v>
+        <v>314</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -900,7 +900,7 @@
         <v>0.2673611111111111</v>
       </c>
       <c r="D23">
-        <v>626</v>
+        <v>428</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -912,10 +912,10 @@
         <v>23</v>
       </c>
       <c r="C24" s="1">
-        <v>0.27083333333333331</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D24">
-        <v>316</v>
+        <v>626</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -930,7 +930,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D25">
-        <v>366</v>
+        <v>316</v>
       </c>
       <c r="G25" s="1"/>
     </row>
@@ -945,7 +945,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D26">
-        <v>561</v>
+        <v>366</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -954,13 +954,13 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C27" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D27">
-        <v>591</v>
+        <v>561</v>
       </c>
       <c r="G27" s="1"/>
     </row>
@@ -969,13 +969,13 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C28" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D28">
-        <v>671</v>
+        <v>591</v>
       </c>
       <c r="G28" s="1"/>
     </row>
@@ -984,44 +984,44 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C29" s="1">
-        <v>0.29166666666666669</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="D29">
-        <v>521</v>
+        <v>671</v>
       </c>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="1"/>
-      <c r="E30">
-        <v>4326</v>
-      </c>
-      <c r="F30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0.29791666666666666</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="D30">
+        <v>521</v>
+      </c>
+      <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>319</v>
+        <v>4326</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G31" s="1">
-        <v>0.3125</v>
+        <v>0.29791666666666666</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F32" t="s">
         <v>23</v>
@@ -1045,10 +1045,10 @@
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="F33" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G33" s="1">
         <v>0.3125</v>
@@ -1063,7 +1063,7 @@
         <v>396</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G34" s="1">
         <v>0.3125</v>
@@ -1071,17 +1071,17 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C35" s="1"/>
       <c r="E35">
-        <v>310</v>
+        <v>884</v>
       </c>
       <c r="F35" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G35" s="1">
-        <v>0.31597222222222221</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1090,10 +1090,10 @@
       </c>
       <c r="C36" s="1"/>
       <c r="E36">
-        <v>440</v>
+        <v>310</v>
       </c>
       <c r="F36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G36" s="1">
         <v>0.31597222222222221</v>
@@ -1105,10 +1105,10 @@
       </c>
       <c r="C37" s="1"/>
       <c r="E37">
-        <v>536</v>
+        <v>440</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G37" s="1">
         <v>0.31597222222222221</v>
@@ -1120,40 +1120,40 @@
       </c>
       <c r="C38" s="1"/>
       <c r="E38">
-        <v>444</v>
+        <v>536</v>
       </c>
       <c r="F38" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G38" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.31597222222222221</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="1"/>
-      <c r="E39">
-        <v>562</v>
-      </c>
-      <c r="F39" t="s">
-        <v>25</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0.32291666666666669</v>
-      </c>
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="D39">
+        <v>321</v>
+      </c>
+      <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C40" s="1"/>
       <c r="E40">
-        <v>4322</v>
+        <v>444</v>
       </c>
       <c r="F40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G40" s="1">
         <v>0.32291666666666669</v>
@@ -1165,13 +1165,13 @@
       </c>
       <c r="C41" s="1"/>
       <c r="E41">
-        <v>368</v>
+        <v>562</v>
       </c>
       <c r="F41" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G41" s="1">
-        <v>0.33333333333333331</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1180,10 +1180,10 @@
       </c>
       <c r="C42" s="1"/>
       <c r="E42">
-        <v>522</v>
+        <v>368</v>
       </c>
       <c r="F42" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G42" s="1">
         <v>0.33333333333333331</v>
@@ -1193,16 +1193,16 @@
       <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="B43" t="s">
-        <v>26</v>
-      </c>
-      <c r="C43" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D43">
-        <v>309</v>
-      </c>
-      <c r="G43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="E43">
+        <v>522</v>
+      </c>
+      <c r="F43" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0.33333333333333331</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -1215,7 +1215,7 @@
         <v>0.33680555555555558</v>
       </c>
       <c r="D44">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="G44" s="1"/>
     </row>
@@ -1228,7 +1228,7 @@
         <v>383</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G45" s="1">
         <v>0.33680555555555558</v>
@@ -1270,10 +1270,10 @@
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="F48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G48" s="1">
         <v>0.34375</v>
@@ -1281,33 +1281,33 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>884</v>
+        <v>430</v>
       </c>
       <c r="F49" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G49" s="1">
-        <v>0.35347222222222219</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>9</v>
       </c>
-      <c r="C50" s="1"/>
-      <c r="E50">
-        <v>422</v>
-      </c>
-      <c r="F50" t="s">
-        <v>36</v>
-      </c>
-      <c r="G50" s="1">
-        <v>0.36458333333333331</v>
-      </c>
+      <c r="B50" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="D50">
+        <v>451</v>
+      </c>
+      <c r="G50" s="1"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
@@ -1315,29 +1315,29 @@
       </c>
       <c r="C51" s="1"/>
       <c r="E51">
-        <v>430</v>
+        <v>526</v>
       </c>
       <c r="F51" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="G51" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" t="s">
-        <v>25</v>
-      </c>
-      <c r="C52" s="1">
-        <v>0.37847222222222221</v>
-      </c>
-      <c r="D52">
-        <v>559</v>
-      </c>
-      <c r="G52" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="E52">
+        <v>4320</v>
+      </c>
+      <c r="F52" t="s">
+        <v>30</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.38333333333333336</v>
+      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -1345,13 +1345,13 @@
       </c>
       <c r="C53" s="1"/>
       <c r="E53">
-        <v>524</v>
+        <v>369</v>
       </c>
       <c r="F53" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="G53" s="1">
-        <v>0.38194444444444442</v>
+        <v>0.3888888888888889</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -1360,36 +1360,36 @@
       </c>
       <c r="C54" s="1"/>
       <c r="E54">
-        <v>369</v>
+        <v>582</v>
       </c>
       <c r="F54" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G54" s="1">
-        <v>0.3888888888888889</v>
+        <v>0.39930555555555558</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C55" s="1"/>
-      <c r="E55">
-        <v>582</v>
-      </c>
-      <c r="F55" t="s">
-        <v>13</v>
-      </c>
-      <c r="G55" s="1">
-        <v>0.39930555555555558</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55" s="1">
+        <v>0.40902777777777777</v>
+      </c>
+      <c r="D55">
+        <v>4337</v>
+      </c>
+      <c r="G55" s="1"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C56" s="1">
         <v>0.41319444444444442</v>
@@ -1401,18 +1401,18 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>27</v>
-      </c>
-      <c r="B57" t="s">
-        <v>28</v>
-      </c>
-      <c r="C57" s="1">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D57">
-        <v>342</v>
-      </c>
-      <c r="G57" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C57" s="1"/>
+      <c r="E57">
+        <v>392</v>
+      </c>
+      <c r="F57" t="s">
+        <v>21</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0.41319444444444442</v>
+      </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -1420,42 +1420,42 @@
       </c>
       <c r="C58" s="1"/>
       <c r="E58">
-        <v>609</v>
+        <v>408</v>
       </c>
       <c r="F58" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G58" s="1">
-        <v>0.4236111111111111</v>
+        <v>0.41319444444444442</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>9</v>
       </c>
-      <c r="B59" t="s">
-        <v>14</v>
-      </c>
-      <c r="C59" s="1">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="D59">
-        <v>537</v>
-      </c>
-      <c r="G59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="E59">
+        <v>609</v>
+      </c>
+      <c r="F59" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0.4236111111111111</v>
+      </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C60" s="1">
-        <v>0.44791666666666669</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="D60">
-        <v>455</v>
+        <v>537</v>
       </c>
       <c r="G60" s="1"/>
     </row>
@@ -1464,13 +1464,13 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C61" s="1">
-        <v>0.4548611111111111</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="D61">
-        <v>318</v>
+        <v>455</v>
       </c>
       <c r="G61" s="1"/>
     </row>
@@ -1479,75 +1479,75 @@
         <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C62" s="1">
-        <v>0.46180555555555558</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="D62">
-        <v>384</v>
+        <v>573</v>
       </c>
       <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>27</v>
-      </c>
-      <c r="C63" s="1"/>
-      <c r="E63">
-        <v>343</v>
-      </c>
-      <c r="F63" t="s">
-        <v>28</v>
-      </c>
-      <c r="G63" s="1">
-        <v>0.46180555555555558</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B63" t="s">
+        <v>23</v>
+      </c>
+      <c r="C63" s="1">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="D63">
+        <v>318</v>
+      </c>
+      <c r="G63" s="1"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C64" s="1">
-        <v>0.47291666666666665</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D64">
-        <v>495</v>
+        <v>384</v>
       </c>
       <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C65" s="1">
-        <v>0.47847222222222219</v>
+        <v>0.47291666666666665</v>
       </c>
       <c r="D65">
-        <v>1194</v>
+        <v>495</v>
       </c>
       <c r="G65" s="1"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>9</v>
-      </c>
-      <c r="C66" s="1"/>
-      <c r="E66">
-        <v>584</v>
-      </c>
-      <c r="F66" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" t="s">
         <v>13</v>
       </c>
-      <c r="G66" s="1">
-        <v>0.49305555555555558</v>
-      </c>
+      <c r="C66" s="1">
+        <v>0.47847222222222219</v>
+      </c>
+      <c r="D66">
+        <v>1194</v>
+      </c>
+      <c r="G66" s="1"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
@@ -1555,13 +1555,13 @@
       </c>
       <c r="C67" s="1"/>
       <c r="E67">
-        <v>385</v>
+        <v>584</v>
       </c>
       <c r="F67" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G67" s="1">
-        <v>0.50347222222222221</v>
+        <v>0.49305555555555558</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -1570,253 +1570,253 @@
       </c>
       <c r="C68" s="1"/>
       <c r="E68">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="F68" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G68" s="1">
-        <v>0.50347222222222221</v>
+        <v>0.49652777777777779</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>7</v>
-      </c>
-      <c r="B69" t="s">
-        <v>30</v>
-      </c>
-      <c r="C69" s="1">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="D69">
-        <v>1441</v>
-      </c>
-      <c r="G69" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C69" s="1"/>
+      <c r="E69">
+        <v>385</v>
+      </c>
+      <c r="F69" t="s">
+        <v>25</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C70" s="1"/>
       <c r="E70">
-        <v>1508</v>
+        <v>424</v>
       </c>
       <c r="F70" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G70" s="1">
-        <v>0.51597222222222228</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>31</v>
-      </c>
-      <c r="B71" t="s">
-        <v>32</v>
-      </c>
-      <c r="C71" s="1">
-        <v>0.5180555555555556</v>
-      </c>
-      <c r="D71">
-        <v>1910</v>
-      </c>
-      <c r="G71" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C71" s="1"/>
+      <c r="E71">
+        <v>442</v>
+      </c>
+      <c r="F71" t="s">
+        <v>33</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C72" s="1">
-        <v>0.52916666666666667</v>
+        <v>0.51041666666666663</v>
       </c>
       <c r="D72">
-        <v>937</v>
+        <v>1441</v>
       </c>
       <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>33</v>
-      </c>
-      <c r="B73" t="s">
-        <v>23</v>
-      </c>
-      <c r="C73" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D73">
-        <v>816</v>
-      </c>
-      <c r="G73" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C73" s="1"/>
+      <c r="E73">
+        <v>1508</v>
+      </c>
+      <c r="F73" t="s">
+        <v>29</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0.51597222222222228</v>
+      </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="E74">
-        <v>1458</v>
-      </c>
-      <c r="F74" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" s="1">
-        <v>0.55555555555555558</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B74" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" s="1">
+        <v>0.5180555555555556</v>
+      </c>
+      <c r="D74">
+        <v>1910</v>
+      </c>
+      <c r="G74" s="1"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>29</v>
-      </c>
-      <c r="C75" s="1"/>
-      <c r="E75">
-        <v>380</v>
-      </c>
-      <c r="F75" t="s">
         <v>28</v>
       </c>
-      <c r="G75" s="1">
-        <v>0.57222222222222219</v>
-      </c>
+      <c r="B75" t="s">
+        <v>33</v>
+      </c>
+      <c r="C75" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D75">
+        <v>937</v>
+      </c>
+      <c r="G75" s="1"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="1"/>
-      <c r="E76">
-        <v>1468</v>
-      </c>
-      <c r="F76" t="s">
-        <v>30</v>
-      </c>
-      <c r="G76" s="1">
-        <v>0.57638888888888895</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B76" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D76">
+        <v>816</v>
+      </c>
+      <c r="G76" s="1"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C77" s="1"/>
       <c r="E77">
-        <v>1978</v>
+        <v>1458</v>
       </c>
       <c r="F77" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G77" s="1">
-        <v>0.57708333333333328</v>
+        <v>0.55555555555555558</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C78" s="1"/>
       <c r="E78">
-        <v>871</v>
+        <v>380</v>
       </c>
       <c r="F78" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G78" s="1">
-        <v>0.58194444444444449</v>
+        <v>0.57222222222222219</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>34</v>
-      </c>
-      <c r="B79" t="s">
-        <v>18</v>
-      </c>
-      <c r="C79" s="1">
-        <v>0.59375</v>
-      </c>
-      <c r="D79">
-        <v>628</v>
-      </c>
-      <c r="G79" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="E79">
+        <v>1468</v>
+      </c>
+      <c r="F79" t="s">
+        <v>30</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0.57638888888888895</v>
+      </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>7</v>
-      </c>
-      <c r="B80" t="s">
-        <v>30</v>
-      </c>
-      <c r="C80" s="1">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D80">
-        <v>1290</v>
-      </c>
-      <c r="G80" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="E80">
+        <v>1978</v>
+      </c>
+      <c r="F80" t="s">
+        <v>32</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0.57708333333333328</v>
+      </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>9</v>
-      </c>
-      <c r="B81" t="s">
-        <v>19</v>
-      </c>
-      <c r="C81" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="D81">
-        <v>557</v>
-      </c>
-      <c r="G81" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="E81">
+        <v>871</v>
+      </c>
+      <c r="F81" t="s">
+        <v>24</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0.58194444444444449</v>
+      </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>34</v>
-      </c>
-      <c r="C82" s="1"/>
-      <c r="E82">
-        <v>629</v>
-      </c>
-      <c r="F82" t="s">
-        <v>18</v>
-      </c>
-      <c r="G82" s="1">
-        <v>0.64722222222222225</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B82" t="s">
+        <v>19</v>
+      </c>
+      <c r="C82" s="1">
+        <v>0.59236111111111112</v>
+      </c>
+      <c r="D82">
+        <v>628</v>
+      </c>
+      <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B83" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C83" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D83">
-        <v>382</v>
+        <v>1290</v>
       </c>
       <c r="G83" s="1"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="C84" s="1"/>
       <c r="E84">
-        <v>1130</v>
+        <v>629</v>
       </c>
       <c r="F84" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G84" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.64722222222222225</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -1824,43 +1824,43 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C85" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="D85">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="G85" s="1"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>9</v>
-      </c>
-      <c r="B86" t="s">
-        <v>35</v>
-      </c>
-      <c r="C86" s="1">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D86">
-        <v>370</v>
-      </c>
-      <c r="G86" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C86" s="1"/>
+      <c r="E86">
+        <v>1130</v>
+      </c>
+      <c r="F86" t="s">
+        <v>30</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C87" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D87">
-        <v>397</v>
+        <v>367</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1869,13 +1869,13 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C88" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D88">
-        <v>441</v>
+        <v>370</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -1884,13 +1884,13 @@
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C89" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D89">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -1899,13 +1899,13 @@
         <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C90" s="1">
-        <v>0.6875</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D90">
-        <v>311</v>
+        <v>553</v>
       </c>
       <c r="G90" s="1"/>
     </row>
@@ -1914,13 +1914,13 @@
         <v>9</v>
       </c>
       <c r="B91" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C91" s="1">
-        <v>0.6875</v>
+        <v>0.68055555555555558</v>
       </c>
       <c r="D91">
-        <v>555</v>
+        <v>441</v>
       </c>
       <c r="G91" s="1"/>
     </row>
@@ -1929,13 +1929,13 @@
         <v>9</v>
       </c>
       <c r="B92" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C92" s="1">
-        <v>0.6875</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D92">
-        <v>610</v>
+        <v>435</v>
       </c>
       <c r="G92" s="1"/>
     </row>
@@ -1944,60 +1944,60 @@
         <v>9</v>
       </c>
       <c r="B93" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C93" s="1">
-        <v>0.70138888888888884</v>
+        <v>0.6875</v>
       </c>
       <c r="D93">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="G93" s="1"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B94" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C94" s="1">
-        <v>0.72777777777777775</v>
+        <v>0.6875</v>
       </c>
       <c r="D94">
-        <v>4327</v>
+        <v>610</v>
       </c>
       <c r="G94" s="1"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>9</v>
-      </c>
-      <c r="C95" s="1"/>
-      <c r="E95">
-        <v>326</v>
-      </c>
-      <c r="F95" t="s">
-        <v>10</v>
-      </c>
-      <c r="G95" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B95" t="s">
+        <v>30</v>
+      </c>
+      <c r="C95" s="1">
+        <v>0.6958333333333333</v>
+      </c>
+      <c r="D95">
+        <v>4321</v>
+      </c>
+      <c r="G95" s="1"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>9</v>
       </c>
-      <c r="C96" s="1"/>
-      <c r="E96">
-        <v>560</v>
-      </c>
-      <c r="F96" t="s">
-        <v>25</v>
-      </c>
-      <c r="G96" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+      <c r="B96" t="s">
+        <v>24</v>
+      </c>
+      <c r="C96" s="1">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="D96">
+        <v>322</v>
+      </c>
+      <c r="G96" s="1"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -2005,29 +2005,29 @@
       </c>
       <c r="C97" s="1"/>
       <c r="E97">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="F97" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G97" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.72222222222222221</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>9</v>
-      </c>
-      <c r="C98" s="1"/>
-      <c r="E98">
-        <v>450</v>
-      </c>
-      <c r="F98" t="s">
-        <v>20</v>
-      </c>
-      <c r="G98" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B98" t="s">
+        <v>30</v>
+      </c>
+      <c r="C98" s="1">
+        <v>0.72777777777777775</v>
+      </c>
+      <c r="D98">
+        <v>4327</v>
+      </c>
+      <c r="G98" s="1"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
@@ -2035,13 +2035,13 @@
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="F99" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G99" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2050,13 +2050,13 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>588</v>
+        <v>560</v>
       </c>
       <c r="F100" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G100" s="1">
-        <v>0.73611111111111116</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -2065,13 +2065,13 @@
       </c>
       <c r="C101" s="1"/>
       <c r="E101">
-        <v>448</v>
+        <v>313</v>
       </c>
       <c r="F101" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G101" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -2080,43 +2080,43 @@
       </c>
       <c r="C102" s="1"/>
       <c r="E102">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="F102" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G102" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>37</v>
-      </c>
-      <c r="B103" t="s">
-        <v>19</v>
-      </c>
-      <c r="C103" s="1">
-        <v>0.74652777777777779</v>
-      </c>
-      <c r="D103">
-        <v>222</v>
-      </c>
-      <c r="G103" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C103" s="1"/>
+      <c r="E103">
+        <v>530</v>
+      </c>
+      <c r="F103" t="s">
+        <v>14</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>4308</v>
+        <v>588</v>
       </c>
       <c r="F104" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G104" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.73611111111111116</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -2125,13 +2125,13 @@
       </c>
       <c r="C105" s="1"/>
       <c r="E105">
-        <v>528</v>
+        <v>448</v>
       </c>
       <c r="F105" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G105" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -2140,27 +2140,27 @@
       </c>
       <c r="C106" s="1"/>
       <c r="E106">
-        <v>660</v>
+        <v>534</v>
       </c>
       <c r="F106" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G106" s="1">
-        <v>0.77083333333333337</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B107" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C107" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.74652777777777779</v>
       </c>
       <c r="D107">
-        <v>742</v>
+        <v>222</v>
       </c>
       <c r="G107" s="1"/>
     </row>
@@ -2170,29 +2170,29 @@
       </c>
       <c r="C108" s="1"/>
       <c r="E108">
-        <v>4312</v>
+        <v>4308</v>
       </c>
       <c r="F108" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G108" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>9</v>
       </c>
-      <c r="B109" t="s">
-        <v>18</v>
-      </c>
-      <c r="C109" s="1">
-        <v>0.79513888888888884</v>
-      </c>
-      <c r="D109">
-        <v>431</v>
-      </c>
-      <c r="G109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="E109">
+        <v>528</v>
+      </c>
+      <c r="F109" t="s">
+        <v>8</v>
+      </c>
+      <c r="G109" s="1">
+        <v>0.76041666666666663</v>
+      </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -2200,72 +2200,72 @@
       </c>
       <c r="C110" s="1"/>
       <c r="E110">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="F110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G110" s="1">
-        <v>0.80555555555555558</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="C111" s="1"/>
       <c r="E111">
-        <v>222</v>
+        <v>558</v>
       </c>
       <c r="F111" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G111" s="1">
-        <v>0.80902777777777779</v>
+        <v>0.77777777777777779</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B112" t="s">
         <v>30</v>
       </c>
       <c r="C112" s="1">
-        <v>0.81944444444444442</v>
+        <v>0.79027777777777775</v>
       </c>
       <c r="D112">
-        <v>425</v>
+        <v>742</v>
       </c>
       <c r="G112" s="1"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>9</v>
-      </c>
-      <c r="B113" t="s">
-        <v>38</v>
-      </c>
-      <c r="C113" s="1">
-        <v>0.82291666666666663</v>
-      </c>
-      <c r="D113">
-        <v>329</v>
-      </c>
-      <c r="G113" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C113" s="1"/>
+      <c r="E113">
+        <v>4312</v>
+      </c>
+      <c r="F113" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113" s="1">
+        <v>0.79027777777777775</v>
+      </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C114" s="1">
-        <v>0.82430555555555551</v>
+        <v>0.79513888888888884</v>
       </c>
       <c r="D114">
-        <v>2657</v>
+        <v>431</v>
       </c>
       <c r="G114" s="1"/>
     </row>
@@ -2273,59 +2273,59 @@
       <c r="A115" t="s">
         <v>9</v>
       </c>
-      <c r="B115" t="s">
-        <v>8</v>
-      </c>
-      <c r="C115" s="1">
-        <v>0.82638888888888884</v>
-      </c>
-      <c r="D115">
-        <v>523</v>
-      </c>
-      <c r="G115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="E115">
+        <v>670</v>
+      </c>
+      <c r="F115" t="s">
+        <v>18</v>
+      </c>
+      <c r="G115" s="1">
+        <v>0.80555555555555558</v>
+      </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>9</v>
-      </c>
-      <c r="B116" t="s">
-        <v>13</v>
-      </c>
-      <c r="C116" s="1">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D116">
-        <v>583</v>
-      </c>
-      <c r="G116" s="1"/>
+        <v>38</v>
+      </c>
+      <c r="C116" s="1"/>
+      <c r="E116">
+        <v>222</v>
+      </c>
+      <c r="F116" t="s">
+        <v>16</v>
+      </c>
+      <c r="G116" s="1">
+        <v>0.80902777777777779</v>
+      </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>9</v>
       </c>
       <c r="B117" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C117" s="1">
-        <v>0.84375</v>
+        <v>0.81944444444444442</v>
       </c>
       <c r="D117">
-        <v>325</v>
+        <v>425</v>
       </c>
       <c r="G117" s="1"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B118" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C118" s="1">
-        <v>0.84375</v>
+        <v>0.82430555555555551</v>
       </c>
       <c r="D118">
-        <v>445</v>
+        <v>2657</v>
       </c>
       <c r="G118" s="1"/>
     </row>
@@ -2333,104 +2333,104 @@
       <c r="A119" t="s">
         <v>9</v>
       </c>
-      <c r="C119" s="1"/>
-      <c r="E119">
-        <v>590</v>
-      </c>
-      <c r="F119" t="s">
+      <c r="B119" t="s">
         <v>13</v>
       </c>
-      <c r="G119" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+      <c r="C119" s="1">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D119">
+        <v>583</v>
+      </c>
+      <c r="G119" s="1"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>9</v>
       </c>
       <c r="B120" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C120" s="1">
-        <v>0.85416666666666663</v>
+        <v>0.84375</v>
       </c>
       <c r="D120">
-        <v>449</v>
+        <v>325</v>
       </c>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B121" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C121" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.84375</v>
       </c>
       <c r="D121">
-        <v>881</v>
+        <v>445</v>
       </c>
       <c r="G121" s="1"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C122" s="1">
-        <v>0.86111111111111116</v>
+        <v>0.85069444444444442</v>
       </c>
       <c r="D122">
-        <v>4323</v>
+        <v>393</v>
       </c>
       <c r="G122" s="1"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>7</v>
-      </c>
-      <c r="B123" t="s">
-        <v>30</v>
-      </c>
-      <c r="C123" s="1">
-        <v>0.86736111111111114</v>
-      </c>
-      <c r="D123">
-        <v>1461</v>
-      </c>
-      <c r="G123" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C123" s="1"/>
+      <c r="E123">
+        <v>590</v>
+      </c>
+      <c r="F123" t="s">
+        <v>13</v>
+      </c>
+      <c r="G123" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C124" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D124">
-        <v>563</v>
+        <v>449</v>
       </c>
       <c r="G124" s="1"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B125" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C125" s="1">
-        <v>0.875</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D125">
-        <v>535</v>
+        <v>881</v>
       </c>
       <c r="G125" s="1"/>
     </row>
@@ -2439,28 +2439,28 @@
         <v>9</v>
       </c>
       <c r="B126" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C126" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86111111111111116</v>
       </c>
       <c r="D126">
-        <v>312</v>
+        <v>523</v>
       </c>
       <c r="G126" s="1"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C127" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D127">
-        <v>525</v>
+        <v>1461</v>
       </c>
       <c r="G127" s="1"/>
     </row>
@@ -2469,28 +2469,28 @@
         <v>9</v>
       </c>
       <c r="B128" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C128" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D128">
-        <v>589</v>
+        <v>443</v>
       </c>
       <c r="G128" s="1"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B129" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C129" s="1">
-        <v>0.89930555555555547</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D129">
-        <v>1425</v>
+        <v>563</v>
       </c>
       <c r="G129" s="1"/>
     </row>
@@ -2499,13 +2499,13 @@
         <v>9</v>
       </c>
       <c r="B130" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C130" s="1">
-        <v>0.91319444444444442</v>
+        <v>0.87152777777777779</v>
       </c>
       <c r="D130">
-        <v>585</v>
+        <v>409</v>
       </c>
       <c r="G130" s="1"/>
     </row>
@@ -2513,76 +2513,76 @@
       <c r="A131" t="s">
         <v>9</v>
       </c>
-      <c r="C131" s="1"/>
-      <c r="E131">
-        <v>315</v>
-      </c>
-      <c r="F131" t="s">
-        <v>20</v>
-      </c>
-      <c r="G131" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B131" t="s">
+        <v>41</v>
+      </c>
+      <c r="C131" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="D131">
+        <v>527</v>
+      </c>
+      <c r="G131" s="1"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>9</v>
       </c>
-      <c r="C132" s="1"/>
-      <c r="E132">
-        <v>365</v>
-      </c>
-      <c r="F132" t="s">
-        <v>24</v>
-      </c>
-      <c r="G132" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B132" t="s">
+        <v>15</v>
+      </c>
+      <c r="C132" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="D132">
+        <v>535</v>
+      </c>
+      <c r="G132" s="1"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>9</v>
       </c>
-      <c r="C133" s="1"/>
-      <c r="E133">
-        <v>600</v>
-      </c>
-      <c r="F133" t="s">
-        <v>13</v>
-      </c>
-      <c r="G133" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B133" t="s">
+        <v>23</v>
+      </c>
+      <c r="C133" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D133">
+        <v>312</v>
+      </c>
+      <c r="G133" s="1"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>9</v>
       </c>
-      <c r="C134" s="1"/>
-      <c r="E134">
-        <v>429</v>
-      </c>
-      <c r="F134" t="s">
-        <v>21</v>
-      </c>
-      <c r="G134" s="1">
-        <v>0.92708333333333337</v>
-      </c>
+      <c r="B134" t="s">
+        <v>20</v>
+      </c>
+      <c r="C134" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D134">
+        <v>589</v>
+      </c>
+      <c r="G134" s="1"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>9</v>
       </c>
-      <c r="C135" s="1"/>
-      <c r="E135">
-        <v>578</v>
-      </c>
-      <c r="F135" t="s">
-        <v>19</v>
-      </c>
-      <c r="G135" s="1">
-        <v>0.93055555555555558</v>
-      </c>
+      <c r="B135" t="s">
+        <v>13</v>
+      </c>
+      <c r="C135" s="1">
+        <v>0.91319444444444442</v>
+      </c>
+      <c r="D135">
+        <v>585</v>
+      </c>
+      <c r="G135" s="1"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
@@ -2590,13 +2590,13 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>627</v>
+        <v>315</v>
       </c>
       <c r="F136" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G136" s="1">
-        <v>0.93402777777777779</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -2605,13 +2605,13 @@
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>574</v>
+        <v>365</v>
       </c>
       <c r="F137" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G137" s="1">
-        <v>0.9375</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -2620,13 +2620,13 @@
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="F138" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G138" s="1">
-        <v>0.94097222222222221</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -2635,43 +2635,43 @@
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>452</v>
+        <v>308</v>
       </c>
       <c r="F139" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G139" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.92361111111111116</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C140" s="1"/>
       <c r="E140">
-        <v>339</v>
+        <v>429</v>
       </c>
       <c r="F140" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="G140" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.92708333333333337</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C141" s="1"/>
       <c r="E141">
-        <v>4336</v>
+        <v>578</v>
       </c>
       <c r="F141" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G141" s="1">
-        <v>0.9506944444444444</v>
+        <v>0.93055555555555558</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -2680,13 +2680,13 @@
       </c>
       <c r="C142" s="1"/>
       <c r="E142">
-        <v>317</v>
+        <v>627</v>
       </c>
       <c r="F142" t="s">
         <v>23</v>
       </c>
       <c r="G142" s="1">
-        <v>0.95486111111111116</v>
+        <v>0.93402777777777779</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -2695,13 +2695,13 @@
       </c>
       <c r="C143" s="1"/>
       <c r="E143">
-        <v>432</v>
+        <v>574</v>
       </c>
       <c r="F143" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G143" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -2710,13 +2710,13 @@
       </c>
       <c r="C144" s="1"/>
       <c r="E144">
-        <v>457</v>
+        <v>568</v>
       </c>
       <c r="F144" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G144" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -2725,29 +2725,89 @@
       </c>
       <c r="C145" s="1"/>
       <c r="E145">
-        <v>552</v>
+        <v>452</v>
       </c>
       <c r="F145" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G145" s="1">
-        <v>0.97222222222222221</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>33</v>
-      </c>
-      <c r="B146" t="s">
-        <v>23</v>
-      </c>
-      <c r="C146" s="1">
+        <v>9</v>
+      </c>
+      <c r="C146" s="1"/>
+      <c r="E146">
+        <v>317</v>
+      </c>
+      <c r="F146" t="s">
+        <v>24</v>
+      </c>
+      <c r="G146" s="1">
+        <v>0.95486111111111116</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>9</v>
+      </c>
+      <c r="C147" s="1"/>
+      <c r="E147">
+        <v>457</v>
+      </c>
+      <c r="F147" t="s">
+        <v>17</v>
+      </c>
+      <c r="G147" s="1">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>9</v>
+      </c>
+      <c r="C148" s="1"/>
+      <c r="E148">
+        <v>300</v>
+      </c>
+      <c r="F148" t="s">
+        <v>16</v>
+      </c>
+      <c r="G148" s="1">
+        <v>0.96180555555555558</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>9</v>
+      </c>
+      <c r="C149" s="1"/>
+      <c r="E149">
+        <v>556</v>
+      </c>
+      <c r="F149" t="s">
+        <v>20</v>
+      </c>
+      <c r="G149" s="1">
+        <v>0.97222222222222221</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>34</v>
+      </c>
+      <c r="B150" t="s">
+        <v>24</v>
+      </c>
+      <c r="C150" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D146">
+      <c r="D150">
         <v>878</v>
       </c>
-      <c r="G146" s="1"/>
+      <c r="G150" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21B5230F-6451-484E-9219-EC117ED0A7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{57095EDA-EE50-428D-91E0-CC2AD1FC0333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{87A6EB5F-1EEE-4D76-9157-B48DE173843C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3FBD5E7D-A5F1-4400-A057-C740AEEE2F0C}"/>
   </bookViews>
   <sheets>
-    <sheet name="20-06" sheetId="1" r:id="rId1"/>
+    <sheet name="21-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="43">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,9 +83,6 @@
     <t>KIAD</t>
   </si>
   <si>
-    <t>KONT</t>
-  </si>
-  <si>
     <t>MHLM</t>
   </si>
   <si>
@@ -122,49 +119,55 @@
     <t>KSFO</t>
   </si>
   <si>
+    <t>KMIA</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
+    <t>KIAH</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>KATL</t>
+  </si>
+  <si>
+    <t>TAG</t>
+  </si>
+  <si>
+    <t>MHRO</t>
+  </si>
+  <si>
+    <t>KDFW</t>
+  </si>
+  <si>
+    <t>CMP</t>
+  </si>
+  <si>
+    <t>AMX</t>
+  </si>
+  <si>
+    <t>SKRG</t>
+  </si>
+  <si>
+    <t>KMCO</t>
+  </si>
+  <si>
+    <t>IBE</t>
+  </si>
+  <si>
+    <t>CYUL</t>
+  </si>
+  <si>
+    <t>KBOS</t>
+  </si>
+  <si>
+    <t>KOAK</t>
+  </si>
+  <si>
     <t>KEWR</t>
-  </si>
-  <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>KMIA</t>
-  </si>
-  <si>
-    <t>KIAH</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>KATL</t>
-  </si>
-  <si>
-    <t>KDFW</t>
-  </si>
-  <si>
-    <t>CMP</t>
-  </si>
-  <si>
-    <t>AMX</t>
-  </si>
-  <si>
-    <t>SKRG</t>
-  </si>
-  <si>
-    <t>MMUN</t>
-  </si>
-  <si>
-    <t>IBE</t>
-  </si>
-  <si>
-    <t>KBOS</t>
-  </si>
-  <si>
-    <t>KORD</t>
-  </si>
-  <si>
-    <t>KLAS</t>
   </si>
 </sst>
 </file>
@@ -539,8 +542,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{994D9681-FB34-4BD8-AD6F-8E5224EAAA3E}">
-  <dimension ref="A1:G150"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{370D314F-24C0-426D-9AB3-5017C0D54CDD}">
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -583,7 +586,7 @@
         <v>2203</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G2" s="1">
         <v>5.2083333333333336E-2</v>
@@ -628,7 +631,7 @@
         <v>879</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1">
         <v>0.20347222222222219</v>
@@ -673,7 +676,7 @@
         <v>300</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1">
         <v>0.21527777777777779</v>
@@ -705,7 +708,7 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D10">
-        <v>531</v>
+        <v>575</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -717,40 +720,40 @@
         <v>15</v>
       </c>
       <c r="C11" s="1">
-        <v>0.22222222222222221</v>
+        <v>0.22916666666666666</v>
       </c>
       <c r="D11">
-        <v>575</v>
+        <v>301</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1">
-        <v>0.22916666666666666</v>
+        <v>0.24444444444444444</v>
       </c>
       <c r="D12">
-        <v>301</v>
+        <v>4309</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C13" s="1">
-        <v>0.24444444444444444</v>
+        <v>0.24652777777777779</v>
       </c>
       <c r="D13">
-        <v>4309</v>
+        <v>456</v>
       </c>
       <c r="G13" s="1"/>
     </row>
@@ -765,35 +768,35 @@
         <v>0.24652777777777779</v>
       </c>
       <c r="D14">
-        <v>456</v>
+        <v>661</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0.24652777777777779</v>
-      </c>
-      <c r="D15">
-        <v>661</v>
-      </c>
-      <c r="G15" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="E15">
+        <v>3154</v>
+      </c>
+      <c r="F15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C16" s="1"/>
       <c r="E16">
-        <v>3154</v>
+        <v>1467</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G16" s="1">
         <v>0.25</v>
@@ -801,33 +804,33 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C17" s="1"/>
       <c r="E17">
-        <v>1467</v>
+        <v>3154</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G17" s="1">
-        <v>0.25</v>
+        <v>0.25069444444444444</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="E18">
-        <v>3154</v>
-      </c>
-      <c r="F18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0.25069444444444444</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.25694444444444442</v>
+      </c>
+      <c r="D18">
+        <v>433</v>
+      </c>
+      <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -840,7 +843,7 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="D19">
-        <v>433</v>
+        <v>579</v>
       </c>
       <c r="G19" s="1"/>
     </row>
@@ -849,13 +852,13 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C20" s="1">
-        <v>0.25694444444444442</v>
+        <v>0.26041666666666669</v>
       </c>
       <c r="D20">
-        <v>579</v>
+        <v>529</v>
       </c>
       <c r="G20" s="1"/>
     </row>
@@ -864,13 +867,13 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" s="1">
-        <v>0.26041666666666669</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="D21">
-        <v>529</v>
+        <v>314</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -882,10 +885,10 @@
         <v>21</v>
       </c>
       <c r="C22" s="1">
-        <v>0.2638888888888889</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D22">
-        <v>314</v>
+        <v>428</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -900,7 +903,7 @@
         <v>0.2673611111111111</v>
       </c>
       <c r="D23">
-        <v>428</v>
+        <v>626</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -912,10 +915,10 @@
         <v>23</v>
       </c>
       <c r="C24" s="1">
-        <v>0.2673611111111111</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="D24">
-        <v>626</v>
+        <v>316</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -930,7 +933,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D25">
-        <v>316</v>
+        <v>366</v>
       </c>
       <c r="G25" s="1"/>
     </row>
@@ -945,7 +948,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D26">
-        <v>366</v>
+        <v>561</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -954,13 +957,13 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C27" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D27">
-        <v>561</v>
+        <v>591</v>
       </c>
       <c r="G27" s="1"/>
     </row>
@@ -969,13 +972,13 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D28">
-        <v>591</v>
+        <v>671</v>
       </c>
       <c r="G28" s="1"/>
     </row>
@@ -984,44 +987,44 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C29" s="1">
-        <v>0.27083333333333331</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="D29">
-        <v>671</v>
+        <v>521</v>
       </c>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="D30">
-        <v>521</v>
-      </c>
-      <c r="G30" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="E30">
+        <v>4326</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0.29791666666666666</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>4326</v>
+        <v>319</v>
       </c>
       <c r="F31" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G31" s="1">
-        <v>0.29791666666666666</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1030,7 +1033,7 @@
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F32" t="s">
         <v>23</v>
@@ -1045,10 +1048,10 @@
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="F33" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G33" s="1">
         <v>0.3125</v>
@@ -1063,7 +1066,7 @@
         <v>396</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G34" s="1">
         <v>0.3125</v>
@@ -1071,17 +1074,17 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C35" s="1"/>
       <c r="E35">
-        <v>884</v>
+        <v>310</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G35" s="1">
-        <v>0.3125</v>
+        <v>0.31597222222222221</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1090,10 +1093,10 @@
       </c>
       <c r="C36" s="1"/>
       <c r="E36">
-        <v>310</v>
+        <v>440</v>
       </c>
       <c r="F36" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G36" s="1">
         <v>0.31597222222222221</v>
@@ -1105,10 +1108,10 @@
       </c>
       <c r="C37" s="1"/>
       <c r="E37">
-        <v>440</v>
+        <v>536</v>
       </c>
       <c r="F37" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G37" s="1">
         <v>0.31597222222222221</v>
@@ -1120,40 +1123,40 @@
       </c>
       <c r="C38" s="1"/>
       <c r="E38">
-        <v>536</v>
+        <v>444</v>
       </c>
       <c r="F38" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G38" s="1">
-        <v>0.31597222222222221</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>9</v>
       </c>
-      <c r="B39" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="1">
-        <v>0.31944444444444442</v>
-      </c>
-      <c r="D39">
-        <v>321</v>
-      </c>
-      <c r="G39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="E39">
+        <v>562</v>
+      </c>
+      <c r="F39" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.32291666666666669</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C40" s="1"/>
       <c r="E40">
-        <v>444</v>
+        <v>4322</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G40" s="1">
         <v>0.32291666666666669</v>
@@ -1165,13 +1168,13 @@
       </c>
       <c r="C41" s="1"/>
       <c r="E41">
-        <v>562</v>
+        <v>368</v>
       </c>
       <c r="F41" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G41" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1180,10 +1183,10 @@
       </c>
       <c r="C42" s="1"/>
       <c r="E42">
-        <v>368</v>
+        <v>522</v>
       </c>
       <c r="F42" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G42" s="1">
         <v>0.33333333333333331</v>
@@ -1193,16 +1196,16 @@
       <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="C43" s="1"/>
-      <c r="E43">
-        <v>522</v>
-      </c>
-      <c r="F43" t="s">
-        <v>8</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0.33333333333333331</v>
-      </c>
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="D43">
+        <v>309</v>
+      </c>
+      <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -1215,7 +1218,7 @@
         <v>0.33680555555555558</v>
       </c>
       <c r="D44">
-        <v>601</v>
+        <v>581</v>
       </c>
       <c r="G44" s="1"/>
     </row>
@@ -1228,7 +1231,7 @@
         <v>383</v>
       </c>
       <c r="F45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G45" s="1">
         <v>0.33680555555555558</v>
@@ -1240,13 +1243,13 @@
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>454</v>
+        <v>324</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G46" s="1">
-        <v>0.34027777777777779</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1255,10 +1258,10 @@
       </c>
       <c r="C47" s="1"/>
       <c r="E47">
-        <v>324</v>
+        <v>554</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G47" s="1">
         <v>0.34375</v>
@@ -1266,17 +1269,17 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>572</v>
+        <v>884</v>
       </c>
       <c r="F48" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G48" s="1">
-        <v>0.34375</v>
+        <v>0.35347222222222219</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1285,10 +1288,10 @@
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="F49" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G49" s="1">
         <v>0.36458333333333331</v>
@@ -1298,45 +1301,45 @@
       <c r="A50" t="s">
         <v>9</v>
       </c>
-      <c r="B50" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50" s="1">
-        <v>0.37152777777777779</v>
-      </c>
-      <c r="D50">
-        <v>451</v>
-      </c>
-      <c r="G50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="E50">
+        <v>430</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0.36458333333333331</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>9</v>
       </c>
-      <c r="C51" s="1"/>
-      <c r="E51">
-        <v>526</v>
-      </c>
-      <c r="F51" t="s">
-        <v>41</v>
-      </c>
-      <c r="G51" s="1">
-        <v>0.375</v>
-      </c>
+      <c r="B51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.37847222222222221</v>
+      </c>
+      <c r="D51">
+        <v>559</v>
+      </c>
+      <c r="G51" s="1"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C52" s="1"/>
       <c r="E52">
-        <v>4320</v>
+        <v>524</v>
       </c>
       <c r="F52" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G52" s="1">
-        <v>0.38333333333333336</v>
+        <v>0.38194444444444442</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -1371,16 +1374,16 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C55" s="1">
-        <v>0.40902777777777777</v>
+        <v>0.41319444444444442</v>
       </c>
       <c r="D55">
-        <v>4337</v>
+        <v>569</v>
       </c>
       <c r="G55" s="1"/>
     </row>
@@ -1388,16 +1391,16 @@
       <c r="A56" t="s">
         <v>9</v>
       </c>
-      <c r="B56" t="s">
-        <v>18</v>
-      </c>
-      <c r="C56" s="1">
+      <c r="C56" s="1"/>
+      <c r="E56">
+        <v>392</v>
+      </c>
+      <c r="F56" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" s="1">
         <v>0.41319444444444442</v>
       </c>
-      <c r="D56">
-        <v>569</v>
-      </c>
-      <c r="G56" s="1"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
@@ -1405,87 +1408,87 @@
       </c>
       <c r="C57" s="1"/>
       <c r="E57">
-        <v>392</v>
+        <v>609</v>
       </c>
       <c r="F57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G57" s="1">
-        <v>0.41319444444444442</v>
+        <v>0.4236111111111111</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>9</v>
       </c>
-      <c r="C58" s="1"/>
-      <c r="E58">
-        <v>408</v>
-      </c>
-      <c r="F58" t="s">
-        <v>40</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0.41319444444444442</v>
-      </c>
+      <c r="B58" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="1">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D58">
+        <v>537</v>
+      </c>
+      <c r="G58" s="1"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>9</v>
       </c>
-      <c r="C59" s="1"/>
-      <c r="E59">
-        <v>609</v>
-      </c>
-      <c r="F59" t="s">
-        <v>23</v>
-      </c>
-      <c r="G59" s="1">
-        <v>0.4236111111111111</v>
-      </c>
+      <c r="B59" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" s="1">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="D59">
+        <v>318</v>
+      </c>
+      <c r="G59" s="1"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C60" s="1">
-        <v>0.42708333333333331</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D60">
-        <v>537</v>
+        <v>70</v>
       </c>
       <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C61" s="1">
-        <v>0.44791666666666669</v>
+        <v>0.47291666666666665</v>
       </c>
       <c r="D61">
-        <v>455</v>
+        <v>495</v>
       </c>
       <c r="G61" s="1"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C62" s="1">
-        <v>0.4513888888888889</v>
+        <v>0.47847222222222219</v>
       </c>
       <c r="D62">
-        <v>573</v>
+        <v>1194</v>
       </c>
       <c r="G62" s="1"/>
     </row>
@@ -1493,299 +1496,299 @@
       <c r="A63" t="s">
         <v>9</v>
       </c>
-      <c r="B63" t="s">
-        <v>23</v>
-      </c>
-      <c r="C63" s="1">
-        <v>0.4548611111111111</v>
-      </c>
-      <c r="D63">
-        <v>318</v>
-      </c>
-      <c r="G63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="E63">
+        <v>584</v>
+      </c>
+      <c r="F63" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0.49305555555555558</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>9</v>
       </c>
-      <c r="B64" t="s">
-        <v>25</v>
-      </c>
-      <c r="C64" s="1">
-        <v>0.46180555555555558</v>
-      </c>
-      <c r="D64">
-        <v>384</v>
-      </c>
-      <c r="G64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="E64">
+        <v>71</v>
+      </c>
+      <c r="F64" t="s">
+        <v>24</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="E65">
+        <v>424</v>
+      </c>
+      <c r="F65" t="s">
         <v>28</v>
       </c>
-      <c r="B65" t="s">
-        <v>29</v>
-      </c>
-      <c r="C65" s="1">
-        <v>0.47291666666666665</v>
-      </c>
-      <c r="D65">
-        <v>495</v>
-      </c>
-      <c r="G65" s="1"/>
+      <c r="G65" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C66" s="1">
-        <v>0.47847222222222219</v>
+        <v>0.51041666666666663</v>
       </c>
       <c r="D66">
-        <v>1194</v>
+        <v>1441</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C67" s="1"/>
       <c r="E67">
-        <v>584</v>
+        <v>1508</v>
       </c>
       <c r="F67" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G67" s="1">
-        <v>0.49305555555555558</v>
+        <v>0.51597222222222228</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" s="1"/>
-      <c r="E68">
-        <v>434</v>
-      </c>
-      <c r="F68" t="s">
-        <v>37</v>
-      </c>
-      <c r="G68" s="1">
-        <v>0.49652777777777779</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B68" t="s">
+        <v>30</v>
+      </c>
+      <c r="C68" s="1">
+        <v>0.5180555555555556</v>
+      </c>
+      <c r="D68">
+        <v>1910</v>
+      </c>
+      <c r="G68" s="1"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69" s="1"/>
-      <c r="E69">
-        <v>385</v>
-      </c>
-      <c r="F69" t="s">
-        <v>25</v>
-      </c>
-      <c r="G69" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B69" t="s">
+        <v>32</v>
+      </c>
+      <c r="C69" s="1">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D69">
+        <v>420</v>
+      </c>
+      <c r="G69" s="1"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>9</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="E70">
-        <v>424</v>
-      </c>
-      <c r="F70" t="s">
-        <v>30</v>
-      </c>
-      <c r="G70" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B70" t="s">
+        <v>33</v>
+      </c>
+      <c r="C70" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D70">
+        <v>937</v>
+      </c>
+      <c r="G70" s="1"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>9</v>
-      </c>
-      <c r="C71" s="1"/>
-      <c r="E71">
-        <v>442</v>
-      </c>
-      <c r="F71" t="s">
-        <v>33</v>
-      </c>
-      <c r="G71" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B71" t="s">
+        <v>23</v>
+      </c>
+      <c r="C71" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D71">
+        <v>816</v>
+      </c>
+      <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>7</v>
-      </c>
-      <c r="B72" t="s">
-        <v>30</v>
-      </c>
-      <c r="C72" s="1">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="D72">
-        <v>1441</v>
-      </c>
-      <c r="G72" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="C72" s="1"/>
+      <c r="E72">
+        <v>421</v>
+      </c>
+      <c r="F72" t="s">
+        <v>32</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0.55208333333333337</v>
+      </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C73" s="1"/>
       <c r="E73">
-        <v>1508</v>
+        <v>1458</v>
       </c>
       <c r="F73" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G73" s="1">
-        <v>0.51597222222222228</v>
+        <v>0.55555555555555558</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>31</v>
-      </c>
-      <c r="B74" t="s">
-        <v>32</v>
-      </c>
-      <c r="C74" s="1">
-        <v>0.5180555555555556</v>
-      </c>
-      <c r="D74">
-        <v>1910</v>
-      </c>
-      <c r="G74" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="E74">
+        <v>380</v>
+      </c>
+      <c r="F74" t="s">
+        <v>33</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0.57222222222222219</v>
+      </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="E75">
+        <v>1468</v>
+      </c>
+      <c r="F75" t="s">
         <v>28</v>
       </c>
-      <c r="B75" t="s">
-        <v>33</v>
-      </c>
-      <c r="C75" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D75">
-        <v>937</v>
-      </c>
-      <c r="G75" s="1"/>
+      <c r="G75" s="1">
+        <v>0.57638888888888895</v>
+      </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>34</v>
-      </c>
-      <c r="B76" t="s">
-        <v>24</v>
-      </c>
-      <c r="C76" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D76">
-        <v>816</v>
-      </c>
-      <c r="G76" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="E76">
+        <v>1978</v>
+      </c>
+      <c r="F76" t="s">
+        <v>30</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0.57708333333333328</v>
+      </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C77" s="1"/>
       <c r="E77">
-        <v>1458</v>
+        <v>871</v>
       </c>
       <c r="F77" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G77" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.58194444444444449</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>28</v>
-      </c>
-      <c r="C78" s="1"/>
-      <c r="E78">
-        <v>380</v>
-      </c>
-      <c r="F78" t="s">
-        <v>33</v>
-      </c>
-      <c r="G78" s="1">
-        <v>0.57222222222222219</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" s="1">
+        <v>0.59375</v>
+      </c>
+      <c r="D78">
+        <v>628</v>
+      </c>
+      <c r="G78" s="1"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>7</v>
       </c>
-      <c r="C79" s="1"/>
-      <c r="E79">
-        <v>1468</v>
-      </c>
-      <c r="F79" t="s">
-        <v>30</v>
-      </c>
-      <c r="G79" s="1">
-        <v>0.57638888888888895</v>
-      </c>
+      <c r="B79" t="s">
+        <v>28</v>
+      </c>
+      <c r="C79" s="1">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D79">
+        <v>1290</v>
+      </c>
+      <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="1"/>
-      <c r="E80">
-        <v>1978</v>
-      </c>
-      <c r="F80" t="s">
-        <v>32</v>
-      </c>
-      <c r="G80" s="1">
-        <v>0.57708333333333328</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="D80">
+        <v>557</v>
+      </c>
+      <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C81" s="1"/>
       <c r="E81">
-        <v>871</v>
+        <v>629</v>
       </c>
       <c r="F81" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G81" s="1">
-        <v>0.58194444444444449</v>
+        <v>0.64722222222222225</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="B82" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C82" s="1">
-        <v>0.59236111111111112</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="D82">
-        <v>628</v>
+        <v>382</v>
       </c>
       <c r="G82" s="1"/>
     </row>
@@ -1793,74 +1796,74 @@
       <c r="A83" t="s">
         <v>7</v>
       </c>
-      <c r="B83" t="s">
-        <v>30</v>
-      </c>
-      <c r="C83" s="1">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D83">
-        <v>1290</v>
-      </c>
-      <c r="G83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="E83">
+        <v>1130</v>
+      </c>
+      <c r="F83" t="s">
+        <v>28</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>35</v>
-      </c>
-      <c r="C84" s="1"/>
-      <c r="E84">
-        <v>629</v>
-      </c>
-      <c r="F84" t="s">
-        <v>19</v>
-      </c>
-      <c r="G84" s="1">
-        <v>0.64722222222222225</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B84" t="s">
+        <v>28</v>
+      </c>
+      <c r="C84" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D84">
+        <v>367</v>
+      </c>
+      <c r="G84" s="1"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C85" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D85">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="G85" s="1"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" s="1"/>
-      <c r="E86">
-        <v>1130</v>
-      </c>
-      <c r="F86" t="s">
-        <v>30</v>
-      </c>
-      <c r="G86" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B86" t="s">
+        <v>20</v>
+      </c>
+      <c r="C86" s="1">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="D86">
+        <v>397</v>
+      </c>
+      <c r="G86" s="1"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C87" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.68055555555555558</v>
       </c>
       <c r="D87">
-        <v>367</v>
+        <v>441</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1869,13 +1872,13 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C88" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D88">
-        <v>370</v>
+        <v>423</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -1884,13 +1887,13 @@
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C89" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.6875</v>
       </c>
       <c r="D89">
-        <v>397</v>
+        <v>311</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -1899,13 +1902,13 @@
         <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C90" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.6875</v>
       </c>
       <c r="D90">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G90" s="1"/>
     </row>
@@ -1914,13 +1917,13 @@
         <v>9</v>
       </c>
       <c r="B91" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C91" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.6875</v>
       </c>
       <c r="D91">
-        <v>441</v>
+        <v>610</v>
       </c>
       <c r="G91" s="1"/>
     </row>
@@ -1929,28 +1932,28 @@
         <v>9</v>
       </c>
       <c r="B92" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C92" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.70138888888888884</v>
       </c>
       <c r="D92">
-        <v>435</v>
+        <v>322</v>
       </c>
       <c r="G92" s="1"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C93" s="1">
-        <v>0.6875</v>
+        <v>0.72777777777777775</v>
       </c>
       <c r="D93">
-        <v>311</v>
+        <v>4327</v>
       </c>
       <c r="G93" s="1"/>
     </row>
@@ -1958,46 +1961,46 @@
       <c r="A94" t="s">
         <v>9</v>
       </c>
-      <c r="B94" t="s">
-        <v>23</v>
-      </c>
-      <c r="C94" s="1">
-        <v>0.6875</v>
-      </c>
-      <c r="D94">
-        <v>610</v>
-      </c>
-      <c r="G94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="E94">
+        <v>326</v>
+      </c>
+      <c r="F94" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>12</v>
-      </c>
-      <c r="B95" t="s">
-        <v>30</v>
-      </c>
-      <c r="C95" s="1">
-        <v>0.6958333333333333</v>
-      </c>
-      <c r="D95">
-        <v>4321</v>
-      </c>
-      <c r="G95" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C95" s="1"/>
+      <c r="E95">
+        <v>560</v>
+      </c>
+      <c r="F95" t="s">
+        <v>25</v>
+      </c>
+      <c r="G95" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>9</v>
       </c>
-      <c r="B96" t="s">
-        <v>24</v>
-      </c>
-      <c r="C96" s="1">
-        <v>0.70138888888888884</v>
-      </c>
-      <c r="D96">
-        <v>322</v>
-      </c>
-      <c r="G96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="E96">
+        <v>313</v>
+      </c>
+      <c r="F96" t="s">
+        <v>22</v>
+      </c>
+      <c r="G96" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -2005,29 +2008,29 @@
       </c>
       <c r="C97" s="1"/>
       <c r="E97">
-        <v>320</v>
+        <v>520</v>
       </c>
       <c r="F97" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G97" s="1">
-        <v>0.72222222222222221</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>12</v>
-      </c>
-      <c r="B98" t="s">
-        <v>30</v>
-      </c>
-      <c r="C98" s="1">
-        <v>0.72777777777777775</v>
-      </c>
-      <c r="D98">
-        <v>4327</v>
-      </c>
-      <c r="G98" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C98" s="1"/>
+      <c r="E98">
+        <v>588</v>
+      </c>
+      <c r="F98" t="s">
+        <v>19</v>
+      </c>
+      <c r="G98" s="1">
+        <v>0.73611111111111116</v>
+      </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
@@ -2035,13 +2038,13 @@
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>326</v>
+        <v>448</v>
       </c>
       <c r="F99" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G99" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2050,43 +2053,43 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>560</v>
+        <v>534</v>
       </c>
       <c r="F100" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G100" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>9</v>
-      </c>
-      <c r="C101" s="1"/>
-      <c r="E101">
-        <v>313</v>
-      </c>
-      <c r="F101" t="s">
-        <v>23</v>
-      </c>
-      <c r="G101" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B101" t="s">
+        <v>19</v>
+      </c>
+      <c r="C101" s="1">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="D101">
+        <v>222</v>
+      </c>
+      <c r="G101" s="1"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C102" s="1"/>
       <c r="E102">
-        <v>520</v>
+        <v>4308</v>
       </c>
       <c r="F102" t="s">
         <v>8</v>
       </c>
       <c r="G102" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -2095,13 +2098,13 @@
       </c>
       <c r="C103" s="1"/>
       <c r="E103">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F103" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G103" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.76041666666666663</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -2110,162 +2113,162 @@
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>588</v>
+        <v>660</v>
       </c>
       <c r="F104" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G104" s="1">
-        <v>0.73611111111111116</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>9</v>
-      </c>
-      <c r="C105" s="1"/>
-      <c r="E105">
-        <v>448</v>
-      </c>
-      <c r="F105" t="s">
-        <v>11</v>
-      </c>
-      <c r="G105" s="1">
-        <v>0.74305555555555558</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B105" t="s">
+        <v>28</v>
+      </c>
+      <c r="C105" s="1">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="D105">
+        <v>742</v>
+      </c>
+      <c r="G105" s="1"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C106" s="1"/>
       <c r="E106">
-        <v>534</v>
+        <v>4312</v>
       </c>
       <c r="F106" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G106" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.79027777777777775</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="B107" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C107" s="1">
-        <v>0.74652777777777779</v>
+        <v>0.79513888888888884</v>
       </c>
       <c r="D107">
-        <v>222</v>
+        <v>431</v>
       </c>
       <c r="G107" s="1"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C108" s="1"/>
       <c r="E108">
-        <v>4308</v>
+        <v>670</v>
       </c>
       <c r="F108" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G108" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.80555555555555558</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C109" s="1"/>
       <c r="E109">
-        <v>528</v>
+        <v>222</v>
       </c>
       <c r="F109" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G109" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.80902777777777779</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>9</v>
       </c>
-      <c r="C110" s="1"/>
-      <c r="E110">
-        <v>660</v>
-      </c>
-      <c r="F110" t="s">
-        <v>18</v>
-      </c>
-      <c r="G110" s="1">
-        <v>0.77083333333333337</v>
-      </c>
+      <c r="B110" t="s">
+        <v>28</v>
+      </c>
+      <c r="C110" s="1">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="D110">
+        <v>425</v>
+      </c>
+      <c r="G110" s="1"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>9</v>
       </c>
-      <c r="C111" s="1"/>
-      <c r="E111">
-        <v>558</v>
-      </c>
-      <c r="F111" t="s">
-        <v>26</v>
-      </c>
-      <c r="G111" s="1">
-        <v>0.77777777777777779</v>
-      </c>
+      <c r="B111" t="s">
+        <v>39</v>
+      </c>
+      <c r="C111" s="1">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D111">
+        <v>329</v>
+      </c>
+      <c r="G111" s="1"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B112" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C112" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.82430555555555551</v>
       </c>
       <c r="D112">
-        <v>742</v>
+        <v>2657</v>
       </c>
       <c r="G112" s="1"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>12</v>
-      </c>
-      <c r="C113" s="1"/>
-      <c r="E113">
-        <v>4312</v>
-      </c>
-      <c r="F113" t="s">
-        <v>13</v>
-      </c>
-      <c r="G113" s="1">
-        <v>0.79027777777777775</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B113" t="s">
+        <v>8</v>
+      </c>
+      <c r="C113" s="1">
+        <v>0.82638888888888884</v>
+      </c>
+      <c r="D113">
+        <v>523</v>
+      </c>
+      <c r="G113" s="1"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C114" s="1">
-        <v>0.79513888888888884</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D114">
-        <v>431</v>
+        <v>583</v>
       </c>
       <c r="G114" s="1"/>
     </row>
@@ -2273,119 +2276,119 @@
       <c r="A115" t="s">
         <v>9</v>
       </c>
-      <c r="C115" s="1"/>
-      <c r="E115">
-        <v>670</v>
-      </c>
-      <c r="F115" t="s">
-        <v>18</v>
-      </c>
-      <c r="G115" s="1">
-        <v>0.80555555555555558</v>
-      </c>
+      <c r="B115" t="s">
+        <v>10</v>
+      </c>
+      <c r="C115" s="1">
+        <v>0.84375</v>
+      </c>
+      <c r="D115">
+        <v>325</v>
+      </c>
+      <c r="G115" s="1"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="1"/>
-      <c r="E116">
-        <v>222</v>
-      </c>
-      <c r="F116" t="s">
-        <v>16</v>
-      </c>
-      <c r="G116" s="1">
-        <v>0.80902777777777779</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B116" t="s">
+        <v>40</v>
+      </c>
+      <c r="C116" s="1">
+        <v>0.84375</v>
+      </c>
+      <c r="D116">
+        <v>445</v>
+      </c>
+      <c r="G116" s="1"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>9</v>
       </c>
       <c r="B117" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C117" s="1">
-        <v>0.81944444444444442</v>
+        <v>0.85069444444444442</v>
       </c>
       <c r="D117">
-        <v>425</v>
+        <v>393</v>
       </c>
       <c r="G117" s="1"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>28</v>
-      </c>
-      <c r="B118" t="s">
-        <v>29</v>
-      </c>
-      <c r="C118" s="1">
-        <v>0.82430555555555551</v>
-      </c>
-      <c r="D118">
-        <v>2657</v>
-      </c>
-      <c r="G118" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C118" s="1"/>
+      <c r="E118">
+        <v>590</v>
+      </c>
+      <c r="F118" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>9</v>
       </c>
       <c r="B119" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C119" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D119">
-        <v>583</v>
+        <v>449</v>
       </c>
       <c r="G119" s="1"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B120" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C120" s="1">
-        <v>0.84375</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D120">
-        <v>325</v>
+        <v>881</v>
       </c>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C121" s="1">
-        <v>0.84375</v>
+        <v>0.86111111111111116</v>
       </c>
       <c r="D121">
-        <v>445</v>
+        <v>4323</v>
       </c>
       <c r="G121" s="1"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C122" s="1">
-        <v>0.85069444444444442</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D122">
-        <v>393</v>
+        <v>1461</v>
       </c>
       <c r="G122" s="1"/>
     </row>
@@ -2393,44 +2396,44 @@
       <c r="A123" t="s">
         <v>9</v>
       </c>
-      <c r="C123" s="1"/>
-      <c r="E123">
-        <v>590</v>
-      </c>
-      <c r="F123" t="s">
-        <v>13</v>
-      </c>
-      <c r="G123" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+      <c r="B123" t="s">
+        <v>25</v>
+      </c>
+      <c r="C123" s="1">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="D123">
+        <v>563</v>
+      </c>
+      <c r="G123" s="1"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C124" s="1">
-        <v>0.85416666666666663</v>
+        <v>0.875</v>
       </c>
       <c r="D124">
-        <v>449</v>
+        <v>535</v>
       </c>
       <c r="G124" s="1"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B125" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C125" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D125">
-        <v>881</v>
+        <v>312</v>
       </c>
       <c r="G125" s="1"/>
     </row>
@@ -2442,40 +2445,40 @@
         <v>8</v>
       </c>
       <c r="C126" s="1">
-        <v>0.86111111111111116</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D126">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G126" s="1"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B127" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C127" s="1">
-        <v>0.86736111111111114</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D127">
-        <v>1461</v>
+        <v>589</v>
       </c>
       <c r="G127" s="1"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B128" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C128" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.89930555555555547</v>
       </c>
       <c r="D128">
-        <v>443</v>
+        <v>1425</v>
       </c>
       <c r="G128" s="1"/>
     </row>
@@ -2484,13 +2487,13 @@
         <v>9</v>
       </c>
       <c r="B129" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C129" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.91319444444444442</v>
       </c>
       <c r="D129">
-        <v>563</v>
+        <v>585</v>
       </c>
       <c r="G129" s="1"/>
     </row>
@@ -2498,91 +2501,91 @@
       <c r="A130" t="s">
         <v>9</v>
       </c>
-      <c r="B130" t="s">
-        <v>40</v>
-      </c>
-      <c r="C130" s="1">
-        <v>0.87152777777777779</v>
-      </c>
-      <c r="D130">
-        <v>409</v>
-      </c>
-      <c r="G130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="E130">
+        <v>315</v>
+      </c>
+      <c r="F130" t="s">
+        <v>20</v>
+      </c>
+      <c r="G130" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>9</v>
       </c>
-      <c r="B131" t="s">
-        <v>41</v>
-      </c>
-      <c r="C131" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="D131">
-        <v>527</v>
-      </c>
-      <c r="G131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="E131">
+        <v>365</v>
+      </c>
+      <c r="F131" t="s">
+        <v>24</v>
+      </c>
+      <c r="G131" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>9</v>
       </c>
-      <c r="B132" t="s">
-        <v>15</v>
-      </c>
-      <c r="C132" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="D132">
-        <v>535</v>
-      </c>
-      <c r="G132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="E132">
+        <v>600</v>
+      </c>
+      <c r="F132" t="s">
+        <v>13</v>
+      </c>
+      <c r="G132" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>9</v>
       </c>
-      <c r="B133" t="s">
-        <v>23</v>
-      </c>
-      <c r="C133" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D133">
-        <v>312</v>
-      </c>
-      <c r="G133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="E133">
+        <v>429</v>
+      </c>
+      <c r="F133" t="s">
+        <v>21</v>
+      </c>
+      <c r="G133" s="1">
+        <v>0.92708333333333337</v>
+      </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>9</v>
       </c>
-      <c r="B134" t="s">
-        <v>20</v>
-      </c>
-      <c r="C134" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D134">
-        <v>589</v>
-      </c>
-      <c r="G134" s="1"/>
+      <c r="C134" s="1"/>
+      <c r="E134">
+        <v>578</v>
+      </c>
+      <c r="F134" t="s">
+        <v>19</v>
+      </c>
+      <c r="G134" s="1">
+        <v>0.93055555555555558</v>
+      </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>9</v>
       </c>
-      <c r="B135" t="s">
-        <v>13</v>
-      </c>
-      <c r="C135" s="1">
-        <v>0.91319444444444442</v>
-      </c>
-      <c r="D135">
-        <v>585</v>
-      </c>
-      <c r="G135" s="1"/>
+      <c r="C135" s="1"/>
+      <c r="E135">
+        <v>627</v>
+      </c>
+      <c r="F135" t="s">
+        <v>22</v>
+      </c>
+      <c r="G135" s="1">
+        <v>0.93402777777777779</v>
+      </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
@@ -2590,13 +2593,13 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>315</v>
+        <v>574</v>
       </c>
       <c r="F136" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G136" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -2605,13 +2608,13 @@
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>365</v>
+        <v>568</v>
       </c>
       <c r="F137" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G137" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -2620,28 +2623,28 @@
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>580</v>
+        <v>452</v>
       </c>
       <c r="F138" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G138" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="F139" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G139" s="1">
-        <v>0.92361111111111116</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -2650,13 +2653,13 @@
       </c>
       <c r="C140" s="1"/>
       <c r="E140">
-        <v>429</v>
+        <v>317</v>
       </c>
       <c r="F140" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G140" s="1">
-        <v>0.92708333333333337</v>
+        <v>0.95486111111111116</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -2665,13 +2668,13 @@
       </c>
       <c r="C141" s="1"/>
       <c r="E141">
-        <v>578</v>
+        <v>457</v>
       </c>
       <c r="F141" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G141" s="1">
-        <v>0.93055555555555558</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -2680,134 +2683,44 @@
       </c>
       <c r="C142" s="1"/>
       <c r="E142">
-        <v>627</v>
+        <v>552</v>
       </c>
       <c r="F142" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G142" s="1">
-        <v>0.93402777777777779</v>
+        <v>0.97222222222222221</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>9</v>
       </c>
-      <c r="C143" s="1"/>
-      <c r="E143">
-        <v>574</v>
-      </c>
-      <c r="F143" t="s">
+      <c r="B143" t="s">
         <v>15</v>
       </c>
-      <c r="G143" s="1">
-        <v>0.9375</v>
-      </c>
+      <c r="C143" s="1">
+        <v>0.97569444444444442</v>
+      </c>
+      <c r="D143">
+        <v>301</v>
+      </c>
+      <c r="G143" s="1"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>9</v>
-      </c>
-      <c r="C144" s="1"/>
-      <c r="E144">
-        <v>568</v>
-      </c>
-      <c r="F144" t="s">
-        <v>18</v>
-      </c>
-      <c r="G144" s="1">
-        <v>0.94097222222222221</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>9</v>
-      </c>
-      <c r="C145" s="1"/>
-      <c r="E145">
-        <v>452</v>
-      </c>
-      <c r="F145" t="s">
-        <v>11</v>
-      </c>
-      <c r="G145" s="1">
-        <v>0.94791666666666663</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>9</v>
-      </c>
-      <c r="C146" s="1"/>
-      <c r="E146">
-        <v>317</v>
-      </c>
-      <c r="F146" t="s">
-        <v>24</v>
-      </c>
-      <c r="G146" s="1">
-        <v>0.95486111111111116</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>9</v>
-      </c>
-      <c r="C147" s="1"/>
-      <c r="E147">
-        <v>457</v>
-      </c>
-      <c r="F147" t="s">
-        <v>17</v>
-      </c>
-      <c r="G147" s="1">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>9</v>
-      </c>
-      <c r="C148" s="1"/>
-      <c r="E148">
-        <v>300</v>
-      </c>
-      <c r="F148" t="s">
-        <v>16</v>
-      </c>
-      <c r="G148" s="1">
-        <v>0.96180555555555558</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>9</v>
-      </c>
-      <c r="C149" s="1"/>
-      <c r="E149">
-        <v>556</v>
-      </c>
-      <c r="F149" t="s">
-        <v>20</v>
-      </c>
-      <c r="G149" s="1">
-        <v>0.97222222222222221</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
         <v>34</v>
       </c>
-      <c r="B150" t="s">
-        <v>24</v>
-      </c>
-      <c r="C150" s="1">
+      <c r="B144" t="s">
+        <v>23</v>
+      </c>
+      <c r="C144" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D150">
+      <c r="D144">
         <v>878</v>
       </c>
-      <c r="G150" s="1"/>
+      <c r="G144" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57095EDA-EE50-428D-91E0-CC2AD1FC0333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BE47FF9-7344-444B-BED8-AAA3AEAF52A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3FBD5E7D-A5F1-4400-A057-C740AEEE2F0C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FA909CEF-1127-4C30-8712-5B16B31F82EB}"/>
   </bookViews>
   <sheets>
-    <sheet name="21-06" sheetId="1" r:id="rId1"/>
+    <sheet name="22-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="41">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -122,6 +122,12 @@
     <t>KMIA</t>
   </si>
   <si>
+    <t>FFT</t>
+  </si>
+  <si>
+    <t>KDFW</t>
+  </si>
+  <si>
     <t>AAL</t>
   </si>
   <si>
@@ -134,15 +140,6 @@
     <t>KATL</t>
   </si>
   <si>
-    <t>TAG</t>
-  </si>
-  <si>
-    <t>MHRO</t>
-  </si>
-  <si>
-    <t>KDFW</t>
-  </si>
-  <si>
     <t>CMP</t>
   </si>
   <si>
@@ -162,9 +159,6 @@
   </si>
   <si>
     <t>KBOS</t>
-  </si>
-  <si>
-    <t>KOAK</t>
   </si>
   <si>
     <t>KEWR</t>
@@ -542,8 +536,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{370D314F-24C0-426D-9AB3-5017C0D54CDD}">
-  <dimension ref="A1:G144"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{747BE2F1-A39D-497C-8626-356BD1A0DB91}">
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -586,7 +580,7 @@
         <v>2203</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2" s="1">
         <v>5.2083333333333336E-2</v>
@@ -624,7 +618,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
@@ -774,7 +768,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15">
@@ -796,7 +790,7 @@
         <v>1467</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G16" s="1">
         <v>0.25</v>
@@ -804,7 +798,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C17" s="1"/>
       <c r="E17">
@@ -999,17 +993,17 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C30" s="1"/>
       <c r="E30">
-        <v>4326</v>
+        <v>319</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G30" s="1">
-        <v>0.29791666666666666</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1018,10 +1012,10 @@
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G31" s="1">
         <v>0.3125</v>
@@ -1033,10 +1027,10 @@
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G32" s="1">
         <v>0.3125</v>
@@ -1048,10 +1042,10 @@
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>328</v>
+        <v>396</v>
       </c>
       <c r="F33" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G33" s="1">
         <v>0.3125</v>
@@ -1059,14 +1053,14 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C34" s="1"/>
       <c r="E34">
-        <v>396</v>
+        <v>884</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G34" s="1">
         <v>0.3125</v>
@@ -1096,7 +1090,7 @@
         <v>440</v>
       </c>
       <c r="F36" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G36" s="1">
         <v>0.31597222222222221</v>
@@ -1108,13 +1102,13 @@
       </c>
       <c r="C37" s="1"/>
       <c r="E37">
-        <v>536</v>
+        <v>444</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="G37" s="1">
-        <v>0.31597222222222221</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1123,10 +1117,10 @@
       </c>
       <c r="C38" s="1"/>
       <c r="E38">
-        <v>444</v>
+        <v>562</v>
       </c>
       <c r="F38" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G38" s="1">
         <v>0.32291666666666669</v>
@@ -1138,89 +1132,89 @@
       </c>
       <c r="C39" s="1"/>
       <c r="E39">
-        <v>562</v>
+        <v>368</v>
       </c>
       <c r="F39" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G39" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C40" s="1"/>
       <c r="E40">
-        <v>4322</v>
+        <v>522</v>
       </c>
       <c r="F40" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="G40" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="1"/>
-      <c r="E41">
-        <v>368</v>
-      </c>
-      <c r="F41" t="s">
-        <v>28</v>
-      </c>
-      <c r="G41" s="1">
-        <v>0.33333333333333331</v>
-      </c>
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" s="1">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="D41">
+        <v>309</v>
+      </c>
+      <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="1"/>
-      <c r="E42">
-        <v>522</v>
-      </c>
-      <c r="F42" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0.33333333333333331</v>
-      </c>
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="D42">
+        <v>601</v>
+      </c>
+      <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="B43" t="s">
-        <v>26</v>
-      </c>
-      <c r="C43" s="1">
+      <c r="C43" s="1"/>
+      <c r="E43">
+        <v>383</v>
+      </c>
+      <c r="F43" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" s="1">
         <v>0.33680555555555558</v>
       </c>
-      <c r="D43">
-        <v>309</v>
-      </c>
-      <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>9</v>
       </c>
-      <c r="B44" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D44">
-        <v>581</v>
-      </c>
-      <c r="G44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="E44">
+        <v>454</v>
+      </c>
+      <c r="F44" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0.34027777777777779</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -1228,13 +1222,13 @@
       </c>
       <c r="C45" s="1"/>
       <c r="E45">
-        <v>383</v>
+        <v>324</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G45" s="1">
-        <v>0.33680555555555558</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1243,10 +1237,10 @@
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>324</v>
+        <v>554</v>
       </c>
       <c r="F46" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G46" s="1">
         <v>0.34375</v>
@@ -1258,28 +1252,28 @@
       </c>
       <c r="C47" s="1"/>
       <c r="E47">
-        <v>554</v>
+        <v>422</v>
       </c>
       <c r="F47" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G47" s="1">
-        <v>0.34375</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>884</v>
+        <v>430</v>
       </c>
       <c r="F48" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G48" s="1">
-        <v>0.35347222222222219</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1288,13 +1282,13 @@
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>422</v>
+        <v>524</v>
       </c>
       <c r="F49" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="G49" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.38194444444444442</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -1303,59 +1297,59 @@
       </c>
       <c r="C50" s="1"/>
       <c r="E50">
-        <v>430</v>
+        <v>369</v>
       </c>
       <c r="F50" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G50" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.3888888888888889</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>9</v>
       </c>
-      <c r="B51" t="s">
-        <v>25</v>
-      </c>
-      <c r="C51" s="1">
-        <v>0.37847222222222221</v>
-      </c>
-      <c r="D51">
-        <v>559</v>
-      </c>
-      <c r="G51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="E51">
+        <v>582</v>
+      </c>
+      <c r="F51" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.39930555555555558</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="1"/>
-      <c r="E52">
-        <v>524</v>
-      </c>
-      <c r="F52" t="s">
-        <v>8</v>
-      </c>
-      <c r="G52" s="1">
-        <v>0.38194444444444442</v>
-      </c>
+      <c r="B52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="D52">
+        <v>569</v>
+      </c>
+      <c r="G52" s="1"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="1"/>
-      <c r="E53">
-        <v>369</v>
-      </c>
-      <c r="F53" t="s">
-        <v>36</v>
-      </c>
-      <c r="G53" s="1">
-        <v>0.3888888888888889</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D53">
+        <v>342</v>
+      </c>
+      <c r="G53" s="1"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -1363,13 +1357,13 @@
       </c>
       <c r="C54" s="1"/>
       <c r="E54">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="F54" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G54" s="1">
-        <v>0.39930555555555558</v>
+        <v>0.4236111111111111</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -1377,13 +1371,13 @@
         <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C55" s="1">
-        <v>0.41319444444444442</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="D55">
-        <v>569</v>
+        <v>455</v>
       </c>
       <c r="G55" s="1"/>
     </row>
@@ -1391,106 +1385,106 @@
       <c r="A56" t="s">
         <v>9</v>
       </c>
-      <c r="C56" s="1"/>
-      <c r="E56">
-        <v>392</v>
-      </c>
-      <c r="F56" t="s">
-        <v>20</v>
-      </c>
-      <c r="G56" s="1">
-        <v>0.41319444444444442</v>
-      </c>
+      <c r="B56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="1">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="D56">
+        <v>318</v>
+      </c>
+      <c r="G56" s="1"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>9</v>
       </c>
-      <c r="C57" s="1"/>
-      <c r="E57">
-        <v>609</v>
-      </c>
-      <c r="F57" t="s">
-        <v>22</v>
-      </c>
-      <c r="G57" s="1">
-        <v>0.4236111111111111</v>
-      </c>
+      <c r="B57" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="1">
+        <v>0.46180555555555558</v>
+      </c>
+      <c r="D57">
+        <v>384</v>
+      </c>
+      <c r="G57" s="1"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>9</v>
-      </c>
-      <c r="B58" t="s">
-        <v>14</v>
-      </c>
-      <c r="C58" s="1">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="D58">
-        <v>537</v>
-      </c>
-      <c r="G58" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C58" s="1"/>
+      <c r="E58">
+        <v>343</v>
+      </c>
+      <c r="F58" t="s">
+        <v>28</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0.46180555555555558</v>
+      </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B59" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C59" s="1">
-        <v>0.4548611111111111</v>
+        <v>0.47291666666666665</v>
       </c>
       <c r="D59">
-        <v>318</v>
+        <v>495</v>
       </c>
       <c r="G59" s="1"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C60" s="1">
-        <v>0.46180555555555558</v>
+        <v>0.47847222222222219</v>
       </c>
       <c r="D60">
-        <v>70</v>
+        <v>1194</v>
       </c>
       <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>27</v>
-      </c>
-      <c r="B61" t="s">
-        <v>26</v>
-      </c>
-      <c r="C61" s="1">
-        <v>0.47291666666666665</v>
-      </c>
-      <c r="D61">
-        <v>495</v>
-      </c>
-      <c r="G61" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C61" s="1"/>
+      <c r="E61">
+        <v>584</v>
+      </c>
+      <c r="F61" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0.49305555555555558</v>
+      </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>7</v>
-      </c>
-      <c r="B62" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="1">
-        <v>0.47847222222222219</v>
-      </c>
-      <c r="D62">
-        <v>1194</v>
-      </c>
-      <c r="G62" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="E62">
+        <v>385</v>
+      </c>
+      <c r="F62" t="s">
+        <v>24</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
@@ -1498,134 +1492,134 @@
       </c>
       <c r="C63" s="1"/>
       <c r="E63">
-        <v>584</v>
+        <v>424</v>
       </c>
       <c r="F63" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G63" s="1">
-        <v>0.49305555555555558</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" s="1"/>
-      <c r="E64">
-        <v>71</v>
-      </c>
-      <c r="F64" t="s">
-        <v>24</v>
-      </c>
-      <c r="G64" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B64" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" s="1">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D64">
+        <v>1441</v>
+      </c>
+      <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C65" s="1"/>
       <c r="E65">
-        <v>424</v>
+        <v>1508</v>
       </c>
       <c r="F65" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G65" s="1">
-        <v>0.50347222222222221</v>
+        <v>0.51597222222222228</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B66" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C66" s="1">
-        <v>0.51041666666666663</v>
+        <v>0.5180555555555556</v>
       </c>
       <c r="D66">
-        <v>1441</v>
+        <v>1910</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>27</v>
-      </c>
-      <c r="C67" s="1"/>
-      <c r="E67">
-        <v>1508</v>
-      </c>
-      <c r="F67" t="s">
-        <v>26</v>
-      </c>
-      <c r="G67" s="1">
-        <v>0.51597222222222228</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B67" t="s">
+        <v>28</v>
+      </c>
+      <c r="C67" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D67">
+        <v>937</v>
+      </c>
+      <c r="G67" s="1"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C68" s="1">
-        <v>0.5180555555555556</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="D68">
-        <v>1910</v>
+        <v>816</v>
       </c>
       <c r="G68" s="1"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>31</v>
-      </c>
-      <c r="B69" t="s">
-        <v>32</v>
-      </c>
-      <c r="C69" s="1">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D69">
-        <v>420</v>
-      </c>
-      <c r="G69" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C69" s="1"/>
+      <c r="E69">
+        <v>1458</v>
+      </c>
+      <c r="F69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0.55555555555555558</v>
+      </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>27</v>
-      </c>
-      <c r="B70" t="s">
-        <v>33</v>
-      </c>
-      <c r="C70" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D70">
-        <v>937</v>
-      </c>
-      <c r="G70" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="E70">
+        <v>380</v>
+      </c>
+      <c r="F70" t="s">
+        <v>28</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0.57222222222222219</v>
+      </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>34</v>
-      </c>
-      <c r="B71" t="s">
-        <v>23</v>
-      </c>
-      <c r="C71" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D71">
-        <v>816</v>
-      </c>
-      <c r="G71" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C71" s="1"/>
+      <c r="E71">
+        <v>1468</v>
+      </c>
+      <c r="F71" t="s">
+        <v>30</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0.57638888888888895</v>
+      </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
@@ -1633,117 +1627,117 @@
       </c>
       <c r="C72" s="1"/>
       <c r="E72">
-        <v>421</v>
+        <v>1978</v>
       </c>
       <c r="F72" t="s">
         <v>32</v>
       </c>
       <c r="G72" s="1">
-        <v>0.55208333333333337</v>
+        <v>0.57708333333333328</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C73" s="1"/>
       <c r="E73">
-        <v>1458</v>
+        <v>871</v>
       </c>
       <c r="F73" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G73" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.58194444444444449</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>27</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="E74">
-        <v>380</v>
-      </c>
-      <c r="F74" t="s">
-        <v>33</v>
-      </c>
-      <c r="G74" s="1">
-        <v>0.57222222222222219</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74" s="1">
+        <v>0.59375</v>
+      </c>
+      <c r="D74">
+        <v>628</v>
+      </c>
+      <c r="G74" s="1"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>7</v>
       </c>
-      <c r="C75" s="1"/>
-      <c r="E75">
-        <v>1468</v>
-      </c>
-      <c r="F75" t="s">
-        <v>28</v>
-      </c>
-      <c r="G75" s="1">
-        <v>0.57638888888888895</v>
-      </c>
+      <c r="B75" t="s">
+        <v>30</v>
+      </c>
+      <c r="C75" s="1">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D75">
+        <v>1290</v>
+      </c>
+      <c r="G75" s="1"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C76" s="1"/>
       <c r="E76">
-        <v>1978</v>
+        <v>629</v>
       </c>
       <c r="F76" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G76" s="1">
-        <v>0.57708333333333328</v>
+        <v>0.64722222222222225</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>34</v>
-      </c>
-      <c r="C77" s="1"/>
-      <c r="E77">
-        <v>871</v>
-      </c>
-      <c r="F77" t="s">
-        <v>23</v>
-      </c>
-      <c r="G77" s="1">
-        <v>0.58194444444444449</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B77" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" s="1">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D77">
+        <v>382</v>
+      </c>
+      <c r="G77" s="1"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>35</v>
-      </c>
-      <c r="B78" t="s">
-        <v>18</v>
-      </c>
-      <c r="C78" s="1">
-        <v>0.59375</v>
-      </c>
-      <c r="D78">
-        <v>628</v>
-      </c>
-      <c r="G78" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="E78">
+        <v>1130</v>
+      </c>
+      <c r="F78" t="s">
+        <v>30</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C79" s="1">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D79">
-        <v>1290</v>
+        <v>367</v>
       </c>
       <c r="G79" s="1"/>
     </row>
@@ -1752,73 +1746,73 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C80" s="1">
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D80">
-        <v>557</v>
+        <v>370</v>
       </c>
       <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>35</v>
-      </c>
-      <c r="C81" s="1"/>
-      <c r="E81">
-        <v>629</v>
-      </c>
-      <c r="F81" t="s">
-        <v>18</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0.64722222222222225</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B81" t="s">
+        <v>20</v>
+      </c>
+      <c r="C81" s="1">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="D81">
+        <v>397</v>
+      </c>
+      <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>9</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C82" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D82">
-        <v>382</v>
+        <v>553</v>
       </c>
       <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="1"/>
-      <c r="E83">
-        <v>1130</v>
-      </c>
-      <c r="F83" t="s">
+        <v>9</v>
+      </c>
+      <c r="B83" t="s">
         <v>28</v>
       </c>
-      <c r="G83" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+      <c r="C83" s="1">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="D83">
+        <v>441</v>
+      </c>
+      <c r="G83" s="1"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C84" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D84">
-        <v>367</v>
+        <v>423</v>
       </c>
       <c r="G84" s="1"/>
     </row>
@@ -1827,13 +1821,13 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C85" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.6875</v>
       </c>
       <c r="D85">
-        <v>370</v>
+        <v>311</v>
       </c>
       <c r="G85" s="1"/>
     </row>
@@ -1842,13 +1836,13 @@
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C86" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.6875</v>
       </c>
       <c r="D86">
-        <v>397</v>
+        <v>555</v>
       </c>
       <c r="G86" s="1"/>
     </row>
@@ -1857,13 +1851,13 @@
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C87" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.6875</v>
       </c>
       <c r="D87">
-        <v>441</v>
+        <v>610</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1872,13 +1866,13 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C88" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.70138888888888884</v>
       </c>
       <c r="D88">
-        <v>423</v>
+        <v>322</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -1886,76 +1880,76 @@
       <c r="A89" t="s">
         <v>9</v>
       </c>
-      <c r="B89" t="s">
-        <v>26</v>
-      </c>
-      <c r="C89" s="1">
-        <v>0.6875</v>
-      </c>
-      <c r="D89">
-        <v>311</v>
-      </c>
-      <c r="G89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="E89">
+        <v>326</v>
+      </c>
+      <c r="F89" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>9</v>
       </c>
-      <c r="B90" t="s">
-        <v>19</v>
-      </c>
-      <c r="C90" s="1">
-        <v>0.6875</v>
-      </c>
-      <c r="D90">
-        <v>555</v>
-      </c>
-      <c r="G90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="E90">
+        <v>560</v>
+      </c>
+      <c r="F90" t="s">
+        <v>25</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>9</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" s="1"/>
+      <c r="E91">
+        <v>313</v>
+      </c>
+      <c r="F91" t="s">
         <v>22</v>
       </c>
-      <c r="C91" s="1">
-        <v>0.6875</v>
-      </c>
-      <c r="D91">
-        <v>610</v>
-      </c>
-      <c r="G91" s="1"/>
+      <c r="G91" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>9</v>
       </c>
-      <c r="B92" t="s">
-        <v>23</v>
-      </c>
-      <c r="C92" s="1">
-        <v>0.70138888888888884</v>
-      </c>
-      <c r="D92">
-        <v>322</v>
-      </c>
-      <c r="G92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="E92">
+        <v>450</v>
+      </c>
+      <c r="F92" t="s">
+        <v>20</v>
+      </c>
+      <c r="G92" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>12</v>
-      </c>
-      <c r="B93" t="s">
-        <v>28</v>
-      </c>
-      <c r="C93" s="1">
-        <v>0.72777777777777775</v>
-      </c>
-      <c r="D93">
-        <v>4327</v>
-      </c>
-      <c r="G93" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C93" s="1"/>
+      <c r="E93">
+        <v>520</v>
+      </c>
+      <c r="F93" t="s">
+        <v>8</v>
+      </c>
+      <c r="G93" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
@@ -1963,13 +1957,13 @@
       </c>
       <c r="C94" s="1"/>
       <c r="E94">
-        <v>326</v>
+        <v>588</v>
       </c>
       <c r="F94" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G94" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.73611111111111116</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -1978,13 +1972,13 @@
       </c>
       <c r="C95" s="1"/>
       <c r="E95">
-        <v>560</v>
+        <v>448</v>
       </c>
       <c r="F95" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G95" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -1993,43 +1987,43 @@
       </c>
       <c r="C96" s="1"/>
       <c r="E96">
-        <v>313</v>
+        <v>534</v>
       </c>
       <c r="F96" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G96" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>9</v>
-      </c>
-      <c r="C97" s="1"/>
-      <c r="E97">
-        <v>520</v>
-      </c>
-      <c r="F97" t="s">
-        <v>8</v>
-      </c>
-      <c r="G97" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B97" t="s">
+        <v>19</v>
+      </c>
+      <c r="C97" s="1">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="D97">
+        <v>222</v>
+      </c>
+      <c r="G97" s="1"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C98" s="1"/>
       <c r="E98">
-        <v>588</v>
+        <v>4308</v>
       </c>
       <c r="F98" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G98" s="1">
-        <v>0.73611111111111116</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -2038,13 +2032,13 @@
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>448</v>
+        <v>528</v>
       </c>
       <c r="F99" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G99" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.76041666666666663</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2053,27 +2047,27 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>534</v>
+        <v>660</v>
       </c>
       <c r="F100" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G100" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="B101" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C101" s="1">
-        <v>0.74652777777777779</v>
+        <v>0.79027777777777775</v>
       </c>
       <c r="D101">
-        <v>222</v>
+        <v>742</v>
       </c>
       <c r="G101" s="1"/>
     </row>
@@ -2083,29 +2077,29 @@
       </c>
       <c r="C102" s="1"/>
       <c r="E102">
-        <v>4308</v>
+        <v>4312</v>
       </c>
       <c r="F102" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G102" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.79027777777777775</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>9</v>
       </c>
-      <c r="C103" s="1"/>
-      <c r="E103">
-        <v>528</v>
-      </c>
-      <c r="F103" t="s">
-        <v>8</v>
-      </c>
-      <c r="G103" s="1">
-        <v>0.76041666666666663</v>
-      </c>
+      <c r="B103" t="s">
+        <v>18</v>
+      </c>
+      <c r="C103" s="1">
+        <v>0.79513888888888884</v>
+      </c>
+      <c r="D103">
+        <v>431</v>
+      </c>
+      <c r="G103" s="1"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
@@ -2113,102 +2107,102 @@
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="F104" t="s">
         <v>17</v>
       </c>
       <c r="G104" s="1">
-        <v>0.77083333333333337</v>
+        <v>0.80555555555555558</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>7</v>
-      </c>
-      <c r="B105" t="s">
-        <v>28</v>
-      </c>
-      <c r="C105" s="1">
-        <v>0.79027777777777775</v>
-      </c>
-      <c r="D105">
-        <v>742</v>
-      </c>
-      <c r="G105" s="1"/>
+        <v>37</v>
+      </c>
+      <c r="C105" s="1"/>
+      <c r="E105">
+        <v>222</v>
+      </c>
+      <c r="F105" t="s">
+        <v>15</v>
+      </c>
+      <c r="G105" s="1">
+        <v>0.80902777777777779</v>
+      </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>12</v>
-      </c>
-      <c r="C106" s="1"/>
-      <c r="E106">
-        <v>4312</v>
-      </c>
-      <c r="F106" t="s">
-        <v>13</v>
-      </c>
-      <c r="G106" s="1">
-        <v>0.79027777777777775</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B106" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="1">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="D106">
+        <v>425</v>
+      </c>
+      <c r="G106" s="1"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>9</v>
       </c>
       <c r="B107" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C107" s="1">
-        <v>0.79513888888888884</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="D107">
-        <v>431</v>
+        <v>329</v>
       </c>
       <c r="G107" s="1"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>9</v>
-      </c>
-      <c r="C108" s="1"/>
-      <c r="E108">
-        <v>670</v>
-      </c>
-      <c r="F108" t="s">
-        <v>17</v>
-      </c>
-      <c r="G108" s="1">
-        <v>0.80555555555555558</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B108" t="s">
+        <v>26</v>
+      </c>
+      <c r="C108" s="1">
+        <v>0.82430555555555551</v>
+      </c>
+      <c r="D108">
+        <v>2657</v>
+      </c>
+      <c r="G108" s="1"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>38</v>
-      </c>
-      <c r="C109" s="1"/>
-      <c r="E109">
-        <v>222</v>
-      </c>
-      <c r="F109" t="s">
-        <v>15</v>
-      </c>
-      <c r="G109" s="1">
-        <v>0.80902777777777779</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B109" t="s">
+        <v>26</v>
+      </c>
+      <c r="C109" s="1">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="D109">
+        <v>2657</v>
+      </c>
+      <c r="G109" s="1"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>9</v>
       </c>
       <c r="B110" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C110" s="1">
-        <v>0.81944444444444442</v>
+        <v>0.82638888888888884</v>
       </c>
       <c r="D110">
-        <v>425</v>
+        <v>523</v>
       </c>
       <c r="G110" s="1"/>
     </row>
@@ -2217,28 +2211,28 @@
         <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C111" s="1">
-        <v>0.82291666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D111">
-        <v>329</v>
+        <v>583</v>
       </c>
       <c r="G111" s="1"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B112" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C112" s="1">
-        <v>0.82430555555555551</v>
+        <v>0.84375</v>
       </c>
       <c r="D112">
-        <v>2657</v>
+        <v>325</v>
       </c>
       <c r="G112" s="1"/>
     </row>
@@ -2247,13 +2241,13 @@
         <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="C113" s="1">
-        <v>0.82638888888888884</v>
+        <v>0.84375</v>
       </c>
       <c r="D113">
-        <v>523</v>
+        <v>445</v>
       </c>
       <c r="G113" s="1"/>
     </row>
@@ -2261,59 +2255,59 @@
       <c r="A114" t="s">
         <v>9</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C114" s="1"/>
+      <c r="E114">
+        <v>590</v>
+      </c>
+      <c r="F114" t="s">
         <v>13</v>
       </c>
-      <c r="C114" s="1">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D114">
-        <v>583</v>
-      </c>
-      <c r="G114" s="1"/>
+      <c r="G114" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C115" s="1">
-        <v>0.84375</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D115">
-        <v>325</v>
+        <v>449</v>
       </c>
       <c r="G115" s="1"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B116" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C116" s="1">
-        <v>0.84375</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D116">
-        <v>445</v>
+        <v>881</v>
       </c>
       <c r="G116" s="1"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B117" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C117" s="1">
-        <v>0.85069444444444442</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D117">
-        <v>393</v>
+        <v>1461</v>
       </c>
       <c r="G117" s="1"/>
     </row>
@@ -2321,89 +2315,89 @@
       <c r="A118" t="s">
         <v>9</v>
       </c>
-      <c r="C118" s="1"/>
-      <c r="E118">
-        <v>590</v>
-      </c>
-      <c r="F118" t="s">
-        <v>13</v>
-      </c>
-      <c r="G118" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+      <c r="B118" t="s">
+        <v>25</v>
+      </c>
+      <c r="C118" s="1">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="D118">
+        <v>563</v>
+      </c>
+      <c r="G118" s="1"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>9</v>
       </c>
       <c r="B119" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C119" s="1">
-        <v>0.85416666666666663</v>
+        <v>0.875</v>
       </c>
       <c r="D119">
-        <v>449</v>
+        <v>535</v>
       </c>
       <c r="G119" s="1"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B120" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C120" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D120">
-        <v>881</v>
+        <v>312</v>
       </c>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B121" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="C121" s="1">
-        <v>0.86111111111111116</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D121">
-        <v>4323</v>
+        <v>525</v>
       </c>
       <c r="G121" s="1"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C122" s="1">
-        <v>0.86736111111111114</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D122">
-        <v>1461</v>
+        <v>589</v>
       </c>
       <c r="G122" s="1"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C123" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.89930555555555547</v>
       </c>
       <c r="D123">
-        <v>563</v>
+        <v>1425</v>
       </c>
       <c r="G123" s="1"/>
     </row>
@@ -2412,13 +2406,13 @@
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C124" s="1">
-        <v>0.875</v>
+        <v>0.91319444444444442</v>
       </c>
       <c r="D124">
-        <v>535</v>
+        <v>585</v>
       </c>
       <c r="G124" s="1"/>
     </row>
@@ -2426,76 +2420,76 @@
       <c r="A125" t="s">
         <v>9</v>
       </c>
-      <c r="B125" t="s">
-        <v>22</v>
-      </c>
-      <c r="C125" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D125">
-        <v>312</v>
-      </c>
-      <c r="G125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="E125">
+        <v>315</v>
+      </c>
+      <c r="F125" t="s">
+        <v>20</v>
+      </c>
+      <c r="G125" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>9</v>
       </c>
-      <c r="B126" t="s">
-        <v>8</v>
-      </c>
-      <c r="C126" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D126">
-        <v>525</v>
-      </c>
-      <c r="G126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="E126">
+        <v>365</v>
+      </c>
+      <c r="F126" t="s">
+        <v>24</v>
+      </c>
+      <c r="G126" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>9</v>
       </c>
-      <c r="B127" t="s">
-        <v>19</v>
-      </c>
-      <c r="C127" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D127">
-        <v>589</v>
-      </c>
-      <c r="G127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="E127">
+        <v>580</v>
+      </c>
+      <c r="F127" t="s">
+        <v>13</v>
+      </c>
+      <c r="G127" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>7</v>
-      </c>
-      <c r="B128" t="s">
-        <v>42</v>
-      </c>
-      <c r="C128" s="1">
-        <v>0.89930555555555547</v>
-      </c>
-      <c r="D128">
-        <v>1425</v>
-      </c>
-      <c r="G128" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C128" s="1"/>
+      <c r="E128">
+        <v>429</v>
+      </c>
+      <c r="F128" t="s">
+        <v>21</v>
+      </c>
+      <c r="G128" s="1">
+        <v>0.92708333333333337</v>
+      </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>9</v>
       </c>
-      <c r="B129" t="s">
-        <v>13</v>
-      </c>
-      <c r="C129" s="1">
-        <v>0.91319444444444442</v>
-      </c>
-      <c r="D129">
-        <v>585</v>
-      </c>
-      <c r="G129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="E129">
+        <v>578</v>
+      </c>
+      <c r="F129" t="s">
+        <v>19</v>
+      </c>
+      <c r="G129" s="1">
+        <v>0.93055555555555558</v>
+      </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
@@ -2503,13 +2497,13 @@
       </c>
       <c r="C130" s="1"/>
       <c r="E130">
-        <v>315</v>
+        <v>627</v>
       </c>
       <c r="F130" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G130" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.93402777777777779</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -2518,13 +2512,13 @@
       </c>
       <c r="C131" s="1"/>
       <c r="E131">
-        <v>365</v>
+        <v>574</v>
       </c>
       <c r="F131" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G131" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -2533,13 +2527,13 @@
       </c>
       <c r="C132" s="1"/>
       <c r="E132">
-        <v>600</v>
+        <v>568</v>
       </c>
       <c r="F132" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G132" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -2548,43 +2542,43 @@
       </c>
       <c r="C133" s="1"/>
       <c r="E133">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="F133" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G133" s="1">
-        <v>0.92708333333333337</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C134" s="1"/>
       <c r="E134">
-        <v>578</v>
+        <v>339</v>
       </c>
       <c r="F134" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="G134" s="1">
-        <v>0.93055555555555558</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C135" s="1"/>
       <c r="E135">
-        <v>627</v>
+        <v>4336</v>
       </c>
       <c r="F135" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G135" s="1">
-        <v>0.93402777777777779</v>
+        <v>0.9506944444444444</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -2593,13 +2587,13 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>574</v>
+        <v>317</v>
       </c>
       <c r="F136" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G136" s="1">
-        <v>0.9375</v>
+        <v>0.95486111111111116</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -2608,13 +2602,13 @@
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>568</v>
+        <v>432</v>
       </c>
       <c r="F137" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G137" s="1">
-        <v>0.94097222222222221</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -2623,104 +2617,44 @@
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F138" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G138" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>339</v>
+        <v>552</v>
       </c>
       <c r="F139" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="G139" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.97222222222222221</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>9</v>
-      </c>
-      <c r="C140" s="1"/>
-      <c r="E140">
-        <v>317</v>
-      </c>
-      <c r="F140" t="s">
+        <v>33</v>
+      </c>
+      <c r="B140" t="s">
         <v>23</v>
       </c>
-      <c r="G140" s="1">
-        <v>0.95486111111111116</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>9</v>
-      </c>
-      <c r="C141" s="1"/>
-      <c r="E141">
-        <v>457</v>
-      </c>
-      <c r="F141" t="s">
-        <v>16</v>
-      </c>
-      <c r="G141" s="1">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>9</v>
-      </c>
-      <c r="C142" s="1"/>
-      <c r="E142">
-        <v>552</v>
-      </c>
-      <c r="F142" t="s">
-        <v>19</v>
-      </c>
-      <c r="G142" s="1">
-        <v>0.97222222222222221</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>9</v>
-      </c>
-      <c r="B143" t="s">
-        <v>15</v>
-      </c>
-      <c r="C143" s="1">
-        <v>0.97569444444444442</v>
-      </c>
-      <c r="D143">
-        <v>301</v>
-      </c>
-      <c r="G143" s="1"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>34</v>
-      </c>
-      <c r="B144" t="s">
-        <v>23</v>
-      </c>
-      <c r="C144" s="1">
+      <c r="C140" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D144">
+      <c r="D140">
         <v>878</v>
       </c>
-      <c r="G144" s="1"/>
+      <c r="G140" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BE47FF9-7344-444B-BED8-AAA3AEAF52A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44235B4B-8675-46DA-89EF-626DB473EFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FA909CEF-1127-4C30-8712-5B16B31F82EB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D8700B65-2256-40A6-AED5-254D2A76C14D}"/>
   </bookViews>
   <sheets>
-    <sheet name="22-06" sheetId="1" r:id="rId1"/>
+    <sheet name="23-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="42">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,6 +83,9 @@
     <t>KIAD</t>
   </si>
   <si>
+    <t>KONT</t>
+  </si>
+  <si>
     <t>MHLM</t>
   </si>
   <si>
@@ -119,27 +122,27 @@
     <t>KSFO</t>
   </si>
   <si>
+    <t>KEWR</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
     <t>KMIA</t>
   </si>
   <si>
-    <t>FFT</t>
+    <t>KIAH</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>KATL</t>
   </si>
   <si>
     <t>KDFW</t>
   </si>
   <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>KIAH</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>KATL</t>
-  </si>
-  <si>
     <t>CMP</t>
   </si>
   <si>
@@ -149,19 +152,19 @@
     <t>SKRG</t>
   </si>
   <si>
-    <t>KMCO</t>
+    <t>MMUN</t>
   </si>
   <si>
     <t>IBE</t>
   </si>
   <si>
-    <t>CYUL</t>
-  </si>
-  <si>
     <t>KBOS</t>
   </si>
   <si>
-    <t>KEWR</t>
+    <t>KORD</t>
+  </si>
+  <si>
+    <t>KLAS</t>
   </si>
 </sst>
 </file>
@@ -536,8 +539,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{747BE2F1-A39D-497C-8626-356BD1A0DB91}">
-  <dimension ref="A1:G140"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B562B382-9782-45B9-A919-1C208FAB4C1E}">
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -618,14 +621,14 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
         <v>879</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5" s="1">
         <v>0.20347222222222219</v>
@@ -670,7 +673,7 @@
         <v>300</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" s="1">
         <v>0.21527777777777779</v>
@@ -702,7 +705,7 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D10">
-        <v>575</v>
+        <v>531</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -714,40 +717,40 @@
         <v>15</v>
       </c>
       <c r="C11" s="1">
-        <v>0.22916666666666666</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="D11">
-        <v>301</v>
+        <v>575</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1">
-        <v>0.24444444444444444</v>
+        <v>0.22916666666666666</v>
       </c>
       <c r="D12">
-        <v>4309</v>
+        <v>301</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C13" s="1">
-        <v>0.24652777777777779</v>
+        <v>0.24444444444444444</v>
       </c>
       <c r="D13">
-        <v>456</v>
+        <v>4309</v>
       </c>
       <c r="G13" s="1"/>
     </row>
@@ -762,35 +765,35 @@
         <v>0.24652777777777779</v>
       </c>
       <c r="D14">
-        <v>661</v>
+        <v>456</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="E15">
-        <v>3154</v>
-      </c>
-      <c r="F15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0.25</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.24652777777777779</v>
+      </c>
+      <c r="D15">
+        <v>661</v>
+      </c>
+      <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C16" s="1"/>
       <c r="E16">
-        <v>1467</v>
+        <v>3154</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G16" s="1">
         <v>0.25</v>
@@ -798,33 +801,33 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1"/>
       <c r="E17">
-        <v>3154</v>
+        <v>1467</v>
       </c>
       <c r="F17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G17" s="1">
-        <v>0.25069444444444444</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="1">
-        <v>0.25694444444444442</v>
-      </c>
-      <c r="D18">
-        <v>433</v>
-      </c>
-      <c r="G18" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="E18">
+        <v>3154</v>
+      </c>
+      <c r="F18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.25069444444444444</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -837,7 +840,7 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="D19">
-        <v>579</v>
+        <v>433</v>
       </c>
       <c r="G19" s="1"/>
     </row>
@@ -846,13 +849,13 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C20" s="1">
-        <v>0.26041666666666669</v>
+        <v>0.25694444444444442</v>
       </c>
       <c r="D20">
-        <v>529</v>
+        <v>579</v>
       </c>
       <c r="G20" s="1"/>
     </row>
@@ -861,13 +864,13 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C21" s="1">
-        <v>0.2638888888888889</v>
+        <v>0.26041666666666669</v>
       </c>
       <c r="D21">
-        <v>314</v>
+        <v>529</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -879,10 +882,10 @@
         <v>21</v>
       </c>
       <c r="C22" s="1">
-        <v>0.2673611111111111</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="D22">
-        <v>428</v>
+        <v>314</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -897,7 +900,7 @@
         <v>0.2673611111111111</v>
       </c>
       <c r="D23">
-        <v>626</v>
+        <v>428</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -909,10 +912,10 @@
         <v>23</v>
       </c>
       <c r="C24" s="1">
-        <v>0.27083333333333331</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D24">
-        <v>316</v>
+        <v>626</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -927,7 +930,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D25">
-        <v>366</v>
+        <v>316</v>
       </c>
       <c r="G25" s="1"/>
     </row>
@@ -942,7 +945,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D26">
-        <v>561</v>
+        <v>366</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -951,13 +954,13 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C27" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D27">
-        <v>591</v>
+        <v>561</v>
       </c>
       <c r="G27" s="1"/>
     </row>
@@ -966,13 +969,13 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C28" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D28">
-        <v>671</v>
+        <v>591</v>
       </c>
       <c r="G28" s="1"/>
     </row>
@@ -981,13 +984,13 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C29" s="1">
-        <v>0.29166666666666669</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="D29">
-        <v>521</v>
+        <v>671</v>
       </c>
       <c r="G29" s="1"/>
     </row>
@@ -995,30 +998,30 @@
       <c r="A30" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="1"/>
-      <c r="E30">
-        <v>319</v>
-      </c>
-      <c r="F30" t="s">
-        <v>22</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0.3125</v>
-      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="D30">
+        <v>521</v>
+      </c>
+      <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>323</v>
+        <v>3154</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G31" s="1">
-        <v>0.3125</v>
+        <v>0.29236111111111113</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1027,10 +1030,10 @@
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="F32" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="G32" s="1">
         <v>0.3125</v>
@@ -1042,10 +1045,10 @@
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>396</v>
+        <v>323</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G33" s="1">
         <v>0.3125</v>
@@ -1053,14 +1056,14 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C34" s="1"/>
       <c r="E34">
-        <v>884</v>
+        <v>396</v>
       </c>
       <c r="F34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G34" s="1">
         <v>0.3125</v>
@@ -1075,7 +1078,7 @@
         <v>310</v>
       </c>
       <c r="F35" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G35" s="1">
         <v>0.31597222222222221</v>
@@ -1090,7 +1093,7 @@
         <v>440</v>
       </c>
       <c r="F36" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G36" s="1">
         <v>0.31597222222222221</v>
@@ -1102,29 +1105,29 @@
       </c>
       <c r="C37" s="1"/>
       <c r="E37">
-        <v>444</v>
+        <v>536</v>
       </c>
       <c r="F37" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G37" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.31597222222222221</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="E38">
-        <v>562</v>
-      </c>
-      <c r="F38" t="s">
-        <v>25</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0.32291666666666669</v>
-      </c>
+      <c r="B38" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="D38">
+        <v>321</v>
+      </c>
+      <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
@@ -1132,13 +1135,13 @@
       </c>
       <c r="C39" s="1"/>
       <c r="E39">
-        <v>368</v>
+        <v>444</v>
       </c>
       <c r="F39" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G39" s="1">
-        <v>0.33333333333333331</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -1147,59 +1150,59 @@
       </c>
       <c r="C40" s="1"/>
       <c r="E40">
-        <v>522</v>
+        <v>562</v>
       </c>
       <c r="F40" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="G40" s="1">
-        <v>0.33333333333333331</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>9</v>
       </c>
-      <c r="B41" t="s">
-        <v>26</v>
-      </c>
-      <c r="C41" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D41">
-        <v>309</v>
-      </c>
-      <c r="G41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="E41">
+        <v>368</v>
+      </c>
+      <c r="F41" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0.33333333333333331</v>
+      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>9</v>
       </c>
-      <c r="B42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D42">
-        <v>601</v>
-      </c>
-      <c r="G42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="E42">
+        <v>522</v>
+      </c>
+      <c r="F42" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.33333333333333331</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="C43" s="1"/>
-      <c r="E43">
-        <v>383</v>
-      </c>
-      <c r="F43" t="s">
-        <v>24</v>
-      </c>
-      <c r="G43" s="1">
+      <c r="B43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="1">
         <v>0.33680555555555558</v>
       </c>
+      <c r="D43">
+        <v>581</v>
+      </c>
+      <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -1207,13 +1210,13 @@
       </c>
       <c r="C44" s="1"/>
       <c r="E44">
-        <v>454</v>
+        <v>383</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G44" s="1">
-        <v>0.34027777777777779</v>
+        <v>0.33680555555555558</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1222,13 +1225,13 @@
       </c>
       <c r="C45" s="1"/>
       <c r="E45">
-        <v>324</v>
+        <v>454</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G45" s="1">
-        <v>0.34375</v>
+        <v>0.34027777777777779</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1237,10 +1240,10 @@
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>554</v>
+        <v>324</v>
       </c>
       <c r="F46" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G46" s="1">
         <v>0.34375</v>
@@ -1252,28 +1255,28 @@
       </c>
       <c r="C47" s="1"/>
       <c r="E47">
-        <v>422</v>
+        <v>572</v>
       </c>
       <c r="F47" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G47" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>430</v>
+        <v>884</v>
       </c>
       <c r="F48" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G48" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.35347222222222219</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1282,29 +1285,29 @@
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>524</v>
+        <v>430</v>
       </c>
       <c r="F49" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G49" s="1">
-        <v>0.38194444444444442</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>9</v>
       </c>
-      <c r="C50" s="1"/>
-      <c r="E50">
-        <v>369</v>
-      </c>
-      <c r="F50" t="s">
-        <v>35</v>
-      </c>
-      <c r="G50" s="1">
-        <v>0.3888888888888889</v>
-      </c>
+      <c r="B50" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="D50">
+        <v>451</v>
+      </c>
+      <c r="G50" s="1"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
@@ -1312,72 +1315,72 @@
       </c>
       <c r="C51" s="1"/>
       <c r="E51">
-        <v>582</v>
+        <v>526</v>
       </c>
       <c r="F51" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="G51" s="1">
-        <v>0.39930555555555558</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>9</v>
       </c>
-      <c r="B52" t="s">
-        <v>17</v>
-      </c>
-      <c r="C52" s="1">
-        <v>0.41319444444444442</v>
-      </c>
-      <c r="D52">
-        <v>569</v>
-      </c>
-      <c r="G52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="E52">
+        <v>369</v>
+      </c>
+      <c r="F52" t="s">
+        <v>36</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.3888888888888889</v>
+      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>27</v>
-      </c>
-      <c r="B53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C53" s="1">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D53">
-        <v>342</v>
-      </c>
-      <c r="G53" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="E53">
+        <v>582</v>
+      </c>
+      <c r="F53" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0.39930555555555558</v>
+      </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" s="1"/>
-      <c r="E54">
-        <v>609</v>
-      </c>
-      <c r="F54" t="s">
-        <v>22</v>
-      </c>
-      <c r="G54" s="1">
-        <v>0.4236111111111111</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B54" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" s="1">
+        <v>0.40902777777777777</v>
+      </c>
+      <c r="D54">
+        <v>4337</v>
+      </c>
+      <c r="G54" s="1"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C55" s="1">
-        <v>0.44791666666666669</v>
+        <v>0.41319444444444442</v>
       </c>
       <c r="D55">
-        <v>455</v>
+        <v>569</v>
       </c>
       <c r="G55" s="1"/>
     </row>
@@ -1385,74 +1388,74 @@
       <c r="A56" t="s">
         <v>9</v>
       </c>
-      <c r="B56" t="s">
-        <v>22</v>
-      </c>
-      <c r="C56" s="1">
-        <v>0.4548611111111111</v>
-      </c>
-      <c r="D56">
-        <v>318</v>
-      </c>
-      <c r="G56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="E56">
+        <v>392</v>
+      </c>
+      <c r="F56" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0.41319444444444442</v>
+      </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>9</v>
       </c>
-      <c r="B57" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="1">
-        <v>0.46180555555555558</v>
-      </c>
-      <c r="D57">
-        <v>384</v>
-      </c>
-      <c r="G57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="E57">
+        <v>408</v>
+      </c>
+      <c r="F57" t="s">
+        <v>40</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0.41319444444444442</v>
+      </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C58" s="1"/>
       <c r="E58">
-        <v>343</v>
+        <v>609</v>
       </c>
       <c r="F58" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G58" s="1">
-        <v>0.46180555555555558</v>
+        <v>0.4236111111111111</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C59" s="1">
-        <v>0.47291666666666665</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="D59">
-        <v>495</v>
+        <v>537</v>
       </c>
       <c r="G59" s="1"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C60" s="1">
-        <v>0.47847222222222219</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="D60">
-        <v>1194</v>
+        <v>455</v>
       </c>
       <c r="G60" s="1"/>
     </row>
@@ -1460,256 +1463,256 @@
       <c r="A61" t="s">
         <v>9</v>
       </c>
-      <c r="C61" s="1"/>
-      <c r="E61">
-        <v>584</v>
-      </c>
-      <c r="F61" t="s">
-        <v>13</v>
-      </c>
-      <c r="G61" s="1">
-        <v>0.49305555555555558</v>
-      </c>
+      <c r="B61" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="1">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="D61">
+        <v>573</v>
+      </c>
+      <c r="G61" s="1"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>9</v>
       </c>
-      <c r="C62" s="1"/>
-      <c r="E62">
-        <v>385</v>
-      </c>
-      <c r="F62" t="s">
-        <v>24</v>
-      </c>
-      <c r="G62" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+      <c r="B62" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62" s="1">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="D62">
+        <v>318</v>
+      </c>
+      <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>9</v>
       </c>
-      <c r="C63" s="1"/>
-      <c r="E63">
-        <v>424</v>
-      </c>
-      <c r="F63" t="s">
-        <v>30</v>
-      </c>
-      <c r="G63" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+      <c r="B63" t="s">
+        <v>25</v>
+      </c>
+      <c r="C63" s="1">
+        <v>0.46180555555555558</v>
+      </c>
+      <c r="D63">
+        <v>384</v>
+      </c>
+      <c r="G63" s="1"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C64" s="1">
-        <v>0.51041666666666663</v>
+        <v>0.47291666666666665</v>
       </c>
       <c r="D64">
-        <v>1441</v>
+        <v>495</v>
       </c>
       <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>29</v>
-      </c>
-      <c r="C65" s="1"/>
-      <c r="E65">
-        <v>1508</v>
-      </c>
-      <c r="F65" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="1">
-        <v>0.51597222222222228</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="1">
+        <v>0.47847222222222219</v>
+      </c>
+      <c r="D65">
+        <v>1194</v>
+      </c>
+      <c r="G65" s="1"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>31</v>
-      </c>
-      <c r="B66" t="s">
-        <v>32</v>
-      </c>
-      <c r="C66" s="1">
-        <v>0.5180555555555556</v>
-      </c>
-      <c r="D66">
-        <v>1910</v>
-      </c>
-      <c r="G66" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="E66">
+        <v>584</v>
+      </c>
+      <c r="F66" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0.49305555555555558</v>
+      </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>29</v>
-      </c>
-      <c r="B67" t="s">
-        <v>28</v>
-      </c>
-      <c r="C67" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D67">
-        <v>937</v>
-      </c>
-      <c r="G67" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C67" s="1"/>
+      <c r="E67">
+        <v>434</v>
+      </c>
+      <c r="F67" t="s">
+        <v>37</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0.49652777777777779</v>
+      </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>33</v>
-      </c>
-      <c r="B68" t="s">
-        <v>23</v>
-      </c>
-      <c r="C68" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D68">
-        <v>816</v>
-      </c>
-      <c r="G68" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="E68">
+        <v>385</v>
+      </c>
+      <c r="F68" t="s">
+        <v>25</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C69" s="1"/>
       <c r="E69">
-        <v>1458</v>
+        <v>424</v>
       </c>
       <c r="F69" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G69" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C70" s="1"/>
       <c r="E70">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="F70" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G70" s="1">
-        <v>0.57222222222222219</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>7</v>
       </c>
-      <c r="C71" s="1"/>
-      <c r="E71">
-        <v>1468</v>
-      </c>
-      <c r="F71" t="s">
+      <c r="B71" t="s">
         <v>30</v>
       </c>
-      <c r="G71" s="1">
-        <v>0.57638888888888895</v>
-      </c>
+      <c r="C71" s="1">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D71">
+        <v>1441</v>
+      </c>
+      <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C72" s="1"/>
       <c r="E72">
-        <v>1978</v>
+        <v>1508</v>
       </c>
       <c r="F72" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G72" s="1">
-        <v>0.57708333333333328</v>
+        <v>0.51597222222222228</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>33</v>
-      </c>
-      <c r="C73" s="1"/>
-      <c r="E73">
-        <v>871</v>
-      </c>
-      <c r="F73" t="s">
-        <v>23</v>
-      </c>
-      <c r="G73" s="1">
-        <v>0.58194444444444449</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B73" t="s">
+        <v>32</v>
+      </c>
+      <c r="C73" s="1">
+        <v>0.5180555555555556</v>
+      </c>
+      <c r="D73">
+        <v>1910</v>
+      </c>
+      <c r="G73" s="1"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B74" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C74" s="1">
-        <v>0.59375</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="D74">
-        <v>628</v>
+        <v>937</v>
       </c>
       <c r="G74" s="1"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B75" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C75" s="1">
-        <v>0.60416666666666663</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="D75">
-        <v>1290</v>
+        <v>816</v>
       </c>
       <c r="G75" s="1"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C76" s="1"/>
       <c r="E76">
-        <v>629</v>
+        <v>1458</v>
       </c>
       <c r="F76" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G76" s="1">
-        <v>0.64722222222222225</v>
+        <v>0.55555555555555558</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>9</v>
-      </c>
-      <c r="B77" t="s">
-        <v>24</v>
-      </c>
-      <c r="C77" s="1">
-        <v>0.65277777777777779</v>
-      </c>
-      <c r="D77">
-        <v>382</v>
-      </c>
-      <c r="G77" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="E77">
+        <v>380</v>
+      </c>
+      <c r="F77" t="s">
+        <v>33</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0.57222222222222219</v>
+      </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
@@ -1717,132 +1720,132 @@
       </c>
       <c r="C78" s="1"/>
       <c r="E78">
-        <v>1130</v>
+        <v>1468</v>
       </c>
       <c r="F78" t="s">
         <v>30</v>
       </c>
       <c r="G78" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.57638888888888895</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>9</v>
-      </c>
-      <c r="B79" t="s">
-        <v>30</v>
-      </c>
-      <c r="C79" s="1">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D79">
-        <v>367</v>
-      </c>
-      <c r="G79" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="E79">
+        <v>1978</v>
+      </c>
+      <c r="F79" t="s">
+        <v>32</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0.57708333333333328</v>
+      </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>9</v>
-      </c>
-      <c r="B80" t="s">
-        <v>35</v>
-      </c>
-      <c r="C80" s="1">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D80">
-        <v>370</v>
-      </c>
-      <c r="G80" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="E80">
+        <v>871</v>
+      </c>
+      <c r="F80" t="s">
+        <v>24</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0.58194444444444449</v>
+      </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B81" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C81" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.59236111111111112</v>
       </c>
       <c r="D81">
-        <v>397</v>
+        <v>628</v>
       </c>
       <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B82" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C82" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D82">
-        <v>553</v>
+        <v>1290</v>
       </c>
       <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>9</v>
-      </c>
-      <c r="B83" t="s">
-        <v>28</v>
-      </c>
-      <c r="C83" s="1">
-        <v>0.68055555555555558</v>
-      </c>
-      <c r="D83">
-        <v>441</v>
-      </c>
-      <c r="G83" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="C83" s="1"/>
+      <c r="E83">
+        <v>629</v>
+      </c>
+      <c r="F83" t="s">
+        <v>19</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0.64722222222222225</v>
+      </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C84" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="D84">
-        <v>423</v>
+        <v>382</v>
       </c>
       <c r="G84" s="1"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>9</v>
-      </c>
-      <c r="B85" t="s">
-        <v>26</v>
-      </c>
-      <c r="C85" s="1">
-        <v>0.6875</v>
-      </c>
-      <c r="D85">
-        <v>311</v>
-      </c>
-      <c r="G85" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C85" s="1"/>
+      <c r="E85">
+        <v>1130</v>
+      </c>
+      <c r="F85" t="s">
+        <v>30</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C86" s="1">
-        <v>0.6875</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D86">
-        <v>555</v>
+        <v>367</v>
       </c>
       <c r="G86" s="1"/>
     </row>
@@ -1851,13 +1854,13 @@
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C87" s="1">
-        <v>0.6875</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D87">
-        <v>610</v>
+        <v>370</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1866,13 +1869,13 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C88" s="1">
-        <v>0.70138888888888884</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D88">
-        <v>322</v>
+        <v>397</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -1880,91 +1883,91 @@
       <c r="A89" t="s">
         <v>9</v>
       </c>
-      <c r="C89" s="1"/>
-      <c r="E89">
-        <v>326</v>
-      </c>
-      <c r="F89" t="s">
-        <v>10</v>
-      </c>
-      <c r="G89" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+      <c r="B89" t="s">
+        <v>20</v>
+      </c>
+      <c r="C89" s="1">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="D89">
+        <v>553</v>
+      </c>
+      <c r="G89" s="1"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>9</v>
       </c>
-      <c r="C90" s="1"/>
-      <c r="E90">
-        <v>560</v>
-      </c>
-      <c r="F90" t="s">
-        <v>25</v>
-      </c>
-      <c r="G90" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+      <c r="B90" t="s">
+        <v>33</v>
+      </c>
+      <c r="C90" s="1">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="D90">
+        <v>441</v>
+      </c>
+      <c r="G90" s="1"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>9</v>
       </c>
-      <c r="C91" s="1"/>
-      <c r="E91">
-        <v>313</v>
-      </c>
-      <c r="F91" t="s">
-        <v>22</v>
-      </c>
-      <c r="G91" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+      <c r="B91" t="s">
+        <v>37</v>
+      </c>
+      <c r="C91" s="1">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="D91">
+        <v>435</v>
+      </c>
+      <c r="G91" s="1"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>9</v>
       </c>
-      <c r="C92" s="1"/>
-      <c r="E92">
-        <v>450</v>
-      </c>
-      <c r="F92" t="s">
-        <v>20</v>
-      </c>
-      <c r="G92" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+      <c r="B92" t="s">
+        <v>29</v>
+      </c>
+      <c r="C92" s="1">
+        <v>0.6875</v>
+      </c>
+      <c r="D92">
+        <v>311</v>
+      </c>
+      <c r="G92" s="1"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>9</v>
       </c>
-      <c r="C93" s="1"/>
-      <c r="E93">
-        <v>520</v>
-      </c>
-      <c r="F93" t="s">
-        <v>8</v>
-      </c>
-      <c r="G93" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+      <c r="B93" t="s">
+        <v>23</v>
+      </c>
+      <c r="C93" s="1">
+        <v>0.6875</v>
+      </c>
+      <c r="D93">
+        <v>610</v>
+      </c>
+      <c r="G93" s="1"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>9</v>
       </c>
-      <c r="C94" s="1"/>
-      <c r="E94">
-        <v>588</v>
-      </c>
-      <c r="F94" t="s">
-        <v>19</v>
-      </c>
-      <c r="G94" s="1">
-        <v>0.73611111111111116</v>
-      </c>
+      <c r="B94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C94" s="1">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="D94">
+        <v>322</v>
+      </c>
+      <c r="G94" s="1"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
@@ -1972,13 +1975,13 @@
       </c>
       <c r="C95" s="1"/>
       <c r="E95">
-        <v>448</v>
+        <v>320</v>
       </c>
       <c r="F95" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G95" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.72222222222222221</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -1987,43 +1990,43 @@
       </c>
       <c r="C96" s="1"/>
       <c r="E96">
-        <v>534</v>
+        <v>326</v>
       </c>
       <c r="F96" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G96" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>37</v>
-      </c>
-      <c r="B97" t="s">
-        <v>19</v>
-      </c>
-      <c r="C97" s="1">
-        <v>0.74652777777777779</v>
-      </c>
-      <c r="D97">
-        <v>222</v>
-      </c>
-      <c r="G97" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C97" s="1"/>
+      <c r="E97">
+        <v>560</v>
+      </c>
+      <c r="F97" t="s">
+        <v>26</v>
+      </c>
+      <c r="G97" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C98" s="1"/>
       <c r="E98">
-        <v>4308</v>
+        <v>313</v>
       </c>
       <c r="F98" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G98" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -2032,13 +2035,13 @@
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="F99" t="s">
         <v>8</v>
       </c>
       <c r="G99" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2047,129 +2050,129 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>660</v>
+        <v>530</v>
       </c>
       <c r="F100" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G100" s="1">
-        <v>0.77083333333333337</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>7</v>
-      </c>
-      <c r="B101" t="s">
-        <v>30</v>
-      </c>
-      <c r="C101" s="1">
-        <v>0.79027777777777775</v>
-      </c>
-      <c r="D101">
-        <v>742</v>
-      </c>
-      <c r="G101" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C101" s="1"/>
+      <c r="E101">
+        <v>588</v>
+      </c>
+      <c r="F101" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" s="1">
+        <v>0.73611111111111116</v>
+      </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C102" s="1"/>
       <c r="E102">
-        <v>4312</v>
+        <v>534</v>
       </c>
       <c r="F102" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G102" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="B103" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C103" s="1">
-        <v>0.79513888888888884</v>
+        <v>0.74652777777777779</v>
       </c>
       <c r="D103">
-        <v>431</v>
+        <v>222</v>
       </c>
       <c r="G103" s="1"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>670</v>
+        <v>4308</v>
       </c>
       <c r="F104" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G104" s="1">
-        <v>0.80555555555555558</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="C105" s="1"/>
       <c r="E105">
-        <v>222</v>
+        <v>528</v>
       </c>
       <c r="F105" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G105" s="1">
-        <v>0.80902777777777779</v>
+        <v>0.76041666666666663</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>9</v>
       </c>
-      <c r="B106" t="s">
-        <v>30</v>
-      </c>
-      <c r="C106" s="1">
-        <v>0.81944444444444442</v>
-      </c>
-      <c r="D106">
-        <v>425</v>
-      </c>
-      <c r="G106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="E106">
+        <v>660</v>
+      </c>
+      <c r="F106" t="s">
+        <v>18</v>
+      </c>
+      <c r="G106" s="1">
+        <v>0.77083333333333337</v>
+      </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>9</v>
       </c>
-      <c r="B107" t="s">
-        <v>38</v>
-      </c>
-      <c r="C107" s="1">
-        <v>0.82291666666666663</v>
-      </c>
-      <c r="D107">
-        <v>329</v>
-      </c>
-      <c r="G107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="E107">
+        <v>558</v>
+      </c>
+      <c r="F107" t="s">
+        <v>26</v>
+      </c>
+      <c r="G107" s="1">
+        <v>0.77777777777777779</v>
+      </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>28</v>
+      </c>
+      <c r="B108" t="s">
         <v>29</v>
       </c>
-      <c r="B108" t="s">
-        <v>26</v>
-      </c>
       <c r="C108" s="1">
-        <v>0.82430555555555551</v>
+        <v>0.77847222222222223</v>
       </c>
       <c r="D108">
         <v>2657</v>
@@ -2178,46 +2181,46 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B109" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C109" s="1">
-        <v>0.82499999999999996</v>
+        <v>0.79027777777777775</v>
       </c>
       <c r="D109">
-        <v>2657</v>
+        <v>742</v>
       </c>
       <c r="G109" s="1"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>9</v>
-      </c>
-      <c r="B110" t="s">
-        <v>8</v>
-      </c>
-      <c r="C110" s="1">
-        <v>0.82638888888888884</v>
-      </c>
-      <c r="D110">
-        <v>523</v>
-      </c>
-      <c r="G110" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C110" s="1"/>
+      <c r="E110">
+        <v>4312</v>
+      </c>
+      <c r="F110" t="s">
+        <v>13</v>
+      </c>
+      <c r="G110" s="1">
+        <v>0.79027777777777775</v>
+      </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C111" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.79513888888888884</v>
       </c>
       <c r="D111">
-        <v>583</v>
+        <v>431</v>
       </c>
       <c r="G111" s="1"/>
     </row>
@@ -2225,45 +2228,45 @@
       <c r="A112" t="s">
         <v>9</v>
       </c>
-      <c r="B112" t="s">
-        <v>10</v>
-      </c>
-      <c r="C112" s="1">
-        <v>0.84375</v>
-      </c>
-      <c r="D112">
-        <v>325</v>
-      </c>
-      <c r="G112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="E112">
+        <v>670</v>
+      </c>
+      <c r="F112" t="s">
+        <v>18</v>
+      </c>
+      <c r="G112" s="1">
+        <v>0.80555555555555558</v>
+      </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>9</v>
-      </c>
-      <c r="B113" t="s">
-        <v>39</v>
-      </c>
-      <c r="C113" s="1">
-        <v>0.84375</v>
-      </c>
-      <c r="D113">
-        <v>445</v>
-      </c>
-      <c r="G113" s="1"/>
+        <v>38</v>
+      </c>
+      <c r="C113" s="1"/>
+      <c r="E113">
+        <v>222</v>
+      </c>
+      <c r="F113" t="s">
+        <v>16</v>
+      </c>
+      <c r="G113" s="1">
+        <v>0.80902777777777779</v>
+      </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C114" s="1"/>
       <c r="E114">
-        <v>590</v>
+        <v>4300</v>
       </c>
       <c r="F114" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G114" s="1">
-        <v>0.85069444444444442</v>
+        <v>0.81388888888888888</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -2271,43 +2274,43 @@
         <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C115" s="1">
-        <v>0.85416666666666663</v>
+        <v>0.81944444444444442</v>
       </c>
       <c r="D115">
-        <v>449</v>
+        <v>425</v>
       </c>
       <c r="G115" s="1"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B116" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C116" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D116">
-        <v>881</v>
+        <v>583</v>
       </c>
       <c r="G116" s="1"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B117" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C117" s="1">
-        <v>0.86736111111111114</v>
+        <v>0.84375</v>
       </c>
       <c r="D117">
-        <v>1461</v>
+        <v>325</v>
       </c>
       <c r="G117" s="1"/>
     </row>
@@ -2316,13 +2319,13 @@
         <v>9</v>
       </c>
       <c r="B118" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C118" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.84375</v>
       </c>
       <c r="D118">
-        <v>563</v>
+        <v>445</v>
       </c>
       <c r="G118" s="1"/>
     </row>
@@ -2331,13 +2334,13 @@
         <v>9</v>
       </c>
       <c r="B119" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C119" s="1">
-        <v>0.875</v>
+        <v>0.85069444444444442</v>
       </c>
       <c r="D119">
-        <v>535</v>
+        <v>393</v>
       </c>
       <c r="G119" s="1"/>
     </row>
@@ -2345,29 +2348,29 @@
       <c r="A120" t="s">
         <v>9</v>
       </c>
-      <c r="B120" t="s">
-        <v>22</v>
-      </c>
-      <c r="C120" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D120">
-        <v>312</v>
-      </c>
-      <c r="G120" s="1"/>
+      <c r="C120" s="1"/>
+      <c r="E120">
+        <v>590</v>
+      </c>
+      <c r="F120" t="s">
+        <v>13</v>
+      </c>
+      <c r="G120" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B121" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C121" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D121">
-        <v>525</v>
+        <v>881</v>
       </c>
       <c r="G121" s="1"/>
     </row>
@@ -2376,13 +2379,13 @@
         <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C122" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86111111111111116</v>
       </c>
       <c r="D122">
-        <v>589</v>
+        <v>523</v>
       </c>
       <c r="G122" s="1"/>
     </row>
@@ -2391,13 +2394,13 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C123" s="1">
-        <v>0.89930555555555547</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D123">
-        <v>1425</v>
+        <v>1461</v>
       </c>
       <c r="G123" s="1"/>
     </row>
@@ -2406,13 +2409,13 @@
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C124" s="1">
-        <v>0.91319444444444442</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D124">
-        <v>585</v>
+        <v>443</v>
       </c>
       <c r="G124" s="1"/>
     </row>
@@ -2420,121 +2423,121 @@
       <c r="A125" t="s">
         <v>9</v>
       </c>
-      <c r="C125" s="1"/>
-      <c r="E125">
-        <v>315</v>
-      </c>
-      <c r="F125" t="s">
-        <v>20</v>
-      </c>
-      <c r="G125" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B125" t="s">
+        <v>26</v>
+      </c>
+      <c r="C125" s="1">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="D125">
+        <v>563</v>
+      </c>
+      <c r="G125" s="1"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>9</v>
       </c>
-      <c r="C126" s="1"/>
-      <c r="E126">
-        <v>365</v>
-      </c>
-      <c r="F126" t="s">
-        <v>24</v>
-      </c>
-      <c r="G126" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B126" t="s">
+        <v>40</v>
+      </c>
+      <c r="C126" s="1">
+        <v>0.87152777777777779</v>
+      </c>
+      <c r="D126">
+        <v>409</v>
+      </c>
+      <c r="G126" s="1"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>9</v>
       </c>
-      <c r="C127" s="1"/>
-      <c r="E127">
-        <v>580</v>
-      </c>
-      <c r="F127" t="s">
-        <v>13</v>
-      </c>
-      <c r="G127" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B127" t="s">
+        <v>41</v>
+      </c>
+      <c r="C127" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="D127">
+        <v>527</v>
+      </c>
+      <c r="G127" s="1"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>9</v>
       </c>
-      <c r="C128" s="1"/>
-      <c r="E128">
-        <v>429</v>
-      </c>
-      <c r="F128" t="s">
-        <v>21</v>
-      </c>
-      <c r="G128" s="1">
-        <v>0.92708333333333337</v>
-      </c>
+      <c r="B128" t="s">
+        <v>15</v>
+      </c>
+      <c r="C128" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="D128">
+        <v>535</v>
+      </c>
+      <c r="G128" s="1"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>9</v>
       </c>
-      <c r="C129" s="1"/>
-      <c r="E129">
-        <v>578</v>
-      </c>
-      <c r="F129" t="s">
-        <v>19</v>
-      </c>
-      <c r="G129" s="1">
-        <v>0.93055555555555558</v>
-      </c>
+      <c r="B129" t="s">
+        <v>23</v>
+      </c>
+      <c r="C129" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D129">
+        <v>312</v>
+      </c>
+      <c r="G129" s="1"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>9</v>
       </c>
-      <c r="C130" s="1"/>
-      <c r="E130">
-        <v>627</v>
-      </c>
-      <c r="F130" t="s">
-        <v>22</v>
-      </c>
-      <c r="G130" s="1">
-        <v>0.93402777777777779</v>
-      </c>
+      <c r="B130" t="s">
+        <v>20</v>
+      </c>
+      <c r="C130" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D130">
+        <v>589</v>
+      </c>
+      <c r="G130" s="1"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>9</v>
-      </c>
-      <c r="C131" s="1"/>
-      <c r="E131">
-        <v>574</v>
-      </c>
-      <c r="F131" t="s">
-        <v>14</v>
-      </c>
-      <c r="G131" s="1">
-        <v>0.9375</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B131" t="s">
+        <v>27</v>
+      </c>
+      <c r="C131" s="1">
+        <v>0.89930555555555547</v>
+      </c>
+      <c r="D131">
+        <v>1425</v>
+      </c>
+      <c r="G131" s="1"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>9</v>
       </c>
-      <c r="C132" s="1"/>
-      <c r="E132">
-        <v>568</v>
-      </c>
-      <c r="F132" t="s">
-        <v>17</v>
-      </c>
-      <c r="G132" s="1">
-        <v>0.94097222222222221</v>
-      </c>
+      <c r="B132" t="s">
+        <v>13</v>
+      </c>
+      <c r="C132" s="1">
+        <v>0.91319444444444442</v>
+      </c>
+      <c r="D132">
+        <v>585</v>
+      </c>
+      <c r="G132" s="1"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
@@ -2542,43 +2545,43 @@
       </c>
       <c r="C133" s="1"/>
       <c r="E133">
-        <v>452</v>
+        <v>315</v>
       </c>
       <c r="F133" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G133" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C134" s="1"/>
       <c r="E134">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="F134" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G134" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C135" s="1"/>
       <c r="E135">
-        <v>4336</v>
+        <v>580</v>
       </c>
       <c r="F135" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="G135" s="1">
-        <v>0.9506944444444444</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -2587,13 +2590,13 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="F136" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G136" s="1">
-        <v>0.95486111111111116</v>
+        <v>0.92361111111111116</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -2602,13 +2605,13 @@
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F137" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G137" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.92708333333333337</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -2617,13 +2620,13 @@
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>457</v>
+        <v>578</v>
       </c>
       <c r="F138" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G138" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.93055555555555558</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -2632,29 +2635,149 @@
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>552</v>
+        <v>627</v>
       </c>
       <c r="F139" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G139" s="1">
-        <v>0.97222222222222221</v>
+        <v>0.93402777777777779</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>33</v>
-      </c>
-      <c r="B140" t="s">
-        <v>23</v>
-      </c>
-      <c r="C140" s="1">
+        <v>9</v>
+      </c>
+      <c r="C140" s="1"/>
+      <c r="E140">
+        <v>574</v>
+      </c>
+      <c r="F140" t="s">
+        <v>15</v>
+      </c>
+      <c r="G140" s="1">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>9</v>
+      </c>
+      <c r="C141" s="1"/>
+      <c r="E141">
+        <v>568</v>
+      </c>
+      <c r="F141" t="s">
+        <v>18</v>
+      </c>
+      <c r="G141" s="1">
+        <v>0.94097222222222221</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="1"/>
+      <c r="E142">
+        <v>452</v>
+      </c>
+      <c r="F142" t="s">
+        <v>11</v>
+      </c>
+      <c r="G142" s="1">
+        <v>0.94791666666666663</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>7</v>
+      </c>
+      <c r="C143" s="1"/>
+      <c r="E143">
+        <v>339</v>
+      </c>
+      <c r="F143" t="s">
+        <v>27</v>
+      </c>
+      <c r="G143" s="1">
+        <v>0.94791666666666663</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>9</v>
+      </c>
+      <c r="C144" s="1"/>
+      <c r="E144">
+        <v>317</v>
+      </c>
+      <c r="F144" t="s">
+        <v>24</v>
+      </c>
+      <c r="G144" s="1">
+        <v>0.95486111111111116</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145" s="1"/>
+      <c r="E145">
+        <v>457</v>
+      </c>
+      <c r="F145" t="s">
+        <v>17</v>
+      </c>
+      <c r="G145" s="1">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="1"/>
+      <c r="E146">
+        <v>300</v>
+      </c>
+      <c r="F146" t="s">
+        <v>16</v>
+      </c>
+      <c r="G146" s="1">
+        <v>0.96180555555555558</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>9</v>
+      </c>
+      <c r="C147" s="1"/>
+      <c r="E147">
+        <v>556</v>
+      </c>
+      <c r="F147" t="s">
+        <v>20</v>
+      </c>
+      <c r="G147" s="1">
+        <v>0.97222222222222221</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>34</v>
+      </c>
+      <c r="B148" t="s">
+        <v>24</v>
+      </c>
+      <c r="C148" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D140">
+      <c r="D148">
         <v>878</v>
       </c>
-      <c r="G140" s="1"/>
+      <c r="G148" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29A02B10-0837-47AD-AE21-73E02F9A219C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0319FB0-11BE-49BA-BE08-801B9DF7E46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{86F89E4B-DC5A-4577-AB47-F52E6A39DC6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{12E07602-D7BB-4CA4-8D16-99799E5D676C}"/>
   </bookViews>
   <sheets>
-    <sheet name="24-06" sheetId="1" r:id="rId1"/>
+    <sheet name="25-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="44">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,48 +83,54 @@
     <t>KIAD</t>
   </si>
   <si>
+    <t>KONT</t>
+  </si>
+  <si>
+    <t>LEMD</t>
+  </si>
+  <si>
+    <t>SEQM</t>
+  </si>
+  <si>
+    <t>KJFK</t>
+  </si>
+  <si>
+    <t>MMMX</t>
+  </si>
+  <si>
+    <t>MGGT</t>
+  </si>
+  <si>
+    <t>MNMG</t>
+  </si>
+  <si>
+    <t>SPJC</t>
+  </si>
+  <si>
+    <t>MROC</t>
+  </si>
+  <si>
+    <t>MPTO</t>
+  </si>
+  <si>
+    <t>SKBO</t>
+  </si>
+  <si>
+    <t>KSFO</t>
+  </si>
+  <si>
+    <t>KEWR</t>
+  </si>
+  <si>
     <t>MHLM</t>
   </si>
   <si>
-    <t>LEMD</t>
-  </si>
-  <si>
-    <t>SEQM</t>
-  </si>
-  <si>
-    <t>KJFK</t>
-  </si>
-  <si>
-    <t>MMMX</t>
-  </si>
-  <si>
-    <t>MGGT</t>
-  </si>
-  <si>
-    <t>MNMG</t>
-  </si>
-  <si>
-    <t>SPJC</t>
-  </si>
-  <si>
-    <t>MROC</t>
-  </si>
-  <si>
-    <t>MPTO</t>
-  </si>
-  <si>
-    <t>SKBO</t>
-  </si>
-  <si>
-    <t>KSFO</t>
+    <t>AAL</t>
   </si>
   <si>
     <t>KMIA</t>
   </si>
   <si>
-    <t>AAL</t>
-  </si>
-  <si>
     <t>KIAH</t>
   </si>
   <si>
@@ -134,6 +140,12 @@
     <t>KATL</t>
   </si>
   <si>
+    <t>TAG</t>
+  </si>
+  <si>
+    <t>MHRO</t>
+  </si>
+  <si>
     <t>KDFW</t>
   </si>
   <si>
@@ -146,22 +158,19 @@
     <t>SKRG</t>
   </si>
   <si>
-    <t>KMCO</t>
+    <t>MMUN</t>
   </si>
   <si>
     <t>IBE</t>
   </si>
   <si>
-    <t>CYUL</t>
-  </si>
-  <si>
     <t>KBOS</t>
   </si>
   <si>
-    <t>KOAK</t>
-  </si>
-  <si>
-    <t>KEWR</t>
+    <t>KORD</t>
+  </si>
+  <si>
+    <t>KLAS</t>
   </si>
 </sst>
 </file>
@@ -536,8 +545,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3250A7C2-ACD2-4344-85DB-D010B5DCCCF4}">
-  <dimension ref="A1:G143"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCA15754-F77F-4F74-B84D-A6F5F9CD9671}">
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -580,7 +589,7 @@
         <v>2203</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2" s="1">
         <v>5.2083333333333336E-2</v>
@@ -618,7 +627,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
@@ -702,7 +711,7 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D10">
-        <v>575</v>
+        <v>531</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -768,14 +777,14 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15">
         <v>3154</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G15" s="1">
         <v>0.25</v>
@@ -790,7 +799,7 @@
         <v>1467</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G16" s="1">
         <v>0.25</v>
@@ -798,14 +807,14 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1"/>
       <c r="E17">
         <v>3154</v>
       </c>
       <c r="F17" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G17" s="1">
         <v>0.25069444444444444</v>
@@ -993,17 +1002,17 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C30" s="1"/>
       <c r="E30">
-        <v>3154</v>
+        <v>319</v>
       </c>
       <c r="F30" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G30" s="1">
-        <v>0.29236111111111113</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1012,10 +1021,10 @@
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G31" s="1">
         <v>0.3125</v>
@@ -1027,10 +1036,10 @@
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>323</v>
+        <v>396</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G32" s="1">
         <v>0.3125</v>
@@ -1038,14 +1047,14 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>328</v>
+        <v>884</v>
       </c>
       <c r="F33" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G33" s="1">
         <v>0.3125</v>
@@ -1057,13 +1066,13 @@
       </c>
       <c r="C34" s="1"/>
       <c r="E34">
-        <v>396</v>
+        <v>310</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G34" s="1">
-        <v>0.3125</v>
+        <v>0.31597222222222221</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1072,10 +1081,10 @@
       </c>
       <c r="C35" s="1"/>
       <c r="E35">
-        <v>310</v>
+        <v>440</v>
       </c>
       <c r="F35" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G35" s="1">
         <v>0.31597222222222221</v>
@@ -1087,10 +1096,10 @@
       </c>
       <c r="C36" s="1"/>
       <c r="E36">
-        <v>440</v>
+        <v>536</v>
       </c>
       <c r="F36" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G36" s="1">
         <v>0.31597222222222221</v>
@@ -1100,16 +1109,16 @@
       <c r="A37" t="s">
         <v>9</v>
       </c>
-      <c r="C37" s="1"/>
-      <c r="E37">
-        <v>536</v>
-      </c>
-      <c r="F37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0.31597222222222221</v>
-      </c>
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="D37">
+        <v>321</v>
+      </c>
+      <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
@@ -1120,7 +1129,7 @@
         <v>444</v>
       </c>
       <c r="F38" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G38" s="1">
         <v>0.32291666666666669</v>
@@ -1143,17 +1152,17 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C40" s="1"/>
       <c r="E40">
-        <v>4322</v>
+        <v>368</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G40" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1162,10 +1171,10 @@
       </c>
       <c r="C41" s="1"/>
       <c r="E41">
-        <v>368</v>
+        <v>522</v>
       </c>
       <c r="F41" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G41" s="1">
         <v>0.33333333333333331</v>
@@ -1175,46 +1184,46 @@
       <c r="A42" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="1"/>
-      <c r="E42">
-        <v>522</v>
-      </c>
-      <c r="F42" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0.33333333333333331</v>
-      </c>
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="D42">
+        <v>601</v>
+      </c>
+      <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="B43" t="s">
-        <v>26</v>
-      </c>
-      <c r="C43" s="1">
+      <c r="C43" s="1"/>
+      <c r="E43">
+        <v>383</v>
+      </c>
+      <c r="F43" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" s="1">
         <v>0.33680555555555558</v>
       </c>
-      <c r="D43">
-        <v>309</v>
-      </c>
-      <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>9</v>
       </c>
-      <c r="B44" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D44">
-        <v>581</v>
-      </c>
-      <c r="G44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="E44">
+        <v>454</v>
+      </c>
+      <c r="F44" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0.34027777777777779</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -1222,13 +1231,13 @@
       </c>
       <c r="C45" s="1"/>
       <c r="E45">
-        <v>383</v>
+        <v>324</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G45" s="1">
-        <v>0.33680555555555558</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1237,13 +1246,13 @@
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>454</v>
+        <v>572</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G46" s="1">
-        <v>0.34027777777777779</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1252,58 +1261,58 @@
       </c>
       <c r="C47" s="1"/>
       <c r="E47">
-        <v>324</v>
+        <v>430</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G47" s="1">
-        <v>0.34375</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>9</v>
       </c>
-      <c r="C48" s="1"/>
-      <c r="E48">
-        <v>554</v>
-      </c>
-      <c r="F48" t="s">
-        <v>19</v>
-      </c>
-      <c r="G48" s="1">
-        <v>0.34375</v>
-      </c>
+      <c r="B48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="D48">
+        <v>451</v>
+      </c>
+      <c r="G48" s="1"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>884</v>
+        <v>526</v>
       </c>
       <c r="F49" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G49" s="1">
-        <v>0.35347222222222219</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C50" s="1"/>
       <c r="E50">
-        <v>422</v>
+        <v>4320</v>
       </c>
       <c r="F50" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G50" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.38333333333333336</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -1312,59 +1321,59 @@
       </c>
       <c r="C51" s="1"/>
       <c r="E51">
-        <v>430</v>
+        <v>369</v>
       </c>
       <c r="F51" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="G51" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.3888888888888889</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>9</v>
       </c>
-      <c r="B52" t="s">
-        <v>25</v>
-      </c>
-      <c r="C52" s="1">
-        <v>0.37847222222222221</v>
-      </c>
-      <c r="D52">
-        <v>559</v>
-      </c>
-      <c r="G52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="E52">
+        <v>582</v>
+      </c>
+      <c r="F52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.39930555555555558</v>
+      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="1"/>
-      <c r="E53">
-        <v>524</v>
-      </c>
-      <c r="F53" t="s">
-        <v>8</v>
-      </c>
-      <c r="G53" s="1">
-        <v>0.38194444444444442</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0.40902777777777777</v>
+      </c>
+      <c r="D53">
+        <v>4337</v>
+      </c>
+      <c r="G53" s="1"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="1"/>
-      <c r="E54">
-        <v>369</v>
-      </c>
-      <c r="F54" t="s">
-        <v>34</v>
-      </c>
-      <c r="G54" s="1">
-        <v>0.3888888888888889</v>
-      </c>
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" s="1">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="D54">
+        <v>569</v>
+      </c>
+      <c r="G54" s="1"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
@@ -1372,29 +1381,29 @@
       </c>
       <c r="C55" s="1"/>
       <c r="E55">
-        <v>582</v>
+        <v>392</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G55" s="1">
-        <v>0.39930555555555558</v>
+        <v>0.41319444444444442</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
-      <c r="B56" t="s">
-        <v>17</v>
-      </c>
-      <c r="C56" s="1">
+      <c r="C56" s="1"/>
+      <c r="E56">
+        <v>408</v>
+      </c>
+      <c r="F56" t="s">
+        <v>42</v>
+      </c>
+      <c r="G56" s="1">
         <v>0.41319444444444442</v>
       </c>
-      <c r="D56">
-        <v>569</v>
-      </c>
-      <c r="G56" s="1"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
@@ -1416,7 +1425,7 @@
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C58" s="1">
         <v>0.42708333333333331</v>
@@ -1446,13 +1455,13 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C60" s="1">
-        <v>0.4548611111111111</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="D60">
-        <v>318</v>
+        <v>573</v>
       </c>
       <c r="G60" s="1"/>
     </row>
@@ -1461,75 +1470,75 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C61" s="1">
-        <v>0.46180555555555558</v>
+        <v>0.4548611111111111</v>
       </c>
       <c r="D61">
-        <v>384</v>
+        <v>318</v>
       </c>
       <c r="G61" s="1"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C62" s="1">
-        <v>0.47291666666666665</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D62">
-        <v>495</v>
+        <v>384</v>
       </c>
       <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C63" s="1">
-        <v>0.47847222222222219</v>
+        <v>0.47291666666666665</v>
       </c>
       <c r="D63">
-        <v>1194</v>
+        <v>495</v>
       </c>
       <c r="G63" s="1"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" s="1"/>
-      <c r="E64">
-        <v>584</v>
-      </c>
-      <c r="F64" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" t="s">
         <v>13</v>
       </c>
-      <c r="G64" s="1">
-        <v>0.49305555555555558</v>
-      </c>
+      <c r="C64" s="1">
+        <v>0.47847222222222219</v>
+      </c>
+      <c r="D64">
+        <v>1194</v>
+      </c>
+      <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>12</v>
-      </c>
-      <c r="B65" t="s">
-        <v>18</v>
-      </c>
-      <c r="C65" s="1">
-        <v>0.49444444444444446</v>
-      </c>
-      <c r="D65">
-        <v>4301</v>
-      </c>
-      <c r="G65" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="E65">
+        <v>584</v>
+      </c>
+      <c r="F65" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0.49305555555555558</v>
+      </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
@@ -1537,13 +1546,13 @@
       </c>
       <c r="C66" s="1"/>
       <c r="E66">
-        <v>385</v>
+        <v>434</v>
       </c>
       <c r="F66" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G66" s="1">
-        <v>0.50347222222222221</v>
+        <v>0.49652777777777779</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -1552,10 +1561,10 @@
       </c>
       <c r="C67" s="1"/>
       <c r="E67">
-        <v>424</v>
+        <v>385</v>
       </c>
       <c r="F67" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G67" s="1">
         <v>0.50347222222222221</v>
@@ -1563,226 +1572,226 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>7</v>
-      </c>
-      <c r="B68" t="s">
-        <v>28</v>
-      </c>
-      <c r="C68" s="1">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="D68">
-        <v>1441</v>
-      </c>
-      <c r="G68" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="E68">
+        <v>424</v>
+      </c>
+      <c r="F68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C69" s="1"/>
       <c r="E69">
-        <v>1508</v>
+        <v>442</v>
       </c>
       <c r="F69" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G69" s="1">
-        <v>0.51597222222222228</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B70" t="s">
         <v>30</v>
       </c>
       <c r="C70" s="1">
-        <v>0.5180555555555556</v>
+        <v>0.51041666666666663</v>
       </c>
       <c r="D70">
-        <v>1910</v>
+        <v>1441</v>
       </c>
       <c r="G70" s="1"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>27</v>
-      </c>
-      <c r="B71" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D71">
-        <v>937</v>
-      </c>
-      <c r="G71" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C71" s="1"/>
+      <c r="E71">
+        <v>1508</v>
+      </c>
+      <c r="F71" t="s">
+        <v>29</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0.51597222222222228</v>
+      </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>31</v>
+      </c>
+      <c r="B72" t="s">
         <v>32</v>
       </c>
-      <c r="B72" t="s">
-        <v>23</v>
-      </c>
       <c r="C72" s="1">
-        <v>0.52916666666666667</v>
+        <v>0.5180555555555556</v>
       </c>
       <c r="D72">
-        <v>816</v>
+        <v>1910</v>
       </c>
       <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="1"/>
-      <c r="E73">
-        <v>1458</v>
-      </c>
-      <c r="F73" t="s">
-        <v>13</v>
-      </c>
-      <c r="G73" s="1">
-        <v>0.55555555555555558</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B73" t="s">
+        <v>34</v>
+      </c>
+      <c r="C73" s="1">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D73">
+        <v>420</v>
+      </c>
+      <c r="G73" s="1"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>27</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="E74">
-        <v>380</v>
-      </c>
-      <c r="F74" t="s">
-        <v>31</v>
-      </c>
-      <c r="G74" s="1">
-        <v>0.57222222222222219</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B74" t="s">
+        <v>35</v>
+      </c>
+      <c r="C74" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D74">
+        <v>937</v>
+      </c>
+      <c r="G74" s="1"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" s="1"/>
-      <c r="E75">
-        <v>1468</v>
-      </c>
-      <c r="F75" t="s">
-        <v>28</v>
-      </c>
-      <c r="G75" s="1">
-        <v>0.57638888888888895</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B75" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D75">
+        <v>816</v>
+      </c>
+      <c r="G75" s="1"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C76" s="1"/>
       <c r="E76">
-        <v>1978</v>
+        <v>421</v>
       </c>
       <c r="F76" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G76" s="1">
-        <v>0.57708333333333328</v>
+        <v>0.55208333333333337</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C77" s="1"/>
       <c r="E77">
-        <v>871</v>
+        <v>1458</v>
       </c>
       <c r="F77" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G77" s="1">
-        <v>0.58194444444444449</v>
+        <v>0.55555555555555558</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>33</v>
-      </c>
-      <c r="B78" t="s">
-        <v>18</v>
-      </c>
-      <c r="C78" s="1">
-        <v>0.59236111111111112</v>
-      </c>
-      <c r="D78">
-        <v>628</v>
-      </c>
-      <c r="G78" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="E78">
+        <v>380</v>
+      </c>
+      <c r="F78" t="s">
+        <v>35</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0.57222222222222219</v>
+      </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>7</v>
       </c>
-      <c r="B79" t="s">
-        <v>28</v>
-      </c>
-      <c r="C79" s="1">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D79">
-        <v>1290</v>
-      </c>
-      <c r="G79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="E79">
+        <v>1468</v>
+      </c>
+      <c r="F79" t="s">
+        <v>30</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0.57638888888888895</v>
+      </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>9</v>
-      </c>
-      <c r="B80" t="s">
-        <v>19</v>
-      </c>
-      <c r="C80" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="D80">
-        <v>557</v>
-      </c>
-      <c r="G80" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="E80">
+        <v>1978</v>
+      </c>
+      <c r="F80" t="s">
+        <v>32</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0.57708333333333328</v>
+      </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C81" s="1"/>
       <c r="E81">
-        <v>629</v>
+        <v>871</v>
       </c>
       <c r="F81" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G81" s="1">
-        <v>0.64722222222222225</v>
+        <v>0.58194444444444449</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C82" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.59375</v>
       </c>
       <c r="D82">
-        <v>382</v>
+        <v>628</v>
       </c>
       <c r="G82" s="1"/>
     </row>
@@ -1790,74 +1799,74 @@
       <c r="A83" t="s">
         <v>7</v>
       </c>
-      <c r="C83" s="1"/>
-      <c r="E83">
-        <v>1130</v>
-      </c>
-      <c r="F83" t="s">
-        <v>28</v>
-      </c>
-      <c r="G83" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+      <c r="B83" t="s">
+        <v>30</v>
+      </c>
+      <c r="C83" s="1">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D83">
+        <v>1290</v>
+      </c>
+      <c r="G83" s="1"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C84" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="D84">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="G84" s="1"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>9</v>
-      </c>
-      <c r="B85" t="s">
-        <v>34</v>
-      </c>
-      <c r="C85" s="1">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D85">
-        <v>370</v>
-      </c>
-      <c r="G85" s="1"/>
+        <v>37</v>
+      </c>
+      <c r="C85" s="1"/>
+      <c r="E85">
+        <v>629</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>9</v>
-      </c>
-      <c r="B86" t="s">
-        <v>20</v>
-      </c>
-      <c r="C86" s="1">
-        <v>0.67361111111111116</v>
-      </c>
-      <c r="D86">
-        <v>397</v>
-      </c>
-      <c r="G86" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C86" s="1"/>
+      <c r="E86">
+        <v>1130</v>
+      </c>
+      <c r="F86" t="s">
+        <v>30</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C87" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D87">
-        <v>441</v>
+        <v>367</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1866,13 +1875,13 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C88" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D88">
-        <v>423</v>
+        <v>370</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -1881,13 +1890,13 @@
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C89" s="1">
-        <v>0.6875</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D89">
-        <v>311</v>
+        <v>397</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -1899,10 +1908,10 @@
         <v>19</v>
       </c>
       <c r="C90" s="1">
-        <v>0.6875</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D90">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="G90" s="1"/>
     </row>
@@ -1911,13 +1920,13 @@
         <v>9</v>
       </c>
       <c r="B91" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C91" s="1">
-        <v>0.6875</v>
+        <v>0.68055555555555558</v>
       </c>
       <c r="D91">
-        <v>610</v>
+        <v>441</v>
       </c>
       <c r="G91" s="1"/>
     </row>
@@ -1926,13 +1935,13 @@
         <v>9</v>
       </c>
       <c r="B92" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C92" s="1">
-        <v>0.70138888888888884</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D92">
-        <v>322</v>
+        <v>435</v>
       </c>
       <c r="G92" s="1"/>
     </row>
@@ -1940,61 +1949,61 @@
       <c r="A93" t="s">
         <v>9</v>
       </c>
-      <c r="C93" s="1"/>
-      <c r="E93">
-        <v>326</v>
-      </c>
-      <c r="F93" t="s">
-        <v>10</v>
-      </c>
-      <c r="G93" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+      <c r="B93" t="s">
+        <v>29</v>
+      </c>
+      <c r="C93" s="1">
+        <v>0.6875</v>
+      </c>
+      <c r="D93">
+        <v>311</v>
+      </c>
+      <c r="G93" s="1"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>9</v>
       </c>
-      <c r="C94" s="1"/>
-      <c r="E94">
-        <v>560</v>
-      </c>
-      <c r="F94" t="s">
-        <v>25</v>
-      </c>
-      <c r="G94" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+      <c r="B94" t="s">
+        <v>22</v>
+      </c>
+      <c r="C94" s="1">
+        <v>0.6875</v>
+      </c>
+      <c r="D94">
+        <v>610</v>
+      </c>
+      <c r="G94" s="1"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>9</v>
-      </c>
-      <c r="C95" s="1"/>
-      <c r="E95">
-        <v>313</v>
-      </c>
-      <c r="F95" t="s">
-        <v>22</v>
-      </c>
-      <c r="G95" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B95" t="s">
+        <v>30</v>
+      </c>
+      <c r="C95" s="1">
+        <v>0.6958333333333333</v>
+      </c>
+      <c r="D95">
+        <v>4321</v>
+      </c>
+      <c r="G95" s="1"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>9</v>
       </c>
-      <c r="C96" s="1"/>
-      <c r="E96">
-        <v>450</v>
-      </c>
-      <c r="F96" t="s">
-        <v>20</v>
-      </c>
-      <c r="G96" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+      <c r="B96" t="s">
+        <v>23</v>
+      </c>
+      <c r="C96" s="1">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="D96">
+        <v>322</v>
+      </c>
+      <c r="G96" s="1"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -2002,13 +2011,13 @@
       </c>
       <c r="C97" s="1"/>
       <c r="E97">
-        <v>520</v>
+        <v>320</v>
       </c>
       <c r="F97" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G97" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.72222222222222221</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -2017,13 +2026,13 @@
       </c>
       <c r="C98" s="1"/>
       <c r="E98">
-        <v>588</v>
+        <v>326</v>
       </c>
       <c r="F98" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G98" s="1">
-        <v>0.73611111111111116</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -2032,13 +2041,13 @@
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>448</v>
+        <v>560</v>
       </c>
       <c r="F99" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G99" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2047,43 +2056,43 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>534</v>
+        <v>313</v>
       </c>
       <c r="F100" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G100" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>36</v>
-      </c>
-      <c r="B101" t="s">
-        <v>19</v>
-      </c>
-      <c r="C101" s="1">
-        <v>0.75694444444444442</v>
-      </c>
-      <c r="D101">
-        <v>222</v>
-      </c>
-      <c r="G101" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C101" s="1"/>
+      <c r="E101">
+        <v>520</v>
+      </c>
+      <c r="F101" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C102" s="1"/>
       <c r="E102">
-        <v>4308</v>
+        <v>530</v>
       </c>
       <c r="F102" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G102" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -2092,13 +2101,13 @@
       </c>
       <c r="C103" s="1"/>
       <c r="E103">
-        <v>528</v>
+        <v>588</v>
       </c>
       <c r="F103" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G103" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.73611111111111116</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -2107,42 +2116,42 @@
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>660</v>
+        <v>448</v>
       </c>
       <c r="F104" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G104" s="1">
-        <v>0.77083333333333337</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>9</v>
+      </c>
+      <c r="C105" s="1"/>
+      <c r="E105">
+        <v>534</v>
+      </c>
+      <c r="F105" t="s">
         <v>27</v>
       </c>
-      <c r="B105" t="s">
-        <v>26</v>
-      </c>
-      <c r="C105" s="1">
-        <v>0.77847222222222223</v>
-      </c>
-      <c r="D105">
-        <v>2657</v>
-      </c>
-      <c r="G105" s="1"/>
+      <c r="G105" s="1">
+        <v>0.74305555555555558</v>
+      </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B106" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C106" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.75694444444444442</v>
       </c>
       <c r="D106">
-        <v>742</v>
+        <v>222</v>
       </c>
       <c r="G106" s="1"/>
     </row>
@@ -2152,29 +2161,29 @@
       </c>
       <c r="C107" s="1"/>
       <c r="E107">
-        <v>4312</v>
+        <v>4308</v>
       </c>
       <c r="F107" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G107" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>9</v>
       </c>
-      <c r="B108" t="s">
-        <v>18</v>
-      </c>
-      <c r="C108" s="1">
-        <v>0.79513888888888884</v>
-      </c>
-      <c r="D108">
-        <v>431</v>
-      </c>
-      <c r="G108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="E108">
+        <v>528</v>
+      </c>
+      <c r="F108" t="s">
+        <v>8</v>
+      </c>
+      <c r="G108" s="1">
+        <v>0.76041666666666663</v>
+      </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
@@ -2182,72 +2191,72 @@
       </c>
       <c r="C109" s="1"/>
       <c r="E109">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="F109" t="s">
         <v>17</v>
       </c>
       <c r="G109" s="1">
-        <v>0.80555555555555558</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>9</v>
       </c>
-      <c r="B110" t="s">
-        <v>28</v>
-      </c>
-      <c r="C110" s="1">
-        <v>0.81944444444444442</v>
-      </c>
-      <c r="D110">
-        <v>425</v>
-      </c>
-      <c r="G110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="E110">
+        <v>558</v>
+      </c>
+      <c r="F110" t="s">
+        <v>25</v>
+      </c>
+      <c r="G110" s="1">
+        <v>0.77777777777777779</v>
+      </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>36</v>
-      </c>
-      <c r="C111" s="1"/>
-      <c r="E111">
-        <v>222</v>
-      </c>
-      <c r="F111" t="s">
-        <v>15</v>
-      </c>
-      <c r="G111" s="1">
-        <v>0.81944444444444442</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B111" t="s">
+        <v>30</v>
+      </c>
+      <c r="C111" s="1">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="D111">
+        <v>742</v>
+      </c>
+      <c r="G111" s="1"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>9</v>
-      </c>
-      <c r="B112" t="s">
-        <v>37</v>
-      </c>
-      <c r="C112" s="1">
-        <v>0.82291666666666663</v>
-      </c>
-      <c r="D112">
-        <v>329</v>
-      </c>
-      <c r="G112" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C112" s="1"/>
+      <c r="E112">
+        <v>4312</v>
+      </c>
+      <c r="F112" t="s">
+        <v>13</v>
+      </c>
+      <c r="G112" s="1">
+        <v>0.79027777777777775</v>
+      </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C113" s="1">
-        <v>0.82638888888888884</v>
+        <v>0.79513888888888884</v>
       </c>
       <c r="D113">
-        <v>523</v>
+        <v>431</v>
       </c>
       <c r="G113" s="1"/>
     </row>
@@ -2255,119 +2264,119 @@
       <c r="A114" t="s">
         <v>9</v>
       </c>
-      <c r="B114" t="s">
-        <v>13</v>
-      </c>
-      <c r="C114" s="1">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D114">
-        <v>583</v>
-      </c>
-      <c r="G114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="E114">
+        <v>670</v>
+      </c>
+      <c r="F114" t="s">
+        <v>17</v>
+      </c>
+      <c r="G114" s="1">
+        <v>0.80555555555555558</v>
+      </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C115" s="1">
-        <v>0.84375</v>
+        <v>0.81944444444444442</v>
       </c>
       <c r="D115">
-        <v>325</v>
+        <v>425</v>
       </c>
       <c r="G115" s="1"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>9</v>
-      </c>
-      <c r="B116" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="1">
-        <v>0.84375</v>
-      </c>
-      <c r="D116">
-        <v>445</v>
-      </c>
-      <c r="G116" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="C116" s="1"/>
+      <c r="E116">
+        <v>222</v>
+      </c>
+      <c r="F116" t="s">
+        <v>15</v>
+      </c>
+      <c r="G116" s="1">
+        <v>0.81944444444444442</v>
+      </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>9</v>
-      </c>
-      <c r="C117" s="1"/>
-      <c r="E117">
-        <v>590</v>
-      </c>
-      <c r="F117" t="s">
-        <v>13</v>
-      </c>
-      <c r="G117" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B117" t="s">
+        <v>29</v>
+      </c>
+      <c r="C117" s="1">
+        <v>0.82430555555555551</v>
+      </c>
+      <c r="D117">
+        <v>2657</v>
+      </c>
+      <c r="G117" s="1"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>9</v>
       </c>
       <c r="B118" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C118" s="1">
-        <v>0.85416666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D118">
-        <v>449</v>
+        <v>583</v>
       </c>
       <c r="G118" s="1"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B119" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C119" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.84375</v>
       </c>
       <c r="D119">
-        <v>881</v>
+        <v>325</v>
       </c>
       <c r="G119" s="1"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B120" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C120" s="1">
-        <v>0.86111111111111116</v>
+        <v>0.84375</v>
       </c>
       <c r="D120">
-        <v>4323</v>
+        <v>445</v>
       </c>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B121" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C121" s="1">
-        <v>0.86736111111111114</v>
+        <v>0.85069444444444442</v>
       </c>
       <c r="D121">
-        <v>1461</v>
+        <v>393</v>
       </c>
       <c r="G121" s="1"/>
     </row>
@@ -2375,44 +2384,44 @@
       <c r="A122" t="s">
         <v>9</v>
       </c>
-      <c r="B122" t="s">
-        <v>25</v>
-      </c>
-      <c r="C122" s="1">
-        <v>0.86805555555555558</v>
-      </c>
-      <c r="D122">
-        <v>563</v>
-      </c>
-      <c r="G122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="E122">
+        <v>590</v>
+      </c>
+      <c r="F122" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>9</v>
       </c>
       <c r="B123" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C123" s="1">
-        <v>0.875</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D123">
-        <v>535</v>
+        <v>449</v>
       </c>
       <c r="G123" s="1"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B124" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C124" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D124">
-        <v>312</v>
+        <v>881</v>
       </c>
       <c r="G124" s="1"/>
     </row>
@@ -2424,40 +2433,40 @@
         <v>8</v>
       </c>
       <c r="C125" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86111111111111116</v>
       </c>
       <c r="D125">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G125" s="1"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B126" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C126" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D126">
-        <v>589</v>
+        <v>1461</v>
       </c>
       <c r="G126" s="1"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B127" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C127" s="1">
-        <v>0.89930555555555547</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D127">
-        <v>1425</v>
+        <v>443</v>
       </c>
       <c r="G127" s="1"/>
     </row>
@@ -2466,13 +2475,13 @@
         <v>9</v>
       </c>
       <c r="B128" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C128" s="1">
-        <v>0.91319444444444442</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D128">
-        <v>585</v>
+        <v>563</v>
       </c>
       <c r="G128" s="1"/>
     </row>
@@ -2480,91 +2489,91 @@
       <c r="A129" t="s">
         <v>9</v>
       </c>
-      <c r="C129" s="1"/>
-      <c r="E129">
-        <v>315</v>
-      </c>
-      <c r="F129" t="s">
-        <v>20</v>
-      </c>
-      <c r="G129" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B129" t="s">
+        <v>42</v>
+      </c>
+      <c r="C129" s="1">
+        <v>0.87152777777777779</v>
+      </c>
+      <c r="D129">
+        <v>409</v>
+      </c>
+      <c r="G129" s="1"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>9</v>
       </c>
-      <c r="C130" s="1"/>
-      <c r="E130">
-        <v>365</v>
-      </c>
-      <c r="F130" t="s">
-        <v>24</v>
-      </c>
-      <c r="G130" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B130" t="s">
+        <v>43</v>
+      </c>
+      <c r="C130" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="D130">
+        <v>527</v>
+      </c>
+      <c r="G130" s="1"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>9</v>
       </c>
-      <c r="C131" s="1"/>
-      <c r="E131">
-        <v>600</v>
-      </c>
-      <c r="F131" t="s">
-        <v>13</v>
-      </c>
-      <c r="G131" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B131" t="s">
+        <v>27</v>
+      </c>
+      <c r="C131" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="D131">
+        <v>535</v>
+      </c>
+      <c r="G131" s="1"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>9</v>
       </c>
-      <c r="C132" s="1"/>
-      <c r="E132">
-        <v>429</v>
-      </c>
-      <c r="F132" t="s">
-        <v>21</v>
-      </c>
-      <c r="G132" s="1">
-        <v>0.92708333333333337</v>
-      </c>
+      <c r="B132" t="s">
+        <v>22</v>
+      </c>
+      <c r="C132" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D132">
+        <v>312</v>
+      </c>
+      <c r="G132" s="1"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>9</v>
       </c>
-      <c r="C133" s="1"/>
-      <c r="E133">
-        <v>578</v>
-      </c>
-      <c r="F133" t="s">
+      <c r="B133" t="s">
         <v>19</v>
       </c>
-      <c r="G133" s="1">
-        <v>0.93055555555555558</v>
-      </c>
+      <c r="C133" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D133">
+        <v>589</v>
+      </c>
+      <c r="G133" s="1"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>9</v>
       </c>
-      <c r="C134" s="1"/>
-      <c r="E134">
-        <v>627</v>
-      </c>
-      <c r="F134" t="s">
-        <v>22</v>
-      </c>
-      <c r="G134" s="1">
-        <v>0.93402777777777779</v>
-      </c>
+      <c r="B134" t="s">
+        <v>13</v>
+      </c>
+      <c r="C134" s="1">
+        <v>0.91319444444444442</v>
+      </c>
+      <c r="D134">
+        <v>585</v>
+      </c>
+      <c r="G134" s="1"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
@@ -2572,13 +2581,13 @@
       </c>
       <c r="C135" s="1"/>
       <c r="E135">
-        <v>568</v>
+        <v>315</v>
       </c>
       <c r="F135" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G135" s="1">
-        <v>0.94097222222222221</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -2587,43 +2596,43 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>452</v>
+        <v>365</v>
       </c>
       <c r="F136" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G136" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>339</v>
+        <v>580</v>
       </c>
       <c r="F137" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="G137" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>4336</v>
+        <v>308</v>
       </c>
       <c r="F138" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G138" s="1">
-        <v>0.9506944444444444</v>
+        <v>0.92361111111111116</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -2632,13 +2641,13 @@
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>317</v>
+        <v>429</v>
       </c>
       <c r="F139" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G139" s="1">
-        <v>0.95486111111111116</v>
+        <v>0.92708333333333337</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -2647,13 +2656,13 @@
       </c>
       <c r="C140" s="1"/>
       <c r="E140">
-        <v>432</v>
+        <v>578</v>
       </c>
       <c r="F140" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G140" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.93055555555555558</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -2662,13 +2671,13 @@
       </c>
       <c r="C141" s="1"/>
       <c r="E141">
-        <v>457</v>
+        <v>627</v>
       </c>
       <c r="F141" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G141" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.93402777777777779</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -2677,29 +2686,119 @@
       </c>
       <c r="C142" s="1"/>
       <c r="E142">
-        <v>552</v>
+        <v>574</v>
       </c>
       <c r="F142" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G142" s="1">
-        <v>0.97222222222222221</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>32</v>
-      </c>
-      <c r="B143" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143" s="1"/>
+      <c r="E143">
+        <v>568</v>
+      </c>
+      <c r="F143" t="s">
+        <v>17</v>
+      </c>
+      <c r="G143" s="1">
+        <v>0.94097222222222221</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>9</v>
+      </c>
+      <c r="C144" s="1"/>
+      <c r="E144">
+        <v>452</v>
+      </c>
+      <c r="F144" t="s">
+        <v>11</v>
+      </c>
+      <c r="G144" s="1">
+        <v>0.94791666666666663</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145" s="1"/>
+      <c r="E145">
+        <v>317</v>
+      </c>
+      <c r="F145" t="s">
         <v>23</v>
       </c>
-      <c r="C143" s="1">
+      <c r="G145" s="1">
+        <v>0.95486111111111116</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="1"/>
+      <c r="E146">
+        <v>457</v>
+      </c>
+      <c r="F146" t="s">
+        <v>16</v>
+      </c>
+      <c r="G146" s="1">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>9</v>
+      </c>
+      <c r="C147" s="1"/>
+      <c r="E147">
+        <v>300</v>
+      </c>
+      <c r="F147" t="s">
+        <v>15</v>
+      </c>
+      <c r="G147" s="1">
+        <v>0.96180555555555558</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>9</v>
+      </c>
+      <c r="C148" s="1"/>
+      <c r="E148">
+        <v>556</v>
+      </c>
+      <c r="F148" t="s">
+        <v>19</v>
+      </c>
+      <c r="G148" s="1">
+        <v>0.97222222222222221</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>36</v>
+      </c>
+      <c r="B149" t="s">
+        <v>23</v>
+      </c>
+      <c r="C149" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D143">
+      <c r="D149">
         <v>878</v>
       </c>
-      <c r="G143" s="1"/>
+      <c r="G149" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0319FB0-11BE-49BA-BE08-801B9DF7E46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FC3D9F2-6FC2-478E-BFC2-1613F538C128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{12E07602-D7BB-4CA4-8D16-99799E5D676C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{576BA9EA-7021-43FB-A0A4-3CE759193A8A}"/>
   </bookViews>
   <sheets>
-    <sheet name="25-06" sheetId="1" r:id="rId1"/>
+    <sheet name="26-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="42">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,7 +83,7 @@
     <t>KIAD</t>
   </si>
   <si>
-    <t>KONT</t>
+    <t>MHLM</t>
   </si>
   <si>
     <t>LEMD</t>
@@ -119,58 +119,52 @@
     <t>KSFO</t>
   </si>
   <si>
+    <t>KMIA</t>
+  </si>
+  <si>
+    <t>FFT</t>
+  </si>
+  <si>
+    <t>KDFW</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
+    <t>KIAH</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>KATL</t>
+  </si>
+  <si>
+    <t>CMP</t>
+  </si>
+  <si>
+    <t>AMX</t>
+  </si>
+  <si>
+    <t>SKRG</t>
+  </si>
+  <si>
+    <t>KMCO</t>
+  </si>
+  <si>
+    <t>IBE</t>
+  </si>
+  <si>
+    <t>CYUL</t>
+  </si>
+  <si>
+    <t>KBOS</t>
+  </si>
+  <si>
+    <t>KOAK</t>
+  </si>
+  <si>
     <t>KEWR</t>
-  </si>
-  <si>
-    <t>MHLM</t>
-  </si>
-  <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>KMIA</t>
-  </si>
-  <si>
-    <t>KIAH</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>KATL</t>
-  </si>
-  <si>
-    <t>TAG</t>
-  </si>
-  <si>
-    <t>MHRO</t>
-  </si>
-  <si>
-    <t>KDFW</t>
-  </si>
-  <si>
-    <t>CMP</t>
-  </si>
-  <si>
-    <t>AMX</t>
-  </si>
-  <si>
-    <t>SKRG</t>
-  </si>
-  <si>
-    <t>MMUN</t>
-  </si>
-  <si>
-    <t>IBE</t>
-  </si>
-  <si>
-    <t>KBOS</t>
-  </si>
-  <si>
-    <t>KORD</t>
-  </si>
-  <si>
-    <t>KLAS</t>
   </si>
 </sst>
 </file>
@@ -545,8 +539,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCA15754-F77F-4F74-B84D-A6F5F9CD9671}">
-  <dimension ref="A1:G149"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E06A59-FAC5-489A-8C64-0E50E9793DB9}">
+  <dimension ref="A1:G146"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -627,7 +621,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
@@ -711,7 +705,7 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D10">
-        <v>531</v>
+        <v>575</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -777,14 +771,14 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15">
         <v>3154</v>
       </c>
       <c r="F15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G15" s="1">
         <v>0.25</v>
@@ -807,14 +801,14 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" s="1"/>
       <c r="E17">
         <v>3154</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G17" s="1">
         <v>0.25069444444444444</v>
@@ -1002,17 +996,17 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C30" s="1"/>
       <c r="E30">
-        <v>319</v>
+        <v>4326</v>
       </c>
       <c r="F30" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G30" s="1">
-        <v>0.3125</v>
+        <v>0.29791666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1021,10 +1015,10 @@
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G31" s="1">
         <v>0.3125</v>
@@ -1036,10 +1030,10 @@
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>396</v>
+        <v>323</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G32" s="1">
         <v>0.3125</v>
@@ -1047,14 +1041,14 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>884</v>
+        <v>328</v>
       </c>
       <c r="F33" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G33" s="1">
         <v>0.3125</v>
@@ -1066,13 +1060,13 @@
       </c>
       <c r="C34" s="1"/>
       <c r="E34">
-        <v>310</v>
+        <v>396</v>
       </c>
       <c r="F34" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G34" s="1">
-        <v>0.31597222222222221</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1081,10 +1075,10 @@
       </c>
       <c r="C35" s="1"/>
       <c r="E35">
-        <v>440</v>
+        <v>310</v>
       </c>
       <c r="F35" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G35" s="1">
         <v>0.31597222222222221</v>
@@ -1096,10 +1090,10 @@
       </c>
       <c r="C36" s="1"/>
       <c r="E36">
-        <v>536</v>
+        <v>440</v>
       </c>
       <c r="F36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G36" s="1">
         <v>0.31597222222222221</v>
@@ -1109,16 +1103,16 @@
       <c r="A37" t="s">
         <v>9</v>
       </c>
-      <c r="B37" t="s">
-        <v>19</v>
-      </c>
-      <c r="C37" s="1">
-        <v>0.31944444444444442</v>
-      </c>
-      <c r="D37">
-        <v>321</v>
-      </c>
-      <c r="G37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="E37">
+        <v>536</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.31597222222222221</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
@@ -1129,7 +1123,7 @@
         <v>444</v>
       </c>
       <c r="F38" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G38" s="1">
         <v>0.32291666666666669</v>
@@ -1152,17 +1146,17 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C40" s="1"/>
       <c r="E40">
-        <v>368</v>
+        <v>4322</v>
       </c>
       <c r="F40" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G40" s="1">
-        <v>0.33333333333333331</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1171,10 +1165,10 @@
       </c>
       <c r="C41" s="1"/>
       <c r="E41">
-        <v>522</v>
+        <v>368</v>
       </c>
       <c r="F41" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G41" s="1">
         <v>0.33333333333333331</v>
@@ -1184,46 +1178,46 @@
       <c r="A42" t="s">
         <v>9</v>
       </c>
-      <c r="B42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D42">
-        <v>601</v>
-      </c>
-      <c r="G42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="E42">
+        <v>522</v>
+      </c>
+      <c r="F42" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.33333333333333331</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="C43" s="1"/>
-      <c r="E43">
-        <v>383</v>
-      </c>
-      <c r="F43" t="s">
-        <v>24</v>
-      </c>
-      <c r="G43" s="1">
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" s="1">
         <v>0.33680555555555558</v>
       </c>
+      <c r="D43">
+        <v>309</v>
+      </c>
+      <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="1"/>
-      <c r="E44">
-        <v>454</v>
-      </c>
-      <c r="F44" t="s">
-        <v>11</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0.34027777777777779</v>
-      </c>
+      <c r="B44" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="1">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="D44">
+        <v>581</v>
+      </c>
+      <c r="G44" s="1"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -1231,13 +1225,13 @@
       </c>
       <c r="C45" s="1"/>
       <c r="E45">
-        <v>324</v>
+        <v>383</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G45" s="1">
-        <v>0.34375</v>
+        <v>0.33680555555555558</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1246,13 +1240,13 @@
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>572</v>
+        <v>454</v>
       </c>
       <c r="F46" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G46" s="1">
-        <v>0.34375</v>
+        <v>0.34027777777777779</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1261,58 +1255,58 @@
       </c>
       <c r="C47" s="1"/>
       <c r="E47">
-        <v>430</v>
+        <v>324</v>
       </c>
       <c r="F47" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G47" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>9</v>
       </c>
-      <c r="B48" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="1">
-        <v>0.37152777777777779</v>
-      </c>
-      <c r="D48">
-        <v>451</v>
-      </c>
-      <c r="G48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="E48">
+        <v>554</v>
+      </c>
+      <c r="F48" t="s">
+        <v>19</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0.34375</v>
+      </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>526</v>
+        <v>884</v>
       </c>
       <c r="F49" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G49" s="1">
-        <v>0.375</v>
+        <v>0.35347222222222219</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C50" s="1"/>
       <c r="E50">
-        <v>4320</v>
+        <v>422</v>
       </c>
       <c r="F50" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G50" s="1">
-        <v>0.38333333333333336</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -1321,59 +1315,59 @@
       </c>
       <c r="C51" s="1"/>
       <c r="E51">
-        <v>369</v>
+        <v>430</v>
       </c>
       <c r="F51" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G51" s="1">
-        <v>0.3888888888888889</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="1"/>
-      <c r="E52">
-        <v>582</v>
-      </c>
-      <c r="F52" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="1">
-        <v>0.39930555555555558</v>
-      </c>
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.37847222222222221</v>
+      </c>
+      <c r="D52">
+        <v>559</v>
+      </c>
+      <c r="G52" s="1"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>12</v>
-      </c>
-      <c r="B53" t="s">
-        <v>26</v>
-      </c>
-      <c r="C53" s="1">
-        <v>0.40902777777777777</v>
-      </c>
-      <c r="D53">
-        <v>4337</v>
-      </c>
-      <c r="G53" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="E53">
+        <v>524</v>
+      </c>
+      <c r="F53" t="s">
+        <v>8</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0.38194444444444442</v>
+      </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>9</v>
       </c>
-      <c r="B54" t="s">
-        <v>17</v>
-      </c>
-      <c r="C54" s="1">
-        <v>0.41319444444444442</v>
-      </c>
-      <c r="D54">
-        <v>569</v>
-      </c>
-      <c r="G54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="E54">
+        <v>369</v>
+      </c>
+      <c r="F54" t="s">
+        <v>35</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0.3888888888888889</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
@@ -1381,72 +1375,72 @@
       </c>
       <c r="C55" s="1"/>
       <c r="E55">
-        <v>392</v>
+        <v>582</v>
       </c>
       <c r="F55" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G55" s="1">
-        <v>0.41319444444444442</v>
+        <v>0.39930555555555558</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
-      <c r="C56" s="1"/>
-      <c r="E56">
-        <v>408</v>
-      </c>
-      <c r="F56" t="s">
-        <v>42</v>
-      </c>
-      <c r="G56" s="1">
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" s="1">
         <v>0.41319444444444442</v>
       </c>
+      <c r="D56">
+        <v>569</v>
+      </c>
+      <c r="G56" s="1"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>9</v>
-      </c>
-      <c r="C57" s="1"/>
-      <c r="E57">
-        <v>609</v>
-      </c>
-      <c r="F57" t="s">
-        <v>22</v>
-      </c>
-      <c r="G57" s="1">
-        <v>0.4236111111111111</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B57" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D57">
+        <v>342</v>
+      </c>
+      <c r="G57" s="1"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>9</v>
       </c>
-      <c r="B58" t="s">
-        <v>27</v>
-      </c>
-      <c r="C58" s="1">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="D58">
-        <v>537</v>
-      </c>
-      <c r="G58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="E58">
+        <v>609</v>
+      </c>
+      <c r="F58" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0.4236111111111111</v>
+      </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C59" s="1">
-        <v>0.44791666666666669</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="D59">
-        <v>455</v>
+        <v>537</v>
       </c>
       <c r="G59" s="1"/>
     </row>
@@ -1455,13 +1449,13 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C60" s="1">
-        <v>0.4513888888888889</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="D60">
-        <v>573</v>
+        <v>455</v>
       </c>
       <c r="G60" s="1"/>
     </row>
@@ -1497,48 +1491,48 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>27</v>
+      </c>
+      <c r="C63" s="1"/>
+      <c r="E63">
+        <v>343</v>
+      </c>
+      <c r="F63" t="s">
         <v>28</v>
       </c>
-      <c r="B63" t="s">
-        <v>29</v>
-      </c>
-      <c r="C63" s="1">
-        <v>0.47291666666666665</v>
-      </c>
-      <c r="D63">
-        <v>495</v>
-      </c>
-      <c r="G63" s="1"/>
+      <c r="G63" s="1">
+        <v>0.46180555555555558</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B64" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C64" s="1">
-        <v>0.47847222222222219</v>
+        <v>0.47291666666666665</v>
       </c>
       <c r="D64">
-        <v>1194</v>
+        <v>495</v>
       </c>
       <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>9</v>
-      </c>
-      <c r="C65" s="1"/>
-      <c r="E65">
-        <v>584</v>
-      </c>
-      <c r="F65" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" t="s">
         <v>13</v>
       </c>
-      <c r="G65" s="1">
-        <v>0.49305555555555558</v>
-      </c>
+      <c r="C65" s="1">
+        <v>0.47847222222222219</v>
+      </c>
+      <c r="D65">
+        <v>1194</v>
+      </c>
+      <c r="G65" s="1"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
@@ -1546,13 +1540,13 @@
       </c>
       <c r="C66" s="1"/>
       <c r="E66">
-        <v>434</v>
+        <v>584</v>
       </c>
       <c r="F66" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G66" s="1">
-        <v>0.49652777777777779</v>
+        <v>0.49305555555555558</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -1587,61 +1581,61 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69" s="1"/>
-      <c r="E69">
-        <v>442</v>
-      </c>
-      <c r="F69" t="s">
-        <v>35</v>
-      </c>
-      <c r="G69" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B69" t="s">
+        <v>30</v>
+      </c>
+      <c r="C69" s="1">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D69">
+        <v>1441</v>
+      </c>
+      <c r="G69" s="1"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>7</v>
-      </c>
-      <c r="B70" t="s">
-        <v>30</v>
-      </c>
-      <c r="C70" s="1">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="D70">
-        <v>1441</v>
-      </c>
-      <c r="G70" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="E70">
+        <v>1508</v>
+      </c>
+      <c r="F70" t="s">
+        <v>26</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0.51597222222222228</v>
+      </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>28</v>
-      </c>
-      <c r="C71" s="1"/>
-      <c r="E71">
-        <v>1508</v>
-      </c>
-      <c r="F71" t="s">
-        <v>29</v>
-      </c>
-      <c r="G71" s="1">
-        <v>0.51597222222222228</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B71" t="s">
+        <v>32</v>
+      </c>
+      <c r="C71" s="1">
+        <v>0.5180555555555556</v>
+      </c>
+      <c r="D71">
+        <v>1910</v>
+      </c>
+      <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C72" s="1">
-        <v>0.5180555555555556</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="D72">
-        <v>1910</v>
+        <v>937</v>
       </c>
       <c r="G72" s="1"/>
     </row>
@@ -1650,223 +1644,223 @@
         <v>33</v>
       </c>
       <c r="B73" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C73" s="1">
-        <v>0.52083333333333337</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="D73">
-        <v>420</v>
+        <v>816</v>
       </c>
       <c r="G73" s="1"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>28</v>
-      </c>
-      <c r="B74" t="s">
-        <v>35</v>
-      </c>
-      <c r="C74" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D74">
-        <v>937</v>
-      </c>
-      <c r="G74" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="E74">
+        <v>1458</v>
+      </c>
+      <c r="F74" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0.55555555555555558</v>
+      </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>36</v>
-      </c>
-      <c r="B75" t="s">
-        <v>23</v>
-      </c>
-      <c r="C75" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D75">
-        <v>816</v>
-      </c>
-      <c r="G75" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="E75">
+        <v>380</v>
+      </c>
+      <c r="F75" t="s">
+        <v>28</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0.57222222222222219</v>
+      </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C76" s="1"/>
       <c r="E76">
-        <v>421</v>
+        <v>1468</v>
       </c>
       <c r="F76" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G76" s="1">
-        <v>0.55208333333333337</v>
+        <v>0.57638888888888895</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C77" s="1"/>
       <c r="E77">
-        <v>1458</v>
+        <v>1978</v>
       </c>
       <c r="F77" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G77" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.57708333333333328</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C78" s="1"/>
       <c r="E78">
-        <v>380</v>
+        <v>871</v>
       </c>
       <c r="F78" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G78" s="1">
-        <v>0.57222222222222219</v>
+        <v>0.58194444444444449</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="1"/>
-      <c r="E79">
-        <v>1468</v>
-      </c>
-      <c r="F79" t="s">
-        <v>30</v>
-      </c>
-      <c r="G79" s="1">
-        <v>0.57638888888888895</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="1">
+        <v>0.59375</v>
+      </c>
+      <c r="D79">
+        <v>628</v>
+      </c>
+      <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="1"/>
-      <c r="E80">
-        <v>1978</v>
-      </c>
-      <c r="F80" t="s">
-        <v>32</v>
-      </c>
-      <c r="G80" s="1">
-        <v>0.57708333333333328</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B80" t="s">
+        <v>30</v>
+      </c>
+      <c r="C80" s="1">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D80">
+        <v>1290</v>
+      </c>
+      <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>36</v>
-      </c>
-      <c r="C81" s="1"/>
-      <c r="E81">
-        <v>871</v>
-      </c>
-      <c r="F81" t="s">
-        <v>23</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0.58194444444444449</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B81" t="s">
+        <v>19</v>
+      </c>
+      <c r="C81" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="D81">
+        <v>557</v>
+      </c>
+      <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="B82" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C82" s="1">
-        <v>0.59375</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="D82">
-        <v>628</v>
+        <v>382</v>
       </c>
       <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>7</v>
-      </c>
-      <c r="B83" t="s">
-        <v>30</v>
-      </c>
-      <c r="C83" s="1">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D83">
-        <v>1290</v>
-      </c>
-      <c r="G83" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="C83" s="1"/>
+      <c r="E83">
+        <v>629</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>9</v>
-      </c>
-      <c r="B84" t="s">
-        <v>24</v>
-      </c>
-      <c r="C84" s="1">
+        <v>7</v>
+      </c>
+      <c r="C84" s="1"/>
+      <c r="E84">
+        <v>1130</v>
+      </c>
+      <c r="F84" t="s">
+        <v>30</v>
+      </c>
+      <c r="G84" s="1">
         <v>0.65277777777777779</v>
       </c>
-      <c r="D84">
-        <v>382</v>
-      </c>
-      <c r="G84" s="1"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>37</v>
-      </c>
-      <c r="C85" s="1"/>
-      <c r="E85">
-        <v>629</v>
-      </c>
-      <c r="F85" t="s">
-        <v>18</v>
-      </c>
-      <c r="G85" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B85" t="s">
+        <v>30</v>
+      </c>
+      <c r="C85" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D85">
+        <v>367</v>
+      </c>
+      <c r="G85" s="1"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" s="1"/>
-      <c r="E86">
-        <v>1130</v>
-      </c>
-      <c r="F86" t="s">
-        <v>30</v>
-      </c>
-      <c r="G86" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B86" t="s">
+        <v>35</v>
+      </c>
+      <c r="C86" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D86">
+        <v>370</v>
+      </c>
+      <c r="G86" s="1"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C87" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D87">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1875,13 +1869,13 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C88" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.68055555555555558</v>
       </c>
       <c r="D88">
-        <v>370</v>
+        <v>441</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -1890,13 +1884,13 @@
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C89" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D89">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -1905,13 +1899,13 @@
         <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C90" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.6875</v>
       </c>
       <c r="D90">
-        <v>553</v>
+        <v>311</v>
       </c>
       <c r="G90" s="1"/>
     </row>
@@ -1920,13 +1914,13 @@
         <v>9</v>
       </c>
       <c r="B91" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C91" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.6875</v>
       </c>
       <c r="D91">
-        <v>441</v>
+        <v>555</v>
       </c>
       <c r="G91" s="1"/>
     </row>
@@ -1935,13 +1929,13 @@
         <v>9</v>
       </c>
       <c r="B92" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C92" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.6875</v>
       </c>
       <c r="D92">
-        <v>435</v>
+        <v>610</v>
       </c>
       <c r="G92" s="1"/>
     </row>
@@ -1950,60 +1944,60 @@
         <v>9</v>
       </c>
       <c r="B93" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C93" s="1">
-        <v>0.6875</v>
+        <v>0.70138888888888884</v>
       </c>
       <c r="D93">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="G93" s="1"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C94" s="1">
-        <v>0.6875</v>
+        <v>0.72777777777777775</v>
       </c>
       <c r="D94">
-        <v>610</v>
+        <v>4327</v>
       </c>
       <c r="G94" s="1"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>12</v>
-      </c>
-      <c r="B95" t="s">
-        <v>30</v>
-      </c>
-      <c r="C95" s="1">
-        <v>0.6958333333333333</v>
-      </c>
-      <c r="D95">
-        <v>4321</v>
-      </c>
-      <c r="G95" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C95" s="1"/>
+      <c r="E95">
+        <v>326</v>
+      </c>
+      <c r="F95" t="s">
+        <v>10</v>
+      </c>
+      <c r="G95" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>9</v>
       </c>
-      <c r="B96" t="s">
-        <v>23</v>
-      </c>
-      <c r="C96" s="1">
-        <v>0.70138888888888884</v>
-      </c>
-      <c r="D96">
-        <v>322</v>
-      </c>
-      <c r="G96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="E96">
+        <v>560</v>
+      </c>
+      <c r="F96" t="s">
+        <v>25</v>
+      </c>
+      <c r="G96" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -2011,13 +2005,13 @@
       </c>
       <c r="C97" s="1"/>
       <c r="E97">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F97" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G97" s="1">
-        <v>0.72222222222222221</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -2026,13 +2020,13 @@
       </c>
       <c r="C98" s="1"/>
       <c r="E98">
-        <v>326</v>
+        <v>450</v>
       </c>
       <c r="F98" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G98" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -2041,13 +2035,13 @@
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>560</v>
+        <v>520</v>
       </c>
       <c r="F99" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G99" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2056,13 +2050,13 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>313</v>
+        <v>588</v>
       </c>
       <c r="F100" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G100" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.73611111111111116</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -2071,13 +2065,13 @@
       </c>
       <c r="C101" s="1"/>
       <c r="E101">
-        <v>520</v>
+        <v>448</v>
       </c>
       <c r="F101" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G101" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -2086,43 +2080,43 @@
       </c>
       <c r="C102" s="1"/>
       <c r="E102">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F102" t="s">
         <v>14</v>
       </c>
       <c r="G102" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>9</v>
-      </c>
-      <c r="C103" s="1"/>
-      <c r="E103">
-        <v>588</v>
-      </c>
-      <c r="F103" t="s">
+        <v>37</v>
+      </c>
+      <c r="B103" t="s">
         <v>19</v>
       </c>
-      <c r="G103" s="1">
-        <v>0.73611111111111116</v>
-      </c>
+      <c r="C103" s="1">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="D103">
+        <v>222</v>
+      </c>
+      <c r="G103" s="1"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>448</v>
+        <v>4308</v>
       </c>
       <c r="F104" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G104" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -2131,74 +2125,74 @@
       </c>
       <c r="C105" s="1"/>
       <c r="E105">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="F105" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="G105" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.76041666666666663</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>40</v>
-      </c>
-      <c r="B106" t="s">
-        <v>19</v>
-      </c>
-      <c r="C106" s="1">
-        <v>0.75694444444444442</v>
-      </c>
-      <c r="D106">
-        <v>222</v>
-      </c>
-      <c r="G106" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C106" s="1"/>
+      <c r="E106">
+        <v>660</v>
+      </c>
+      <c r="F106" t="s">
+        <v>17</v>
+      </c>
+      <c r="G106" s="1">
+        <v>0.77083333333333337</v>
+      </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>12</v>
-      </c>
-      <c r="C107" s="1"/>
-      <c r="E107">
-        <v>4308</v>
-      </c>
-      <c r="F107" t="s">
-        <v>8</v>
-      </c>
-      <c r="G107" s="1">
-        <v>0.75763888888888886</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B107" t="s">
+        <v>30</v>
+      </c>
+      <c r="C107" s="1">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="D107">
+        <v>742</v>
+      </c>
+      <c r="G107" s="1"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C108" s="1"/>
       <c r="E108">
-        <v>528</v>
+        <v>4312</v>
       </c>
       <c r="F108" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G108" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.79027777777777775</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>9</v>
       </c>
-      <c r="C109" s="1"/>
-      <c r="E109">
-        <v>660</v>
-      </c>
-      <c r="F109" t="s">
-        <v>17</v>
-      </c>
-      <c r="G109" s="1">
-        <v>0.77083333333333337</v>
-      </c>
+      <c r="B109" t="s">
+        <v>18</v>
+      </c>
+      <c r="C109" s="1">
+        <v>0.79513888888888884</v>
+      </c>
+      <c r="D109">
+        <v>431</v>
+      </c>
+      <c r="G109" s="1"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -2206,117 +2200,117 @@
       </c>
       <c r="C110" s="1"/>
       <c r="E110">
-        <v>558</v>
+        <v>670</v>
       </c>
       <c r="F110" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G110" s="1">
-        <v>0.77777777777777779</v>
+        <v>0.80555555555555558</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>7</v>
-      </c>
-      <c r="B111" t="s">
-        <v>30</v>
-      </c>
-      <c r="C111" s="1">
-        <v>0.79027777777777775</v>
-      </c>
-      <c r="D111">
-        <v>742</v>
-      </c>
-      <c r="G111" s="1"/>
+        <v>37</v>
+      </c>
+      <c r="C111" s="1"/>
+      <c r="E111">
+        <v>222</v>
+      </c>
+      <c r="F111" t="s">
+        <v>15</v>
+      </c>
+      <c r="G111" s="1">
+        <v>0.80902777777777779</v>
+      </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>12</v>
-      </c>
-      <c r="C112" s="1"/>
-      <c r="E112">
-        <v>4312</v>
-      </c>
-      <c r="F112" t="s">
-        <v>13</v>
-      </c>
-      <c r="G112" s="1">
-        <v>0.79027777777777775</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B112" t="s">
+        <v>30</v>
+      </c>
+      <c r="C112" s="1">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="D112">
+        <v>425</v>
+      </c>
+      <c r="G112" s="1"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C113" s="1">
-        <v>0.79513888888888884</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="D113">
-        <v>431</v>
+        <v>329</v>
       </c>
       <c r="G113" s="1"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>9</v>
-      </c>
-      <c r="C114" s="1"/>
-      <c r="E114">
-        <v>670</v>
-      </c>
-      <c r="F114" t="s">
-        <v>17</v>
-      </c>
-      <c r="G114" s="1">
-        <v>0.80555555555555558</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B114" t="s">
+        <v>26</v>
+      </c>
+      <c r="C114" s="1">
+        <v>0.82430555555555551</v>
+      </c>
+      <c r="D114">
+        <v>2657</v>
+      </c>
+      <c r="G114" s="1"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C115" s="1">
-        <v>0.81944444444444442</v>
+        <v>0.82638888888888884</v>
       </c>
       <c r="D115">
-        <v>425</v>
+        <v>523</v>
       </c>
       <c r="G115" s="1"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>40</v>
-      </c>
-      <c r="C116" s="1"/>
-      <c r="E116">
-        <v>222</v>
-      </c>
-      <c r="F116" t="s">
-        <v>15</v>
-      </c>
-      <c r="G116" s="1">
-        <v>0.81944444444444442</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B116" t="s">
+        <v>13</v>
+      </c>
+      <c r="C116" s="1">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D116">
+        <v>583</v>
+      </c>
+      <c r="G116" s="1"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B117" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C117" s="1">
-        <v>0.82430555555555551</v>
+        <v>0.84375</v>
       </c>
       <c r="D117">
-        <v>2657</v>
+        <v>325</v>
       </c>
       <c r="G117" s="1"/>
     </row>
@@ -2325,13 +2319,13 @@
         <v>9</v>
       </c>
       <c r="B118" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C118" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.84375</v>
       </c>
       <c r="D118">
-        <v>583</v>
+        <v>445</v>
       </c>
       <c r="G118" s="1"/>
     </row>
@@ -2339,89 +2333,89 @@
       <c r="A119" t="s">
         <v>9</v>
       </c>
-      <c r="B119" t="s">
-        <v>10</v>
-      </c>
-      <c r="C119" s="1">
-        <v>0.84375</v>
-      </c>
-      <c r="D119">
-        <v>325</v>
-      </c>
-      <c r="G119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="E119">
+        <v>590</v>
+      </c>
+      <c r="F119" t="s">
+        <v>13</v>
+      </c>
+      <c r="G119" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>9</v>
       </c>
       <c r="B120" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C120" s="1">
-        <v>0.84375</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D120">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B121" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C121" s="1">
-        <v>0.85069444444444442</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D121">
-        <v>393</v>
+        <v>881</v>
       </c>
       <c r="G121" s="1"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>9</v>
-      </c>
-      <c r="C122" s="1"/>
-      <c r="E122">
-        <v>590</v>
-      </c>
-      <c r="F122" t="s">
-        <v>13</v>
-      </c>
-      <c r="G122" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B122" t="s">
+        <v>40</v>
+      </c>
+      <c r="C122" s="1">
+        <v>0.86111111111111116</v>
+      </c>
+      <c r="D122">
+        <v>4323</v>
+      </c>
+      <c r="G122" s="1"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C123" s="1">
-        <v>0.85416666666666663</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D123">
-        <v>449</v>
+        <v>1461</v>
       </c>
       <c r="G123" s="1"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C124" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D124">
-        <v>881</v>
+        <v>563</v>
       </c>
       <c r="G124" s="1"/>
     </row>
@@ -2430,28 +2424,28 @@
         <v>9</v>
       </c>
       <c r="B125" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C125" s="1">
-        <v>0.86111111111111116</v>
+        <v>0.875</v>
       </c>
       <c r="D125">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="G125" s="1"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B126" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C126" s="1">
-        <v>0.86736111111111114</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D126">
-        <v>1461</v>
+        <v>312</v>
       </c>
       <c r="G126" s="1"/>
     </row>
@@ -2460,13 +2454,13 @@
         <v>9</v>
       </c>
       <c r="B127" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C127" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D127">
-        <v>443</v>
+        <v>525</v>
       </c>
       <c r="G127" s="1"/>
     </row>
@@ -2475,28 +2469,28 @@
         <v>9</v>
       </c>
       <c r="B128" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C128" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D128">
-        <v>563</v>
+        <v>589</v>
       </c>
       <c r="G128" s="1"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B129" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C129" s="1">
-        <v>0.87152777777777779</v>
+        <v>0.89930555555555547</v>
       </c>
       <c r="D129">
-        <v>409</v>
+        <v>1425</v>
       </c>
       <c r="G129" s="1"/>
     </row>
@@ -2505,13 +2499,13 @@
         <v>9</v>
       </c>
       <c r="B130" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="C130" s="1">
-        <v>0.875</v>
+        <v>0.91319444444444442</v>
       </c>
       <c r="D130">
-        <v>527</v>
+        <v>585</v>
       </c>
       <c r="G130" s="1"/>
     </row>
@@ -2519,61 +2513,61 @@
       <c r="A131" t="s">
         <v>9</v>
       </c>
-      <c r="B131" t="s">
-        <v>27</v>
-      </c>
-      <c r="C131" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="D131">
-        <v>535</v>
-      </c>
-      <c r="G131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="E131">
+        <v>315</v>
+      </c>
+      <c r="F131" t="s">
+        <v>20</v>
+      </c>
+      <c r="G131" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>9</v>
       </c>
-      <c r="B132" t="s">
-        <v>22</v>
-      </c>
-      <c r="C132" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D132">
-        <v>312</v>
-      </c>
-      <c r="G132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="E132">
+        <v>365</v>
+      </c>
+      <c r="F132" t="s">
+        <v>24</v>
+      </c>
+      <c r="G132" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>9</v>
       </c>
-      <c r="B133" t="s">
-        <v>19</v>
-      </c>
-      <c r="C133" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D133">
-        <v>589</v>
-      </c>
-      <c r="G133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="E133">
+        <v>600</v>
+      </c>
+      <c r="F133" t="s">
+        <v>13</v>
+      </c>
+      <c r="G133" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>9</v>
       </c>
-      <c r="B134" t="s">
-        <v>13</v>
-      </c>
-      <c r="C134" s="1">
-        <v>0.91319444444444442</v>
-      </c>
-      <c r="D134">
-        <v>585</v>
-      </c>
-      <c r="G134" s="1"/>
+      <c r="C134" s="1"/>
+      <c r="E134">
+        <v>429</v>
+      </c>
+      <c r="F134" t="s">
+        <v>21</v>
+      </c>
+      <c r="G134" s="1">
+        <v>0.92708333333333337</v>
+      </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
@@ -2581,13 +2575,13 @@
       </c>
       <c r="C135" s="1"/>
       <c r="E135">
-        <v>315</v>
+        <v>578</v>
       </c>
       <c r="F135" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G135" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.93055555555555558</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -2596,13 +2590,13 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>365</v>
+        <v>627</v>
       </c>
       <c r="F136" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G136" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.93402777777777779</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -2611,13 +2605,13 @@
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="F137" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G137" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -2626,13 +2620,13 @@
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>308</v>
+        <v>568</v>
       </c>
       <c r="F138" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G138" s="1">
-        <v>0.92361111111111116</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -2641,43 +2635,43 @@
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="F139" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G139" s="1">
-        <v>0.92708333333333337</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C140" s="1"/>
       <c r="E140">
-        <v>578</v>
+        <v>339</v>
       </c>
       <c r="F140" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="G140" s="1">
-        <v>0.93055555555555558</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C141" s="1"/>
       <c r="E141">
-        <v>627</v>
+        <v>4336</v>
       </c>
       <c r="F141" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G141" s="1">
-        <v>0.93402777777777779</v>
+        <v>0.9506944444444444</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -2686,13 +2680,13 @@
       </c>
       <c r="C142" s="1"/>
       <c r="E142">
-        <v>574</v>
+        <v>317</v>
       </c>
       <c r="F142" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G142" s="1">
-        <v>0.9375</v>
+        <v>0.95486111111111116</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -2701,13 +2695,13 @@
       </c>
       <c r="C143" s="1"/>
       <c r="E143">
-        <v>568</v>
+        <v>432</v>
       </c>
       <c r="F143" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G143" s="1">
-        <v>0.94097222222222221</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -2716,13 +2710,13 @@
       </c>
       <c r="C144" s="1"/>
       <c r="E144">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F144" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G144" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -2731,74 +2725,29 @@
       </c>
       <c r="C145" s="1"/>
       <c r="E145">
-        <v>317</v>
+        <v>552</v>
       </c>
       <c r="F145" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G145" s="1">
-        <v>0.95486111111111116</v>
+        <v>0.97222222222222221</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>9</v>
-      </c>
-      <c r="C146" s="1"/>
-      <c r="E146">
-        <v>457</v>
-      </c>
-      <c r="F146" t="s">
-        <v>16</v>
-      </c>
-      <c r="G146" s="1">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>9</v>
-      </c>
-      <c r="C147" s="1"/>
-      <c r="E147">
-        <v>300</v>
-      </c>
-      <c r="F147" t="s">
-        <v>15</v>
-      </c>
-      <c r="G147" s="1">
-        <v>0.96180555555555558</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>9</v>
-      </c>
-      <c r="C148" s="1"/>
-      <c r="E148">
-        <v>556</v>
-      </c>
-      <c r="F148" t="s">
-        <v>19</v>
-      </c>
-      <c r="G148" s="1">
-        <v>0.97222222222222221</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>36</v>
-      </c>
-      <c r="B149" t="s">
+        <v>33</v>
+      </c>
+      <c r="B146" t="s">
         <v>23</v>
       </c>
-      <c r="C149" s="1">
+      <c r="C146" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D149">
+      <c r="D146">
         <v>878</v>
       </c>
-      <c r="G149" s="1"/>
+      <c r="G146" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FC3D9F2-6FC2-478E-BFC2-1613F538C128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94C4B9C2-E2C6-4507-8A87-78FE11F7AF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{576BA9EA-7021-43FB-A0A4-3CE759193A8A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FB723472-D0A6-4FEE-BC00-280F76ACF404}"/>
   </bookViews>
   <sheets>
-    <sheet name="26-06" sheetId="1" r:id="rId1"/>
+    <sheet name="27-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="42">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,6 +83,9 @@
     <t>KIAD</t>
   </si>
   <si>
+    <t>KONT</t>
+  </si>
+  <si>
     <t>MHLM</t>
   </si>
   <si>
@@ -119,27 +122,27 @@
     <t>KSFO</t>
   </si>
   <si>
+    <t>KEWR</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
     <t>KMIA</t>
   </si>
   <si>
-    <t>FFT</t>
+    <t>KIAH</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>KATL</t>
   </si>
   <si>
     <t>KDFW</t>
   </si>
   <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>KIAH</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>KATL</t>
-  </si>
-  <si>
     <t>CMP</t>
   </si>
   <si>
@@ -149,22 +152,19 @@
     <t>SKRG</t>
   </si>
   <si>
-    <t>KMCO</t>
+    <t>MMUN</t>
   </si>
   <si>
     <t>IBE</t>
   </si>
   <si>
-    <t>CYUL</t>
-  </si>
-  <si>
     <t>KBOS</t>
   </si>
   <si>
-    <t>KOAK</t>
-  </si>
-  <si>
-    <t>KEWR</t>
+    <t>KORD</t>
+  </si>
+  <si>
+    <t>KLAS</t>
   </si>
 </sst>
 </file>
@@ -539,8 +539,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E06A59-FAC5-489A-8C64-0E50E9793DB9}">
-  <dimension ref="A1:G146"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C91CB52C-AE4B-433B-A31E-86EE70370DD2}">
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -621,14 +621,14 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
         <v>879</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5" s="1">
         <v>0.20347222222222219</v>
@@ -673,7 +673,7 @@
         <v>300</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" s="1">
         <v>0.21527777777777779</v>
@@ -705,7 +705,7 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D10">
-        <v>575</v>
+        <v>531</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -717,40 +717,40 @@
         <v>15</v>
       </c>
       <c r="C11" s="1">
-        <v>0.22916666666666666</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="D11">
-        <v>301</v>
+        <v>575</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1">
-        <v>0.24444444444444444</v>
+        <v>0.22916666666666666</v>
       </c>
       <c r="D12">
-        <v>4309</v>
+        <v>301</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C13" s="1">
-        <v>0.24652777777777779</v>
+        <v>0.24444444444444444</v>
       </c>
       <c r="D13">
-        <v>456</v>
+        <v>4309</v>
       </c>
       <c r="G13" s="1"/>
     </row>
@@ -765,35 +765,35 @@
         <v>0.24652777777777779</v>
       </c>
       <c r="D14">
-        <v>661</v>
+        <v>456</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="E15">
-        <v>3154</v>
-      </c>
-      <c r="F15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0.25</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.24652777777777779</v>
+      </c>
+      <c r="D15">
+        <v>661</v>
+      </c>
+      <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C16" s="1"/>
       <c r="E16">
-        <v>1467</v>
+        <v>3154</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G16" s="1">
         <v>0.25</v>
@@ -801,33 +801,33 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1"/>
       <c r="E17">
-        <v>3154</v>
+        <v>1467</v>
       </c>
       <c r="F17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G17" s="1">
-        <v>0.25069444444444444</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="1">
-        <v>0.25694444444444442</v>
-      </c>
-      <c r="D18">
-        <v>433</v>
-      </c>
-      <c r="G18" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="E18">
+        <v>3154</v>
+      </c>
+      <c r="F18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.25069444444444444</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -840,7 +840,7 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="D19">
-        <v>579</v>
+        <v>433</v>
       </c>
       <c r="G19" s="1"/>
     </row>
@@ -849,13 +849,13 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C20" s="1">
-        <v>0.26041666666666669</v>
+        <v>0.25694444444444442</v>
       </c>
       <c r="D20">
-        <v>529</v>
+        <v>579</v>
       </c>
       <c r="G20" s="1"/>
     </row>
@@ -864,13 +864,13 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C21" s="1">
-        <v>0.2638888888888889</v>
+        <v>0.26041666666666669</v>
       </c>
       <c r="D21">
-        <v>314</v>
+        <v>529</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -882,10 +882,10 @@
         <v>21</v>
       </c>
       <c r="C22" s="1">
-        <v>0.2673611111111111</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="D22">
-        <v>428</v>
+        <v>314</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -900,7 +900,7 @@
         <v>0.2673611111111111</v>
       </c>
       <c r="D23">
-        <v>626</v>
+        <v>428</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -912,10 +912,10 @@
         <v>23</v>
       </c>
       <c r="C24" s="1">
-        <v>0.27083333333333331</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D24">
-        <v>316</v>
+        <v>626</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -930,7 +930,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D25">
-        <v>366</v>
+        <v>316</v>
       </c>
       <c r="G25" s="1"/>
     </row>
@@ -945,7 +945,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D26">
-        <v>561</v>
+        <v>366</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -954,13 +954,13 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C27" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D27">
-        <v>591</v>
+        <v>561</v>
       </c>
       <c r="G27" s="1"/>
     </row>
@@ -969,13 +969,13 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C28" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D28">
-        <v>671</v>
+        <v>591</v>
       </c>
       <c r="G28" s="1"/>
     </row>
@@ -984,44 +984,44 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C29" s="1">
-        <v>0.29166666666666669</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="D29">
-        <v>521</v>
+        <v>671</v>
       </c>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="1"/>
-      <c r="E30">
-        <v>4326</v>
-      </c>
-      <c r="F30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0.29791666666666666</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="D30">
+        <v>521</v>
+      </c>
+      <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>319</v>
+        <v>4326</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G31" s="1">
-        <v>0.3125</v>
+        <v>0.29791666666666666</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F32" t="s">
         <v>23</v>
@@ -1045,10 +1045,10 @@
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="F33" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G33" s="1">
         <v>0.3125</v>
@@ -1063,7 +1063,7 @@
         <v>396</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G34" s="1">
         <v>0.3125</v>
@@ -1071,17 +1071,17 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C35" s="1"/>
       <c r="E35">
-        <v>310</v>
+        <v>884</v>
       </c>
       <c r="F35" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G35" s="1">
-        <v>0.31597222222222221</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1090,10 +1090,10 @@
       </c>
       <c r="C36" s="1"/>
       <c r="E36">
-        <v>440</v>
+        <v>310</v>
       </c>
       <c r="F36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G36" s="1">
         <v>0.31597222222222221</v>
@@ -1105,10 +1105,10 @@
       </c>
       <c r="C37" s="1"/>
       <c r="E37">
-        <v>536</v>
+        <v>440</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G37" s="1">
         <v>0.31597222222222221</v>
@@ -1120,40 +1120,40 @@
       </c>
       <c r="C38" s="1"/>
       <c r="E38">
-        <v>444</v>
+        <v>536</v>
       </c>
       <c r="F38" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G38" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.31597222222222221</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="1"/>
-      <c r="E39">
-        <v>562</v>
-      </c>
-      <c r="F39" t="s">
-        <v>25</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0.32291666666666669</v>
-      </c>
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="D39">
+        <v>321</v>
+      </c>
+      <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C40" s="1"/>
       <c r="E40">
-        <v>4322</v>
+        <v>444</v>
       </c>
       <c r="F40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G40" s="1">
         <v>0.32291666666666669</v>
@@ -1165,13 +1165,13 @@
       </c>
       <c r="C41" s="1"/>
       <c r="E41">
-        <v>368</v>
+        <v>562</v>
       </c>
       <c r="F41" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G41" s="1">
-        <v>0.33333333333333331</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1180,10 +1180,10 @@
       </c>
       <c r="C42" s="1"/>
       <c r="E42">
-        <v>522</v>
+        <v>368</v>
       </c>
       <c r="F42" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G42" s="1">
         <v>0.33333333333333331</v>
@@ -1193,16 +1193,16 @@
       <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="B43" t="s">
-        <v>26</v>
-      </c>
-      <c r="C43" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D43">
-        <v>309</v>
-      </c>
-      <c r="G43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="E43">
+        <v>522</v>
+      </c>
+      <c r="F43" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0.33333333333333331</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -1215,7 +1215,7 @@
         <v>0.33680555555555558</v>
       </c>
       <c r="D44">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="G44" s="1"/>
     </row>
@@ -1228,7 +1228,7 @@
         <v>383</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G45" s="1">
         <v>0.33680555555555558</v>
@@ -1270,10 +1270,10 @@
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="F48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G48" s="1">
         <v>0.34375</v>
@@ -1281,33 +1281,33 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>884</v>
+        <v>430</v>
       </c>
       <c r="F49" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G49" s="1">
-        <v>0.35347222222222219</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>9</v>
       </c>
-      <c r="C50" s="1"/>
-      <c r="E50">
-        <v>422</v>
-      </c>
-      <c r="F50" t="s">
-        <v>36</v>
-      </c>
-      <c r="G50" s="1">
-        <v>0.36458333333333331</v>
-      </c>
+      <c r="B50" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="D50">
+        <v>451</v>
+      </c>
+      <c r="G50" s="1"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
@@ -1315,29 +1315,29 @@
       </c>
       <c r="C51" s="1"/>
       <c r="E51">
-        <v>430</v>
+        <v>526</v>
       </c>
       <c r="F51" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="G51" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" t="s">
-        <v>25</v>
-      </c>
-      <c r="C52" s="1">
-        <v>0.37847222222222221</v>
-      </c>
-      <c r="D52">
-        <v>559</v>
-      </c>
-      <c r="G52" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="E52">
+        <v>4320</v>
+      </c>
+      <c r="F52" t="s">
+        <v>30</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.38333333333333336</v>
+      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -1345,13 +1345,13 @@
       </c>
       <c r="C53" s="1"/>
       <c r="E53">
-        <v>524</v>
+        <v>369</v>
       </c>
       <c r="F53" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="G53" s="1">
-        <v>0.38194444444444442</v>
+        <v>0.3888888888888889</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -1360,36 +1360,36 @@
       </c>
       <c r="C54" s="1"/>
       <c r="E54">
-        <v>369</v>
+        <v>582</v>
       </c>
       <c r="F54" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G54" s="1">
-        <v>0.3888888888888889</v>
+        <v>0.39930555555555558</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C55" s="1"/>
-      <c r="E55">
-        <v>582</v>
-      </c>
-      <c r="F55" t="s">
-        <v>13</v>
-      </c>
-      <c r="G55" s="1">
-        <v>0.39930555555555558</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55" s="1">
+        <v>0.40902777777777777</v>
+      </c>
+      <c r="D55">
+        <v>4337</v>
+      </c>
+      <c r="G55" s="1"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C56" s="1">
         <v>0.41319444444444442</v>
@@ -1401,18 +1401,18 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>27</v>
-      </c>
-      <c r="B57" t="s">
-        <v>28</v>
-      </c>
-      <c r="C57" s="1">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D57">
-        <v>342</v>
-      </c>
-      <c r="G57" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C57" s="1"/>
+      <c r="E57">
+        <v>392</v>
+      </c>
+      <c r="F57" t="s">
+        <v>21</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0.41319444444444442</v>
+      </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -1420,42 +1420,42 @@
       </c>
       <c r="C58" s="1"/>
       <c r="E58">
-        <v>609</v>
+        <v>408</v>
       </c>
       <c r="F58" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G58" s="1">
-        <v>0.4236111111111111</v>
+        <v>0.41319444444444442</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>9</v>
       </c>
-      <c r="B59" t="s">
-        <v>14</v>
-      </c>
-      <c r="C59" s="1">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="D59">
-        <v>537</v>
-      </c>
-      <c r="G59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="E59">
+        <v>609</v>
+      </c>
+      <c r="F59" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0.4236111111111111</v>
+      </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C60" s="1">
-        <v>0.44791666666666669</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="D60">
-        <v>455</v>
+        <v>537</v>
       </c>
       <c r="G60" s="1"/>
     </row>
@@ -1464,13 +1464,13 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C61" s="1">
-        <v>0.4548611111111111</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="D61">
-        <v>318</v>
+        <v>455</v>
       </c>
       <c r="G61" s="1"/>
     </row>
@@ -1479,75 +1479,75 @@
         <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C62" s="1">
-        <v>0.46180555555555558</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="D62">
-        <v>384</v>
+        <v>573</v>
       </c>
       <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>27</v>
-      </c>
-      <c r="C63" s="1"/>
-      <c r="E63">
-        <v>343</v>
-      </c>
-      <c r="F63" t="s">
-        <v>28</v>
-      </c>
-      <c r="G63" s="1">
-        <v>0.46180555555555558</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B63" t="s">
+        <v>23</v>
+      </c>
+      <c r="C63" s="1">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="D63">
+        <v>318</v>
+      </c>
+      <c r="G63" s="1"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C64" s="1">
-        <v>0.47291666666666665</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D64">
-        <v>495</v>
+        <v>384</v>
       </c>
       <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C65" s="1">
-        <v>0.47847222222222219</v>
+        <v>0.47291666666666665</v>
       </c>
       <c r="D65">
-        <v>1194</v>
+        <v>495</v>
       </c>
       <c r="G65" s="1"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>9</v>
-      </c>
-      <c r="C66" s="1"/>
-      <c r="E66">
-        <v>584</v>
-      </c>
-      <c r="F66" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" t="s">
         <v>13</v>
       </c>
-      <c r="G66" s="1">
-        <v>0.49305555555555558</v>
-      </c>
+      <c r="C66" s="1">
+        <v>0.47847222222222219</v>
+      </c>
+      <c r="D66">
+        <v>1194</v>
+      </c>
+      <c r="G66" s="1"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
@@ -1555,13 +1555,13 @@
       </c>
       <c r="C67" s="1"/>
       <c r="E67">
-        <v>385</v>
+        <v>584</v>
       </c>
       <c r="F67" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G67" s="1">
-        <v>0.50347222222222221</v>
+        <v>0.49305555555555558</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -1570,297 +1570,297 @@
       </c>
       <c r="C68" s="1"/>
       <c r="E68">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="F68" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G68" s="1">
-        <v>0.50347222222222221</v>
+        <v>0.49652777777777779</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>7</v>
-      </c>
-      <c r="B69" t="s">
-        <v>30</v>
-      </c>
-      <c r="C69" s="1">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="D69">
-        <v>1441</v>
-      </c>
-      <c r="G69" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C69" s="1"/>
+      <c r="E69">
+        <v>385</v>
+      </c>
+      <c r="F69" t="s">
+        <v>25</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C70" s="1"/>
       <c r="E70">
-        <v>1508</v>
+        <v>424</v>
       </c>
       <c r="F70" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G70" s="1">
-        <v>0.51597222222222228</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>31</v>
-      </c>
-      <c r="B71" t="s">
-        <v>32</v>
-      </c>
-      <c r="C71" s="1">
-        <v>0.5180555555555556</v>
-      </c>
-      <c r="D71">
-        <v>1910</v>
-      </c>
-      <c r="G71" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C71" s="1"/>
+      <c r="E71">
+        <v>442</v>
+      </c>
+      <c r="F71" t="s">
+        <v>33</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C72" s="1">
-        <v>0.52916666666666667</v>
+        <v>0.51041666666666663</v>
       </c>
       <c r="D72">
-        <v>937</v>
+        <v>1441</v>
       </c>
       <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>33</v>
-      </c>
-      <c r="B73" t="s">
-        <v>23</v>
-      </c>
-      <c r="C73" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D73">
-        <v>816</v>
-      </c>
-      <c r="G73" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C73" s="1"/>
+      <c r="E73">
+        <v>1508</v>
+      </c>
+      <c r="F73" t="s">
+        <v>29</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0.51597222222222228</v>
+      </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="E74">
-        <v>1458</v>
-      </c>
-      <c r="F74" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" s="1">
-        <v>0.55555555555555558</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B74" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" s="1">
+        <v>0.5180555555555556</v>
+      </c>
+      <c r="D74">
+        <v>1910</v>
+      </c>
+      <c r="G74" s="1"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>29</v>
-      </c>
-      <c r="C75" s="1"/>
-      <c r="E75">
-        <v>380</v>
-      </c>
-      <c r="F75" t="s">
         <v>28</v>
       </c>
-      <c r="G75" s="1">
-        <v>0.57222222222222219</v>
-      </c>
+      <c r="B75" t="s">
+        <v>33</v>
+      </c>
+      <c r="C75" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D75">
+        <v>937</v>
+      </c>
+      <c r="G75" s="1"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="1"/>
-      <c r="E76">
-        <v>1468</v>
-      </c>
-      <c r="F76" t="s">
-        <v>30</v>
-      </c>
-      <c r="G76" s="1">
-        <v>0.57638888888888895</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B76" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D76">
+        <v>816</v>
+      </c>
+      <c r="G76" s="1"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C77" s="1"/>
       <c r="E77">
-        <v>1978</v>
+        <v>1458</v>
       </c>
       <c r="F77" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G77" s="1">
-        <v>0.57708333333333328</v>
+        <v>0.55555555555555558</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C78" s="1"/>
       <c r="E78">
-        <v>871</v>
+        <v>380</v>
       </c>
       <c r="F78" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G78" s="1">
-        <v>0.58194444444444449</v>
+        <v>0.57222222222222219</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>34</v>
-      </c>
-      <c r="B79" t="s">
-        <v>18</v>
-      </c>
-      <c r="C79" s="1">
-        <v>0.59375</v>
-      </c>
-      <c r="D79">
-        <v>628</v>
-      </c>
-      <c r="G79" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="E79">
+        <v>1468</v>
+      </c>
+      <c r="F79" t="s">
+        <v>30</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0.57638888888888895</v>
+      </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>7</v>
-      </c>
-      <c r="B80" t="s">
-        <v>30</v>
-      </c>
-      <c r="C80" s="1">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D80">
-        <v>1290</v>
-      </c>
-      <c r="G80" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="E80">
+        <v>1978</v>
+      </c>
+      <c r="F80" t="s">
+        <v>32</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0.57708333333333328</v>
+      </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>9</v>
-      </c>
-      <c r="B81" t="s">
-        <v>19</v>
-      </c>
-      <c r="C81" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="D81">
-        <v>557</v>
-      </c>
-      <c r="G81" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="E81">
+        <v>871</v>
+      </c>
+      <c r="F81" t="s">
+        <v>24</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0.58194444444444449</v>
+      </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C82" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.59375</v>
       </c>
       <c r="D82">
-        <v>382</v>
+        <v>628</v>
       </c>
       <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>34</v>
-      </c>
-      <c r="C83" s="1"/>
-      <c r="E83">
-        <v>629</v>
-      </c>
-      <c r="F83" t="s">
-        <v>18</v>
-      </c>
-      <c r="G83" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B83" t="s">
+        <v>30</v>
+      </c>
+      <c r="C83" s="1">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D83">
+        <v>1290</v>
+      </c>
+      <c r="G83" s="1"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="1"/>
-      <c r="E84">
-        <v>1130</v>
-      </c>
-      <c r="F84" t="s">
-        <v>30</v>
-      </c>
-      <c r="G84" s="1">
+        <v>9</v>
+      </c>
+      <c r="B84" t="s">
+        <v>25</v>
+      </c>
+      <c r="C84" s="1">
         <v>0.65277777777777779</v>
       </c>
+      <c r="D84">
+        <v>382</v>
+      </c>
+      <c r="G84" s="1"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>9</v>
-      </c>
-      <c r="B85" t="s">
-        <v>30</v>
-      </c>
-      <c r="C85" s="1">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D85">
-        <v>367</v>
-      </c>
-      <c r="G85" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="C85" s="1"/>
+      <c r="E85">
+        <v>629</v>
+      </c>
+      <c r="F85" t="s">
+        <v>19</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>9</v>
-      </c>
-      <c r="B86" t="s">
-        <v>35</v>
-      </c>
-      <c r="C86" s="1">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D86">
-        <v>370</v>
-      </c>
-      <c r="G86" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C86" s="1"/>
+      <c r="E86">
+        <v>1130</v>
+      </c>
+      <c r="F86" t="s">
+        <v>30</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C87" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D87">
-        <v>397</v>
+        <v>367</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1869,13 +1869,13 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C88" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D88">
-        <v>441</v>
+        <v>370</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -1884,13 +1884,13 @@
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C89" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D89">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -1899,13 +1899,13 @@
         <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C90" s="1">
-        <v>0.6875</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D90">
-        <v>311</v>
+        <v>553</v>
       </c>
       <c r="G90" s="1"/>
     </row>
@@ -1914,13 +1914,13 @@
         <v>9</v>
       </c>
       <c r="B91" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C91" s="1">
-        <v>0.6875</v>
+        <v>0.68055555555555558</v>
       </c>
       <c r="D91">
-        <v>555</v>
+        <v>441</v>
       </c>
       <c r="G91" s="1"/>
     </row>
@@ -1929,13 +1929,13 @@
         <v>9</v>
       </c>
       <c r="B92" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C92" s="1">
-        <v>0.6875</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D92">
-        <v>610</v>
+        <v>435</v>
       </c>
       <c r="G92" s="1"/>
     </row>
@@ -1944,60 +1944,60 @@
         <v>9</v>
       </c>
       <c r="B93" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C93" s="1">
-        <v>0.70138888888888884</v>
+        <v>0.6875</v>
       </c>
       <c r="D93">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="G93" s="1"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B94" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C94" s="1">
-        <v>0.72777777777777775</v>
+        <v>0.6875</v>
       </c>
       <c r="D94">
-        <v>4327</v>
+        <v>610</v>
       </c>
       <c r="G94" s="1"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>9</v>
-      </c>
-      <c r="C95" s="1"/>
-      <c r="E95">
-        <v>326</v>
-      </c>
-      <c r="F95" t="s">
-        <v>10</v>
-      </c>
-      <c r="G95" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B95" t="s">
+        <v>30</v>
+      </c>
+      <c r="C95" s="1">
+        <v>0.6958333333333333</v>
+      </c>
+      <c r="D95">
+        <v>4321</v>
+      </c>
+      <c r="G95" s="1"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>9</v>
       </c>
-      <c r="C96" s="1"/>
-      <c r="E96">
-        <v>560</v>
-      </c>
-      <c r="F96" t="s">
-        <v>25</v>
-      </c>
-      <c r="G96" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+      <c r="B96" t="s">
+        <v>24</v>
+      </c>
+      <c r="C96" s="1">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="D96">
+        <v>322</v>
+      </c>
+      <c r="G96" s="1"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -2005,29 +2005,29 @@
       </c>
       <c r="C97" s="1"/>
       <c r="E97">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="F97" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G97" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.72222222222222221</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>9</v>
-      </c>
-      <c r="C98" s="1"/>
-      <c r="E98">
-        <v>450</v>
-      </c>
-      <c r="F98" t="s">
-        <v>20</v>
-      </c>
-      <c r="G98" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B98" t="s">
+        <v>30</v>
+      </c>
+      <c r="C98" s="1">
+        <v>0.72777777777777775</v>
+      </c>
+      <c r="D98">
+        <v>4327</v>
+      </c>
+      <c r="G98" s="1"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
@@ -2035,13 +2035,13 @@
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="F99" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G99" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2050,13 +2050,13 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>588</v>
+        <v>560</v>
       </c>
       <c r="F100" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G100" s="1">
-        <v>0.73611111111111116</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -2065,13 +2065,13 @@
       </c>
       <c r="C101" s="1"/>
       <c r="E101">
-        <v>448</v>
+        <v>313</v>
       </c>
       <c r="F101" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G101" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -2080,43 +2080,43 @@
       </c>
       <c r="C102" s="1"/>
       <c r="E102">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="F102" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G102" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>37</v>
-      </c>
-      <c r="B103" t="s">
-        <v>19</v>
-      </c>
-      <c r="C103" s="1">
-        <v>0.74652777777777779</v>
-      </c>
-      <c r="D103">
-        <v>222</v>
-      </c>
-      <c r="G103" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C103" s="1"/>
+      <c r="E103">
+        <v>530</v>
+      </c>
+      <c r="F103" t="s">
+        <v>14</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>4308</v>
+        <v>588</v>
       </c>
       <c r="F104" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G104" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.73611111111111116</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -2125,13 +2125,13 @@
       </c>
       <c r="C105" s="1"/>
       <c r="E105">
-        <v>528</v>
+        <v>448</v>
       </c>
       <c r="F105" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G105" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -2140,27 +2140,27 @@
       </c>
       <c r="C106" s="1"/>
       <c r="E106">
-        <v>660</v>
+        <v>534</v>
       </c>
       <c r="F106" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G106" s="1">
-        <v>0.77083333333333337</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B107" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C107" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.74652777777777779</v>
       </c>
       <c r="D107">
-        <v>742</v>
+        <v>222</v>
       </c>
       <c r="G107" s="1"/>
     </row>
@@ -2170,29 +2170,29 @@
       </c>
       <c r="C108" s="1"/>
       <c r="E108">
-        <v>4312</v>
+        <v>4308</v>
       </c>
       <c r="F108" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G108" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>9</v>
       </c>
-      <c r="B109" t="s">
-        <v>18</v>
-      </c>
-      <c r="C109" s="1">
-        <v>0.79513888888888884</v>
-      </c>
-      <c r="D109">
-        <v>431</v>
-      </c>
-      <c r="G109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="E109">
+        <v>528</v>
+      </c>
+      <c r="F109" t="s">
+        <v>8</v>
+      </c>
+      <c r="G109" s="1">
+        <v>0.76041666666666663</v>
+      </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -2200,72 +2200,72 @@
       </c>
       <c r="C110" s="1"/>
       <c r="E110">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="F110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G110" s="1">
-        <v>0.80555555555555558</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="C111" s="1"/>
       <c r="E111">
-        <v>222</v>
+        <v>558</v>
       </c>
       <c r="F111" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G111" s="1">
-        <v>0.80902777777777779</v>
+        <v>0.77777777777777779</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B112" t="s">
         <v>30</v>
       </c>
       <c r="C112" s="1">
-        <v>0.81944444444444442</v>
+        <v>0.79027777777777775</v>
       </c>
       <c r="D112">
-        <v>425</v>
+        <v>742</v>
       </c>
       <c r="G112" s="1"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>9</v>
-      </c>
-      <c r="B113" t="s">
-        <v>38</v>
-      </c>
-      <c r="C113" s="1">
-        <v>0.82291666666666663</v>
-      </c>
-      <c r="D113">
-        <v>329</v>
-      </c>
-      <c r="G113" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C113" s="1"/>
+      <c r="E113">
+        <v>4312</v>
+      </c>
+      <c r="F113" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113" s="1">
+        <v>0.79027777777777775</v>
+      </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C114" s="1">
-        <v>0.82430555555555551</v>
+        <v>0.79513888888888884</v>
       </c>
       <c r="D114">
-        <v>2657</v>
+        <v>431</v>
       </c>
       <c r="G114" s="1"/>
     </row>
@@ -2273,59 +2273,59 @@
       <c r="A115" t="s">
         <v>9</v>
       </c>
-      <c r="B115" t="s">
-        <v>8</v>
-      </c>
-      <c r="C115" s="1">
-        <v>0.82638888888888884</v>
-      </c>
-      <c r="D115">
-        <v>523</v>
-      </c>
-      <c r="G115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="E115">
+        <v>670</v>
+      </c>
+      <c r="F115" t="s">
+        <v>18</v>
+      </c>
+      <c r="G115" s="1">
+        <v>0.80555555555555558</v>
+      </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>9</v>
-      </c>
-      <c r="B116" t="s">
-        <v>13</v>
-      </c>
-      <c r="C116" s="1">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D116">
-        <v>583</v>
-      </c>
-      <c r="G116" s="1"/>
+        <v>38</v>
+      </c>
+      <c r="C116" s="1"/>
+      <c r="E116">
+        <v>222</v>
+      </c>
+      <c r="F116" t="s">
+        <v>16</v>
+      </c>
+      <c r="G116" s="1">
+        <v>0.80902777777777779</v>
+      </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>9</v>
       </c>
       <c r="B117" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C117" s="1">
-        <v>0.84375</v>
+        <v>0.81944444444444442</v>
       </c>
       <c r="D117">
-        <v>325</v>
+        <v>425</v>
       </c>
       <c r="G117" s="1"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B118" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C118" s="1">
-        <v>0.84375</v>
+        <v>0.82430555555555551</v>
       </c>
       <c r="D118">
-        <v>445</v>
+        <v>2657</v>
       </c>
       <c r="G118" s="1"/>
     </row>
@@ -2333,104 +2333,104 @@
       <c r="A119" t="s">
         <v>9</v>
       </c>
-      <c r="C119" s="1"/>
-      <c r="E119">
-        <v>590</v>
-      </c>
-      <c r="F119" t="s">
+      <c r="B119" t="s">
         <v>13</v>
       </c>
-      <c r="G119" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+      <c r="C119" s="1">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D119">
+        <v>583</v>
+      </c>
+      <c r="G119" s="1"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>9</v>
       </c>
       <c r="B120" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C120" s="1">
-        <v>0.85416666666666663</v>
+        <v>0.84375</v>
       </c>
       <c r="D120">
-        <v>449</v>
+        <v>325</v>
       </c>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B121" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C121" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.84375</v>
       </c>
       <c r="D121">
-        <v>881</v>
+        <v>445</v>
       </c>
       <c r="G121" s="1"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C122" s="1">
-        <v>0.86111111111111116</v>
+        <v>0.85069444444444442</v>
       </c>
       <c r="D122">
-        <v>4323</v>
+        <v>393</v>
       </c>
       <c r="G122" s="1"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>7</v>
-      </c>
-      <c r="B123" t="s">
-        <v>30</v>
-      </c>
-      <c r="C123" s="1">
-        <v>0.86736111111111114</v>
-      </c>
-      <c r="D123">
-        <v>1461</v>
-      </c>
-      <c r="G123" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C123" s="1"/>
+      <c r="E123">
+        <v>590</v>
+      </c>
+      <c r="F123" t="s">
+        <v>13</v>
+      </c>
+      <c r="G123" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C124" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D124">
-        <v>563</v>
+        <v>449</v>
       </c>
       <c r="G124" s="1"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B125" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C125" s="1">
-        <v>0.875</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D125">
-        <v>535</v>
+        <v>881</v>
       </c>
       <c r="G125" s="1"/>
     </row>
@@ -2439,28 +2439,28 @@
         <v>9</v>
       </c>
       <c r="B126" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C126" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86111111111111116</v>
       </c>
       <c r="D126">
-        <v>312</v>
+        <v>523</v>
       </c>
       <c r="G126" s="1"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C127" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D127">
-        <v>525</v>
+        <v>1461</v>
       </c>
       <c r="G127" s="1"/>
     </row>
@@ -2469,28 +2469,28 @@
         <v>9</v>
       </c>
       <c r="B128" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C128" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D128">
-        <v>589</v>
+        <v>443</v>
       </c>
       <c r="G128" s="1"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B129" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C129" s="1">
-        <v>0.89930555555555547</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D129">
-        <v>1425</v>
+        <v>563</v>
       </c>
       <c r="G129" s="1"/>
     </row>
@@ -2499,13 +2499,13 @@
         <v>9</v>
       </c>
       <c r="B130" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C130" s="1">
-        <v>0.91319444444444442</v>
+        <v>0.87152777777777779</v>
       </c>
       <c r="D130">
-        <v>585</v>
+        <v>409</v>
       </c>
       <c r="G130" s="1"/>
     </row>
@@ -2513,76 +2513,76 @@
       <c r="A131" t="s">
         <v>9</v>
       </c>
-      <c r="C131" s="1"/>
-      <c r="E131">
-        <v>315</v>
-      </c>
-      <c r="F131" t="s">
-        <v>20</v>
-      </c>
-      <c r="G131" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B131" t="s">
+        <v>41</v>
+      </c>
+      <c r="C131" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="D131">
+        <v>527</v>
+      </c>
+      <c r="G131" s="1"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>9</v>
       </c>
-      <c r="C132" s="1"/>
-      <c r="E132">
-        <v>365</v>
-      </c>
-      <c r="F132" t="s">
-        <v>24</v>
-      </c>
-      <c r="G132" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B132" t="s">
+        <v>15</v>
+      </c>
+      <c r="C132" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="D132">
+        <v>535</v>
+      </c>
+      <c r="G132" s="1"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>9</v>
       </c>
-      <c r="C133" s="1"/>
-      <c r="E133">
-        <v>600</v>
-      </c>
-      <c r="F133" t="s">
-        <v>13</v>
-      </c>
-      <c r="G133" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B133" t="s">
+        <v>23</v>
+      </c>
+      <c r="C133" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D133">
+        <v>312</v>
+      </c>
+      <c r="G133" s="1"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>9</v>
       </c>
-      <c r="C134" s="1"/>
-      <c r="E134">
-        <v>429</v>
-      </c>
-      <c r="F134" t="s">
-        <v>21</v>
-      </c>
-      <c r="G134" s="1">
-        <v>0.92708333333333337</v>
-      </c>
+      <c r="B134" t="s">
+        <v>20</v>
+      </c>
+      <c r="C134" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D134">
+        <v>589</v>
+      </c>
+      <c r="G134" s="1"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>9</v>
       </c>
-      <c r="C135" s="1"/>
-      <c r="E135">
-        <v>578</v>
-      </c>
-      <c r="F135" t="s">
-        <v>19</v>
-      </c>
-      <c r="G135" s="1">
-        <v>0.93055555555555558</v>
-      </c>
+      <c r="B135" t="s">
+        <v>13</v>
+      </c>
+      <c r="C135" s="1">
+        <v>0.91319444444444442</v>
+      </c>
+      <c r="D135">
+        <v>585</v>
+      </c>
+      <c r="G135" s="1"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
@@ -2590,13 +2590,13 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>627</v>
+        <v>315</v>
       </c>
       <c r="F136" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G136" s="1">
-        <v>0.93402777777777779</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -2605,13 +2605,13 @@
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>574</v>
+        <v>365</v>
       </c>
       <c r="F137" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G137" s="1">
-        <v>0.9375</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -2620,13 +2620,13 @@
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="F138" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G138" s="1">
-        <v>0.94097222222222221</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -2635,43 +2635,43 @@
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>452</v>
+        <v>308</v>
       </c>
       <c r="F139" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G139" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.92361111111111116</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C140" s="1"/>
       <c r="E140">
-        <v>339</v>
+        <v>429</v>
       </c>
       <c r="F140" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="G140" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.92708333333333337</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C141" s="1"/>
       <c r="E141">
-        <v>4336</v>
+        <v>578</v>
       </c>
       <c r="F141" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G141" s="1">
-        <v>0.9506944444444444</v>
+        <v>0.93055555555555558</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -2680,13 +2680,13 @@
       </c>
       <c r="C142" s="1"/>
       <c r="E142">
-        <v>317</v>
+        <v>627</v>
       </c>
       <c r="F142" t="s">
         <v>23</v>
       </c>
       <c r="G142" s="1">
-        <v>0.95486111111111116</v>
+        <v>0.93402777777777779</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -2695,13 +2695,13 @@
       </c>
       <c r="C143" s="1"/>
       <c r="E143">
-        <v>432</v>
+        <v>574</v>
       </c>
       <c r="F143" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G143" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -2710,13 +2710,13 @@
       </c>
       <c r="C144" s="1"/>
       <c r="E144">
-        <v>457</v>
+        <v>568</v>
       </c>
       <c r="F144" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G144" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -2725,29 +2725,89 @@
       </c>
       <c r="C145" s="1"/>
       <c r="E145">
-        <v>552</v>
+        <v>452</v>
       </c>
       <c r="F145" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G145" s="1">
-        <v>0.97222222222222221</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>33</v>
-      </c>
-      <c r="B146" t="s">
-        <v>23</v>
-      </c>
-      <c r="C146" s="1">
+        <v>9</v>
+      </c>
+      <c r="C146" s="1"/>
+      <c r="E146">
+        <v>317</v>
+      </c>
+      <c r="F146" t="s">
+        <v>24</v>
+      </c>
+      <c r="G146" s="1">
+        <v>0.95486111111111116</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>9</v>
+      </c>
+      <c r="C147" s="1"/>
+      <c r="E147">
+        <v>457</v>
+      </c>
+      <c r="F147" t="s">
+        <v>17</v>
+      </c>
+      <c r="G147" s="1">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>9</v>
+      </c>
+      <c r="C148" s="1"/>
+      <c r="E148">
+        <v>300</v>
+      </c>
+      <c r="F148" t="s">
+        <v>16</v>
+      </c>
+      <c r="G148" s="1">
+        <v>0.96180555555555558</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>9</v>
+      </c>
+      <c r="C149" s="1"/>
+      <c r="E149">
+        <v>556</v>
+      </c>
+      <c r="F149" t="s">
+        <v>20</v>
+      </c>
+      <c r="G149" s="1">
+        <v>0.97222222222222221</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>34</v>
+      </c>
+      <c r="B150" t="s">
+        <v>24</v>
+      </c>
+      <c r="C150" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D146">
+      <c r="D150">
         <v>878</v>
       </c>
-      <c r="G146" s="1"/>
+      <c r="G150" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94C4B9C2-E2C6-4507-8A87-78FE11F7AF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4F53766-C699-426A-9850-784C1B2462CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FB723472-D0A6-4FEE-BC00-280F76ACF404}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EB472DA7-C2F5-41B5-92C2-BD522628A1A1}"/>
   </bookViews>
   <sheets>
-    <sheet name="27-06" sheetId="1" r:id="rId1"/>
+    <sheet name="28-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="43">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,9 +83,6 @@
     <t>KIAD</t>
   </si>
   <si>
-    <t>KONT</t>
-  </si>
-  <si>
     <t>MHLM</t>
   </si>
   <si>
@@ -122,49 +119,55 @@
     <t>KSFO</t>
   </si>
   <si>
+    <t>KMIA</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
+    <t>KIAH</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>KATL</t>
+  </si>
+  <si>
+    <t>TAG</t>
+  </si>
+  <si>
+    <t>MHRO</t>
+  </si>
+  <si>
+    <t>KDFW</t>
+  </si>
+  <si>
+    <t>CMP</t>
+  </si>
+  <si>
+    <t>AMX</t>
+  </si>
+  <si>
+    <t>SKRG</t>
+  </si>
+  <si>
+    <t>KMCO</t>
+  </si>
+  <si>
+    <t>IBE</t>
+  </si>
+  <si>
+    <t>CYUL</t>
+  </si>
+  <si>
+    <t>KBOS</t>
+  </si>
+  <si>
+    <t>KOAK</t>
+  </si>
+  <si>
     <t>KEWR</t>
-  </si>
-  <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>KMIA</t>
-  </si>
-  <si>
-    <t>KIAH</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>KATL</t>
-  </si>
-  <si>
-    <t>KDFW</t>
-  </si>
-  <si>
-    <t>CMP</t>
-  </si>
-  <si>
-    <t>AMX</t>
-  </si>
-  <si>
-    <t>SKRG</t>
-  </si>
-  <si>
-    <t>MMUN</t>
-  </si>
-  <si>
-    <t>IBE</t>
-  </si>
-  <si>
-    <t>KBOS</t>
-  </si>
-  <si>
-    <t>KORD</t>
-  </si>
-  <si>
-    <t>KLAS</t>
   </si>
 </sst>
 </file>
@@ -539,8 +542,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C91CB52C-AE4B-433B-A31E-86EE70370DD2}">
-  <dimension ref="A1:G150"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A2C9424-511F-47FE-B583-8BC66302570F}">
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -583,7 +586,7 @@
         <v>2203</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G2" s="1">
         <v>5.2083333333333336E-2</v>
@@ -628,7 +631,7 @@
         <v>879</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1">
         <v>0.20347222222222219</v>
@@ -673,7 +676,7 @@
         <v>300</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1">
         <v>0.21527777777777779</v>
@@ -705,7 +708,7 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="D10">
-        <v>531</v>
+        <v>575</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -717,40 +720,40 @@
         <v>15</v>
       </c>
       <c r="C11" s="1">
-        <v>0.22222222222222221</v>
+        <v>0.22916666666666666</v>
       </c>
       <c r="D11">
-        <v>575</v>
+        <v>301</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1">
-        <v>0.22916666666666666</v>
+        <v>0.24444444444444444</v>
       </c>
       <c r="D12">
-        <v>301</v>
+        <v>4309</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C13" s="1">
-        <v>0.24444444444444444</v>
+        <v>0.24652777777777779</v>
       </c>
       <c r="D13">
-        <v>4309</v>
+        <v>456</v>
       </c>
       <c r="G13" s="1"/>
     </row>
@@ -765,35 +768,35 @@
         <v>0.24652777777777779</v>
       </c>
       <c r="D14">
-        <v>456</v>
+        <v>661</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0.24652777777777779</v>
-      </c>
-      <c r="D15">
-        <v>661</v>
-      </c>
-      <c r="G15" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="E15">
+        <v>3154</v>
+      </c>
+      <c r="F15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C16" s="1"/>
       <c r="E16">
-        <v>3154</v>
+        <v>1467</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G16" s="1">
         <v>0.25</v>
@@ -801,33 +804,33 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C17" s="1"/>
       <c r="E17">
-        <v>1467</v>
+        <v>3154</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G17" s="1">
-        <v>0.25</v>
+        <v>0.25069444444444444</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="E18">
-        <v>3154</v>
-      </c>
-      <c r="F18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0.25069444444444444</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.25694444444444442</v>
+      </c>
+      <c r="D18">
+        <v>433</v>
+      </c>
+      <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -840,7 +843,7 @@
         <v>0.25694444444444442</v>
       </c>
       <c r="D19">
-        <v>433</v>
+        <v>579</v>
       </c>
       <c r="G19" s="1"/>
     </row>
@@ -849,13 +852,13 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C20" s="1">
-        <v>0.25694444444444442</v>
+        <v>0.26041666666666669</v>
       </c>
       <c r="D20">
-        <v>579</v>
+        <v>529</v>
       </c>
       <c r="G20" s="1"/>
     </row>
@@ -864,13 +867,13 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" s="1">
-        <v>0.26041666666666669</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="D21">
-        <v>529</v>
+        <v>314</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -882,10 +885,10 @@
         <v>21</v>
       </c>
       <c r="C22" s="1">
-        <v>0.2638888888888889</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D22">
-        <v>314</v>
+        <v>428</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -900,7 +903,7 @@
         <v>0.2673611111111111</v>
       </c>
       <c r="D23">
-        <v>428</v>
+        <v>626</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -912,10 +915,10 @@
         <v>23</v>
       </c>
       <c r="C24" s="1">
-        <v>0.2673611111111111</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="D24">
-        <v>626</v>
+        <v>316</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -930,7 +933,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D25">
-        <v>316</v>
+        <v>366</v>
       </c>
       <c r="G25" s="1"/>
     </row>
@@ -945,7 +948,7 @@
         <v>0.27083333333333331</v>
       </c>
       <c r="D26">
-        <v>366</v>
+        <v>561</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -954,13 +957,13 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C27" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D27">
-        <v>561</v>
+        <v>591</v>
       </c>
       <c r="G27" s="1"/>
     </row>
@@ -969,13 +972,13 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D28">
-        <v>591</v>
+        <v>671</v>
       </c>
       <c r="G28" s="1"/>
     </row>
@@ -984,44 +987,44 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C29" s="1">
-        <v>0.27083333333333331</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="D29">
-        <v>671</v>
+        <v>521</v>
       </c>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="D30">
-        <v>521</v>
-      </c>
-      <c r="G30" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="E30">
+        <v>4326</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0.29791666666666666</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>4326</v>
+        <v>319</v>
       </c>
       <c r="F31" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G31" s="1">
-        <v>0.29791666666666666</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1030,7 +1033,7 @@
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F32" t="s">
         <v>23</v>
@@ -1045,10 +1048,10 @@
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="F33" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G33" s="1">
         <v>0.3125</v>
@@ -1063,7 +1066,7 @@
         <v>396</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G34" s="1">
         <v>0.3125</v>
@@ -1071,17 +1074,17 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C35" s="1"/>
       <c r="E35">
-        <v>884</v>
+        <v>310</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G35" s="1">
-        <v>0.3125</v>
+        <v>0.31597222222222221</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1090,10 +1093,10 @@
       </c>
       <c r="C36" s="1"/>
       <c r="E36">
-        <v>310</v>
+        <v>440</v>
       </c>
       <c r="F36" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G36" s="1">
         <v>0.31597222222222221</v>
@@ -1105,10 +1108,10 @@
       </c>
       <c r="C37" s="1"/>
       <c r="E37">
-        <v>440</v>
+        <v>536</v>
       </c>
       <c r="F37" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G37" s="1">
         <v>0.31597222222222221</v>
@@ -1120,40 +1123,40 @@
       </c>
       <c r="C38" s="1"/>
       <c r="E38">
-        <v>536</v>
+        <v>444</v>
       </c>
       <c r="F38" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G38" s="1">
-        <v>0.31597222222222221</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>9</v>
       </c>
-      <c r="B39" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="1">
-        <v>0.31944444444444442</v>
-      </c>
-      <c r="D39">
-        <v>321</v>
-      </c>
-      <c r="G39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="E39">
+        <v>562</v>
+      </c>
+      <c r="F39" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.32291666666666669</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C40" s="1"/>
       <c r="E40">
-        <v>444</v>
+        <v>4322</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G40" s="1">
         <v>0.32291666666666669</v>
@@ -1165,13 +1168,13 @@
       </c>
       <c r="C41" s="1"/>
       <c r="E41">
-        <v>562</v>
+        <v>368</v>
       </c>
       <c r="F41" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G41" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1180,10 +1183,10 @@
       </c>
       <c r="C42" s="1"/>
       <c r="E42">
-        <v>368</v>
+        <v>522</v>
       </c>
       <c r="F42" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G42" s="1">
         <v>0.33333333333333331</v>
@@ -1193,16 +1196,16 @@
       <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="C43" s="1"/>
-      <c r="E43">
-        <v>522</v>
-      </c>
-      <c r="F43" t="s">
-        <v>8</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0.33333333333333331</v>
-      </c>
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="D43">
+        <v>309</v>
+      </c>
+      <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -1215,7 +1218,7 @@
         <v>0.33680555555555558</v>
       </c>
       <c r="D44">
-        <v>601</v>
+        <v>581</v>
       </c>
       <c r="G44" s="1"/>
     </row>
@@ -1228,7 +1231,7 @@
         <v>383</v>
       </c>
       <c r="F45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G45" s="1">
         <v>0.33680555555555558</v>
@@ -1240,13 +1243,13 @@
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>454</v>
+        <v>324</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G46" s="1">
-        <v>0.34027777777777779</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1255,10 +1258,10 @@
       </c>
       <c r="C47" s="1"/>
       <c r="E47">
-        <v>324</v>
+        <v>554</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G47" s="1">
         <v>0.34375</v>
@@ -1266,17 +1269,17 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>572</v>
+        <v>884</v>
       </c>
       <c r="F48" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G48" s="1">
-        <v>0.34375</v>
+        <v>0.35347222222222219</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1285,10 +1288,10 @@
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="F49" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G49" s="1">
         <v>0.36458333333333331</v>
@@ -1298,45 +1301,45 @@
       <c r="A50" t="s">
         <v>9</v>
       </c>
-      <c r="B50" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50" s="1">
-        <v>0.37152777777777779</v>
-      </c>
-      <c r="D50">
-        <v>451</v>
-      </c>
-      <c r="G50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="E50">
+        <v>430</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0.36458333333333331</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>9</v>
       </c>
-      <c r="C51" s="1"/>
-      <c r="E51">
-        <v>526</v>
-      </c>
-      <c r="F51" t="s">
-        <v>41</v>
-      </c>
-      <c r="G51" s="1">
-        <v>0.375</v>
-      </c>
+      <c r="B51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.37847222222222221</v>
+      </c>
+      <c r="D51">
+        <v>559</v>
+      </c>
+      <c r="G51" s="1"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C52" s="1"/>
       <c r="E52">
-        <v>4320</v>
+        <v>524</v>
       </c>
       <c r="F52" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G52" s="1">
-        <v>0.38333333333333336</v>
+        <v>0.38194444444444442</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -1371,16 +1374,16 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C55" s="1">
-        <v>0.40902777777777777</v>
+        <v>0.41319444444444442</v>
       </c>
       <c r="D55">
-        <v>4337</v>
+        <v>569</v>
       </c>
       <c r="G55" s="1"/>
     </row>
@@ -1388,16 +1391,16 @@
       <c r="A56" t="s">
         <v>9</v>
       </c>
-      <c r="B56" t="s">
-        <v>18</v>
-      </c>
-      <c r="C56" s="1">
+      <c r="C56" s="1"/>
+      <c r="E56">
+        <v>392</v>
+      </c>
+      <c r="F56" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" s="1">
         <v>0.41319444444444442</v>
       </c>
-      <c r="D56">
-        <v>569</v>
-      </c>
-      <c r="G56" s="1"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
@@ -1405,87 +1408,87 @@
       </c>
       <c r="C57" s="1"/>
       <c r="E57">
-        <v>392</v>
+        <v>609</v>
       </c>
       <c r="F57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G57" s="1">
-        <v>0.41319444444444442</v>
+        <v>0.4236111111111111</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>9</v>
       </c>
-      <c r="C58" s="1"/>
-      <c r="E58">
-        <v>408</v>
-      </c>
-      <c r="F58" t="s">
-        <v>40</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0.41319444444444442</v>
-      </c>
+      <c r="B58" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="1">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D58">
+        <v>537</v>
+      </c>
+      <c r="G58" s="1"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>9</v>
       </c>
-      <c r="C59" s="1"/>
-      <c r="E59">
-        <v>609</v>
-      </c>
-      <c r="F59" t="s">
-        <v>23</v>
-      </c>
-      <c r="G59" s="1">
-        <v>0.4236111111111111</v>
-      </c>
+      <c r="B59" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" s="1">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="D59">
+        <v>318</v>
+      </c>
+      <c r="G59" s="1"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C60" s="1">
-        <v>0.42708333333333331</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D60">
-        <v>537</v>
+        <v>70</v>
       </c>
       <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C61" s="1">
-        <v>0.44791666666666669</v>
+        <v>0.47291666666666665</v>
       </c>
       <c r="D61">
-        <v>455</v>
+        <v>495</v>
       </c>
       <c r="G61" s="1"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C62" s="1">
-        <v>0.4513888888888889</v>
+        <v>0.47847222222222219</v>
       </c>
       <c r="D62">
-        <v>573</v>
+        <v>1194</v>
       </c>
       <c r="G62" s="1"/>
     </row>
@@ -1493,374 +1496,374 @@
       <c r="A63" t="s">
         <v>9</v>
       </c>
-      <c r="B63" t="s">
-        <v>23</v>
-      </c>
-      <c r="C63" s="1">
-        <v>0.4548611111111111</v>
-      </c>
-      <c r="D63">
-        <v>318</v>
-      </c>
-      <c r="G63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="E63">
+        <v>584</v>
+      </c>
+      <c r="F63" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0.49305555555555558</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>9</v>
       </c>
-      <c r="B64" t="s">
-        <v>25</v>
-      </c>
-      <c r="C64" s="1">
-        <v>0.46180555555555558</v>
-      </c>
-      <c r="D64">
-        <v>384</v>
-      </c>
-      <c r="G64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="E64">
+        <v>71</v>
+      </c>
+      <c r="F64" t="s">
+        <v>24</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="E65">
+        <v>424</v>
+      </c>
+      <c r="F65" t="s">
         <v>28</v>
       </c>
-      <c r="B65" t="s">
-        <v>29</v>
-      </c>
-      <c r="C65" s="1">
-        <v>0.47291666666666665</v>
-      </c>
-      <c r="D65">
-        <v>495</v>
-      </c>
-      <c r="G65" s="1"/>
+      <c r="G65" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C66" s="1">
-        <v>0.47847222222222219</v>
+        <v>0.51041666666666663</v>
       </c>
       <c r="D66">
-        <v>1194</v>
+        <v>1441</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C67" s="1"/>
       <c r="E67">
-        <v>584</v>
+        <v>1508</v>
       </c>
       <c r="F67" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G67" s="1">
-        <v>0.49305555555555558</v>
+        <v>0.51597222222222228</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" s="1"/>
-      <c r="E68">
-        <v>434</v>
-      </c>
-      <c r="F68" t="s">
-        <v>37</v>
-      </c>
-      <c r="G68" s="1">
-        <v>0.49652777777777779</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B68" t="s">
+        <v>30</v>
+      </c>
+      <c r="C68" s="1">
+        <v>0.5180555555555556</v>
+      </c>
+      <c r="D68">
+        <v>1910</v>
+      </c>
+      <c r="G68" s="1"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69" s="1"/>
-      <c r="E69">
-        <v>385</v>
-      </c>
-      <c r="F69" t="s">
-        <v>25</v>
-      </c>
-      <c r="G69" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B69" t="s">
+        <v>32</v>
+      </c>
+      <c r="C69" s="1">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D69">
+        <v>420</v>
+      </c>
+      <c r="G69" s="1"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>9</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="E70">
-        <v>424</v>
-      </c>
-      <c r="F70" t="s">
-        <v>30</v>
-      </c>
-      <c r="G70" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B70" t="s">
+        <v>33</v>
+      </c>
+      <c r="C70" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D70">
+        <v>937</v>
+      </c>
+      <c r="G70" s="1"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>9</v>
-      </c>
-      <c r="C71" s="1"/>
-      <c r="E71">
-        <v>442</v>
-      </c>
-      <c r="F71" t="s">
-        <v>33</v>
-      </c>
-      <c r="G71" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B71" t="s">
+        <v>23</v>
+      </c>
+      <c r="C71" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D71">
+        <v>816</v>
+      </c>
+      <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>7</v>
-      </c>
-      <c r="B72" t="s">
-        <v>30</v>
-      </c>
-      <c r="C72" s="1">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="D72">
-        <v>1441</v>
-      </c>
-      <c r="G72" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="C72" s="1"/>
+      <c r="E72">
+        <v>421</v>
+      </c>
+      <c r="F72" t="s">
+        <v>32</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0.55208333333333337</v>
+      </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C73" s="1"/>
       <c r="E73">
-        <v>1508</v>
+        <v>1458</v>
       </c>
       <c r="F73" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G73" s="1">
-        <v>0.51597222222222228</v>
+        <v>0.55555555555555558</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>31</v>
-      </c>
-      <c r="B74" t="s">
-        <v>32</v>
-      </c>
-      <c r="C74" s="1">
-        <v>0.5180555555555556</v>
-      </c>
-      <c r="D74">
-        <v>1910</v>
-      </c>
-      <c r="G74" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="E74">
+        <v>380</v>
+      </c>
+      <c r="F74" t="s">
+        <v>33</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0.57222222222222219</v>
+      </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="E75">
+        <v>1468</v>
+      </c>
+      <c r="F75" t="s">
         <v>28</v>
       </c>
-      <c r="B75" t="s">
-        <v>33</v>
-      </c>
-      <c r="C75" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D75">
-        <v>937</v>
-      </c>
-      <c r="G75" s="1"/>
+      <c r="G75" s="1">
+        <v>0.57638888888888895</v>
+      </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>34</v>
-      </c>
-      <c r="B76" t="s">
-        <v>24</v>
-      </c>
-      <c r="C76" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D76">
-        <v>816</v>
-      </c>
-      <c r="G76" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="E76">
+        <v>1978</v>
+      </c>
+      <c r="F76" t="s">
+        <v>30</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0.57708333333333328</v>
+      </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C77" s="1"/>
       <c r="E77">
-        <v>1458</v>
+        <v>871</v>
       </c>
       <c r="F77" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G77" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.58194444444444449</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>28</v>
-      </c>
-      <c r="C78" s="1"/>
-      <c r="E78">
-        <v>380</v>
-      </c>
-      <c r="F78" t="s">
-        <v>33</v>
-      </c>
-      <c r="G78" s="1">
-        <v>0.57222222222222219</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" s="1">
+        <v>0.59375</v>
+      </c>
+      <c r="D78">
+        <v>628</v>
+      </c>
+      <c r="G78" s="1"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>7</v>
       </c>
-      <c r="C79" s="1"/>
-      <c r="E79">
-        <v>1468</v>
-      </c>
-      <c r="F79" t="s">
-        <v>30</v>
-      </c>
-      <c r="G79" s="1">
-        <v>0.57638888888888895</v>
-      </c>
+      <c r="B79" t="s">
+        <v>28</v>
+      </c>
+      <c r="C79" s="1">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D79">
+        <v>1290</v>
+      </c>
+      <c r="G79" s="1"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="1"/>
-      <c r="E80">
-        <v>1978</v>
-      </c>
-      <c r="F80" t="s">
-        <v>32</v>
-      </c>
-      <c r="G80" s="1">
-        <v>0.57708333333333328</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="D80">
+        <v>557</v>
+      </c>
+      <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>34</v>
-      </c>
-      <c r="C81" s="1"/>
-      <c r="E81">
-        <v>871</v>
-      </c>
-      <c r="F81" t="s">
+        <v>9</v>
+      </c>
+      <c r="B81" t="s">
         <v>24</v>
       </c>
-      <c r="G81" s="1">
-        <v>0.58194444444444449</v>
-      </c>
+      <c r="C81" s="1">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D81">
+        <v>382</v>
+      </c>
+      <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>35</v>
       </c>
-      <c r="B82" t="s">
-        <v>19</v>
-      </c>
-      <c r="C82" s="1">
-        <v>0.59375</v>
-      </c>
-      <c r="D82">
-        <v>628</v>
-      </c>
-      <c r="G82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="E82">
+        <v>629</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>7</v>
       </c>
-      <c r="B83" t="s">
-        <v>30</v>
-      </c>
-      <c r="C83" s="1">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D83">
-        <v>1290</v>
-      </c>
-      <c r="G83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="E83">
+        <v>1130</v>
+      </c>
+      <c r="F83" t="s">
+        <v>28</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C84" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D84">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="G84" s="1"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>35</v>
-      </c>
-      <c r="C85" s="1"/>
-      <c r="E85">
-        <v>629</v>
-      </c>
-      <c r="F85" t="s">
-        <v>19</v>
-      </c>
-      <c r="G85" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B85" t="s">
+        <v>36</v>
+      </c>
+      <c r="C85" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D85">
+        <v>370</v>
+      </c>
+      <c r="G85" s="1"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" s="1"/>
-      <c r="E86">
-        <v>1130</v>
-      </c>
-      <c r="F86" t="s">
-        <v>30</v>
-      </c>
-      <c r="G86" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B86" t="s">
+        <v>20</v>
+      </c>
+      <c r="C86" s="1">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="D86">
+        <v>397</v>
+      </c>
+      <c r="G86" s="1"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C87" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.68055555555555558</v>
       </c>
       <c r="D87">
-        <v>367</v>
+        <v>441</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1869,13 +1872,13 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C88" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D88">
-        <v>370</v>
+        <v>423</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -1884,13 +1887,13 @@
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C89" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.6875</v>
       </c>
       <c r="D89">
-        <v>397</v>
+        <v>311</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -1899,13 +1902,13 @@
         <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C90" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.6875</v>
       </c>
       <c r="D90">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G90" s="1"/>
     </row>
@@ -1914,13 +1917,13 @@
         <v>9</v>
       </c>
       <c r="B91" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C91" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.6875</v>
       </c>
       <c r="D91">
-        <v>441</v>
+        <v>610</v>
       </c>
       <c r="G91" s="1"/>
     </row>
@@ -1929,28 +1932,28 @@
         <v>9</v>
       </c>
       <c r="B92" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C92" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.70138888888888884</v>
       </c>
       <c r="D92">
-        <v>435</v>
+        <v>322</v>
       </c>
       <c r="G92" s="1"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C93" s="1">
-        <v>0.6875</v>
+        <v>0.72777777777777775</v>
       </c>
       <c r="D93">
-        <v>311</v>
+        <v>4327</v>
       </c>
       <c r="G93" s="1"/>
     </row>
@@ -1958,46 +1961,46 @@
       <c r="A94" t="s">
         <v>9</v>
       </c>
-      <c r="B94" t="s">
-        <v>23</v>
-      </c>
-      <c r="C94" s="1">
-        <v>0.6875</v>
-      </c>
-      <c r="D94">
-        <v>610</v>
-      </c>
-      <c r="G94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="E94">
+        <v>326</v>
+      </c>
+      <c r="F94" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>12</v>
-      </c>
-      <c r="B95" t="s">
-        <v>30</v>
-      </c>
-      <c r="C95" s="1">
-        <v>0.6958333333333333</v>
-      </c>
-      <c r="D95">
-        <v>4321</v>
-      </c>
-      <c r="G95" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C95" s="1"/>
+      <c r="E95">
+        <v>560</v>
+      </c>
+      <c r="F95" t="s">
+        <v>25</v>
+      </c>
+      <c r="G95" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>9</v>
       </c>
-      <c r="B96" t="s">
-        <v>24</v>
-      </c>
-      <c r="C96" s="1">
-        <v>0.70138888888888884</v>
-      </c>
-      <c r="D96">
-        <v>322</v>
-      </c>
-      <c r="G96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="E96">
+        <v>313</v>
+      </c>
+      <c r="F96" t="s">
+        <v>22</v>
+      </c>
+      <c r="G96" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -2005,29 +2008,29 @@
       </c>
       <c r="C97" s="1"/>
       <c r="E97">
-        <v>320</v>
+        <v>520</v>
       </c>
       <c r="F97" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G97" s="1">
-        <v>0.72222222222222221</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>12</v>
-      </c>
-      <c r="B98" t="s">
-        <v>30</v>
-      </c>
-      <c r="C98" s="1">
-        <v>0.72777777777777775</v>
-      </c>
-      <c r="D98">
-        <v>4327</v>
-      </c>
-      <c r="G98" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C98" s="1"/>
+      <c r="E98">
+        <v>588</v>
+      </c>
+      <c r="F98" t="s">
+        <v>19</v>
+      </c>
+      <c r="G98" s="1">
+        <v>0.73611111111111116</v>
+      </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
@@ -2035,13 +2038,13 @@
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>326</v>
+        <v>448</v>
       </c>
       <c r="F99" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G99" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2050,43 +2053,43 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>560</v>
+        <v>534</v>
       </c>
       <c r="F100" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G100" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>9</v>
-      </c>
-      <c r="C101" s="1"/>
-      <c r="E101">
-        <v>313</v>
-      </c>
-      <c r="F101" t="s">
-        <v>23</v>
-      </c>
-      <c r="G101" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B101" t="s">
+        <v>19</v>
+      </c>
+      <c r="C101" s="1">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="D101">
+        <v>222</v>
+      </c>
+      <c r="G101" s="1"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C102" s="1"/>
       <c r="E102">
-        <v>520</v>
+        <v>4308</v>
       </c>
       <c r="F102" t="s">
         <v>8</v>
       </c>
       <c r="G102" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -2095,13 +2098,13 @@
       </c>
       <c r="C103" s="1"/>
       <c r="E103">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F103" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G103" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.76041666666666663</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -2110,162 +2113,162 @@
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>588</v>
+        <v>660</v>
       </c>
       <c r="F104" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G104" s="1">
-        <v>0.73611111111111116</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>9</v>
-      </c>
-      <c r="C105" s="1"/>
-      <c r="E105">
-        <v>448</v>
-      </c>
-      <c r="F105" t="s">
-        <v>11</v>
-      </c>
-      <c r="G105" s="1">
-        <v>0.74305555555555558</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B105" t="s">
+        <v>28</v>
+      </c>
+      <c r="C105" s="1">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="D105">
+        <v>742</v>
+      </c>
+      <c r="G105" s="1"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C106" s="1"/>
       <c r="E106">
-        <v>534</v>
+        <v>4312</v>
       </c>
       <c r="F106" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G106" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.79027777777777775</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="B107" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C107" s="1">
-        <v>0.74652777777777779</v>
+        <v>0.79513888888888884</v>
       </c>
       <c r="D107">
-        <v>222</v>
+        <v>431</v>
       </c>
       <c r="G107" s="1"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C108" s="1"/>
       <c r="E108">
-        <v>4308</v>
+        <v>670</v>
       </c>
       <c r="F108" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G108" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.80555555555555558</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C109" s="1"/>
       <c r="E109">
-        <v>528</v>
+        <v>222</v>
       </c>
       <c r="F109" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G109" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.80902777777777779</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>9</v>
       </c>
-      <c r="C110" s="1"/>
-      <c r="E110">
-        <v>660</v>
-      </c>
-      <c r="F110" t="s">
-        <v>18</v>
-      </c>
-      <c r="G110" s="1">
-        <v>0.77083333333333337</v>
-      </c>
+      <c r="B110" t="s">
+        <v>28</v>
+      </c>
+      <c r="C110" s="1">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="D110">
+        <v>425</v>
+      </c>
+      <c r="G110" s="1"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>9</v>
       </c>
-      <c r="C111" s="1"/>
-      <c r="E111">
-        <v>558</v>
-      </c>
-      <c r="F111" t="s">
-        <v>26</v>
-      </c>
-      <c r="G111" s="1">
-        <v>0.77777777777777779</v>
-      </c>
+      <c r="B111" t="s">
+        <v>39</v>
+      </c>
+      <c r="C111" s="1">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="D111">
+        <v>329</v>
+      </c>
+      <c r="G111" s="1"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B112" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C112" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.82430555555555551</v>
       </c>
       <c r="D112">
-        <v>742</v>
+        <v>2657</v>
       </c>
       <c r="G112" s="1"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>12</v>
-      </c>
-      <c r="C113" s="1"/>
-      <c r="E113">
-        <v>4312</v>
-      </c>
-      <c r="F113" t="s">
-        <v>13</v>
-      </c>
-      <c r="G113" s="1">
-        <v>0.79027777777777775</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B113" t="s">
+        <v>8</v>
+      </c>
+      <c r="C113" s="1">
+        <v>0.82638888888888884</v>
+      </c>
+      <c r="D113">
+        <v>523</v>
+      </c>
+      <c r="G113" s="1"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C114" s="1">
-        <v>0.79513888888888884</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D114">
-        <v>431</v>
+        <v>583</v>
       </c>
       <c r="G114" s="1"/>
     </row>
@@ -2273,119 +2276,119 @@
       <c r="A115" t="s">
         <v>9</v>
       </c>
-      <c r="C115" s="1"/>
-      <c r="E115">
-        <v>670</v>
-      </c>
-      <c r="F115" t="s">
-        <v>18</v>
-      </c>
-      <c r="G115" s="1">
-        <v>0.80555555555555558</v>
-      </c>
+      <c r="B115" t="s">
+        <v>10</v>
+      </c>
+      <c r="C115" s="1">
+        <v>0.84375</v>
+      </c>
+      <c r="D115">
+        <v>325</v>
+      </c>
+      <c r="G115" s="1"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="1"/>
-      <c r="E116">
-        <v>222</v>
-      </c>
-      <c r="F116" t="s">
-        <v>16</v>
-      </c>
-      <c r="G116" s="1">
-        <v>0.80902777777777779</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B116" t="s">
+        <v>40</v>
+      </c>
+      <c r="C116" s="1">
+        <v>0.84375</v>
+      </c>
+      <c r="D116">
+        <v>445</v>
+      </c>
+      <c r="G116" s="1"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>9</v>
       </c>
       <c r="B117" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C117" s="1">
-        <v>0.81944444444444442</v>
+        <v>0.85069444444444442</v>
       </c>
       <c r="D117">
-        <v>425</v>
+        <v>393</v>
       </c>
       <c r="G117" s="1"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>28</v>
-      </c>
-      <c r="B118" t="s">
-        <v>29</v>
-      </c>
-      <c r="C118" s="1">
-        <v>0.82430555555555551</v>
-      </c>
-      <c r="D118">
-        <v>2657</v>
-      </c>
-      <c r="G118" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C118" s="1"/>
+      <c r="E118">
+        <v>590</v>
+      </c>
+      <c r="F118" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>9</v>
       </c>
       <c r="B119" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C119" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D119">
-        <v>583</v>
+        <v>449</v>
       </c>
       <c r="G119" s="1"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B120" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C120" s="1">
-        <v>0.84375</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D120">
-        <v>325</v>
+        <v>881</v>
       </c>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C121" s="1">
-        <v>0.84375</v>
+        <v>0.86111111111111116</v>
       </c>
       <c r="D121">
-        <v>445</v>
+        <v>4323</v>
       </c>
       <c r="G121" s="1"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C122" s="1">
-        <v>0.85069444444444442</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D122">
-        <v>393</v>
+        <v>1461</v>
       </c>
       <c r="G122" s="1"/>
     </row>
@@ -2393,44 +2396,44 @@
       <c r="A123" t="s">
         <v>9</v>
       </c>
-      <c r="C123" s="1"/>
-      <c r="E123">
-        <v>590</v>
-      </c>
-      <c r="F123" t="s">
-        <v>13</v>
-      </c>
-      <c r="G123" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+      <c r="B123" t="s">
+        <v>25</v>
+      </c>
+      <c r="C123" s="1">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="D123">
+        <v>563</v>
+      </c>
+      <c r="G123" s="1"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C124" s="1">
-        <v>0.85416666666666663</v>
+        <v>0.875</v>
       </c>
       <c r="D124">
-        <v>449</v>
+        <v>535</v>
       </c>
       <c r="G124" s="1"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B125" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C125" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D125">
-        <v>881</v>
+        <v>312</v>
       </c>
       <c r="G125" s="1"/>
     </row>
@@ -2442,40 +2445,40 @@
         <v>8</v>
       </c>
       <c r="C126" s="1">
-        <v>0.86111111111111116</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D126">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G126" s="1"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B127" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C127" s="1">
-        <v>0.86736111111111114</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D127">
-        <v>1461</v>
+        <v>589</v>
       </c>
       <c r="G127" s="1"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B128" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C128" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.89930555555555547</v>
       </c>
       <c r="D128">
-        <v>443</v>
+        <v>1425</v>
       </c>
       <c r="G128" s="1"/>
     </row>
@@ -2484,13 +2487,13 @@
         <v>9</v>
       </c>
       <c r="B129" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C129" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.91319444444444442</v>
       </c>
       <c r="D129">
-        <v>563</v>
+        <v>585</v>
       </c>
       <c r="G129" s="1"/>
     </row>
@@ -2498,91 +2501,91 @@
       <c r="A130" t="s">
         <v>9</v>
       </c>
-      <c r="B130" t="s">
-        <v>40</v>
-      </c>
-      <c r="C130" s="1">
-        <v>0.87152777777777779</v>
-      </c>
-      <c r="D130">
-        <v>409</v>
-      </c>
-      <c r="G130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="E130">
+        <v>315</v>
+      </c>
+      <c r="F130" t="s">
+        <v>20</v>
+      </c>
+      <c r="G130" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>9</v>
       </c>
-      <c r="B131" t="s">
-        <v>41</v>
-      </c>
-      <c r="C131" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="D131">
-        <v>527</v>
-      </c>
-      <c r="G131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="E131">
+        <v>365</v>
+      </c>
+      <c r="F131" t="s">
+        <v>24</v>
+      </c>
+      <c r="G131" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>9</v>
       </c>
-      <c r="B132" t="s">
-        <v>15</v>
-      </c>
-      <c r="C132" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="D132">
-        <v>535</v>
-      </c>
-      <c r="G132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="E132">
+        <v>600</v>
+      </c>
+      <c r="F132" t="s">
+        <v>13</v>
+      </c>
+      <c r="G132" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>9</v>
       </c>
-      <c r="B133" t="s">
-        <v>23</v>
-      </c>
-      <c r="C133" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D133">
-        <v>312</v>
-      </c>
-      <c r="G133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="E133">
+        <v>429</v>
+      </c>
+      <c r="F133" t="s">
+        <v>21</v>
+      </c>
+      <c r="G133" s="1">
+        <v>0.92708333333333337</v>
+      </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>9</v>
       </c>
-      <c r="B134" t="s">
-        <v>20</v>
-      </c>
-      <c r="C134" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D134">
-        <v>589</v>
-      </c>
-      <c r="G134" s="1"/>
+      <c r="C134" s="1"/>
+      <c r="E134">
+        <v>578</v>
+      </c>
+      <c r="F134" t="s">
+        <v>19</v>
+      </c>
+      <c r="G134" s="1">
+        <v>0.93055555555555558</v>
+      </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>9</v>
       </c>
-      <c r="B135" t="s">
-        <v>13</v>
-      </c>
-      <c r="C135" s="1">
-        <v>0.91319444444444442</v>
-      </c>
-      <c r="D135">
-        <v>585</v>
-      </c>
-      <c r="G135" s="1"/>
+      <c r="C135" s="1"/>
+      <c r="E135">
+        <v>627</v>
+      </c>
+      <c r="F135" t="s">
+        <v>22</v>
+      </c>
+      <c r="G135" s="1">
+        <v>0.93402777777777779</v>
+      </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
@@ -2590,13 +2593,13 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>315</v>
+        <v>574</v>
       </c>
       <c r="F136" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G136" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -2605,13 +2608,13 @@
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>365</v>
+        <v>568</v>
       </c>
       <c r="F137" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G137" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -2620,28 +2623,28 @@
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>580</v>
+        <v>452</v>
       </c>
       <c r="F138" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G138" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="F139" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G139" s="1">
-        <v>0.92361111111111116</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -2650,13 +2653,13 @@
       </c>
       <c r="C140" s="1"/>
       <c r="E140">
-        <v>429</v>
+        <v>317</v>
       </c>
       <c r="F140" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G140" s="1">
-        <v>0.92708333333333337</v>
+        <v>0.95486111111111116</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -2665,13 +2668,13 @@
       </c>
       <c r="C141" s="1"/>
       <c r="E141">
-        <v>578</v>
+        <v>457</v>
       </c>
       <c r="F141" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G141" s="1">
-        <v>0.93055555555555558</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -2680,134 +2683,44 @@
       </c>
       <c r="C142" s="1"/>
       <c r="E142">
-        <v>627</v>
+        <v>552</v>
       </c>
       <c r="F142" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G142" s="1">
-        <v>0.93402777777777779</v>
+        <v>0.97222222222222221</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>9</v>
       </c>
-      <c r="C143" s="1"/>
-      <c r="E143">
-        <v>574</v>
-      </c>
-      <c r="F143" t="s">
+      <c r="B143" t="s">
         <v>15</v>
       </c>
-      <c r="G143" s="1">
-        <v>0.9375</v>
-      </c>
+      <c r="C143" s="1">
+        <v>0.97569444444444442</v>
+      </c>
+      <c r="D143">
+        <v>301</v>
+      </c>
+      <c r="G143" s="1"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>9</v>
-      </c>
-      <c r="C144" s="1"/>
-      <c r="E144">
-        <v>568</v>
-      </c>
-      <c r="F144" t="s">
-        <v>18</v>
-      </c>
-      <c r="G144" s="1">
-        <v>0.94097222222222221</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>9</v>
-      </c>
-      <c r="C145" s="1"/>
-      <c r="E145">
-        <v>452</v>
-      </c>
-      <c r="F145" t="s">
-        <v>11</v>
-      </c>
-      <c r="G145" s="1">
-        <v>0.94791666666666663</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>9</v>
-      </c>
-      <c r="C146" s="1"/>
-      <c r="E146">
-        <v>317</v>
-      </c>
-      <c r="F146" t="s">
-        <v>24</v>
-      </c>
-      <c r="G146" s="1">
-        <v>0.95486111111111116</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>9</v>
-      </c>
-      <c r="C147" s="1"/>
-      <c r="E147">
-        <v>457</v>
-      </c>
-      <c r="F147" t="s">
-        <v>17</v>
-      </c>
-      <c r="G147" s="1">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>9</v>
-      </c>
-      <c r="C148" s="1"/>
-      <c r="E148">
-        <v>300</v>
-      </c>
-      <c r="F148" t="s">
-        <v>16</v>
-      </c>
-      <c r="G148" s="1">
-        <v>0.96180555555555558</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>9</v>
-      </c>
-      <c r="C149" s="1"/>
-      <c r="E149">
-        <v>556</v>
-      </c>
-      <c r="F149" t="s">
-        <v>20</v>
-      </c>
-      <c r="G149" s="1">
-        <v>0.97222222222222221</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
         <v>34</v>
       </c>
-      <c r="B150" t="s">
-        <v>24</v>
-      </c>
-      <c r="C150" s="1">
+      <c r="B144" t="s">
+        <v>23</v>
+      </c>
+      <c r="C144" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D150">
+      <c r="D144">
         <v>878</v>
       </c>
-      <c r="G150" s="1"/>
+      <c r="G144" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4F53766-C699-426A-9850-784C1B2462CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AD682BF-1B5A-4381-86C2-7461320C8DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EB472DA7-C2F5-41B5-92C2-BD522628A1A1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{56A920BD-E3B3-4090-98A5-5BAAD87A4C56}"/>
   </bookViews>
   <sheets>
-    <sheet name="28-06" sheetId="1" r:id="rId1"/>
+    <sheet name="29-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="41">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -122,6 +122,12 @@
     <t>KMIA</t>
   </si>
   <si>
+    <t>FFT</t>
+  </si>
+  <si>
+    <t>KDFW</t>
+  </si>
+  <si>
     <t>AAL</t>
   </si>
   <si>
@@ -134,15 +140,6 @@
     <t>KATL</t>
   </si>
   <si>
-    <t>TAG</t>
-  </si>
-  <si>
-    <t>MHRO</t>
-  </si>
-  <si>
-    <t>KDFW</t>
-  </si>
-  <si>
     <t>CMP</t>
   </si>
   <si>
@@ -162,9 +159,6 @@
   </si>
   <si>
     <t>KBOS</t>
-  </si>
-  <si>
-    <t>KOAK</t>
   </si>
   <si>
     <t>KEWR</t>
@@ -542,8 +536,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A2C9424-511F-47FE-B583-8BC66302570F}">
-  <dimension ref="A1:G144"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{349EE1C5-604A-4D0D-92F5-0E8237AA5F70}">
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -586,7 +580,7 @@
         <v>2203</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2" s="1">
         <v>5.2083333333333336E-2</v>
@@ -624,7 +618,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
@@ -774,7 +768,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15">
@@ -796,7 +790,7 @@
         <v>1467</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G16" s="1">
         <v>0.25</v>
@@ -804,7 +798,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C17" s="1"/>
       <c r="E17">
@@ -999,17 +993,17 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C30" s="1"/>
       <c r="E30">
-        <v>4326</v>
+        <v>319</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G30" s="1">
-        <v>0.29791666666666666</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1018,10 +1012,10 @@
       </c>
       <c r="C31" s="1"/>
       <c r="E31">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G31" s="1">
         <v>0.3125</v>
@@ -1033,10 +1027,10 @@
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G32" s="1">
         <v>0.3125</v>
@@ -1048,10 +1042,10 @@
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>328</v>
+        <v>396</v>
       </c>
       <c r="F33" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G33" s="1">
         <v>0.3125</v>
@@ -1059,14 +1053,14 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C34" s="1"/>
       <c r="E34">
-        <v>396</v>
+        <v>884</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G34" s="1">
         <v>0.3125</v>
@@ -1096,7 +1090,7 @@
         <v>440</v>
       </c>
       <c r="F36" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G36" s="1">
         <v>0.31597222222222221</v>
@@ -1108,13 +1102,13 @@
       </c>
       <c r="C37" s="1"/>
       <c r="E37">
-        <v>536</v>
+        <v>444</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="G37" s="1">
-        <v>0.31597222222222221</v>
+        <v>0.32291666666666669</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1123,10 +1117,10 @@
       </c>
       <c r="C38" s="1"/>
       <c r="E38">
-        <v>444</v>
+        <v>562</v>
       </c>
       <c r="F38" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G38" s="1">
         <v>0.32291666666666669</v>
@@ -1138,89 +1132,89 @@
       </c>
       <c r="C39" s="1"/>
       <c r="E39">
-        <v>562</v>
+        <v>368</v>
       </c>
       <c r="F39" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G39" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C40" s="1"/>
       <c r="E40">
-        <v>4322</v>
+        <v>522</v>
       </c>
       <c r="F40" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="G40" s="1">
-        <v>0.32291666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="1"/>
-      <c r="E41">
-        <v>368</v>
-      </c>
-      <c r="F41" t="s">
-        <v>28</v>
-      </c>
-      <c r="G41" s="1">
-        <v>0.33333333333333331</v>
-      </c>
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" s="1">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="D41">
+        <v>309</v>
+      </c>
+      <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="1"/>
-      <c r="E42">
-        <v>522</v>
-      </c>
-      <c r="F42" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0.33333333333333331</v>
-      </c>
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.33680555555555558</v>
+      </c>
+      <c r="D42">
+        <v>601</v>
+      </c>
+      <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="B43" t="s">
-        <v>26</v>
-      </c>
-      <c r="C43" s="1">
+      <c r="C43" s="1"/>
+      <c r="E43">
+        <v>383</v>
+      </c>
+      <c r="F43" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" s="1">
         <v>0.33680555555555558</v>
       </c>
-      <c r="D43">
-        <v>309</v>
-      </c>
-      <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>9</v>
       </c>
-      <c r="B44" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="1">
-        <v>0.33680555555555558</v>
-      </c>
-      <c r="D44">
-        <v>581</v>
-      </c>
-      <c r="G44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="E44">
+        <v>454</v>
+      </c>
+      <c r="F44" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0.34027777777777779</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -1228,13 +1222,13 @@
       </c>
       <c r="C45" s="1"/>
       <c r="E45">
-        <v>383</v>
+        <v>324</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G45" s="1">
-        <v>0.33680555555555558</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1243,10 +1237,10 @@
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>324</v>
+        <v>554</v>
       </c>
       <c r="F46" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G46" s="1">
         <v>0.34375</v>
@@ -1258,28 +1252,28 @@
       </c>
       <c r="C47" s="1"/>
       <c r="E47">
-        <v>554</v>
+        <v>422</v>
       </c>
       <c r="F47" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G47" s="1">
-        <v>0.34375</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>884</v>
+        <v>430</v>
       </c>
       <c r="F48" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G48" s="1">
-        <v>0.35347222222222219</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1288,13 +1282,13 @@
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>422</v>
+        <v>524</v>
       </c>
       <c r="F49" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="G49" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.38194444444444442</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -1303,59 +1297,59 @@
       </c>
       <c r="C50" s="1"/>
       <c r="E50">
-        <v>430</v>
+        <v>369</v>
       </c>
       <c r="F50" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G50" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.3888888888888889</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>9</v>
       </c>
-      <c r="B51" t="s">
-        <v>25</v>
-      </c>
-      <c r="C51" s="1">
-        <v>0.37847222222222221</v>
-      </c>
-      <c r="D51">
-        <v>559</v>
-      </c>
-      <c r="G51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="E51">
+        <v>582</v>
+      </c>
+      <c r="F51" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.39930555555555558</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="1"/>
-      <c r="E52">
-        <v>524</v>
-      </c>
-      <c r="F52" t="s">
-        <v>8</v>
-      </c>
-      <c r="G52" s="1">
-        <v>0.38194444444444442</v>
-      </c>
+      <c r="B52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="D52">
+        <v>569</v>
+      </c>
+      <c r="G52" s="1"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="1"/>
-      <c r="E53">
-        <v>369</v>
-      </c>
-      <c r="F53" t="s">
-        <v>36</v>
-      </c>
-      <c r="G53" s="1">
-        <v>0.3888888888888889</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D53">
+        <v>342</v>
+      </c>
+      <c r="G53" s="1"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -1363,13 +1357,13 @@
       </c>
       <c r="C54" s="1"/>
       <c r="E54">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="F54" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G54" s="1">
-        <v>0.39930555555555558</v>
+        <v>0.4236111111111111</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -1377,13 +1371,13 @@
         <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C55" s="1">
-        <v>0.41319444444444442</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="D55">
-        <v>569</v>
+        <v>455</v>
       </c>
       <c r="G55" s="1"/>
     </row>
@@ -1391,106 +1385,106 @@
       <c r="A56" t="s">
         <v>9</v>
       </c>
-      <c r="C56" s="1"/>
-      <c r="E56">
-        <v>392</v>
-      </c>
-      <c r="F56" t="s">
-        <v>20</v>
-      </c>
-      <c r="G56" s="1">
-        <v>0.41319444444444442</v>
-      </c>
+      <c r="B56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="1">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="D56">
+        <v>318</v>
+      </c>
+      <c r="G56" s="1"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>9</v>
       </c>
-      <c r="C57" s="1"/>
-      <c r="E57">
-        <v>609</v>
-      </c>
-      <c r="F57" t="s">
-        <v>22</v>
-      </c>
-      <c r="G57" s="1">
-        <v>0.4236111111111111</v>
-      </c>
+      <c r="B57" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="1">
+        <v>0.46180555555555558</v>
+      </c>
+      <c r="D57">
+        <v>384</v>
+      </c>
+      <c r="G57" s="1"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>9</v>
-      </c>
-      <c r="B58" t="s">
-        <v>14</v>
-      </c>
-      <c r="C58" s="1">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="D58">
-        <v>537</v>
-      </c>
-      <c r="G58" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C58" s="1"/>
+      <c r="E58">
+        <v>343</v>
+      </c>
+      <c r="F58" t="s">
+        <v>28</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0.46180555555555558</v>
+      </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B59" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C59" s="1">
-        <v>0.4548611111111111</v>
+        <v>0.47291666666666665</v>
       </c>
       <c r="D59">
-        <v>318</v>
+        <v>495</v>
       </c>
       <c r="G59" s="1"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C60" s="1">
-        <v>0.46180555555555558</v>
+        <v>0.47847222222222219</v>
       </c>
       <c r="D60">
-        <v>70</v>
+        <v>1194</v>
       </c>
       <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>27</v>
-      </c>
-      <c r="B61" t="s">
-        <v>26</v>
-      </c>
-      <c r="C61" s="1">
-        <v>0.47291666666666665</v>
-      </c>
-      <c r="D61">
-        <v>495</v>
-      </c>
-      <c r="G61" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C61" s="1"/>
+      <c r="E61">
+        <v>584</v>
+      </c>
+      <c r="F61" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0.49305555555555558</v>
+      </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>7</v>
-      </c>
-      <c r="B62" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="1">
-        <v>0.47847222222222219</v>
-      </c>
-      <c r="D62">
-        <v>1194</v>
-      </c>
-      <c r="G62" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="E62">
+        <v>385</v>
+      </c>
+      <c r="F62" t="s">
+        <v>24</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
@@ -1498,134 +1492,134 @@
       </c>
       <c r="C63" s="1"/>
       <c r="E63">
-        <v>584</v>
+        <v>424</v>
       </c>
       <c r="F63" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G63" s="1">
-        <v>0.49305555555555558</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" s="1"/>
-      <c r="E64">
-        <v>71</v>
-      </c>
-      <c r="F64" t="s">
-        <v>24</v>
-      </c>
-      <c r="G64" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B64" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" s="1">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D64">
+        <v>1441</v>
+      </c>
+      <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C65" s="1"/>
       <c r="E65">
-        <v>424</v>
+        <v>1508</v>
       </c>
       <c r="F65" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G65" s="1">
-        <v>0.50347222222222221</v>
+        <v>0.51597222222222228</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B66" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C66" s="1">
-        <v>0.51041666666666663</v>
+        <v>0.5180555555555556</v>
       </c>
       <c r="D66">
-        <v>1441</v>
+        <v>1910</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>27</v>
-      </c>
-      <c r="C67" s="1"/>
-      <c r="E67">
-        <v>1508</v>
-      </c>
-      <c r="F67" t="s">
-        <v>26</v>
-      </c>
-      <c r="G67" s="1">
-        <v>0.51597222222222228</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B67" t="s">
+        <v>28</v>
+      </c>
+      <c r="C67" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D67">
+        <v>937</v>
+      </c>
+      <c r="G67" s="1"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C68" s="1">
-        <v>0.5180555555555556</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="D68">
-        <v>1910</v>
+        <v>816</v>
       </c>
       <c r="G68" s="1"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>31</v>
-      </c>
-      <c r="B69" t="s">
-        <v>32</v>
-      </c>
-      <c r="C69" s="1">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D69">
-        <v>420</v>
-      </c>
-      <c r="G69" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C69" s="1"/>
+      <c r="E69">
+        <v>1458</v>
+      </c>
+      <c r="F69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0.55555555555555558</v>
+      </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>27</v>
-      </c>
-      <c r="B70" t="s">
-        <v>33</v>
-      </c>
-      <c r="C70" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D70">
-        <v>937</v>
-      </c>
-      <c r="G70" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="E70">
+        <v>380</v>
+      </c>
+      <c r="F70" t="s">
+        <v>28</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0.57222222222222219</v>
+      </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>34</v>
-      </c>
-      <c r="B71" t="s">
-        <v>23</v>
-      </c>
-      <c r="C71" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D71">
-        <v>816</v>
-      </c>
-      <c r="G71" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C71" s="1"/>
+      <c r="E71">
+        <v>1468</v>
+      </c>
+      <c r="F71" t="s">
+        <v>30</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0.57638888888888895</v>
+      </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
@@ -1633,74 +1627,74 @@
       </c>
       <c r="C72" s="1"/>
       <c r="E72">
-        <v>421</v>
+        <v>1978</v>
       </c>
       <c r="F72" t="s">
         <v>32</v>
       </c>
       <c r="G72" s="1">
-        <v>0.55208333333333337</v>
+        <v>0.57708333333333328</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C73" s="1"/>
       <c r="E73">
-        <v>1458</v>
+        <v>871</v>
       </c>
       <c r="F73" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G73" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.58194444444444449</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>27</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="E74">
-        <v>380</v>
-      </c>
-      <c r="F74" t="s">
-        <v>33</v>
-      </c>
-      <c r="G74" s="1">
-        <v>0.57222222222222219</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74" s="1">
+        <v>0.59375</v>
+      </c>
+      <c r="D74">
+        <v>628</v>
+      </c>
+      <c r="G74" s="1"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>7</v>
       </c>
-      <c r="C75" s="1"/>
-      <c r="E75">
-        <v>1468</v>
-      </c>
-      <c r="F75" t="s">
-        <v>28</v>
-      </c>
-      <c r="G75" s="1">
-        <v>0.57638888888888895</v>
-      </c>
+      <c r="B75" t="s">
+        <v>30</v>
+      </c>
+      <c r="C75" s="1">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D75">
+        <v>1290</v>
+      </c>
+      <c r="G75" s="1"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>29</v>
-      </c>
-      <c r="C76" s="1"/>
-      <c r="E76">
-        <v>1978</v>
-      </c>
-      <c r="F76" t="s">
-        <v>30</v>
-      </c>
-      <c r="G76" s="1">
-        <v>0.57708333333333328</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B76" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="1">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="D76">
+        <v>382</v>
+      </c>
+      <c r="G76" s="1"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
@@ -1708,42 +1702,42 @@
       </c>
       <c r="C77" s="1"/>
       <c r="E77">
-        <v>871</v>
+        <v>629</v>
       </c>
       <c r="F77" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G77" s="1">
-        <v>0.58194444444444449</v>
+        <v>0.65277777777777779</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>35</v>
-      </c>
-      <c r="B78" t="s">
-        <v>18</v>
-      </c>
-      <c r="C78" s="1">
-        <v>0.59375</v>
-      </c>
-      <c r="D78">
-        <v>628</v>
-      </c>
-      <c r="G78" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="E78">
+        <v>1130</v>
+      </c>
+      <c r="F78" t="s">
+        <v>30</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C79" s="1">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D79">
-        <v>1290</v>
+        <v>367</v>
       </c>
       <c r="G79" s="1"/>
     </row>
@@ -1752,13 +1746,13 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C80" s="1">
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D80">
-        <v>557</v>
+        <v>370</v>
       </c>
       <c r="G80" s="1"/>
     </row>
@@ -1767,58 +1761,58 @@
         <v>9</v>
       </c>
       <c r="B81" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C81" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D81">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="G81" s="1"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>35</v>
-      </c>
-      <c r="C82" s="1"/>
-      <c r="E82">
-        <v>629</v>
-      </c>
-      <c r="F82" t="s">
-        <v>18</v>
-      </c>
-      <c r="G82" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B82" t="s">
+        <v>19</v>
+      </c>
+      <c r="C82" s="1">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="D82">
+        <v>553</v>
+      </c>
+      <c r="G82" s="1"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="1"/>
-      <c r="E83">
-        <v>1130</v>
-      </c>
-      <c r="F83" t="s">
+        <v>9</v>
+      </c>
+      <c r="B83" t="s">
         <v>28</v>
       </c>
-      <c r="G83" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+      <c r="C83" s="1">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="D83">
+        <v>441</v>
+      </c>
+      <c r="G83" s="1"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C84" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D84">
-        <v>367</v>
+        <v>423</v>
       </c>
       <c r="G84" s="1"/>
     </row>
@@ -1827,13 +1821,13 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C85" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.6875</v>
       </c>
       <c r="D85">
-        <v>370</v>
+        <v>311</v>
       </c>
       <c r="G85" s="1"/>
     </row>
@@ -1842,13 +1836,13 @@
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C86" s="1">
-        <v>0.67361111111111116</v>
+        <v>0.6875</v>
       </c>
       <c r="D86">
-        <v>397</v>
+        <v>555</v>
       </c>
       <c r="G86" s="1"/>
     </row>
@@ -1857,13 +1851,13 @@
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C87" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.6875</v>
       </c>
       <c r="D87">
-        <v>441</v>
+        <v>610</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1872,13 +1866,13 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C88" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.70138888888888884</v>
       </c>
       <c r="D88">
-        <v>423</v>
+        <v>322</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -1886,76 +1880,76 @@
       <c r="A89" t="s">
         <v>9</v>
       </c>
-      <c r="B89" t="s">
-        <v>26</v>
-      </c>
-      <c r="C89" s="1">
-        <v>0.6875</v>
-      </c>
-      <c r="D89">
-        <v>311</v>
-      </c>
-      <c r="G89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="E89">
+        <v>326</v>
+      </c>
+      <c r="F89" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>9</v>
       </c>
-      <c r="B90" t="s">
-        <v>19</v>
-      </c>
-      <c r="C90" s="1">
-        <v>0.6875</v>
-      </c>
-      <c r="D90">
-        <v>555</v>
-      </c>
-      <c r="G90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="E90">
+        <v>560</v>
+      </c>
+      <c r="F90" t="s">
+        <v>25</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0.72916666666666663</v>
+      </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>9</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" s="1"/>
+      <c r="E91">
+        <v>313</v>
+      </c>
+      <c r="F91" t="s">
         <v>22</v>
       </c>
-      <c r="C91" s="1">
-        <v>0.6875</v>
-      </c>
-      <c r="D91">
-        <v>610</v>
-      </c>
-      <c r="G91" s="1"/>
+      <c r="G91" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>9</v>
       </c>
-      <c r="B92" t="s">
-        <v>23</v>
-      </c>
-      <c r="C92" s="1">
-        <v>0.70138888888888884</v>
-      </c>
-      <c r="D92">
-        <v>322</v>
-      </c>
-      <c r="G92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="E92">
+        <v>450</v>
+      </c>
+      <c r="F92" t="s">
+        <v>20</v>
+      </c>
+      <c r="G92" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>12</v>
-      </c>
-      <c r="B93" t="s">
-        <v>28</v>
-      </c>
-      <c r="C93" s="1">
-        <v>0.72777777777777775</v>
-      </c>
-      <c r="D93">
-        <v>4327</v>
-      </c>
-      <c r="G93" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C93" s="1"/>
+      <c r="E93">
+        <v>520</v>
+      </c>
+      <c r="F93" t="s">
+        <v>8</v>
+      </c>
+      <c r="G93" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
@@ -1963,13 +1957,13 @@
       </c>
       <c r="C94" s="1"/>
       <c r="E94">
-        <v>326</v>
+        <v>588</v>
       </c>
       <c r="F94" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G94" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.73611111111111116</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -1978,13 +1972,13 @@
       </c>
       <c r="C95" s="1"/>
       <c r="E95">
-        <v>560</v>
+        <v>448</v>
       </c>
       <c r="F95" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G95" s="1">
-        <v>0.72916666666666663</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -1993,43 +1987,43 @@
       </c>
       <c r="C96" s="1"/>
       <c r="E96">
-        <v>313</v>
+        <v>534</v>
       </c>
       <c r="F96" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G96" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>9</v>
-      </c>
-      <c r="C97" s="1"/>
-      <c r="E97">
-        <v>520</v>
-      </c>
-      <c r="F97" t="s">
-        <v>8</v>
-      </c>
-      <c r="G97" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B97" t="s">
+        <v>19</v>
+      </c>
+      <c r="C97" s="1">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="D97">
+        <v>222</v>
+      </c>
+      <c r="G97" s="1"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C98" s="1"/>
       <c r="E98">
-        <v>588</v>
+        <v>4308</v>
       </c>
       <c r="F98" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G98" s="1">
-        <v>0.73611111111111116</v>
+        <v>0.75763888888888886</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -2038,13 +2032,13 @@
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>448</v>
+        <v>528</v>
       </c>
       <c r="F99" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G99" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.76041666666666663</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -2053,27 +2047,27 @@
       </c>
       <c r="C100" s="1"/>
       <c r="E100">
-        <v>534</v>
+        <v>660</v>
       </c>
       <c r="F100" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G100" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="B101" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C101" s="1">
-        <v>0.74652777777777779</v>
+        <v>0.79027777777777775</v>
       </c>
       <c r="D101">
-        <v>222</v>
+        <v>742</v>
       </c>
       <c r="G101" s="1"/>
     </row>
@@ -2083,29 +2077,29 @@
       </c>
       <c r="C102" s="1"/>
       <c r="E102">
-        <v>4308</v>
+        <v>4312</v>
       </c>
       <c r="F102" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G102" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.79027777777777775</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>9</v>
       </c>
-      <c r="C103" s="1"/>
-      <c r="E103">
-        <v>528</v>
-      </c>
-      <c r="F103" t="s">
-        <v>8</v>
-      </c>
-      <c r="G103" s="1">
-        <v>0.76041666666666663</v>
-      </c>
+      <c r="B103" t="s">
+        <v>18</v>
+      </c>
+      <c r="C103" s="1">
+        <v>0.79513888888888884</v>
+      </c>
+      <c r="D103">
+        <v>431</v>
+      </c>
+      <c r="G103" s="1"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
@@ -2113,102 +2107,102 @@
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="F104" t="s">
         <v>17</v>
       </c>
       <c r="G104" s="1">
-        <v>0.77083333333333337</v>
+        <v>0.80555555555555558</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>7</v>
-      </c>
-      <c r="B105" t="s">
-        <v>28</v>
-      </c>
-      <c r="C105" s="1">
-        <v>0.79027777777777775</v>
-      </c>
-      <c r="D105">
-        <v>742</v>
-      </c>
-      <c r="G105" s="1"/>
+        <v>37</v>
+      </c>
+      <c r="C105" s="1"/>
+      <c r="E105">
+        <v>222</v>
+      </c>
+      <c r="F105" t="s">
+        <v>15</v>
+      </c>
+      <c r="G105" s="1">
+        <v>0.80902777777777779</v>
+      </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>12</v>
-      </c>
-      <c r="C106" s="1"/>
-      <c r="E106">
-        <v>4312</v>
-      </c>
-      <c r="F106" t="s">
-        <v>13</v>
-      </c>
-      <c r="G106" s="1">
-        <v>0.79027777777777775</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B106" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="1">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="D106">
+        <v>425</v>
+      </c>
+      <c r="G106" s="1"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>9</v>
       </c>
       <c r="B107" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C107" s="1">
-        <v>0.79513888888888884</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="D107">
-        <v>431</v>
+        <v>329</v>
       </c>
       <c r="G107" s="1"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>9</v>
-      </c>
-      <c r="C108" s="1"/>
-      <c r="E108">
-        <v>670</v>
-      </c>
-      <c r="F108" t="s">
-        <v>17</v>
-      </c>
-      <c r="G108" s="1">
-        <v>0.80555555555555558</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B108" t="s">
+        <v>26</v>
+      </c>
+      <c r="C108" s="1">
+        <v>0.82430555555555551</v>
+      </c>
+      <c r="D108">
+        <v>2657</v>
+      </c>
+      <c r="G108" s="1"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>38</v>
-      </c>
-      <c r="C109" s="1"/>
-      <c r="E109">
-        <v>222</v>
-      </c>
-      <c r="F109" t="s">
-        <v>15</v>
-      </c>
-      <c r="G109" s="1">
-        <v>0.80902777777777779</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B109" t="s">
+        <v>26</v>
+      </c>
+      <c r="C109" s="1">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="D109">
+        <v>2657</v>
+      </c>
+      <c r="G109" s="1"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>9</v>
       </c>
       <c r="B110" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C110" s="1">
-        <v>0.81944444444444442</v>
+        <v>0.82638888888888884</v>
       </c>
       <c r="D110">
-        <v>425</v>
+        <v>523</v>
       </c>
       <c r="G110" s="1"/>
     </row>
@@ -2217,28 +2211,28 @@
         <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C111" s="1">
-        <v>0.82291666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D111">
-        <v>329</v>
+        <v>583</v>
       </c>
       <c r="G111" s="1"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B112" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C112" s="1">
-        <v>0.82430555555555551</v>
+        <v>0.84375</v>
       </c>
       <c r="D112">
-        <v>2657</v>
+        <v>325</v>
       </c>
       <c r="G112" s="1"/>
     </row>
@@ -2247,13 +2241,13 @@
         <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="C113" s="1">
-        <v>0.82638888888888884</v>
+        <v>0.84375</v>
       </c>
       <c r="D113">
-        <v>523</v>
+        <v>445</v>
       </c>
       <c r="G113" s="1"/>
     </row>
@@ -2261,59 +2255,59 @@
       <c r="A114" t="s">
         <v>9</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C114" s="1"/>
+      <c r="E114">
+        <v>590</v>
+      </c>
+      <c r="F114" t="s">
         <v>13</v>
       </c>
-      <c r="C114" s="1">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D114">
-        <v>583</v>
-      </c>
-      <c r="G114" s="1"/>
+      <c r="G114" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C115" s="1">
-        <v>0.84375</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="D115">
-        <v>325</v>
+        <v>449</v>
       </c>
       <c r="G115" s="1"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B116" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C116" s="1">
-        <v>0.84375</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D116">
-        <v>445</v>
+        <v>881</v>
       </c>
       <c r="G116" s="1"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B117" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C117" s="1">
-        <v>0.85069444444444442</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D117">
-        <v>393</v>
+        <v>1461</v>
       </c>
       <c r="G117" s="1"/>
     </row>
@@ -2321,89 +2315,89 @@
       <c r="A118" t="s">
         <v>9</v>
       </c>
-      <c r="C118" s="1"/>
-      <c r="E118">
-        <v>590</v>
-      </c>
-      <c r="F118" t="s">
-        <v>13</v>
-      </c>
-      <c r="G118" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+      <c r="B118" t="s">
+        <v>25</v>
+      </c>
+      <c r="C118" s="1">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="D118">
+        <v>563</v>
+      </c>
+      <c r="G118" s="1"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>9</v>
       </c>
       <c r="B119" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C119" s="1">
-        <v>0.85416666666666663</v>
+        <v>0.875</v>
       </c>
       <c r="D119">
-        <v>449</v>
+        <v>535</v>
       </c>
       <c r="G119" s="1"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B120" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C120" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D120">
-        <v>881</v>
+        <v>312</v>
       </c>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B121" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="C121" s="1">
-        <v>0.86111111111111116</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D121">
-        <v>4323</v>
+        <v>525</v>
       </c>
       <c r="G121" s="1"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C122" s="1">
-        <v>0.86736111111111114</v>
+        <v>0.87847222222222221</v>
       </c>
       <c r="D122">
-        <v>1461</v>
+        <v>589</v>
       </c>
       <c r="G122" s="1"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C123" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.89930555555555547</v>
       </c>
       <c r="D123">
-        <v>563</v>
+        <v>1425</v>
       </c>
       <c r="G123" s="1"/>
     </row>
@@ -2412,13 +2406,13 @@
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C124" s="1">
-        <v>0.875</v>
+        <v>0.91319444444444442</v>
       </c>
       <c r="D124">
-        <v>535</v>
+        <v>585</v>
       </c>
       <c r="G124" s="1"/>
     </row>
@@ -2426,76 +2420,76 @@
       <c r="A125" t="s">
         <v>9</v>
       </c>
-      <c r="B125" t="s">
-        <v>22</v>
-      </c>
-      <c r="C125" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D125">
-        <v>312</v>
-      </c>
-      <c r="G125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="E125">
+        <v>315</v>
+      </c>
+      <c r="F125" t="s">
+        <v>20</v>
+      </c>
+      <c r="G125" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>9</v>
       </c>
-      <c r="B126" t="s">
-        <v>8</v>
-      </c>
-      <c r="C126" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D126">
-        <v>525</v>
-      </c>
-      <c r="G126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="E126">
+        <v>365</v>
+      </c>
+      <c r="F126" t="s">
+        <v>24</v>
+      </c>
+      <c r="G126" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>9</v>
       </c>
-      <c r="B127" t="s">
-        <v>19</v>
-      </c>
-      <c r="C127" s="1">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="D127">
-        <v>589</v>
-      </c>
-      <c r="G127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="E127">
+        <v>580</v>
+      </c>
+      <c r="F127" t="s">
+        <v>13</v>
+      </c>
+      <c r="G127" s="1">
+        <v>0.92013888888888884</v>
+      </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>7</v>
-      </c>
-      <c r="B128" t="s">
-        <v>42</v>
-      </c>
-      <c r="C128" s="1">
-        <v>0.89930555555555547</v>
-      </c>
-      <c r="D128">
-        <v>1425</v>
-      </c>
-      <c r="G128" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C128" s="1"/>
+      <c r="E128">
+        <v>429</v>
+      </c>
+      <c r="F128" t="s">
+        <v>21</v>
+      </c>
+      <c r="G128" s="1">
+        <v>0.92708333333333337</v>
+      </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>9</v>
       </c>
-      <c r="B129" t="s">
-        <v>13</v>
-      </c>
-      <c r="C129" s="1">
-        <v>0.91319444444444442</v>
-      </c>
-      <c r="D129">
-        <v>585</v>
-      </c>
-      <c r="G129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="E129">
+        <v>578</v>
+      </c>
+      <c r="F129" t="s">
+        <v>19</v>
+      </c>
+      <c r="G129" s="1">
+        <v>0.93055555555555558</v>
+      </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
@@ -2503,13 +2497,13 @@
       </c>
       <c r="C130" s="1"/>
       <c r="E130">
-        <v>315</v>
+        <v>627</v>
       </c>
       <c r="F130" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G130" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.93402777777777779</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -2518,13 +2512,13 @@
       </c>
       <c r="C131" s="1"/>
       <c r="E131">
-        <v>365</v>
+        <v>574</v>
       </c>
       <c r="F131" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G131" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -2533,13 +2527,13 @@
       </c>
       <c r="C132" s="1"/>
       <c r="E132">
-        <v>600</v>
+        <v>568</v>
       </c>
       <c r="F132" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G132" s="1">
-        <v>0.92013888888888884</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -2548,43 +2542,43 @@
       </c>
       <c r="C133" s="1"/>
       <c r="E133">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="F133" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G133" s="1">
-        <v>0.92708333333333337</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C134" s="1"/>
       <c r="E134">
-        <v>578</v>
+        <v>339</v>
       </c>
       <c r="F134" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="G134" s="1">
-        <v>0.93055555555555558</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C135" s="1"/>
       <c r="E135">
-        <v>627</v>
+        <v>4336</v>
       </c>
       <c r="F135" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G135" s="1">
-        <v>0.93402777777777779</v>
+        <v>0.9506944444444444</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -2593,13 +2587,13 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>574</v>
+        <v>317</v>
       </c>
       <c r="F136" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G136" s="1">
-        <v>0.9375</v>
+        <v>0.95486111111111116</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -2608,13 +2602,13 @@
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>568</v>
+        <v>432</v>
       </c>
       <c r="F137" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G137" s="1">
-        <v>0.94097222222222221</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -2623,104 +2617,44 @@
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F138" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G138" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>339</v>
+        <v>552</v>
       </c>
       <c r="F139" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="G139" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.97222222222222221</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>9</v>
-      </c>
-      <c r="C140" s="1"/>
-      <c r="E140">
-        <v>317</v>
-      </c>
-      <c r="F140" t="s">
+        <v>33</v>
+      </c>
+      <c r="B140" t="s">
         <v>23</v>
       </c>
-      <c r="G140" s="1">
-        <v>0.95486111111111116</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>9</v>
-      </c>
-      <c r="C141" s="1"/>
-      <c r="E141">
-        <v>457</v>
-      </c>
-      <c r="F141" t="s">
-        <v>16</v>
-      </c>
-      <c r="G141" s="1">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>9</v>
-      </c>
-      <c r="C142" s="1"/>
-      <c r="E142">
-        <v>552</v>
-      </c>
-      <c r="F142" t="s">
-        <v>19</v>
-      </c>
-      <c r="G142" s="1">
-        <v>0.97222222222222221</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>9</v>
-      </c>
-      <c r="B143" t="s">
-        <v>15</v>
-      </c>
-      <c r="C143" s="1">
-        <v>0.97569444444444442</v>
-      </c>
-      <c r="D143">
-        <v>301</v>
-      </c>
-      <c r="G143" s="1"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>34</v>
-      </c>
-      <c r="B144" t="s">
-        <v>23</v>
-      </c>
-      <c r="C144" s="1">
+      <c r="C140" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D144">
+      <c r="D140">
         <v>878</v>
       </c>
-      <c r="G144" s="1"/>
+      <c r="G140" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/operaciones.xlsx
+++ b/public/operaciones.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saulm\Desktop\ATFM\Itinerarios_2026-06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AD682BF-1B5A-4381-86C2-7461320C8DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{495B15F4-F7EC-433D-8DC6-2EAC963B57BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{56A920BD-E3B3-4090-98A5-5BAAD87A4C56}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{17D72A89-5198-4D1D-84A5-C358CF7EEFE1}"/>
   </bookViews>
   <sheets>
-    <sheet name="29-06" sheetId="1" r:id="rId1"/>
+    <sheet name="30-06" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="42">
   <si>
     <t>AEROLINEA</t>
   </si>
@@ -83,6 +83,9 @@
     <t>KIAD</t>
   </si>
   <si>
+    <t>KONT</t>
+  </si>
+  <si>
     <t>MHLM</t>
   </si>
   <si>
@@ -119,27 +122,27 @@
     <t>KSFO</t>
   </si>
   <si>
+    <t>KEWR</t>
+  </si>
+  <si>
+    <t>AAL</t>
+  </si>
+  <si>
     <t>KMIA</t>
   </si>
   <si>
-    <t>FFT</t>
+    <t>KIAH</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>KATL</t>
   </si>
   <si>
     <t>KDFW</t>
   </si>
   <si>
-    <t>AAL</t>
-  </si>
-  <si>
-    <t>KIAH</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>KATL</t>
-  </si>
-  <si>
     <t>CMP</t>
   </si>
   <si>
@@ -149,19 +152,19 @@
     <t>SKRG</t>
   </si>
   <si>
-    <t>KMCO</t>
+    <t>MMUN</t>
   </si>
   <si>
     <t>IBE</t>
   </si>
   <si>
-    <t>CYUL</t>
-  </si>
-  <si>
     <t>KBOS</t>
   </si>
   <si>
-    <t>KEWR</t>
+    <t>KORD</t>
+  </si>
+  <si>
+    <t>KLAS</t>
   </si>
 </sst>
 </file>
@@ -536,8 +539,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{349EE1C5-604A-4D0D-92F5-0E8237AA5F70}">
-  <dimension ref="A1:G140"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC808744-3B76-461A-9781-978E9767A420}">
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -618,14 +621,14 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="1"/>
       <c r="E5">
         <v>879</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5" s="1">
         <v>0.20347222222222219</v>
@@ -663,31 +666,31 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="E8">
-        <v>300</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0.21527777777777779</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.22013888888888888</v>
+      </c>
+      <c r="D8">
+        <v>4313</v>
+      </c>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1">
-        <v>0.22013888888888888</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="D9">
-        <v>4313</v>
+        <v>531</v>
       </c>
       <c r="G9" s="1"/>
     </row>
@@ -696,7 +699,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1">
         <v>0.22222222222222221</v>
@@ -711,7 +714,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1">
         <v>0.22916666666666666</v>
@@ -741,7 +744,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1">
         <v>0.24652777777777779</v>
@@ -756,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" s="1">
         <v>0.24652777777777779</v>
@@ -768,14 +771,14 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15">
         <v>3154</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G15" s="1">
         <v>0.25</v>
@@ -798,31 +801,31 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="E17">
-        <v>3154</v>
-      </c>
-      <c r="F17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0.25069444444444444</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.25694444444444442</v>
+      </c>
+      <c r="D17">
+        <v>433</v>
+      </c>
+      <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1">
         <v>0.25694444444444442</v>
       </c>
       <c r="D18">
-        <v>433</v>
+        <v>579</v>
       </c>
       <c r="G18" s="1"/>
     </row>
@@ -831,13 +834,13 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1">
-        <v>0.25694444444444442</v>
+        <v>0.26041666666666669</v>
       </c>
       <c r="D19">
-        <v>579</v>
+        <v>529</v>
       </c>
       <c r="G19" s="1"/>
     </row>
@@ -846,13 +849,13 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C20" s="1">
-        <v>0.26041666666666669</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="D20">
-        <v>529</v>
+        <v>314</v>
       </c>
       <c r="G20" s="1"/>
     </row>
@@ -861,13 +864,13 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C21" s="1">
-        <v>0.2638888888888889</v>
+        <v>0.2673611111111111</v>
       </c>
       <c r="D21">
-        <v>314</v>
+        <v>428</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -876,13 +879,13 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C22" s="1">
         <v>0.2673611111111111</v>
       </c>
       <c r="D22">
-        <v>428</v>
+        <v>626</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -891,13 +894,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C23" s="1">
-        <v>0.2673611111111111</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="D23">
-        <v>626</v>
+        <v>316</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -906,13 +909,13 @@
         <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C24" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D24">
-        <v>316</v>
+        <v>366</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -921,13 +924,13 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C25" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D25">
-        <v>366</v>
+        <v>561</v>
       </c>
       <c r="G25" s="1"/>
     </row>
@@ -936,13 +939,13 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D26">
-        <v>561</v>
+        <v>591</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -951,13 +954,13 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C27" s="1">
         <v>0.27083333333333331</v>
       </c>
       <c r="D27">
-        <v>591</v>
+        <v>671</v>
       </c>
       <c r="G27" s="1"/>
     </row>
@@ -966,30 +969,30 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C28" s="1">
-        <v>0.27083333333333331</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="D28">
-        <v>671</v>
+        <v>521</v>
       </c>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="1">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="D29">
-        <v>521</v>
-      </c>
-      <c r="G29" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="E29">
+        <v>3154</v>
+      </c>
+      <c r="F29" t="s">
+        <v>29</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0.29236111111111113</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -1000,7 +1003,7 @@
         <v>319</v>
       </c>
       <c r="F30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G30" s="1">
         <v>0.3125</v>
@@ -1015,7 +1018,7 @@
         <v>323</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G31" s="1">
         <v>0.3125</v>
@@ -1027,10 +1030,10 @@
       </c>
       <c r="C32" s="1"/>
       <c r="E32">
-        <v>328</v>
+        <v>396</v>
       </c>
       <c r="F32" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G32" s="1">
         <v>0.3125</v>
@@ -1042,28 +1045,28 @@
       </c>
       <c r="C33" s="1"/>
       <c r="E33">
-        <v>396</v>
+        <v>310</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G33" s="1">
-        <v>0.3125</v>
+        <v>0.31597222222222221</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C34" s="1"/>
       <c r="E34">
-        <v>884</v>
+        <v>440</v>
       </c>
       <c r="F34" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G34" s="1">
-        <v>0.3125</v>
+        <v>0.31597222222222221</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1072,10 +1075,10 @@
       </c>
       <c r="C35" s="1"/>
       <c r="E35">
-        <v>310</v>
+        <v>536</v>
       </c>
       <c r="F35" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G35" s="1">
         <v>0.31597222222222221</v>
@@ -1085,16 +1088,16 @@
       <c r="A36" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="E36">
-        <v>440</v>
-      </c>
-      <c r="F36" t="s">
-        <v>28</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0.31597222222222221</v>
-      </c>
+      <c r="B36" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="D36">
+        <v>321</v>
+      </c>
+      <c r="G36" s="1"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
@@ -1120,7 +1123,7 @@
         <v>562</v>
       </c>
       <c r="F38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G38" s="1">
         <v>0.32291666666666669</v>
@@ -1161,13 +1164,13 @@
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C41" s="1">
         <v>0.33680555555555558</v>
       </c>
       <c r="D41">
-        <v>309</v>
+        <v>581</v>
       </c>
       <c r="G41" s="1"/>
     </row>
@@ -1175,16 +1178,16 @@
       <c r="A42" t="s">
         <v>9</v>
       </c>
-      <c r="B42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="1">
+      <c r="C42" s="1"/>
+      <c r="E42">
+        <v>383</v>
+      </c>
+      <c r="F42" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" s="1">
         <v>0.33680555555555558</v>
       </c>
-      <c r="D42">
-        <v>601</v>
-      </c>
-      <c r="G42" s="1"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -1192,13 +1195,13 @@
       </c>
       <c r="C43" s="1"/>
       <c r="E43">
-        <v>383</v>
+        <v>454</v>
       </c>
       <c r="F43" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G43" s="1">
-        <v>0.33680555555555558</v>
+        <v>0.34027777777777779</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1207,13 +1210,13 @@
       </c>
       <c r="C44" s="1"/>
       <c r="E44">
-        <v>454</v>
+        <v>324</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G44" s="1">
-        <v>0.34027777777777779</v>
+        <v>0.34375</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1222,10 +1225,10 @@
       </c>
       <c r="C45" s="1"/>
       <c r="E45">
-        <v>324</v>
+        <v>572</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G45" s="1">
         <v>0.34375</v>
@@ -1237,29 +1240,29 @@
       </c>
       <c r="C46" s="1"/>
       <c r="E46">
-        <v>554</v>
+        <v>430</v>
       </c>
       <c r="F46" t="s">
         <v>19</v>
       </c>
       <c r="G46" s="1">
-        <v>0.34375</v>
+        <v>0.36458333333333331</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>9</v>
       </c>
-      <c r="C47" s="1"/>
-      <c r="E47">
-        <v>422</v>
-      </c>
-      <c r="F47" t="s">
-        <v>36</v>
-      </c>
-      <c r="G47" s="1">
-        <v>0.36458333333333331</v>
-      </c>
+      <c r="B47" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="D47">
+        <v>451</v>
+      </c>
+      <c r="G47" s="1"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -1267,13 +1270,13 @@
       </c>
       <c r="C48" s="1"/>
       <c r="E48">
-        <v>430</v>
+        <v>526</v>
       </c>
       <c r="F48" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="G48" s="1">
-        <v>0.36458333333333331</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1282,13 +1285,13 @@
       </c>
       <c r="C49" s="1"/>
       <c r="E49">
-        <v>524</v>
+        <v>369</v>
       </c>
       <c r="F49" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="G49" s="1">
-        <v>0.38194444444444442</v>
+        <v>0.3888888888888889</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -1297,36 +1300,36 @@
       </c>
       <c r="C50" s="1"/>
       <c r="E50">
-        <v>369</v>
+        <v>582</v>
       </c>
       <c r="F50" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G50" s="1">
-        <v>0.3888888888888889</v>
+        <v>0.39930555555555558</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C51" s="1"/>
-      <c r="E51">
-        <v>582</v>
-      </c>
-      <c r="F51" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="1">
-        <v>0.39930555555555558</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.40902777777777777</v>
+      </c>
+      <c r="D51">
+        <v>4337</v>
+      </c>
+      <c r="G51" s="1"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C52" s="1">
         <v>0.41319444444444442</v>
@@ -1338,18 +1341,18 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>27</v>
-      </c>
-      <c r="B53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C53" s="1">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D53">
-        <v>342</v>
-      </c>
-      <c r="G53" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="E53">
+        <v>392</v>
+      </c>
+      <c r="F53" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0.41319444444444442</v>
+      </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -1357,42 +1360,42 @@
       </c>
       <c r="C54" s="1"/>
       <c r="E54">
-        <v>609</v>
+        <v>408</v>
       </c>
       <c r="F54" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G54" s="1">
-        <v>0.4236111111111111</v>
+        <v>0.41319444444444442</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>9</v>
       </c>
-      <c r="B55" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" s="1">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="D55">
-        <v>455</v>
-      </c>
-      <c r="G55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="E55">
+        <v>609</v>
+      </c>
+      <c r="F55" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0.4236111111111111</v>
+      </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C56" s="1">
-        <v>0.4548611111111111</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="D56">
-        <v>318</v>
+        <v>537</v>
       </c>
       <c r="G56" s="1"/>
     </row>
@@ -1401,90 +1404,90 @@
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C57" s="1">
-        <v>0.46180555555555558</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="D57">
-        <v>384</v>
+        <v>455</v>
       </c>
       <c r="G57" s="1"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>27</v>
-      </c>
-      <c r="C58" s="1"/>
-      <c r="E58">
-        <v>343</v>
-      </c>
-      <c r="F58" t="s">
-        <v>28</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0.46180555555555558</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B58" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="1">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="D58">
+        <v>573</v>
+      </c>
+      <c r="G58" s="1"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C59" s="1">
-        <v>0.47291666666666665</v>
+        <v>0.4548611111111111</v>
       </c>
       <c r="D59">
-        <v>495</v>
+        <v>318</v>
       </c>
       <c r="G59" s="1"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C60" s="1">
-        <v>0.47847222222222219</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="D60">
-        <v>1194</v>
+        <v>384</v>
       </c>
       <c r="G60" s="1"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>9</v>
-      </c>
-      <c r="C61" s="1"/>
-      <c r="E61">
-        <v>584</v>
-      </c>
-      <c r="F61" t="s">
-        <v>13</v>
-      </c>
-      <c r="G61" s="1">
-        <v>0.49305555555555558</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B61" t="s">
+        <v>29</v>
+      </c>
+      <c r="C61" s="1">
+        <v>0.47291666666666665</v>
+      </c>
+      <c r="D61">
+        <v>495</v>
+      </c>
+      <c r="G61" s="1"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>9</v>
-      </c>
-      <c r="C62" s="1"/>
-      <c r="E62">
-        <v>385</v>
-      </c>
-      <c r="F62" t="s">
-        <v>24</v>
-      </c>
-      <c r="G62" s="1">
-        <v>0.50347222222222221</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B62" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="1">
+        <v>0.47847222222222219</v>
+      </c>
+      <c r="D62">
+        <v>1194</v>
+      </c>
+      <c r="G62" s="1"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
@@ -1492,209 +1495,209 @@
       </c>
       <c r="C63" s="1"/>
       <c r="E63">
-        <v>424</v>
+        <v>584</v>
       </c>
       <c r="F63" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G63" s="1">
-        <v>0.50347222222222221</v>
+        <v>0.49305555555555558</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>7</v>
-      </c>
-      <c r="B64" t="s">
-        <v>30</v>
-      </c>
-      <c r="C64" s="1">
-        <v>0.51041666666666663</v>
-      </c>
-      <c r="D64">
-        <v>1441</v>
-      </c>
-      <c r="G64" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="E64">
+        <v>434</v>
+      </c>
+      <c r="F64" t="s">
+        <v>37</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0.49652777777777779</v>
+      </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C65" s="1"/>
       <c r="E65">
-        <v>1508</v>
+        <v>385</v>
       </c>
       <c r="F65" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G65" s="1">
-        <v>0.51597222222222228</v>
+        <v>0.50347222222222221</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>31</v>
-      </c>
-      <c r="B66" t="s">
-        <v>32</v>
-      </c>
-      <c r="C66" s="1">
-        <v>0.5180555555555556</v>
-      </c>
-      <c r="D66">
-        <v>1910</v>
-      </c>
-      <c r="G66" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="E66">
+        <v>424</v>
+      </c>
+      <c r="F66" t="s">
+        <v>30</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>29</v>
-      </c>
-      <c r="B67" t="s">
-        <v>28</v>
-      </c>
-      <c r="C67" s="1">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="D67">
-        <v>937</v>
-      </c>
-      <c r="G67" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C67" s="1"/>
+      <c r="E67">
+        <v>442</v>
+      </c>
+      <c r="F67" t="s">
+        <v>33</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0.50347222222222221</v>
+      </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C68" s="1">
-        <v>0.52916666666666667</v>
+        <v>0.51041666666666663</v>
       </c>
       <c r="D68">
-        <v>816</v>
+        <v>1441</v>
       </c>
       <c r="G68" s="1"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C69" s="1"/>
       <c r="E69">
-        <v>1458</v>
+        <v>1508</v>
       </c>
       <c r="F69" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G69" s="1">
-        <v>0.55555555555555558</v>
+        <v>0.51597222222222228</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>29</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="E70">
-        <v>380</v>
-      </c>
-      <c r="F70" t="s">
-        <v>28</v>
-      </c>
-      <c r="G70" s="1">
-        <v>0.57222222222222219</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B70" t="s">
+        <v>32</v>
+      </c>
+      <c r="C70" s="1">
+        <v>0.5180555555555556</v>
+      </c>
+      <c r="D70">
+        <v>1910</v>
+      </c>
+      <c r="G70" s="1"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="1"/>
-      <c r="E71">
-        <v>1468</v>
-      </c>
-      <c r="F71" t="s">
-        <v>30</v>
-      </c>
-      <c r="G71" s="1">
-        <v>0.57638888888888895</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B71" t="s">
+        <v>33</v>
+      </c>
+      <c r="C71" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D71">
+        <v>937</v>
+      </c>
+      <c r="G71" s="1"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="1"/>
-      <c r="E72">
-        <v>1978</v>
-      </c>
-      <c r="F72" t="s">
-        <v>32</v>
-      </c>
-      <c r="G72" s="1">
-        <v>0.57708333333333328</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B72" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D72">
+        <v>816</v>
+      </c>
+      <c r="G72" s="1"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C73" s="1"/>
       <c r="E73">
-        <v>871</v>
+        <v>1458</v>
       </c>
       <c r="F73" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G73" s="1">
-        <v>0.58194444444444449</v>
+        <v>0.55555555555555558</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>34</v>
-      </c>
-      <c r="B74" t="s">
-        <v>18</v>
-      </c>
-      <c r="C74" s="1">
-        <v>0.59375</v>
-      </c>
-      <c r="D74">
-        <v>628</v>
-      </c>
-      <c r="G74" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="E74">
+        <v>380</v>
+      </c>
+      <c r="F74" t="s">
+        <v>33</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0.57222222222222219</v>
+      </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>7</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" s="1"/>
+      <c r="E75">
+        <v>1468</v>
+      </c>
+      <c r="F75" t="s">
         <v>30</v>
       </c>
-      <c r="C75" s="1">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="D75">
-        <v>1290</v>
-      </c>
-      <c r="G75" s="1"/>
+      <c r="G75" s="1">
+        <v>0.57638888888888895</v>
+      </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>9</v>
-      </c>
-      <c r="B76" t="s">
-        <v>24</v>
-      </c>
-      <c r="C76" s="1">
-        <v>0.65277777777777779</v>
-      </c>
-      <c r="D76">
-        <v>382</v>
-      </c>
-      <c r="G76" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="E76">
+        <v>1978</v>
+      </c>
+      <c r="F76" t="s">
+        <v>32</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0.57708333333333328</v>
+      </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
@@ -1702,42 +1705,42 @@
       </c>
       <c r="C77" s="1"/>
       <c r="E77">
-        <v>629</v>
+        <v>871</v>
       </c>
       <c r="F77" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G77" s="1">
-        <v>0.65277777777777779</v>
+        <v>0.58194444444444449</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="1"/>
-      <c r="E78">
-        <v>1130</v>
-      </c>
-      <c r="F78" t="s">
-        <v>30</v>
-      </c>
-      <c r="G78" s="1">
-        <v>0.65277777777777779</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B78" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" s="1">
+        <v>0.59375</v>
+      </c>
+      <c r="D78">
+        <v>628</v>
+      </c>
+      <c r="G78" s="1"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B79" t="s">
         <v>30</v>
       </c>
       <c r="C79" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D79">
-        <v>367</v>
+        <v>1290</v>
       </c>
       <c r="G79" s="1"/>
     </row>
@@ -1746,58 +1749,58 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C80" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.65277777777777779</v>
       </c>
       <c r="D80">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="G80" s="1"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>9</v>
-      </c>
-      <c r="B81" t="s">
-        <v>20</v>
-      </c>
-      <c r="C81" s="1">
-        <v>0.67361111111111116</v>
-      </c>
-      <c r="D81">
-        <v>397</v>
-      </c>
-      <c r="G81" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="E81">
+        <v>629</v>
+      </c>
+      <c r="F81" t="s">
+        <v>19</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>9</v>
-      </c>
-      <c r="B82" t="s">
-        <v>19</v>
-      </c>
-      <c r="C82" s="1">
-        <v>0.67361111111111116</v>
-      </c>
-      <c r="D82">
-        <v>553</v>
-      </c>
-      <c r="G82" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="E82">
+        <v>1130</v>
+      </c>
+      <c r="F82" t="s">
+        <v>30</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0.65277777777777779</v>
+      </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>9</v>
       </c>
       <c r="B83" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C83" s="1">
-        <v>0.68055555555555558</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D83">
-        <v>441</v>
+        <v>367</v>
       </c>
       <c r="G83" s="1"/>
     </row>
@@ -1809,10 +1812,10 @@
         <v>36</v>
       </c>
       <c r="C84" s="1">
-        <v>0.68402777777777779</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D84">
-        <v>423</v>
+        <v>370</v>
       </c>
       <c r="G84" s="1"/>
     </row>
@@ -1821,13 +1824,13 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C85" s="1">
-        <v>0.6875</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D85">
-        <v>311</v>
+        <v>397</v>
       </c>
       <c r="G85" s="1"/>
     </row>
@@ -1836,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C86" s="1">
-        <v>0.6875</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="D86">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="G86" s="1"/>
     </row>
@@ -1851,13 +1854,13 @@
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C87" s="1">
-        <v>0.6875</v>
+        <v>0.68055555555555558</v>
       </c>
       <c r="D87">
-        <v>610</v>
+        <v>441</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -1866,13 +1869,13 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C88" s="1">
-        <v>0.70138888888888884</v>
+        <v>0.68402777777777779</v>
       </c>
       <c r="D88">
-        <v>322</v>
+        <v>435</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -1880,46 +1883,46 @@
       <c r="A89" t="s">
         <v>9</v>
       </c>
-      <c r="C89" s="1"/>
-      <c r="E89">
-        <v>326</v>
-      </c>
-      <c r="F89" t="s">
-        <v>10</v>
-      </c>
-      <c r="G89" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+      <c r="B89" t="s">
+        <v>29</v>
+      </c>
+      <c r="C89" s="1">
+        <v>0.6875</v>
+      </c>
+      <c r="D89">
+        <v>311</v>
+      </c>
+      <c r="G89" s="1"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>9</v>
       </c>
-      <c r="C90" s="1"/>
-      <c r="E90">
-        <v>560</v>
-      </c>
-      <c r="F90" t="s">
-        <v>25</v>
-      </c>
-      <c r="G90" s="1">
-        <v>0.72916666666666663</v>
-      </c>
+      <c r="B90" t="s">
+        <v>23</v>
+      </c>
+      <c r="C90" s="1">
+        <v>0.6875</v>
+      </c>
+      <c r="D90">
+        <v>610</v>
+      </c>
+      <c r="G90" s="1"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>9</v>
       </c>
-      <c r="C91" s="1"/>
-      <c r="E91">
-        <v>313</v>
-      </c>
-      <c r="F91" t="s">
-        <v>22</v>
-      </c>
-      <c r="G91" s="1">
-        <v>0.73263888888888884</v>
-      </c>
+      <c r="B91" t="s">
+        <v>24</v>
+      </c>
+      <c r="C91" s="1">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="D91">
+        <v>322</v>
+      </c>
+      <c r="G91" s="1"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
@@ -1927,13 +1930,13 @@
       </c>
       <c r="C92" s="1"/>
       <c r="E92">
-        <v>450</v>
+        <v>320</v>
       </c>
       <c r="F92" t="s">
         <v>20</v>
       </c>
       <c r="G92" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.72222222222222221</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -1942,13 +1945,13 @@
       </c>
       <c r="C93" s="1"/>
       <c r="E93">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="F93" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G93" s="1">
-        <v>0.73263888888888884</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -1957,13 +1960,13 @@
       </c>
       <c r="C94" s="1"/>
       <c r="E94">
-        <v>588</v>
+        <v>560</v>
       </c>
       <c r="F94" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G94" s="1">
-        <v>0.73611111111111116</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -1972,13 +1975,13 @@
       </c>
       <c r="C95" s="1"/>
       <c r="E95">
-        <v>448</v>
+        <v>313</v>
       </c>
       <c r="F95" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G95" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -1987,43 +1990,43 @@
       </c>
       <c r="C96" s="1"/>
       <c r="E96">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="F96" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G96" s="1">
-        <v>0.74305555555555558</v>
+        <v>0.73263888888888884</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>37</v>
-      </c>
-      <c r="B97" t="s">
-        <v>19</v>
-      </c>
-      <c r="C97" s="1">
-        <v>0.74652777777777779</v>
-      </c>
-      <c r="D97">
-        <v>222</v>
-      </c>
-      <c r="G97" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C97" s="1"/>
+      <c r="E97">
+        <v>530</v>
+      </c>
+      <c r="F97" t="s">
+        <v>14</v>
+      </c>
+      <c r="G97" s="1">
+        <v>0.73263888888888884</v>
+      </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C98" s="1"/>
       <c r="E98">
-        <v>4308</v>
+        <v>588</v>
       </c>
       <c r="F98" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G98" s="1">
-        <v>0.75763888888888886</v>
+        <v>0.73611111111111116</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -2032,74 +2035,74 @@
       </c>
       <c r="C99" s="1"/>
       <c r="E99">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="F99" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G99" s="1">
-        <v>0.76041666666666663</v>
+        <v>0.74305555555555558</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>9</v>
-      </c>
-      <c r="C100" s="1"/>
-      <c r="E100">
-        <v>660</v>
-      </c>
-      <c r="F100" t="s">
-        <v>17</v>
-      </c>
-      <c r="G100" s="1">
-        <v>0.77083333333333337</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B100" t="s">
+        <v>20</v>
+      </c>
+      <c r="C100" s="1">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="D100">
+        <v>222</v>
+      </c>
+      <c r="G100" s="1"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>7</v>
-      </c>
-      <c r="B101" t="s">
-        <v>30</v>
-      </c>
-      <c r="C101" s="1">
-        <v>0.79027777777777775</v>
-      </c>
-      <c r="D101">
-        <v>742</v>
-      </c>
-      <c r="G101" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C101" s="1"/>
+      <c r="E101">
+        <v>4308</v>
+      </c>
+      <c r="F101" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="1">
+        <v>0.75763888888888886</v>
+      </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C102" s="1"/>
       <c r="E102">
-        <v>4312</v>
+        <v>528</v>
       </c>
       <c r="F102" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G102" s="1">
-        <v>0.79027777777777775</v>
+        <v>0.76041666666666663</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>9</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" s="1"/>
+      <c r="E103">
+        <v>660</v>
+      </c>
+      <c r="F103" t="s">
         <v>18</v>
       </c>
-      <c r="C103" s="1">
-        <v>0.79513888888888884</v>
-      </c>
-      <c r="D103">
-        <v>431</v>
-      </c>
-      <c r="G103" s="1"/>
+      <c r="G103" s="1">
+        <v>0.77083333333333337</v>
+      </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
@@ -2107,132 +2110,132 @@
       </c>
       <c r="C104" s="1"/>
       <c r="E104">
-        <v>670</v>
+        <v>558</v>
       </c>
       <c r="F104" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G104" s="1">
-        <v>0.80555555555555558</v>
+        <v>0.77777777777777779</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>37</v>
-      </c>
-      <c r="C105" s="1"/>
-      <c r="E105">
-        <v>222</v>
-      </c>
-      <c r="F105" t="s">
-        <v>15</v>
-      </c>
-      <c r="G105" s="1">
-        <v>0.80902777777777779</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B105" t="s">
+        <v>29</v>
+      </c>
+      <c r="C105" s="1">
+        <v>0.77847222222222223</v>
+      </c>
+      <c r="D105">
+        <v>2657</v>
+      </c>
+      <c r="G105" s="1"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B106" t="s">
         <v>30</v>
       </c>
       <c r="C106" s="1">
-        <v>0.81944444444444442</v>
+        <v>0.79027777777777775</v>
       </c>
       <c r="D106">
-        <v>425</v>
+        <v>742</v>
       </c>
       <c r="G106" s="1"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>9</v>
-      </c>
-      <c r="B107" t="s">
-        <v>38</v>
-      </c>
-      <c r="C107" s="1">
-        <v>0.82291666666666663</v>
-      </c>
-      <c r="D107">
-        <v>329</v>
-      </c>
-      <c r="G107" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C107" s="1"/>
+      <c r="E107">
+        <v>4312</v>
+      </c>
+      <c r="F107" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107" s="1">
+        <v>0.79027777777777775</v>
+      </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B108" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C108" s="1">
-        <v>0.82430555555555551</v>
+        <v>0.79513888888888884</v>
       </c>
       <c r="D108">
-        <v>2657</v>
+        <v>431</v>
       </c>
       <c r="G108" s="1"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>29</v>
-      </c>
-      <c r="B109" t="s">
-        <v>26</v>
-      </c>
-      <c r="C109" s="1">
-        <v>0.82499999999999996</v>
-      </c>
-      <c r="D109">
-        <v>2657</v>
-      </c>
-      <c r="G109" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C109" s="1"/>
+      <c r="E109">
+        <v>670</v>
+      </c>
+      <c r="F109" t="s">
+        <v>18</v>
+      </c>
+      <c r="G109" s="1">
+        <v>0.80555555555555558</v>
+      </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>9</v>
-      </c>
-      <c r="B110" t="s">
-        <v>8</v>
-      </c>
-      <c r="C110" s="1">
-        <v>0.82638888888888884</v>
-      </c>
-      <c r="D110">
-        <v>523</v>
-      </c>
-      <c r="G110" s="1"/>
+        <v>38</v>
+      </c>
+      <c r="C110" s="1"/>
+      <c r="E110">
+        <v>222</v>
+      </c>
+      <c r="F110" t="s">
+        <v>16</v>
+      </c>
+      <c r="G110" s="1">
+        <v>0.80902777777777779</v>
+      </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>9</v>
-      </c>
-      <c r="B111" t="s">
-        <v>13</v>
-      </c>
-      <c r="C111" s="1">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D111">
-        <v>583</v>
-      </c>
-      <c r="G111" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C111" s="1"/>
+      <c r="E111">
+        <v>4300</v>
+      </c>
+      <c r="F111" t="s">
+        <v>19</v>
+      </c>
+      <c r="G111" s="1">
+        <v>0.81388888888888888</v>
+      </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>9</v>
       </c>
       <c r="B112" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C112" s="1">
-        <v>0.84375</v>
+        <v>0.81944444444444442</v>
       </c>
       <c r="D112">
-        <v>325</v>
+        <v>425</v>
       </c>
       <c r="G112" s="1"/>
     </row>
@@ -2241,13 +2244,13 @@
         <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C113" s="1">
-        <v>0.84375</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D113">
-        <v>445</v>
+        <v>583</v>
       </c>
       <c r="G113" s="1"/>
     </row>
@@ -2255,74 +2258,74 @@
       <c r="A114" t="s">
         <v>9</v>
       </c>
-      <c r="C114" s="1"/>
-      <c r="E114">
-        <v>590</v>
-      </c>
-      <c r="F114" t="s">
-        <v>13</v>
-      </c>
-      <c r="G114" s="1">
-        <v>0.85069444444444442</v>
-      </c>
+      <c r="B114" t="s">
+        <v>10</v>
+      </c>
+      <c r="C114" s="1">
+        <v>0.84375</v>
+      </c>
+      <c r="D114">
+        <v>325</v>
+      </c>
+      <c r="G114" s="1"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="C115" s="1">
-        <v>0.85416666666666663</v>
+        <v>0.84375</v>
       </c>
       <c r="D115">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="G115" s="1"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B116" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C116" s="1">
-        <v>0.8569444444444444</v>
+        <v>0.85069444444444442</v>
       </c>
       <c r="D116">
-        <v>881</v>
+        <v>393</v>
       </c>
       <c r="G116" s="1"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>7</v>
-      </c>
-      <c r="B117" t="s">
-        <v>30</v>
-      </c>
-      <c r="C117" s="1">
-        <v>0.86736111111111114</v>
-      </c>
-      <c r="D117">
-        <v>1461</v>
-      </c>
-      <c r="G117" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="C117" s="1"/>
+      <c r="E117">
+        <v>590</v>
+      </c>
+      <c r="F117" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117" s="1">
+        <v>0.85069444444444442</v>
+      </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B118" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C118" s="1">
-        <v>0.86805555555555558</v>
+        <v>0.8569444444444444</v>
       </c>
       <c r="D118">
-        <v>563</v>
+        <v>881</v>
       </c>
       <c r="G118" s="1"/>
     </row>
@@ -2331,28 +2334,28 @@
         <v>9</v>
       </c>
       <c r="B119" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C119" s="1">
-        <v>0.875</v>
+        <v>0.86111111111111116</v>
       </c>
       <c r="D119">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="G119" s="1"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C120" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86736111111111114</v>
       </c>
       <c r="D120">
-        <v>312</v>
+        <v>1461</v>
       </c>
       <c r="G120" s="1"/>
     </row>
@@ -2361,13 +2364,13 @@
         <v>9</v>
       </c>
       <c r="B121" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C121" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D121">
-        <v>525</v>
+        <v>443</v>
       </c>
       <c r="G121" s="1"/>
     </row>
@@ -2376,28 +2379,28 @@
         <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C122" s="1">
-        <v>0.87847222222222221</v>
+        <v>0.86805555555555558</v>
       </c>
       <c r="D122">
-        <v>589</v>
+        <v>563</v>
       </c>
       <c r="G122" s="1"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B123" t="s">
         <v>40</v>
       </c>
       <c r="C123" s="1">
-        <v>0.89930555555555547</v>
+        <v>0.87152777777777779</v>
       </c>
       <c r="D123">
-        <v>1425</v>
+        <v>409</v>
       </c>
       <c r="G123" s="1"/>
     </row>
@@ -2406,13 +2409,13 @@
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="C124" s="1">
-        <v>0.91319444444444442</v>
+        <v>0.875</v>
       </c>
       <c r="D124">
-        <v>585</v>
+        <v>527</v>
       </c>
       <c r="G124" s="1"/>
     </row>
@@ -2420,76 +2423,76 @@
       <c r="A125" t="s">
         <v>9</v>
       </c>
-      <c r="C125" s="1"/>
-      <c r="E125">
-        <v>315</v>
-      </c>
-      <c r="F125" t="s">
-        <v>20</v>
-      </c>
-      <c r="G125" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B125" t="s">
+        <v>15</v>
+      </c>
+      <c r="C125" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="D125">
+        <v>535</v>
+      </c>
+      <c r="G125" s="1"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>9</v>
       </c>
-      <c r="C126" s="1"/>
-      <c r="E126">
-        <v>365</v>
-      </c>
-      <c r="F126" t="s">
-        <v>24</v>
-      </c>
-      <c r="G126" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B126" t="s">
+        <v>23</v>
+      </c>
+      <c r="C126" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D126">
+        <v>312</v>
+      </c>
+      <c r="G126" s="1"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>9</v>
       </c>
-      <c r="C127" s="1"/>
-      <c r="E127">
-        <v>580</v>
-      </c>
-      <c r="F127" t="s">
-        <v>13</v>
-      </c>
-      <c r="G127" s="1">
-        <v>0.92013888888888884</v>
-      </c>
+      <c r="B127" t="s">
+        <v>20</v>
+      </c>
+      <c r="C127" s="1">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="D127">
+        <v>589</v>
+      </c>
+      <c r="G127" s="1"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>9</v>
-      </c>
-      <c r="C128" s="1"/>
-      <c r="E128">
-        <v>429</v>
-      </c>
-      <c r="F128" t="s">
-        <v>21</v>
-      </c>
-      <c r="G128" s="1">
-        <v>0.92708333333333337</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B128" t="s">
+        <v>27</v>
+      </c>
+      <c r="C128" s="1">
+        <v>0.89930555555555547</v>
+      </c>
+      <c r="D128">
+        <v>1425</v>
+      </c>
+      <c r="G128" s="1"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>9</v>
       </c>
-      <c r="C129" s="1"/>
-      <c r="E129">
-        <v>578</v>
-      </c>
-      <c r="F129" t="s">
-        <v>19</v>
-      </c>
-      <c r="G129" s="1">
-        <v>0.93055555555555558</v>
-      </c>
+      <c r="B129" t="s">
+        <v>13</v>
+      </c>
+      <c r="C129" s="1">
+        <v>0.91319444444444442</v>
+      </c>
+      <c r="D129">
+        <v>585</v>
+      </c>
+      <c r="G129" s="1"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
@@ -2497,13 +2500,13 @@
       </c>
       <c r="C130" s="1"/>
       <c r="E130">
-        <v>627</v>
+        <v>315</v>
       </c>
       <c r="F130" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G130" s="1">
-        <v>0.93402777777777779</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -2512,13 +2515,13 @@
       </c>
       <c r="C131" s="1"/>
       <c r="E131">
-        <v>574</v>
+        <v>365</v>
       </c>
       <c r="F131" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G131" s="1">
-        <v>0.9375</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -2527,13 +2530,13 @@
       </c>
       <c r="C132" s="1"/>
       <c r="E132">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="F132" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G132" s="1">
-        <v>0.94097222222222221</v>
+        <v>0.92013888888888884</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -2542,43 +2545,43 @@
       </c>
       <c r="C133" s="1"/>
       <c r="E133">
-        <v>452</v>
+        <v>308</v>
       </c>
       <c r="F133" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G133" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.92361111111111116</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C134" s="1"/>
       <c r="E134">
-        <v>339</v>
+        <v>429</v>
       </c>
       <c r="F134" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G134" s="1">
-        <v>0.94791666666666663</v>
+        <v>0.92708333333333337</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C135" s="1"/>
       <c r="E135">
-        <v>4336</v>
+        <v>578</v>
       </c>
       <c r="F135" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G135" s="1">
-        <v>0.9506944444444444</v>
+        <v>0.93055555555555558</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -2587,13 +2590,13 @@
       </c>
       <c r="C136" s="1"/>
       <c r="E136">
-        <v>317</v>
+        <v>627</v>
       </c>
       <c r="F136" t="s">
         <v>23</v>
       </c>
       <c r="G136" s="1">
-        <v>0.95486111111111116</v>
+        <v>0.93402777777777779</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -2602,13 +2605,13 @@
       </c>
       <c r="C137" s="1"/>
       <c r="E137">
-        <v>432</v>
+        <v>574</v>
       </c>
       <c r="F137" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G137" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -2617,13 +2620,13 @@
       </c>
       <c r="C138" s="1"/>
       <c r="E138">
-        <v>457</v>
+        <v>568</v>
       </c>
       <c r="F138" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G138" s="1">
-        <v>0.95833333333333337</v>
+        <v>0.94097222222222221</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -2632,29 +2635,104 @@
       </c>
       <c r="C139" s="1"/>
       <c r="E139">
-        <v>552</v>
+        <v>452</v>
       </c>
       <c r="F139" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G139" s="1">
-        <v>0.97222222222222221</v>
+        <v>0.94791666666666663</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>33</v>
-      </c>
-      <c r="B140" t="s">
-        <v>23</v>
-      </c>
-      <c r="C140" s="1">
+        <v>7</v>
+      </c>
+      <c r="C140" s="1"/>
+      <c r="E140">
+        <v>339</v>
+      </c>
+      <c r="F140" t="s">
+        <v>27</v>
+      </c>
+      <c r="G140" s="1">
+        <v>0.94791666666666663</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>9</v>
+      </c>
+      <c r="C141" s="1"/>
+      <c r="E141">
+        <v>317</v>
+      </c>
+      <c r="F141" t="s">
+        <v>24</v>
+      </c>
+      <c r="G141" s="1">
+        <v>0.95486111111111116</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="1"/>
+      <c r="E142">
+        <v>457</v>
+      </c>
+      <c r="F142" t="s">
+        <v>17</v>
+      </c>
+      <c r="G142" s="1">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143" s="1"/>
+      <c r="E143">
+        <v>300</v>
+      </c>
+      <c r="F143" t="s">
+        <v>16</v>
+      </c>
+      <c r="G143" s="1">
+        <v>0.96180555555555558</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>9</v>
+      </c>
+      <c r="C144" s="1"/>
+      <c r="E144">
+        <v>556</v>
+      </c>
+      <c r="F144" t="s">
+        <v>20</v>
+      </c>
+      <c r="G144" s="1">
+        <v>0.97222222222222221</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>34</v>
+      </c>
+      <c r="B145" t="s">
+        <v>24</v>
+      </c>
+      <c r="C145" s="1">
         <v>0.98402777777777783</v>
       </c>
-      <c r="D140">
+      <c r="D145">
         <v>878</v>
       </c>
-      <c r="G140" s="1"/>
+      <c r="G145" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
